--- a/Config/Datas/__beans__.xlsx
+++ b/Config/Datas/__beans__.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\UnityProject\BBQ\Config\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{860760F2-8147-4C99-8E42-711D95A85242}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BF69B75-B294-49F9-BA98-750FA78EBB85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="14290" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="14290" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="208">
   <si>
     <t>##var</t>
   </si>
@@ -829,6 +829,18 @@
   </si>
   <si>
     <t>foodInfo</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dialogue</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>speakerName</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>content</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -3568,7 +3580,30 @@
         <v>121</v>
       </c>
     </row>
+    <row r="136" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B136" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K136" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="M136" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="137" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K137" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="M137" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="138" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K138" s="1"/>
+    </row>
     <row r="140" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B140" s="1"/>
       <c r="O140" s="6"/>
     </row>
   </sheetData>

--- a/Config/Datas/__beans__.xlsx
+++ b/Config/Datas/__beans__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BF69B75-B294-49F9-BA98-750FA78EBB85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01C22714-AE4C-4748-A2D0-F041F31989F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="14290" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="217">
   <si>
     <t>##var</t>
   </si>
@@ -841,6 +841,42 @@
   </si>
   <si>
     <t>content</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>EncounterType</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>num</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>卡牌</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>事件效果</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>sender</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GA_修改得分乘区</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>isAdd</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>onAddAction</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>EncounterData</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1271,7 +1307,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q140"/>
+  <dimension ref="A1:Q145"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="28.75" customWidth="1"/>
@@ -3025,7 +3061,7 @@
         <v>106</v>
       </c>
       <c r="K96" s="1" t="s">
-        <v>68</v>
+        <v>215</v>
       </c>
       <c r="M96" s="1" t="s">
         <v>62</v>
@@ -3603,8 +3639,56 @@
       <c r="K138" s="1"/>
     </row>
     <row r="140" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B140" s="1"/>
+      <c r="B140" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="K140" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="M140" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="O140" s="6"/>
+    </row>
+    <row r="141" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K141" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M141" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="142" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K142" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M142" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="143" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K143" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M143" s="1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="144" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K144" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="M144" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="145" spans="11:13" x14ac:dyDescent="0.2">
+      <c r="K145" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="M145" s="5" t="s">
+        <v>112</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3618,7 +3702,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EECC075D-9730-41E5-B97E-C301603D1E48}">
-  <dimension ref="A1:Q46"/>
+  <dimension ref="A1:Q52"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="27.375" customWidth="1"/>
@@ -4173,11 +4257,48 @@
       <c r="C46" s="1" t="s">
         <v>53</v>
       </c>
+      <c r="G46" s="1" t="s">
+        <v>210</v>
+      </c>
       <c r="K46" s="1" t="s">
         <v>75</v>
       </c>
       <c r="M46" s="1" t="s">
         <v>137</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A50" s="1"/>
+      <c r="B50" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="K50" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="M50" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="K51" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="M51" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="K52" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="M52" s="1" t="s">
+        <v>103</v>
       </c>
     </row>
   </sheetData>

--- a/Config/Datas/__beans__.xlsx
+++ b/Config/Datas/__beans__.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01C22714-AE4C-4748-A2D0-F041F31989F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77FFFB82-A5F2-433E-AB24-2648F1A52812}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="229">
   <si>
     <t>##var</t>
   </si>
@@ -877,6 +877,54 @@
   </si>
   <si>
     <t>EncounterData</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LevelData</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DifficultyData</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>关卡唯一标识符</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>关卡名称</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>关卡描述</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>level</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DifficultyEffectInLevel</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LevelName</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>effectList</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>effects</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>list,DifficultyEffectInLevel</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>levelEffects</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1307,7 +1355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q145"/>
+  <dimension ref="A1:Q158"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="28.75" customWidth="1"/>
@@ -3682,11 +3730,112 @@
         <v>121</v>
       </c>
     </row>
-    <row r="145" spans="11:13" x14ac:dyDescent="0.2">
+    <row r="145" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K145" s="1" t="s">
         <v>160</v>
       </c>
       <c r="M145" s="5" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="147" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B147" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="K147" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="M147" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O147" s="1" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="148" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K148" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M148" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O148" s="1" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="149" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K149" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M149" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O149" s="1" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="150" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K150" s="1"/>
+    </row>
+    <row r="151" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B151" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="K151" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="M151" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="152" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K152" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M152" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="153" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K153" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M153" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="154" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K154" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="M154" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="155" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K155" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="M155" s="1" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="157" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B157" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="K157" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="M157" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="158" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K158" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="M158" s="1" t="s">
         <v>112</v>
       </c>
     </row>

--- a/Config/Datas/__beans__.xlsx
+++ b/Config/Datas/__beans__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77FFFB82-A5F2-433E-AB24-2648F1A52812}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDE66DAD-8C8A-4A24-8DD5-D4E7DAC0745A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="235">
   <si>
     <t>##var</t>
   </si>
@@ -925,6 +925,30 @@
   </si>
   <si>
     <t>levelEffects</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TileData</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>地块名称</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>地块描述</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GA_方向位移</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>dir</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Direction</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1355,7 +1379,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q158"/>
+  <dimension ref="A1:Q163"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="28.75" customWidth="1"/>
@@ -3839,6 +3863,42 @@
         <v>112</v>
       </c>
     </row>
+    <row r="161" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B161" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="K161" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="M161" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O161" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="162" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K162" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M162" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O162" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="163" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K163" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M163" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O163" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="K1:Q1"/>
@@ -3851,7 +3911,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EECC075D-9730-41E5-B97E-C301603D1E48}">
-  <dimension ref="A1:Q52"/>
+  <dimension ref="A1:Q56"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="27.375" customWidth="1"/>
@@ -4277,13 +4337,13 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B34" s="1" t="s">
-        <v>203</v>
+        <v>232</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>53</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>204</v>
+        <v>127</v>
       </c>
       <c r="M34" s="1" t="s">
         <v>146</v>
@@ -4291,162 +4351,199 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.2">
       <c r="K35" s="1" t="s">
-        <v>196</v>
+        <v>233</v>
       </c>
       <c r="M35" s="1" t="s">
-        <v>197</v>
+        <v>234</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B36" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>53</v>
+      <c r="A36" s="1" t="s">
+        <v>190</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>127</v>
+        <v>75</v>
       </c>
       <c r="M36" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="N36" s="6"/>
+        <v>137</v>
+      </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="N37" s="6"/>
+      <c r="K37" s="1"/>
+      <c r="M37" s="1"/>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B38" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="K38" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="M38" s="1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="K39" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="M39" s="1" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B40" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="K40" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="M40" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="N40" s="6"/>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N41" s="6"/>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B42" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="C38" s="6"/>
-      <c r="D38" s="6"/>
-      <c r="E38" s="6"/>
-      <c r="F38" s="6"/>
-      <c r="G38" s="6"/>
-      <c r="H38" s="6"/>
-      <c r="I38" s="6"/>
-      <c r="J38" s="6"/>
-      <c r="K38" s="1" t="s">
+      <c r="C42" s="6"/>
+      <c r="D42" s="6"/>
+      <c r="E42" s="6"/>
+      <c r="F42" s="6"/>
+      <c r="G42" s="6"/>
+      <c r="H42" s="6"/>
+      <c r="I42" s="6"/>
+      <c r="J42" s="6"/>
+      <c r="K42" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="L38" s="6"/>
-      <c r="M38" s="5" t="s">
+      <c r="L42" s="6"/>
+      <c r="M42" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="N38" s="6"/>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B39" s="6"/>
-      <c r="C39" s="5"/>
-      <c r="D39" s="6"/>
-      <c r="E39" s="6"/>
-      <c r="F39" s="6"/>
-      <c r="G39" s="6"/>
-      <c r="H39" s="6"/>
-      <c r="I39" s="6"/>
-      <c r="J39" s="8"/>
-      <c r="K39" s="5" t="s">
+      <c r="N42" s="6"/>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B43" s="6"/>
+      <c r="C43" s="5"/>
+      <c r="D43" s="6"/>
+      <c r="E43" s="6"/>
+      <c r="F43" s="6"/>
+      <c r="G43" s="6"/>
+      <c r="H43" s="6"/>
+      <c r="I43" s="6"/>
+      <c r="J43" s="8"/>
+      <c r="K43" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="L39" s="6"/>
-      <c r="M39" s="1" t="s">
+      <c r="L43" s="6"/>
+      <c r="M43" s="1" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B40" s="8"/>
-      <c r="C40" s="5"/>
-      <c r="D40" s="6"/>
-      <c r="E40" s="6"/>
-      <c r="F40" s="6"/>
-      <c r="G40" s="6"/>
-      <c r="H40" s="6"/>
-      <c r="I40" s="6"/>
-      <c r="J40" s="6"/>
-      <c r="K40" s="5" t="s">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B44" s="8"/>
+      <c r="C44" s="5"/>
+      <c r="D44" s="6"/>
+      <c r="E44" s="6"/>
+      <c r="F44" s="6"/>
+      <c r="G44" s="6"/>
+      <c r="H44" s="6"/>
+      <c r="I44" s="6"/>
+      <c r="J44" s="6"/>
+      <c r="K44" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="L40" s="6"/>
-      <c r="M40" s="5" t="s">
+      <c r="L44" s="6"/>
+      <c r="M44" s="5" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B41" s="1" t="s">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B45" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="K41" s="1" t="s">
+      <c r="K45" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="M41" s="1" t="s">
+      <c r="M45" s="1" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="K42" s="1" t="s">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="K46" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="M42" s="5" t="s">
+      <c r="M46" s="5" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A44" s="1" t="s">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A48" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="B44" s="1" t="s">
+      <c r="B48" s="1" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B46" s="1" t="s">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B50" s="1" t="s">
         <v>194</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="G46" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="K46" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="M46" s="1" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A50" s="1"/>
-      <c r="B50" s="1" t="s">
-        <v>213</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>53</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="K50" s="1" t="s">
         <v>75</v>
       </c>
       <c r="M50" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A54" s="1"/>
+      <c r="B54" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="K54" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="M54" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="K51" s="1" t="s">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="K55" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="M51" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="K52" s="1" t="s">
+      <c r="M55" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="K56" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="M52" s="1" t="s">
+      <c r="M56" s="1" t="s">
         <v>103</v>
       </c>
     </row>

--- a/Config/Datas/__beans__.xlsx
+++ b/Config/Datas/__beans__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDE66DAD-8C8A-4A24-8DD5-D4E7DAC0745A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E63F9DF6-80C0-4B26-A204-0B1A9E47A26C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="227">
   <si>
     <t>##var</t>
   </si>
@@ -344,10 +344,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>配方规则，通过才能执行</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>rules</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -368,42 +364,10 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>配方规则列表，Match依据</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>GAList</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>GA</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>RecipeRule_食材共存</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>RecipeRule_类型共存</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>FoodIds</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>types</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>(list#sep=,),string</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>(list#sep=,),FoodType</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>MascotData</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -576,10 +540,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>RecipeRule_动态值</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>串签图</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -949,6 +909,14 @@
   </si>
   <si>
     <t>Direction</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CardInfo</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>卡牌检索信息</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1093,15 +1061,15 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1379,7 +1347,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q163"/>
+  <dimension ref="A1:Q162"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="28.75" customWidth="1"/>
@@ -1427,15 +1395,15 @@
       <c r="J1" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="K1" s="13" t="s">
+      <c r="K1" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="L1" s="13"/>
-      <c r="M1" s="13"/>
-      <c r="N1" s="13"/>
-      <c r="O1" s="13"/>
-      <c r="P1" s="13"/>
-      <c r="Q1" s="13"/>
+      <c r="L1" s="12"/>
+      <c r="M1" s="12"/>
+      <c r="N1" s="12"/>
+      <c r="O1" s="12"/>
+      <c r="P1" s="12"/>
+      <c r="Q1" s="12"/>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
@@ -1587,14 +1555,14 @@
     <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A7" s="6"/>
       <c r="B7" s="6" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="6"/>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
       <c r="G7" s="6" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="H7" s="6"/>
       <c r="I7" s="6"/>
@@ -1669,10 +1637,10 @@
       <c r="I10" s="6"/>
       <c r="J10" s="6"/>
       <c r="K10" s="5" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="M10" s="5" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="N10" s="6"/>
       <c r="O10" s="6"/>
@@ -1691,10 +1659,10 @@
       <c r="I11" s="6"/>
       <c r="J11" s="6"/>
       <c r="K11" s="5" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="M11" s="5" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="N11" s="6"/>
       <c r="O11" s="6"/>
@@ -1713,11 +1681,11 @@
       <c r="I12" s="6"/>
       <c r="J12" s="6"/>
       <c r="K12" s="5" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="L12" s="6"/>
       <c r="M12" s="5" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="N12" s="6"/>
       <c r="O12" s="6"/>
@@ -1745,7 +1713,7 @@
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A14" s="6" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B14" s="6"/>
       <c r="C14" s="5"/>
@@ -1805,7 +1773,7 @@
     <row r="17" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A17" s="6"/>
       <c r="B17" s="6" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="C17" s="5"/>
       <c r="D17" s="6"/>
@@ -1820,7 +1788,7 @@
       </c>
       <c r="L17" s="6"/>
       <c r="M17" s="1" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="N17" s="6"/>
       <c r="O17" s="6"/>
@@ -1839,7 +1807,7 @@
       <c r="I18" s="6"/>
       <c r="J18" s="6"/>
       <c r="K18" s="5" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="L18" s="6"/>
       <c r="M18" s="5" t="s">
@@ -1994,7 +1962,7 @@
       <c r="H25" s="6"/>
       <c r="I25" s="6"/>
       <c r="J25" s="6"/>
-      <c r="K25" s="11" t="s">
+      <c r="K25" s="10" t="s">
         <v>36</v>
       </c>
       <c r="M25" s="5" t="s">
@@ -2075,13 +2043,13 @@
     <row r="29" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A29" s="6"/>
       <c r="K29" s="1" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="M29" s="5" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="O29" s="6" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="P29" s="6"/>
       <c r="Q29" s="6"/>
@@ -2089,13 +2057,13 @@
     <row r="30" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A30" s="6"/>
       <c r="K30" s="1" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="M30" s="5" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="P30" s="6"/>
       <c r="Q30" s="6"/>
@@ -2103,13 +2071,13 @@
     <row r="31" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A31" s="6"/>
       <c r="K31" s="1" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="M31" s="5" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="O31" s="6" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="Q31" s="6"/>
     </row>
@@ -2239,7 +2207,7 @@
       </c>
       <c r="N37" s="6"/>
       <c r="O37" s="6" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="P37" s="6"/>
       <c r="Q37" s="6"/>
@@ -2252,10 +2220,10 @@
     <row r="39" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A39" s="6"/>
       <c r="B39" s="1" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="K39" s="5" t="s">
         <v>25</v>
@@ -2278,7 +2246,7 @@
         <v>23</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="P40" s="6"/>
       <c r="Q40" s="6"/>
@@ -2292,7 +2260,7 @@
         <v>23</v>
       </c>
       <c r="O41" s="6" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="P41" s="6"/>
       <c r="Q41" s="6"/>
@@ -2300,7 +2268,7 @@
     <row r="42" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A42" s="6"/>
       <c r="K42" s="5" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="M42" s="5" t="s">
         <v>23</v>
@@ -2312,13 +2280,13 @@
     <row r="43" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A43" s="6"/>
       <c r="K43" s="5" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="M43" s="1" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="O43" s="6" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="P43" s="6"/>
       <c r="Q43" s="6"/>
@@ -2326,13 +2294,13 @@
     <row r="44" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A44" s="6"/>
       <c r="K44" s="5" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="M44" s="5" t="s">
         <v>23</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="P44" s="6"/>
       <c r="Q44" s="6"/>
@@ -2340,13 +2308,13 @@
     <row r="45" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A45" s="6"/>
       <c r="K45" s="5" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="M45" s="5" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="O45" s="6" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="P45" s="6"/>
       <c r="Q45" s="6"/>
@@ -2354,13 +2322,13 @@
     <row r="46" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A46" s="6"/>
       <c r="K46" s="5" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="M46" s="5" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="P46" s="6"/>
       <c r="Q46" s="6"/>
@@ -2435,10 +2403,10 @@
     <row r="54" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A54" s="6"/>
       <c r="B54" s="1" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="K54" s="5" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="M54" s="5" t="s">
         <v>23</v>
@@ -2449,7 +2417,7 @@
     <row r="55" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A55" s="6"/>
       <c r="K55" s="5" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="M55" s="5" t="s">
         <v>23</v>
@@ -2463,7 +2431,7 @@
         <v>33</v>
       </c>
       <c r="M56" s="5" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="P56" s="7"/>
       <c r="Q56" s="6"/>
@@ -2471,7 +2439,7 @@
     <row r="57" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A57" s="6"/>
       <c r="K57" s="5" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="M57" s="6" t="s">
         <v>66</v>
@@ -2578,7 +2546,7 @@
         <v>33</v>
       </c>
       <c r="M63" s="5" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="N63" s="9"/>
       <c r="O63" s="6" t="s">
@@ -2599,11 +2567,11 @@
       <c r="I64" s="6"/>
       <c r="J64" s="6"/>
       <c r="K64" s="8" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="L64" s="6"/>
       <c r="M64" s="8" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="N64" s="6"/>
       <c r="O64" s="8"/>
@@ -2656,13 +2624,13 @@
       <c r="H67" s="6"/>
       <c r="I67" s="6"/>
       <c r="J67" s="6"/>
-      <c r="K67" s="12" t="s">
+      <c r="K67" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="M67" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="O67" s="12" t="s">
+      <c r="M67" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="O67" s="11" t="s">
         <v>81</v>
       </c>
       <c r="P67" s="6"/>
@@ -2679,13 +2647,13 @@
       <c r="H68" s="6"/>
       <c r="I68" s="6"/>
       <c r="J68" s="6"/>
-      <c r="K68" s="12" t="s">
+      <c r="K68" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="M68" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="O68" s="12" t="s">
+      <c r="M68" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="O68" s="11" t="s">
         <v>80</v>
       </c>
       <c r="P68" s="6"/>
@@ -2702,8 +2670,8 @@
       <c r="M69" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="O69" s="12" t="s">
-        <v>87</v>
+      <c r="O69" s="11" t="s">
+        <v>86</v>
       </c>
       <c r="P69" s="6"/>
       <c r="Q69" s="6"/>
@@ -2714,27 +2682,27 @@
       <c r="I70" s="6"/>
       <c r="J70" s="6"/>
       <c r="K70" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M70" s="1" t="s">
         <v>23</v>
       </c>
       <c r="N70" s="6"/>
       <c r="O70" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="P70" s="6"/>
       <c r="Q70" s="6"/>
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A71" s="6"/>
-      <c r="K71" s="12" t="s">
-        <v>154</v>
+      <c r="K71" s="11" t="s">
+        <v>144</v>
       </c>
       <c r="M71" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="O71" s="12" t="s">
+      <c r="O71" s="11" t="s">
         <v>61</v>
       </c>
       <c r="P71" s="6"/>
@@ -2748,29 +2716,21 @@
       <c r="E72" s="6"/>
       <c r="F72" s="6"/>
       <c r="G72" s="6"/>
-      <c r="K72" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="M72" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="O72" s="12" t="s">
-        <v>89</v>
-      </c>
+      <c r="K72" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="M72" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="O72" s="11"/>
       <c r="P72" s="6"/>
       <c r="Q72" s="6"/>
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A73" s="6"/>
-      <c r="K73" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="M73" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="O73" s="12" t="s">
-        <v>90</v>
-      </c>
+      <c r="K73" s="11"/>
+      <c r="M73" s="11"/>
+      <c r="O73" s="11"/>
       <c r="P73" s="6"/>
       <c r="Q73" s="7"/>
     </row>
@@ -2781,16 +2741,12 @@
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A75" s="6"/>
-      <c r="B75" s="6" t="s">
-        <v>82</v>
-      </c>
+      <c r="B75" s="6"/>
       <c r="C75" s="6"/>
       <c r="D75" s="6"/>
       <c r="E75" s="6"/>
       <c r="F75" s="6"/>
-      <c r="G75" s="6" t="s">
-        <v>83</v>
-      </c>
+      <c r="G75" s="6"/>
       <c r="K75" s="1"/>
       <c r="M75" s="1"/>
       <c r="O75" s="1"/>
@@ -2799,22 +2755,27 @@
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A76" s="6"/>
+      <c r="B76" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="K76" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="M76" s="1" t="s">
+        <v>112</v>
+      </c>
       <c r="P76" s="6"/>
       <c r="Q76" s="6"/>
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A77" s="5"/>
-      <c r="B77" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="C77" s="6" t="s">
-        <v>82</v>
-      </c>
+      <c r="B77" s="6"/>
+      <c r="C77" s="6"/>
       <c r="K77" s="1" t="s">
-        <v>94</v>
+        <v>134</v>
       </c>
       <c r="M77" s="1" t="s">
-        <v>96</v>
+        <v>66</v>
       </c>
       <c r="P77" s="6"/>
       <c r="Q77" s="6"/>
@@ -2839,24 +2800,23 @@
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A79" s="6"/>
-      <c r="B79" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="C79" s="6" t="s">
-        <v>82</v>
-      </c>
+      <c r="B79" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="C79" s="5"/>
       <c r="D79" s="6"/>
       <c r="E79" s="6"/>
       <c r="F79" s="6"/>
       <c r="G79" s="6"/>
       <c r="H79" s="6"/>
       <c r="I79" s="6"/>
-      <c r="J79" s="6"/>
-      <c r="K79" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="M79" s="1" t="s">
-        <v>97</v>
+      <c r="J79" s="8"/>
+      <c r="K79" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L79" s="6"/>
+      <c r="M79" s="6" t="s">
+        <v>23</v>
       </c>
       <c r="N79" s="6"/>
       <c r="O79" s="6"/>
@@ -2865,25 +2825,21 @@
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A80" s="6"/>
-      <c r="B80" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="C80" s="5" t="s">
-        <v>82</v>
-      </c>
+      <c r="B80" s="8"/>
+      <c r="C80" s="5"/>
       <c r="D80" s="6"/>
       <c r="E80" s="6"/>
       <c r="F80" s="6"/>
       <c r="G80" s="6"/>
       <c r="H80" s="6"/>
       <c r="I80" s="6"/>
-      <c r="J80" s="5"/>
+      <c r="J80" s="8"/>
       <c r="K80" s="5" t="s">
-        <v>133</v>
+        <v>26</v>
       </c>
       <c r="L80" s="6"/>
-      <c r="M80" s="1" t="s">
-        <v>137</v>
+      <c r="M80" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="N80" s="6"/>
       <c r="O80" s="5"/>
@@ -2892,308 +2848,293 @@
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A81" s="6"/>
-      <c r="K81" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="M81" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="N81" s="6"/>
-      <c r="O81" s="6"/>
-      <c r="P81" s="6"/>
+      <c r="B81" s="6"/>
+      <c r="C81" s="6"/>
+      <c r="D81" s="6"/>
+      <c r="E81" s="6"/>
+      <c r="F81" s="6"/>
+      <c r="G81" s="6"/>
+      <c r="H81" s="6"/>
+      <c r="I81" s="6"/>
+      <c r="J81" s="6"/>
+      <c r="K81" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="L81" s="6"/>
+      <c r="M81" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="N81" s="7"/>
+      <c r="O81" s="5"/>
+      <c r="P81" s="7"/>
       <c r="Q81" s="6"/>
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A82" s="6"/>
-      <c r="K82" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="M82" s="1" t="s">
-        <v>137</v>
+      <c r="B82" s="6"/>
+      <c r="C82" s="6"/>
+      <c r="D82" s="6"/>
+      <c r="E82" s="6"/>
+      <c r="F82" s="6"/>
+      <c r="G82" s="6"/>
+      <c r="H82" s="6"/>
+      <c r="I82" s="6"/>
+      <c r="J82" s="6"/>
+      <c r="K82" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="L82" s="6"/>
+      <c r="M82" s="5" t="s">
+        <v>94</v>
       </c>
       <c r="N82" s="6"/>
-      <c r="O82" s="5"/>
       <c r="P82" s="6"/>
       <c r="Q82" s="6"/>
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A83" s="6"/>
-      <c r="N83" s="6"/>
-      <c r="O83" s="10"/>
+      <c r="B83" s="8"/>
+      <c r="C83" s="5"/>
+      <c r="D83" s="6"/>
+      <c r="E83" s="6"/>
+      <c r="F83" s="6"/>
+      <c r="G83" s="6"/>
+      <c r="H83" s="6"/>
+      <c r="I83" s="6"/>
+      <c r="J83" s="8"/>
+      <c r="K83" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="L83" s="6"/>
+      <c r="M83" s="6" t="s">
+        <v>96</v>
+      </c>
       <c r="P83" s="6"/>
       <c r="Q83" s="6"/>
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A84" s="6"/>
-      <c r="N84" s="6"/>
-      <c r="O84" s="5"/>
-      <c r="P84" s="7"/>
-      <c r="Q84" s="7"/>
+      <c r="B84" s="8"/>
+      <c r="C84" s="5"/>
+      <c r="D84" s="6"/>
+      <c r="E84" s="6"/>
+      <c r="F84" s="6"/>
+      <c r="G84" s="6"/>
+      <c r="H84" s="6"/>
+      <c r="I84" s="6"/>
+      <c r="J84" s="8"/>
+      <c r="K84" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="L84" s="6"/>
+      <c r="M84" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="P84" s="6"/>
+      <c r="Q84" s="6"/>
     </row>
     <row r="85" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A85" s="6"/>
-      <c r="B85" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="C85" s="5"/>
-      <c r="D85" s="6"/>
-      <c r="E85" s="6"/>
-      <c r="F85" s="6"/>
-      <c r="G85" s="6"/>
+      <c r="B85" s="1"/>
+      <c r="G85" s="1"/>
       <c r="H85" s="6"/>
       <c r="I85" s="6"/>
       <c r="J85" s="8"/>
-      <c r="K85" s="6" t="s">
-        <v>25</v>
-      </c>
+      <c r="K85" s="5"/>
       <c r="L85" s="6"/>
-      <c r="M85" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N85" s="6"/>
-      <c r="O85" s="6"/>
-      <c r="P85" s="6"/>
+      <c r="M85" s="5"/>
+      <c r="P85" s="7"/>
       <c r="Q85" s="6"/>
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A86" s="6"/>
-      <c r="B86" s="8"/>
-      <c r="C86" s="5"/>
-      <c r="D86" s="6"/>
-      <c r="E86" s="6"/>
-      <c r="F86" s="6"/>
-      <c r="G86" s="6"/>
       <c r="H86" s="6"/>
       <c r="I86" s="6"/>
       <c r="J86" s="8"/>
-      <c r="K86" s="5" t="s">
-        <v>26</v>
-      </c>
+      <c r="K86" s="5"/>
       <c r="L86" s="6"/>
-      <c r="M86" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="N86" s="6"/>
+      <c r="M86" s="5"/>
       <c r="O86" s="5"/>
-      <c r="P86" s="6"/>
+      <c r="P86" s="7"/>
       <c r="Q86" s="6"/>
     </row>
     <row r="87" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A87" s="6"/>
-      <c r="B87" s="6"/>
-      <c r="C87" s="6"/>
-      <c r="D87" s="6"/>
-      <c r="E87" s="6"/>
-      <c r="F87" s="6"/>
-      <c r="G87" s="6"/>
-      <c r="H87" s="6"/>
-      <c r="I87" s="6"/>
-      <c r="J87" s="6"/>
-      <c r="K87" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="L87" s="6"/>
-      <c r="M87" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="N87" s="7"/>
-      <c r="O87" s="5"/>
+      <c r="B87" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="K87" s="1"/>
+      <c r="M87" s="1"/>
       <c r="P87" s="7"/>
-      <c r="Q87" s="6"/>
+      <c r="Q87" s="7"/>
     </row>
     <row r="88" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A88" s="6"/>
-      <c r="B88" s="6"/>
-      <c r="C88" s="6"/>
-      <c r="D88" s="6"/>
-      <c r="E88" s="6"/>
-      <c r="F88" s="6"/>
-      <c r="G88" s="6"/>
-      <c r="H88" s="6"/>
-      <c r="I88" s="6"/>
-      <c r="J88" s="6"/>
-      <c r="K88" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="L88" s="6"/>
-      <c r="M88" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="N88" s="6"/>
-      <c r="P88" s="6"/>
+      <c r="B88" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="K88" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="M88" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="P88" s="7"/>
       <c r="Q88" s="6"/>
     </row>
     <row r="89" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B89" s="8"/>
-      <c r="C89" s="5"/>
-      <c r="D89" s="6"/>
-      <c r="E89" s="6"/>
-      <c r="F89" s="6"/>
-      <c r="G89" s="6"/>
-      <c r="H89" s="6"/>
-      <c r="I89" s="6"/>
-      <c r="J89" s="8"/>
-      <c r="K89" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="L89" s="6"/>
-      <c r="M89" s="6" t="s">
-        <v>105</v>
+      <c r="K89" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="M89" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="O89" s="1" t="s">
+        <v>98</v>
       </c>
       <c r="P89" s="6"/>
       <c r="Q89" s="6"/>
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B90" s="8"/>
-      <c r="C90" s="5"/>
-      <c r="D90" s="6"/>
-      <c r="E90" s="6"/>
-      <c r="F90" s="6"/>
-      <c r="G90" s="6"/>
-      <c r="H90" s="6"/>
-      <c r="I90" s="6"/>
-      <c r="J90" s="8"/>
-      <c r="K90" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="L90" s="6"/>
-      <c r="M90" s="5" t="s">
-        <v>112</v>
+      <c r="A90" s="6"/>
+      <c r="B90" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="K90" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="M90" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="N90" s="6"/>
+      <c r="O90" s="1" t="s">
+        <v>98</v>
       </c>
       <c r="P90" s="6"/>
       <c r="Q90" s="6"/>
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B91" s="1"/>
-      <c r="G91" s="1"/>
-      <c r="H91" s="6"/>
-      <c r="I91" s="6"/>
-      <c r="J91" s="8"/>
-      <c r="K91" s="5"/>
-      <c r="L91" s="6"/>
-      <c r="M91" s="5"/>
-      <c r="P91" s="7"/>
+      <c r="A91" s="6"/>
+      <c r="K91" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="M91" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="N91" s="6"/>
+      <c r="O91" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="P91" s="6"/>
       <c r="Q91" s="6"/>
     </row>
     <row r="92" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="H92" s="6"/>
-      <c r="I92" s="6"/>
-      <c r="J92" s="8"/>
-      <c r="K92" s="5"/>
-      <c r="L92" s="6"/>
-      <c r="M92" s="5"/>
-      <c r="O92" s="5"/>
+      <c r="A92" s="6"/>
+      <c r="N92" s="6"/>
       <c r="P92" s="7"/>
       <c r="Q92" s="6"/>
     </row>
     <row r="93" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B93" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="K93" s="1"/>
-      <c r="M93" s="1"/>
-      <c r="P93" s="7"/>
-      <c r="Q93" s="7"/>
+      <c r="A93" s="6"/>
+      <c r="N93" s="6"/>
+      <c r="O93" s="5"/>
+      <c r="P93" s="6"/>
+      <c r="Q93" s="6"/>
     </row>
     <row r="94" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B94" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="C94" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="K94" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="M94" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="P94" s="7"/>
+      <c r="A94" s="6"/>
+      <c r="H94" s="6"/>
+      <c r="I94" s="6"/>
+      <c r="J94" s="6"/>
+      <c r="K94" s="5"/>
+      <c r="L94" s="6"/>
+      <c r="M94" s="5"/>
+      <c r="N94" s="6"/>
+      <c r="O94" s="5"/>
+      <c r="P94" s="6"/>
       <c r="Q94" s="6"/>
     </row>
     <row r="95" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="K95" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="M95" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="O95" s="1" t="s">
-        <v>107</v>
-      </c>
+      <c r="A95" s="6"/>
+      <c r="H95" s="6"/>
+      <c r="I95" s="6"/>
+      <c r="J95" s="6"/>
+      <c r="K95" s="6"/>
+      <c r="L95" s="6"/>
+      <c r="M95" s="6"/>
+      <c r="N95" s="6"/>
+      <c r="O95" s="6"/>
       <c r="P95" s="6"/>
       <c r="Q95" s="6"/>
     </row>
     <row r="96" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A96" s="6"/>
-      <c r="B96" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="C96" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="K96" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="M96" s="1" t="s">
-        <v>62</v>
-      </c>
+      <c r="D96" s="6"/>
+      <c r="E96" s="6"/>
+      <c r="F96" s="6"/>
+      <c r="G96" s="6"/>
+      <c r="H96" s="6"/>
+      <c r="I96" s="6"/>
+      <c r="J96" s="8"/>
+      <c r="K96" s="5"/>
+      <c r="L96" s="6"/>
+      <c r="M96" s="5"/>
       <c r="N96" s="6"/>
-      <c r="O96" s="1" t="s">
-        <v>107</v>
-      </c>
+      <c r="O96" s="6"/>
       <c r="P96" s="6"/>
       <c r="Q96" s="6"/>
     </row>
     <row r="97" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A97" s="6"/>
-      <c r="K97" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="M97" s="1" t="s">
-        <v>62</v>
-      </c>
+      <c r="B97" s="8"/>
+      <c r="C97" s="5"/>
+      <c r="D97" s="6"/>
+      <c r="E97" s="6"/>
+      <c r="F97" s="6"/>
+      <c r="G97" s="6"/>
+      <c r="H97" s="6"/>
+      <c r="I97" s="6"/>
+      <c r="J97" s="8"/>
+      <c r="K97" s="5"/>
+      <c r="L97" s="6"/>
+      <c r="M97" s="5"/>
       <c r="N97" s="6"/>
-      <c r="O97" s="1" t="s">
-        <v>107</v>
-      </c>
+      <c r="O97" s="6"/>
       <c r="P97" s="6"/>
       <c r="Q97" s="6"/>
     </row>
     <row r="98" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A98" s="6"/>
-      <c r="N98" s="6"/>
-      <c r="P98" s="7"/>
+      <c r="O98" s="6"/>
+      <c r="P98" s="6"/>
       <c r="Q98" s="6"/>
     </row>
     <row r="99" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A99" s="6"/>
-      <c r="N99" s="6"/>
-      <c r="O99" s="5"/>
+      <c r="O99" s="6"/>
       <c r="P99" s="6"/>
       <c r="Q99" s="6"/>
     </row>
     <row r="100" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A100" s="6"/>
-      <c r="H100" s="6"/>
-      <c r="I100" s="6"/>
-      <c r="J100" s="6"/>
-      <c r="K100" s="5"/>
-      <c r="L100" s="6"/>
-      <c r="M100" s="5"/>
-      <c r="N100" s="6"/>
-      <c r="O100" s="5"/>
+      <c r="O100" s="6"/>
       <c r="P100" s="6"/>
       <c r="Q100" s="6"/>
     </row>
     <row r="101" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A101" s="6"/>
+      <c r="B101" s="8"/>
+      <c r="C101" s="5"/>
+      <c r="D101" s="6"/>
+      <c r="E101" s="6"/>
+      <c r="F101" s="6"/>
+      <c r="G101" s="6"/>
       <c r="H101" s="6"/>
       <c r="I101" s="6"/>
       <c r="J101" s="6"/>
-      <c r="K101" s="6"/>
+      <c r="K101" s="5"/>
       <c r="L101" s="6"/>
-      <c r="M101" s="6"/>
+      <c r="M101" s="5"/>
       <c r="N101" s="6"/>
       <c r="O101" s="6"/>
       <c r="P101" s="6"/>
@@ -3201,13 +3142,16 @@
     </row>
     <row r="102" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A102" s="6"/>
+      <c r="B102" s="1" t="s">
+        <v>119</v>
+      </c>
       <c r="D102" s="6"/>
       <c r="E102" s="6"/>
       <c r="F102" s="6"/>
       <c r="G102" s="6"/>
       <c r="H102" s="6"/>
       <c r="I102" s="6"/>
-      <c r="J102" s="8"/>
+      <c r="J102" s="6"/>
       <c r="K102" s="5"/>
       <c r="L102" s="6"/>
       <c r="M102" s="5"/>
@@ -3218,18 +3162,9 @@
     </row>
     <row r="103" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A103" s="6"/>
-      <c r="B103" s="8"/>
-      <c r="C103" s="5"/>
-      <c r="D103" s="6"/>
-      <c r="E103" s="6"/>
-      <c r="F103" s="6"/>
-      <c r="G103" s="6"/>
-      <c r="H103" s="6"/>
-      <c r="I103" s="6"/>
-      <c r="J103" s="8"/>
+      <c r="B103" s="1"/>
+      <c r="C103" s="1"/>
       <c r="K103" s="5"/>
-      <c r="L103" s="6"/>
-      <c r="M103" s="5"/>
       <c r="N103" s="6"/>
       <c r="O103" s="6"/>
       <c r="P103" s="6"/>
@@ -3237,30 +3172,89 @@
     </row>
     <row r="104" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A104" s="6"/>
+      <c r="B104" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D104" s="6"/>
+      <c r="E104" s="6"/>
+      <c r="F104" s="6"/>
+      <c r="G104" s="6"/>
+      <c r="H104" s="6"/>
+      <c r="I104" s="6"/>
+      <c r="J104" s="6"/>
+      <c r="K104" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="L104" s="6"/>
+      <c r="M104" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="N104" s="6"/>
       <c r="O104" s="6"/>
       <c r="P104" s="6"/>
       <c r="Q104" s="6"/>
     </row>
     <row r="105" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A105" s="6"/>
+      <c r="B105" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D105" s="6"/>
+      <c r="E105" s="6"/>
+      <c r="F105" s="6"/>
+      <c r="G105" s="6"/>
+      <c r="H105" s="6"/>
+      <c r="I105" s="6"/>
+      <c r="J105" s="8"/>
+      <c r="K105" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="L105" s="6"/>
+      <c r="M105" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="N105" s="6"/>
       <c r="O105" s="6"/>
       <c r="P105" s="6"/>
       <c r="Q105" s="6"/>
     </row>
     <row r="106" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A106" s="6"/>
+      <c r="B106" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D106" s="6"/>
+      <c r="E106" s="6"/>
+      <c r="F106" s="6"/>
+      <c r="G106" s="6"/>
+      <c r="H106" s="6"/>
+      <c r="I106" s="6"/>
+      <c r="J106" s="5"/>
+      <c r="K106" s="5"/>
+      <c r="L106" s="6"/>
+      <c r="M106" s="5"/>
+      <c r="N106" s="6"/>
       <c r="O106" s="6"/>
       <c r="P106" s="6"/>
       <c r="Q106" s="6"/>
     </row>
     <row r="107" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A107" s="6"/>
-      <c r="B107" s="8"/>
-      <c r="C107" s="5"/>
-      <c r="D107" s="6"/>
-      <c r="E107" s="6"/>
-      <c r="F107" s="6"/>
-      <c r="G107" s="6"/>
+      <c r="B107" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="C107" s="6" t="s">
+        <v>119</v>
+      </c>
       <c r="H107" s="6"/>
       <c r="I107" s="6"/>
       <c r="J107" s="6"/>
@@ -3274,19 +3268,24 @@
     </row>
     <row r="108" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A108" s="6"/>
-      <c r="B108" s="1" t="s">
-        <v>128</v>
+      <c r="B108" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="C108" s="6" t="s">
+        <v>119</v>
       </c>
       <c r="D108" s="6"/>
       <c r="E108" s="6"/>
       <c r="F108" s="6"/>
-      <c r="G108" s="6"/>
+      <c r="G108" s="6" t="s">
+        <v>130</v>
+      </c>
       <c r="H108" s="6"/>
       <c r="I108" s="6"/>
       <c r="J108" s="6"/>
-      <c r="K108" s="5"/>
+      <c r="K108" s="6"/>
       <c r="L108" s="6"/>
-      <c r="M108" s="5"/>
+      <c r="M108" s="6"/>
       <c r="N108" s="6"/>
       <c r="O108" s="6"/>
       <c r="P108" s="6"/>
@@ -3294,22 +3293,29 @@
     </row>
     <row r="109" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A109" s="6"/>
-      <c r="B109" s="1"/>
-      <c r="C109" s="1"/>
+      <c r="B109" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="C109" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="D109" s="6"/>
+      <c r="E109" s="6"/>
+      <c r="F109" s="6"/>
+      <c r="G109" s="6"/>
+      <c r="H109" s="6"/>
+      <c r="I109" s="6"/>
+      <c r="J109" s="5"/>
       <c r="K109" s="5"/>
+      <c r="L109" s="6"/>
+      <c r="M109" s="5"/>
       <c r="N109" s="6"/>
-      <c r="O109" s="6"/>
+      <c r="O109" s="1"/>
       <c r="P109" s="6"/>
       <c r="Q109" s="6"/>
     </row>
     <row r="110" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A110" s="6"/>
-      <c r="B110" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="C110" s="1" t="s">
-        <v>128</v>
-      </c>
       <c r="D110" s="6"/>
       <c r="E110" s="6"/>
       <c r="F110" s="6"/>
@@ -3317,13 +3323,9 @@
       <c r="H110" s="6"/>
       <c r="I110" s="6"/>
       <c r="J110" s="6"/>
-      <c r="K110" s="5" t="s">
-        <v>184</v>
-      </c>
+      <c r="K110" s="6"/>
       <c r="L110" s="6"/>
-      <c r="M110" s="5" t="s">
-        <v>23</v>
-      </c>
+      <c r="M110" s="6"/>
       <c r="N110" s="6"/>
       <c r="O110" s="6"/>
       <c r="P110" s="6"/>
@@ -3331,26 +3333,18 @@
     </row>
     <row r="111" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A111" s="6"/>
-      <c r="B111" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="C111" s="1" t="s">
-        <v>128</v>
-      </c>
+      <c r="B111" s="5"/>
+      <c r="C111" s="5"/>
       <c r="D111" s="6"/>
       <c r="E111" s="6"/>
       <c r="F111" s="6"/>
       <c r="G111" s="6"/>
       <c r="H111" s="6"/>
       <c r="I111" s="6"/>
-      <c r="J111" s="8"/>
-      <c r="K111" s="5" t="s">
-        <v>131</v>
-      </c>
+      <c r="J111" s="5"/>
+      <c r="K111" s="5"/>
       <c r="L111" s="6"/>
-      <c r="M111" s="5" t="s">
-        <v>121</v>
-      </c>
+      <c r="M111" s="5"/>
       <c r="N111" s="6"/>
       <c r="O111" s="6"/>
       <c r="P111" s="6"/>
@@ -3358,12 +3352,8 @@
     </row>
     <row r="112" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A112" s="6"/>
-      <c r="B112" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="C112" s="1" t="s">
-        <v>128</v>
-      </c>
+      <c r="B112" s="5"/>
+      <c r="C112" s="5"/>
       <c r="D112" s="6"/>
       <c r="E112" s="6"/>
       <c r="F112" s="6"/>
@@ -3381,18 +3371,12 @@
     </row>
     <row r="113" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A113" s="6"/>
-      <c r="B113" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="C113" s="6" t="s">
-        <v>128</v>
-      </c>
+      <c r="B113" s="6"/>
+      <c r="C113" s="6"/>
       <c r="D113" s="6"/>
       <c r="E113" s="6"/>
       <c r="F113" s="6"/>
-      <c r="G113" s="6" t="s">
-        <v>139</v>
-      </c>
+      <c r="G113" s="6"/>
       <c r="H113" s="6"/>
       <c r="I113" s="6"/>
       <c r="J113" s="6"/>
@@ -3406,12 +3390,8 @@
     </row>
     <row r="114" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A114" s="6"/>
-      <c r="B114" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="C114" s="6" t="s">
-        <v>128</v>
-      </c>
+      <c r="B114" s="6"/>
+      <c r="C114" s="6"/>
       <c r="D114" s="6"/>
       <c r="E114" s="6"/>
       <c r="F114" s="6"/>
@@ -3419,281 +3399,202 @@
       <c r="H114" s="6"/>
       <c r="I114" s="6"/>
       <c r="J114" s="6"/>
-      <c r="K114" s="6"/>
+      <c r="K114" s="5"/>
       <c r="L114" s="6"/>
-      <c r="M114" s="6"/>
+      <c r="M114" s="5"/>
       <c r="N114" s="6"/>
       <c r="O114" s="6"/>
       <c r="P114" s="6"/>
       <c r="Q114" s="6"/>
     </row>
     <row r="115" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A115" s="6"/>
-      <c r="B115" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="C115" s="6" t="s">
-        <v>128</v>
-      </c>
+      <c r="A115" s="5"/>
+      <c r="B115" s="8"/>
+      <c r="C115" s="5"/>
       <c r="D115" s="6"/>
       <c r="E115" s="6"/>
       <c r="F115" s="6"/>
       <c r="G115" s="6"/>
       <c r="H115" s="6"/>
       <c r="I115" s="6"/>
-      <c r="J115" s="5"/>
-      <c r="K115" s="5"/>
+      <c r="J115" s="8"/>
+      <c r="K115" s="6"/>
       <c r="L115" s="6"/>
-      <c r="M115" s="5"/>
+      <c r="M115" s="6"/>
       <c r="N115" s="6"/>
-      <c r="O115" s="1"/>
+      <c r="O115" s="5"/>
       <c r="P115" s="6"/>
       <c r="Q115" s="6"/>
     </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A116" s="6"/>
-      <c r="B116" s="6"/>
-      <c r="C116" s="6"/>
-      <c r="D116" s="6"/>
-      <c r="E116" s="6"/>
-      <c r="F116" s="6"/>
-      <c r="G116" s="6"/>
-      <c r="H116" s="6"/>
-      <c r="I116" s="6"/>
-      <c r="J116" s="6"/>
-      <c r="K116" s="6"/>
-      <c r="L116" s="6"/>
-      <c r="M116" s="6"/>
-      <c r="N116" s="6"/>
-      <c r="O116" s="6"/>
-      <c r="P116" s="6"/>
-      <c r="Q116" s="6"/>
-    </row>
     <row r="117" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A117" s="6"/>
-      <c r="B117" s="5"/>
-      <c r="C117" s="5"/>
+      <c r="B117" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="C117" s="6"/>
       <c r="D117" s="6"/>
       <c r="E117" s="6"/>
       <c r="F117" s="6"/>
       <c r="G117" s="6"/>
       <c r="H117" s="6"/>
       <c r="I117" s="6"/>
-      <c r="J117" s="5"/>
+      <c r="J117" s="6"/>
       <c r="K117" s="5"/>
       <c r="L117" s="6"/>
       <c r="M117" s="5"/>
       <c r="N117" s="6"/>
       <c r="O117" s="6"/>
-      <c r="P117" s="6"/>
-      <c r="Q117" s="6"/>
     </row>
     <row r="118" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A118" s="6"/>
-      <c r="B118" s="5"/>
-      <c r="C118" s="5"/>
-      <c r="D118" s="6"/>
-      <c r="E118" s="6"/>
-      <c r="F118" s="6"/>
-      <c r="G118" s="6"/>
-      <c r="H118" s="6"/>
-      <c r="I118" s="6"/>
-      <c r="J118" s="5"/>
-      <c r="K118" s="5"/>
-      <c r="L118" s="6"/>
-      <c r="M118" s="5"/>
       <c r="N118" s="6"/>
       <c r="O118" s="6"/>
-      <c r="P118" s="6"/>
-      <c r="Q118" s="6"/>
     </row>
     <row r="119" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A119" s="6"/>
-      <c r="B119" s="6"/>
-      <c r="C119" s="6"/>
-      <c r="D119" s="6"/>
-      <c r="E119" s="6"/>
-      <c r="F119" s="6"/>
-      <c r="G119" s="6"/>
-      <c r="H119" s="6"/>
-      <c r="I119" s="6"/>
-      <c r="J119" s="6"/>
-      <c r="K119" s="5"/>
-      <c r="L119" s="6"/>
-      <c r="M119" s="5"/>
       <c r="N119" s="6"/>
-      <c r="O119" s="6"/>
-      <c r="P119" s="6"/>
-      <c r="Q119" s="6"/>
     </row>
     <row r="120" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A120" s="6"/>
-      <c r="B120" s="6"/>
-      <c r="C120" s="6"/>
-      <c r="D120" s="6"/>
-      <c r="E120" s="6"/>
-      <c r="F120" s="6"/>
-      <c r="G120" s="6"/>
-      <c r="H120" s="6"/>
-      <c r="I120" s="6"/>
-      <c r="J120" s="6"/>
-      <c r="K120" s="5"/>
-      <c r="L120" s="6"/>
-      <c r="M120" s="5"/>
       <c r="N120" s="6"/>
       <c r="O120" s="6"/>
-      <c r="P120" s="6"/>
-      <c r="Q120" s="6"/>
     </row>
     <row r="121" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A121" s="5"/>
-      <c r="B121" s="8"/>
-      <c r="C121" s="5"/>
+      <c r="B121" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="C121" s="6" t="s">
+        <v>64</v>
+      </c>
       <c r="D121" s="6"/>
       <c r="E121" s="6"/>
       <c r="F121" s="6"/>
       <c r="G121" s="6"/>
       <c r="H121" s="6"/>
       <c r="I121" s="6"/>
-      <c r="J121" s="8"/>
-      <c r="K121" s="6"/>
-      <c r="L121" s="6"/>
-      <c r="M121" s="6"/>
+      <c r="J121" s="6"/>
+      <c r="K121" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="M121" s="1" t="s">
+        <v>128</v>
+      </c>
       <c r="N121" s="6"/>
-      <c r="O121" s="5"/>
-      <c r="P121" s="6"/>
-      <c r="Q121" s="6"/>
+      <c r="O121" s="6"/>
+    </row>
+    <row r="122" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K122" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="M122" s="1" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="123" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B123" s="6" t="s">
+      <c r="K123" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="M123" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="125" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="B125" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C125" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="C123" s="6"/>
-      <c r="D123" s="6"/>
-      <c r="E123" s="6"/>
-      <c r="F123" s="6"/>
-      <c r="G123" s="6"/>
-      <c r="H123" s="6"/>
-      <c r="I123" s="6"/>
-      <c r="J123" s="6"/>
-      <c r="K123" s="5"/>
-      <c r="L123" s="6"/>
-      <c r="M123" s="5"/>
-      <c r="N123" s="6"/>
-      <c r="O123" s="6"/>
-    </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="N124" s="6"/>
-      <c r="O124" s="6"/>
-    </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="N125" s="6"/>
+      <c r="D125" s="6"/>
+      <c r="E125" s="6"/>
+      <c r="F125" s="6"/>
+      <c r="G125" s="6"/>
+      <c r="H125" s="6"/>
+      <c r="I125" s="6"/>
+      <c r="J125" s="6"/>
+      <c r="K125" s="5"/>
+      <c r="L125" s="6"/>
+      <c r="M125" s="5"/>
     </row>
     <row r="126" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="N126" s="6"/>
-      <c r="O126" s="6"/>
+      <c r="B126" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="C126" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D126" s="6"/>
+      <c r="E126" s="6"/>
+      <c r="F126" s="6"/>
+      <c r="G126" s="6"/>
+      <c r="H126" s="6"/>
+      <c r="I126" s="6"/>
+      <c r="J126" s="6"/>
+      <c r="K126" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="M126" s="1" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="127" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B127" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="C127" s="6" t="s">
-        <v>64</v>
-      </c>
+      <c r="C127" s="6"/>
       <c r="D127" s="6"/>
       <c r="E127" s="6"/>
       <c r="F127" s="6"/>
-      <c r="G127" s="6"/>
+      <c r="G127" s="5"/>
       <c r="H127" s="6"/>
       <c r="I127" s="6"/>
-      <c r="J127" s="6"/>
-      <c r="K127" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="M127" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="N127" s="6"/>
-      <c r="O127" s="6"/>
-    </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="K128" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="M128" s="1" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="129" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K129" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="M129" s="1" t="s">
-        <v>137</v>
+      <c r="J127" s="5"/>
+      <c r="K127" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="L127" s="6"/>
+      <c r="M127" s="5" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="130" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B130" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="K130" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="M130" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="131" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B131" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="C131" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="D131" s="6"/>
-      <c r="E131" s="6"/>
-      <c r="F131" s="6"/>
-      <c r="G131" s="6"/>
-      <c r="H131" s="6"/>
-      <c r="I131" s="6"/>
-      <c r="J131" s="6"/>
-      <c r="K131" s="5"/>
-      <c r="L131" s="6"/>
-      <c r="M131" s="5"/>
+      <c r="K131" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="M131" s="1" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="132" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B132" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="C132" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="D132" s="6"/>
-      <c r="E132" s="6"/>
-      <c r="F132" s="6"/>
-      <c r="G132" s="6"/>
-      <c r="H132" s="6"/>
-      <c r="I132" s="6"/>
-      <c r="J132" s="6"/>
-      <c r="K132" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="M132" s="1" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="133" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="C133" s="6"/>
-      <c r="D133" s="6"/>
-      <c r="E133" s="6"/>
-      <c r="F133" s="6"/>
-      <c r="G133" s="5"/>
-      <c r="H133" s="6"/>
-      <c r="I133" s="6"/>
-      <c r="J133" s="5"/>
-      <c r="K133" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="L133" s="6"/>
-      <c r="M133" s="5" t="s">
-        <v>121</v>
+      <c r="K132" s="1"/>
+    </row>
+    <row r="134" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B134" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="K134" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="M134" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O134" s="6"/>
+    </row>
+    <row r="135" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K135" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M135" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="136" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B136" s="1" t="s">
-        <v>205</v>
-      </c>
       <c r="K136" s="1" t="s">
-        <v>206</v>
+        <v>41</v>
       </c>
       <c r="M136" s="1" t="s">
         <v>23</v>
@@ -3701,202 +3602,185 @@
     </row>
     <row r="137" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K137" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M137" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="138" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K138" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="M138" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="139" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K139" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="M139" s="5" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="141" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B141" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="M137" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="138" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K138" s="1"/>
-    </row>
-    <row r="140" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B140" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="K140" s="1" t="s">
+      <c r="K141" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="M140" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="O140" s="6"/>
-    </row>
-    <row r="141" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K141" s="1" t="s">
-        <v>26</v>
-      </c>
       <c r="M141" s="1" t="s">
         <v>23</v>
+      </c>
+      <c r="O141" s="1" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="142" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K142" s="1" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="M142" s="1" t="s">
         <v>23</v>
+      </c>
+      <c r="O142" s="1" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="143" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K143" s="1" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="M143" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O143" s="1" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="144" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K144" s="1"/>
+    </row>
+    <row r="145" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B145" s="1" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="144" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K144" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="M144" s="1" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="145" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K145" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="M145" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="M145" s="1" t="s">
         <v>112</v>
       </c>
     </row>
+    <row r="146" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K146" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M146" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
     <row r="147" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B147" s="1" t="s">
-        <v>217</v>
-      </c>
       <c r="K147" s="1" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="M147" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="O147" s="1" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="148" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K148" s="1" t="s">
-        <v>26</v>
+        <v>216</v>
       </c>
       <c r="M148" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="O148" s="1" t="s">
-        <v>220</v>
+        <v>103</v>
       </c>
     </row>
     <row r="149" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K149" s="1" t="s">
-        <v>41</v>
+        <v>218</v>
       </c>
       <c r="M149" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="O149" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="150" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K150" s="1"/>
+        <v>217</v>
+      </c>
     </row>
     <row r="151" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B151" s="1" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="K151" s="1" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="M151" s="1" t="s">
-        <v>121</v>
+        <v>23</v>
       </c>
     </row>
     <row r="152" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K152" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="M152" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="155" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B155" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="K155" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="M155" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O155" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="156" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K156" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="M152" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="153" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K153" s="1" t="s">
+      <c r="M156" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O156" s="1" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="157" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K157" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="M153" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="154" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K154" s="1" t="s">
+      <c r="M157" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O157" s="1" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="161" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B161" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="G161" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="M154" s="1" t="s">
+      <c r="K161" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="M161" s="1" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="155" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K155" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="M155" s="1" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="157" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B157" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="K157" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="M157" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="158" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K158" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="M158" s="1" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="161" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B161" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="K161" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="M161" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="O161" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="162" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="162" spans="2:13" x14ac:dyDescent="0.2">
       <c r="K162" s="1" t="s">
-        <v>26</v>
+        <v>95</v>
       </c>
       <c r="M162" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="O162" s="1" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="163" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K163" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="M163" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="O163" s="1" t="s">
-        <v>231</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -3948,15 +3832,15 @@
       <c r="J1" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="K1" s="13" t="s">
+      <c r="K1" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="L1" s="13"/>
-      <c r="M1" s="13"/>
-      <c r="N1" s="13"/>
-      <c r="O1" s="13"/>
-      <c r="P1" s="13"/>
-      <c r="Q1" s="13"/>
+      <c r="L1" s="12"/>
+      <c r="M1" s="12"/>
+      <c r="N1" s="12"/>
+      <c r="O1" s="12"/>
+      <c r="P1" s="12"/>
+      <c r="Q1" s="12"/>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
@@ -4049,21 +3933,21 @@
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B8" s="1" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="K8" s="1" t="s">
         <v>33</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="K9" s="1" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="M9" s="1" t="s">
         <v>66</v>
@@ -4074,16 +3958,16 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B11" s="1" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>53</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.2">
@@ -4107,7 +3991,7 @@
       </c>
       <c r="L12" s="6"/>
       <c r="M12" s="1" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="N12" s="7"/>
       <c r="O12" s="6" t="s">
@@ -4129,7 +4013,7 @@
       </c>
       <c r="L13" s="6"/>
       <c r="M13" s="1" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="N13" s="6"/>
       <c r="O13" s="6" t="s">
@@ -4157,14 +4041,14 @@
         <v>53</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="L15" s="6"/>
       <c r="M15" s="5" t="s">
         <v>23</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.2">
@@ -4175,29 +4059,29 @@
         <v>38</v>
       </c>
       <c r="O16" s="6" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B17" s="1" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>53</v>
       </c>
       <c r="K17" s="5" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="M17" s="5" t="s">
         <v>23</v>
       </c>
       <c r="O17" s="6" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
     </row>
     <row r="18" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B18" s="1" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>53</v>
@@ -4206,7 +4090,7 @@
         <v>36</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
     </row>
     <row r="19" spans="2:15" x14ac:dyDescent="0.2">
@@ -4214,20 +4098,20 @@
         <v>37</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
     </row>
     <row r="20" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K20" s="1" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
     </row>
     <row r="21" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B21" s="1" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>53</v>
@@ -4236,12 +4120,12 @@
         <v>75</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
     </row>
     <row r="23" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B23" s="1" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>53</v>
@@ -4250,29 +4134,29 @@
         <v>75</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
     </row>
     <row r="24" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K24" s="1" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
     </row>
     <row r="26" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B26" s="1" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>53</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
     </row>
     <row r="27" spans="2:15" x14ac:dyDescent="0.2">
@@ -4280,7 +4164,7 @@
         <v>33</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
     </row>
     <row r="28" spans="2:15" x14ac:dyDescent="0.2">
@@ -4296,76 +4180,76 @@
         <v>68</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
     </row>
     <row r="31" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B31" s="1" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>53</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="M31" s="1" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
     </row>
     <row r="32" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B32" s="1" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>53</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.2">
       <c r="K33" s="1" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="M33" s="1" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B34" s="1" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>53</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="M34" s="1" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.2">
       <c r="K35" s="1" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="M35" s="1" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="K36" s="1" t="s">
         <v>75</v>
       </c>
       <c r="M36" s="1" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.2">
@@ -4374,38 +4258,38 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B38" s="1" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>53</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="M38" s="1" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.2">
       <c r="K39" s="1" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="M39" s="1" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B40" s="1" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>53</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="M40" s="1" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="N40" s="6"/>
     </row>
@@ -4414,7 +4298,7 @@
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B42" s="1" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="6"/>
@@ -4429,7 +4313,7 @@
       </c>
       <c r="L42" s="6"/>
       <c r="M42" s="5" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="N42" s="6"/>
     </row>
@@ -4448,7 +4332,7 @@
       </c>
       <c r="L43" s="6"/>
       <c r="M43" s="1" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.2">
@@ -4462,67 +4346,67 @@
       <c r="I44" s="6"/>
       <c r="J44" s="6"/>
       <c r="K44" s="5" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="L44" s="6"/>
       <c r="M44" s="5" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B45" s="1" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="K45" s="1" t="s">
         <v>50</v>
       </c>
       <c r="M45" s="1" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.2">
       <c r="K46" s="1" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="M46" s="5" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B50" s="1" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>53</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="K50" s="1" t="s">
         <v>75</v>
       </c>
       <c r="M50" s="1" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A54" s="1"/>
       <c r="B54" s="1" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>53</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="K54" s="1" t="s">
         <v>75</v>
@@ -4533,7 +4417,7 @@
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.2">
       <c r="K55" s="1" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="M55" s="1" t="s">
         <v>23</v>
@@ -4541,10 +4425,10 @@
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.2">
       <c r="K56" s="1" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="M56" s="1" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>

--- a/Config/Datas/__beans__.xlsx
+++ b/Config/Datas/__beans__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E63F9DF6-80C0-4B26-A204-0B1A9E47A26C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC1136AE-988A-4055-98D1-A53E2B1914C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="239">
   <si>
     <t>##var</t>
   </si>
@@ -912,11 +912,59 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>CardInfo</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>卡牌检索信息</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CardSearchInfo</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>InstantEncounterData</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>options</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>(list#sep=,),string</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>OptionData</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DV_回文串</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GA_创建临时乘区</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GA_滑行</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TileCGA</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TileEffectType</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>list,TileCGA</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GA_修改地块</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>tileId</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1034,7 +1082,7 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1067,9 +1115,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1347,7 +1392,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q162"/>
+  <dimension ref="A1:Q176"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="28.75" customWidth="1"/>
@@ -2719,7 +2764,7 @@
       <c r="K72" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="M72" s="13" t="s">
+      <c r="M72" s="1" t="s">
         <v>87</v>
       </c>
       <c r="O72" s="11"/>
@@ -3316,6 +3361,12 @@
     </row>
     <row r="110" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A110" s="6"/>
+      <c r="B110" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="C110" s="6" t="s">
+        <v>119</v>
+      </c>
       <c r="D110" s="6"/>
       <c r="E110" s="6"/>
       <c r="F110" s="6"/>
@@ -3624,54 +3675,55 @@
         <v>103</v>
       </c>
     </row>
+    <row r="140" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B140" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="K140" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="M140" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
     <row r="141" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B141" s="1" t="s">
-        <v>207</v>
-      </c>
+      <c r="B141" s="1"/>
       <c r="K141" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M141" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="O141" s="1" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="142" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K142" s="1" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="M142" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="O142" s="1" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="143" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K143" s="1" t="s">
-        <v>41</v>
+        <v>228</v>
       </c>
       <c r="M143" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="O143" s="1" t="s">
-        <v>211</v>
+        <v>229</v>
       </c>
     </row>
     <row r="144" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K144" s="1"/>
+      <c r="M144" s="1"/>
     </row>
     <row r="145" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B145" s="1" t="s">
-        <v>208</v>
+        <v>230</v>
       </c>
       <c r="K145" s="1" t="s">
-        <v>212</v>
+        <v>25</v>
       </c>
       <c r="M145" s="1" t="s">
-        <v>112</v>
+        <v>23</v>
       </c>
     </row>
     <row r="146" spans="2:15" x14ac:dyDescent="0.2">
@@ -3692,94 +3744,206 @@
     </row>
     <row r="148" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K148" s="1" t="s">
-        <v>216</v>
+        <v>60</v>
       </c>
       <c r="M148" s="1" t="s">
-        <v>103</v>
+        <v>23</v>
       </c>
     </row>
     <row r="149" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K149" s="1" t="s">
-        <v>218</v>
+        <v>134</v>
       </c>
       <c r="M149" s="1" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="151" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B151" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="K151" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="M151" s="1" t="s">
-        <v>23</v>
-      </c>
+        <v>66</v>
+      </c>
+    </row>
+    <row r="150" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K150" s="1"/>
     </row>
     <row r="152" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B152" s="1" t="s">
+        <v>207</v>
+      </c>
       <c r="K152" s="1" t="s">
-        <v>215</v>
+        <v>25</v>
       </c>
       <c r="M152" s="1" t="s">
-        <v>103</v>
+        <v>23</v>
+      </c>
+      <c r="O152" s="1" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="153" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K153" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M153" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O153" s="1" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="154" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K154" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M154" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O154" s="1" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="155" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B155" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="K155" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="M155" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="O155" s="1" t="s">
-        <v>31</v>
-      </c>
+      <c r="K155" s="1"/>
     </row>
     <row r="156" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B156" s="1" t="s">
+        <v>208</v>
+      </c>
       <c r="K156" s="1" t="s">
-        <v>26</v>
+        <v>212</v>
       </c>
       <c r="M156" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="O156" s="1" t="s">
-        <v>220</v>
+        <v>112</v>
       </c>
     </row>
     <row r="157" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K157" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M157" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="158" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K158" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="M157" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="O157" s="1" t="s">
+      <c r="M158" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="159" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K159" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="M159" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="160" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K160" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="M160" s="1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="162" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B162" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="K162" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="M162" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="163" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K163" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="M163" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="166" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B166" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="K166" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="M166" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O166" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="167" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K167" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M167" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O167" s="1" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="168" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K168" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M168" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O168" s="1" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="161" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B161" s="1" t="s">
+    <row r="169" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K169" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="M169" s="1" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="170" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B170" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="K170" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M170" s="1" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="171" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K171" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="M171" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="175" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B175" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="G175" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="G161" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="K161" s="1" t="s">
+      <c r="K175" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="M161" s="1" t="s">
+      <c r="M175" s="1" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="162" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="K162" s="1" t="s">
+    <row r="176" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K176" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="M162" s="1" t="s">
+      <c r="M176" s="1" t="s">
         <v>96</v>
       </c>
     </row>
@@ -3795,7 +3959,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EECC075D-9730-41E5-B97E-C301603D1E48}">
-  <dimension ref="A1:Q56"/>
+  <dimension ref="A1:Q63"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="27.375" customWidth="1"/>
@@ -4429,6 +4593,56 @@
       </c>
       <c r="M56" s="1" t="s">
         <v>94</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B58" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="K58" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="M58" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="K59" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="M59" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B61" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="K61" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="M61" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B63" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="K63" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="M63" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/Config/Datas/__beans__.xlsx
+++ b/Config/Datas/__beans__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC1136AE-988A-4055-98D1-A53E2B1914C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E79DEFA1-18CC-4D95-8F1A-362F016EE911}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="243">
   <si>
     <t>##var</t>
   </si>
@@ -965,6 +965,22 @@
   </si>
   <si>
     <t>tileId</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>EntityData</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>EntityCGA</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>list,EntityCGA</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>EntityGAType</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1392,7 +1408,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q176"/>
+  <dimension ref="A1:Q184"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="28.75" customWidth="1"/>
@@ -3422,18 +3438,24 @@
     </row>
     <row r="113" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A113" s="6"/>
-      <c r="B113" s="6"/>
-      <c r="C113" s="6"/>
+      <c r="B113" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="C113" s="5"/>
       <c r="D113" s="6"/>
       <c r="E113" s="6"/>
       <c r="F113" s="6"/>
       <c r="G113" s="6"/>
       <c r="H113" s="6"/>
       <c r="I113" s="6"/>
-      <c r="J113" s="6"/>
-      <c r="K113" s="5"/>
+      <c r="J113" s="5"/>
+      <c r="K113" s="5" t="s">
+        <v>25</v>
+      </c>
       <c r="L113" s="6"/>
-      <c r="M113" s="5"/>
+      <c r="M113" s="5" t="s">
+        <v>23</v>
+      </c>
       <c r="N113" s="6"/>
       <c r="O113" s="6"/>
       <c r="P113" s="6"/>
@@ -3441,26 +3463,30 @@
     </row>
     <row r="114" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A114" s="6"/>
-      <c r="B114" s="6"/>
-      <c r="C114" s="6"/>
+      <c r="B114" s="5"/>
+      <c r="C114" s="5"/>
       <c r="D114" s="6"/>
       <c r="E114" s="6"/>
       <c r="F114" s="6"/>
       <c r="G114" s="6"/>
       <c r="H114" s="6"/>
       <c r="I114" s="6"/>
-      <c r="J114" s="6"/>
-      <c r="K114" s="5"/>
+      <c r="J114" s="5"/>
+      <c r="K114" s="5" t="s">
+        <v>26</v>
+      </c>
       <c r="L114" s="6"/>
-      <c r="M114" s="5"/>
+      <c r="M114" s="5" t="s">
+        <v>23</v>
+      </c>
       <c r="N114" s="6"/>
       <c r="O114" s="6"/>
       <c r="P114" s="6"/>
       <c r="Q114" s="6"/>
     </row>
     <row r="115" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A115" s="5"/>
-      <c r="B115" s="8"/>
+      <c r="A115" s="6"/>
+      <c r="B115" s="5"/>
       <c r="C115" s="5"/>
       <c r="D115" s="6"/>
       <c r="E115" s="6"/>
@@ -3468,19 +3494,45 @@
       <c r="G115" s="6"/>
       <c r="H115" s="6"/>
       <c r="I115" s="6"/>
-      <c r="J115" s="8"/>
-      <c r="K115" s="6"/>
+      <c r="J115" s="5"/>
+      <c r="K115" s="5" t="s">
+        <v>41</v>
+      </c>
       <c r="L115" s="6"/>
-      <c r="M115" s="6"/>
+      <c r="M115" s="5" t="s">
+        <v>23</v>
+      </c>
       <c r="N115" s="6"/>
-      <c r="O115" s="5"/>
+      <c r="O115" s="6"/>
       <c r="P115" s="6"/>
       <c r="Q115" s="6"/>
     </row>
+    <row r="116" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A116" s="6"/>
+      <c r="B116" s="5"/>
+      <c r="C116" s="5"/>
+      <c r="D116" s="6"/>
+      <c r="E116" s="6"/>
+      <c r="F116" s="6"/>
+      <c r="G116" s="6"/>
+      <c r="H116" s="6"/>
+      <c r="I116" s="6"/>
+      <c r="J116" s="5"/>
+      <c r="K116" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="L116" s="6"/>
+      <c r="M116" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="N116" s="6"/>
+      <c r="O116" s="6"/>
+      <c r="P116" s="6"/>
+      <c r="Q116" s="6"/>
+    </row>
     <row r="117" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B117" s="6" t="s">
-        <v>64</v>
-      </c>
+      <c r="A117" s="6"/>
+      <c r="B117" s="6"/>
       <c r="C117" s="6"/>
       <c r="D117" s="6"/>
       <c r="E117" s="6"/>
@@ -3489,69 +3541,150 @@
       <c r="H117" s="6"/>
       <c r="I117" s="6"/>
       <c r="J117" s="6"/>
-      <c r="K117" s="5"/>
+      <c r="K117" s="5" t="s">
+        <v>60</v>
+      </c>
       <c r="L117" s="6"/>
-      <c r="M117" s="5"/>
+      <c r="M117" s="5" t="s">
+        <v>23</v>
+      </c>
       <c r="N117" s="6"/>
       <c r="O117" s="6"/>
+      <c r="P117" s="6"/>
+      <c r="Q117" s="6"/>
     </row>
     <row r="118" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A118" s="6"/>
+      <c r="B118" s="6"/>
+      <c r="C118" s="6"/>
+      <c r="D118" s="6"/>
+      <c r="E118" s="6"/>
+      <c r="F118" s="6"/>
+      <c r="G118" s="6"/>
+      <c r="H118" s="6"/>
+      <c r="I118" s="6"/>
+      <c r="J118" s="6"/>
+      <c r="K118" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="M118" s="5" t="s">
+        <v>241</v>
+      </c>
       <c r="N118" s="6"/>
       <c r="O118" s="6"/>
+      <c r="P118" s="6"/>
+      <c r="Q118" s="6"/>
     </row>
     <row r="119" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A119" s="5"/>
+      <c r="B119" s="8"/>
+      <c r="C119" s="5"/>
+      <c r="D119" s="6"/>
+      <c r="E119" s="6"/>
+      <c r="F119" s="6"/>
+      <c r="G119" s="6"/>
+      <c r="H119" s="6"/>
+      <c r="I119" s="6"/>
+      <c r="J119" s="8"/>
+      <c r="K119" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="M119" s="5" t="s">
+        <v>103</v>
+      </c>
       <c r="N119" s="6"/>
+      <c r="O119" s="5"/>
+      <c r="P119" s="6"/>
+      <c r="Q119" s="6"/>
     </row>
     <row r="120" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A120" s="5"/>
+      <c r="B120" s="8"/>
+      <c r="C120" s="5"/>
+      <c r="D120" s="6"/>
+      <c r="E120" s="6"/>
+      <c r="F120" s="6"/>
+      <c r="G120" s="6"/>
+      <c r="H120" s="6"/>
+      <c r="I120" s="6"/>
+      <c r="J120" s="8"/>
+      <c r="K120" s="1"/>
+      <c r="M120" s="5"/>
       <c r="N120" s="6"/>
-      <c r="O120" s="6"/>
+      <c r="O120" s="5"/>
+      <c r="P120" s="6"/>
+      <c r="Q120" s="6"/>
     </row>
     <row r="121" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B121" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="C121" s="6" t="s">
-        <v>64</v>
-      </c>
+      <c r="A121" s="5"/>
+      <c r="B121" s="8" t="s">
+        <v>240</v>
+      </c>
+      <c r="C121" s="5"/>
       <c r="D121" s="6"/>
       <c r="E121" s="6"/>
       <c r="F121" s="6"/>
       <c r="G121" s="6"/>
       <c r="H121" s="6"/>
       <c r="I121" s="6"/>
-      <c r="J121" s="6"/>
+      <c r="J121" s="8"/>
       <c r="K121" s="1" t="s">
-        <v>124</v>
+        <v>33</v>
       </c>
       <c r="M121" s="1" t="s">
-        <v>128</v>
+        <v>242</v>
       </c>
       <c r="N121" s="6"/>
-      <c r="O121" s="6"/>
+      <c r="O121" s="5"/>
+      <c r="P121" s="6"/>
+      <c r="Q121" s="6"/>
     </row>
     <row r="122" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A122" s="5"/>
+      <c r="B122" s="8"/>
+      <c r="C122" s="5"/>
+      <c r="D122" s="6"/>
+      <c r="E122" s="6"/>
+      <c r="F122" s="6"/>
+      <c r="G122" s="6"/>
+      <c r="H122" s="6"/>
+      <c r="I122" s="6"/>
+      <c r="J122" s="8"/>
       <c r="K122" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="M122" s="1" t="s">
-        <v>114</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="M122" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="N122" s="6"/>
+      <c r="O122" s="5"/>
+      <c r="P122" s="6"/>
+      <c r="Q122" s="6"/>
     </row>
     <row r="123" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="K123" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="M123" s="1" t="s">
-        <v>128</v>
-      </c>
+      <c r="A123" s="5"/>
+      <c r="B123" s="8"/>
+      <c r="C123" s="5"/>
+      <c r="D123" s="6"/>
+      <c r="E123" s="6"/>
+      <c r="F123" s="6"/>
+      <c r="G123" s="6"/>
+      <c r="H123" s="6"/>
+      <c r="I123" s="6"/>
+      <c r="J123" s="8"/>
+      <c r="K123" s="1"/>
+      <c r="M123" s="5"/>
+      <c r="N123" s="6"/>
+      <c r="O123" s="5"/>
+      <c r="P123" s="6"/>
+      <c r="Q123" s="6"/>
+    </row>
+    <row r="124" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K124" s="1"/>
+      <c r="M124" s="5"/>
     </row>
     <row r="125" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B125" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="C125" s="6" t="s">
-        <v>64</v>
-      </c>
+      <c r="C125" s="6"/>
       <c r="D125" s="6"/>
       <c r="E125" s="6"/>
       <c r="F125" s="6"/>
@@ -3562,388 +3695,461 @@
       <c r="K125" s="5"/>
       <c r="L125" s="6"/>
       <c r="M125" s="5"/>
+      <c r="N125" s="6"/>
+      <c r="O125" s="6"/>
     </row>
     <row r="126" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B126" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="C126" s="6" t="s">
+      <c r="N126" s="6"/>
+      <c r="O126" s="6"/>
+    </row>
+    <row r="127" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="B127" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="D126" s="6"/>
-      <c r="E126" s="6"/>
-      <c r="F126" s="6"/>
-      <c r="G126" s="6"/>
-      <c r="H126" s="6"/>
-      <c r="I126" s="6"/>
-      <c r="J126" s="6"/>
-      <c r="K126" s="1" t="s">
+      <c r="N127" s="6"/>
+    </row>
+    <row r="128" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="N128" s="6"/>
+      <c r="O128" s="6"/>
+    </row>
+    <row r="129" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B129" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="C129" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D129" s="6"/>
+      <c r="E129" s="6"/>
+      <c r="F129" s="6"/>
+      <c r="G129" s="6"/>
+      <c r="H129" s="6"/>
+      <c r="I129" s="6"/>
+      <c r="J129" s="6"/>
+      <c r="K129" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="M129" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="N129" s="6"/>
+      <c r="O129" s="6"/>
+    </row>
+    <row r="130" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K130" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="M126" s="1" t="s">
+      <c r="M130" s="1" t="s">
         <v>114</v>
-      </c>
-    </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="C127" s="6"/>
-      <c r="D127" s="6"/>
-      <c r="E127" s="6"/>
-      <c r="F127" s="6"/>
-      <c r="G127" s="5"/>
-      <c r="H127" s="6"/>
-      <c r="I127" s="6"/>
-      <c r="J127" s="5"/>
-      <c r="K127" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="L127" s="6"/>
-      <c r="M127" s="5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="130" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B130" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="K130" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="M130" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="131" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K131" s="1" t="s">
-        <v>197</v>
+        <v>125</v>
       </c>
       <c r="M131" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="132" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K132" s="1"/>
+        <v>128</v>
+      </c>
+    </row>
+    <row r="133" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B133" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C133" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D133" s="6"/>
+      <c r="E133" s="6"/>
+      <c r="F133" s="6"/>
+      <c r="G133" s="6"/>
+      <c r="H133" s="6"/>
+      <c r="I133" s="6"/>
+      <c r="J133" s="6"/>
+      <c r="K133" s="5"/>
+      <c r="L133" s="6"/>
+      <c r="M133" s="5"/>
     </row>
     <row r="134" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B134" s="1" t="s">
-        <v>206</v>
-      </c>
+      <c r="B134" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="C134" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D134" s="6"/>
+      <c r="E134" s="6"/>
+      <c r="F134" s="6"/>
+      <c r="G134" s="6"/>
+      <c r="H134" s="6"/>
+      <c r="I134" s="6"/>
+      <c r="J134" s="6"/>
       <c r="K134" s="1" t="s">
-        <v>25</v>
+        <v>113</v>
       </c>
       <c r="M134" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="O134" s="6"/>
+        <v>114</v>
+      </c>
     </row>
     <row r="135" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K135" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="M135" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="136" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K136" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="M136" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="137" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K137" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="M137" s="1" t="s">
-        <v>198</v>
+      <c r="C135" s="6"/>
+      <c r="D135" s="6"/>
+      <c r="E135" s="6"/>
+      <c r="F135" s="6"/>
+      <c r="G135" s="5"/>
+      <c r="H135" s="6"/>
+      <c r="I135" s="6"/>
+      <c r="J135" s="5"/>
+      <c r="K135" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="L135" s="6"/>
+      <c r="M135" s="5" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="138" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B138" s="1" t="s">
+        <v>195</v>
+      </c>
       <c r="K138" s="1" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="M138" s="1" t="s">
-        <v>112</v>
+        <v>23</v>
       </c>
     </row>
     <row r="139" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K139" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="M139" s="5" t="s">
-        <v>103</v>
+        <v>197</v>
+      </c>
+      <c r="M139" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="140" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B140" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="K140" s="1" t="s">
+      <c r="K140" s="1"/>
+    </row>
+    <row r="142" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B142" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="K142" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="M140" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="141" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B141" s="1"/>
-      <c r="K141" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="M141" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="142" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K142" s="1" t="s">
-        <v>41</v>
-      </c>
       <c r="M142" s="1" t="s">
         <v>23</v>
       </c>
+      <c r="O142" s="6"/>
     </row>
     <row r="143" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K143" s="1" t="s">
-        <v>228</v>
+        <v>26</v>
       </c>
       <c r="M143" s="1" t="s">
-        <v>229</v>
+        <v>23</v>
       </c>
     </row>
     <row r="144" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K144" s="1"/>
-      <c r="M144" s="1"/>
+      <c r="K144" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M144" s="1" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="145" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B145" s="1" t="s">
-        <v>230</v>
-      </c>
       <c r="K145" s="1" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="M145" s="1" t="s">
-        <v>23</v>
+        <v>198</v>
       </c>
     </row>
     <row r="146" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K146" s="1" t="s">
-        <v>26</v>
+        <v>199</v>
       </c>
       <c r="M146" s="1" t="s">
-        <v>23</v>
+        <v>112</v>
       </c>
     </row>
     <row r="147" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K147" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="M147" s="5" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="148" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B148" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="K148" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="M148" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="149" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B149" s="1"/>
+      <c r="K149" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M149" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="150" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K150" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="M147" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="148" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K148" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="M148" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="149" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K149" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="M149" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="150" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K150" s="1"/>
+      <c r="M150" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="151" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K151" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="M151" s="1" t="s">
+        <v>229</v>
+      </c>
     </row>
     <row r="152" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B152" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="K152" s="1" t="s">
+      <c r="K152" s="1"/>
+      <c r="M152" s="1"/>
+    </row>
+    <row r="153" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B153" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="K153" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="M152" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="O152" s="1" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="153" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K153" s="1" t="s">
-        <v>26</v>
-      </c>
       <c r="M153" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="O153" s="1" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="154" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K154" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M154" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="155" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K155" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="M154" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="O154" s="1" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="155" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K155" s="1"/>
+      <c r="M155" s="1" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="156" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B156" s="1" t="s">
-        <v>208</v>
-      </c>
       <c r="K156" s="1" t="s">
-        <v>212</v>
+        <v>60</v>
       </c>
       <c r="M156" s="1" t="s">
-        <v>112</v>
+        <v>23</v>
       </c>
     </row>
     <row r="157" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K157" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="M157" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="158" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K158" s="1"/>
+    </row>
+    <row r="160" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B160" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="K160" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="M160" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O160" s="1" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="161" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K161" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="M157" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="158" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K158" s="1" t="s">
+      <c r="M161" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O161" s="1" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="162" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K162" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="M158" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="159" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K159" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="M159" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="160" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K160" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="M160" s="1" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="162" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B162" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="K162" s="1" t="s">
-        <v>214</v>
-      </c>
       <c r="M162" s="1" t="s">
         <v>23</v>
       </c>
+      <c r="O162" s="1" t="s">
+        <v>211</v>
+      </c>
     </row>
     <row r="163" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K163" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="M163" s="1" t="s">
-        <v>103</v>
+      <c r="K163" s="1"/>
+    </row>
+    <row r="164" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B164" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="K164" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="M164" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="165" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K165" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M165" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="166" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B166" s="1" t="s">
-        <v>219</v>
-      </c>
       <c r="K166" s="1" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="M166" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="O166" s="1" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="167" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K167" s="1" t="s">
-        <v>26</v>
+        <v>216</v>
       </c>
       <c r="M167" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="O167" s="1" t="s">
-        <v>220</v>
+        <v>103</v>
       </c>
     </row>
     <row r="168" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K168" s="1" t="s">
-        <v>41</v>
+        <v>218</v>
       </c>
       <c r="M168" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="O168" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="169" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K169" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="M169" s="1" t="s">
-        <v>236</v>
+        <v>217</v>
       </c>
     </row>
     <row r="170" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B170" s="1" t="s">
-        <v>234</v>
+        <v>213</v>
       </c>
       <c r="K170" s="1" t="s">
-        <v>33</v>
+        <v>214</v>
       </c>
       <c r="M170" s="1" t="s">
-        <v>235</v>
+        <v>23</v>
       </c>
     </row>
     <row r="171" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K171" s="1" t="s">
-        <v>134</v>
+        <v>215</v>
       </c>
       <c r="M171" s="1" t="s">
-        <v>66</v>
+        <v>103</v>
+      </c>
+    </row>
+    <row r="174" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B174" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="K174" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="M174" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O174" s="1" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="175" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B175" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="G175" s="1" t="s">
-        <v>225</v>
-      </c>
       <c r="K175" s="1" t="s">
-        <v>111</v>
+        <v>26</v>
       </c>
       <c r="M175" s="1" t="s">
-        <v>112</v>
+        <v>23</v>
+      </c>
+      <c r="O175" s="1" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="176" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K176" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M176" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O176" s="1" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="177" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="K177" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="M177" s="1" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="178" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B178" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="K178" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M178" s="1" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="179" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="K179" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="M179" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="183" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B183" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="G183" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="K183" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="M183" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="184" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="K184" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="M176" s="1" t="s">
+      <c r="M184" s="1" t="s">
         <v>96</v>
       </c>
     </row>

--- a/Config/Datas/__beans__.xlsx
+++ b/Config/Datas/__beans__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E79DEFA1-18CC-4D95-8F1A-362F016EE911}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E31E431E-9B47-46FD-A3FC-5477BF62B7FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="246">
   <si>
     <t>##var</t>
   </si>
@@ -981,6 +981,18 @@
   </si>
   <si>
     <t>EntityGAType</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>maxFoodCount</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GA_创建实体</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>entityID</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1408,24 +1420,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q184"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:Q185"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="28.75" customWidth="1"/>
     <col min="3" max="3" width="22" customWidth="1"/>
-    <col min="4" max="4" width="9.375" customWidth="1"/>
+    <col min="4" max="4" width="9.33203125" customWidth="1"/>
     <col min="5" max="5" width="9.5" customWidth="1"/>
-    <col min="6" max="6" width="5.875" customWidth="1"/>
+    <col min="6" max="6" width="5.83203125" customWidth="1"/>
     <col min="7" max="7" width="16" customWidth="1"/>
-    <col min="8" max="8" width="6.625" customWidth="1"/>
+    <col min="8" max="8" width="6.58203125" customWidth="1"/>
     <col min="9" max="9" width="6.75" customWidth="1"/>
-    <col min="10" max="10" width="7.375" customWidth="1"/>
+    <col min="10" max="10" width="7.33203125" customWidth="1"/>
     <col min="11" max="12" width="13.5" customWidth="1"/>
-    <col min="13" max="13" width="11.875" customWidth="1"/>
+    <col min="13" max="13" width="11.83203125" customWidth="1"/>
     <col min="14" max="14" width="20.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1466,7 +1478,7 @@
       <c r="P1" s="12"/>
       <c r="Q1" s="12"/>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -1501,7 +1513,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>11</v>
       </c>
@@ -1538,7 +1550,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
         <v>29</v>
       </c>
@@ -1567,7 +1579,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
         <v>29</v>
       </c>
@@ -1594,7 +1606,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" s="6"/>
       <c r="B6" s="6"/>
       <c r="C6" s="5"/>
@@ -1613,7 +1625,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" s="6"/>
       <c r="B7" s="6" t="s">
         <v>176</v>
@@ -1640,7 +1652,7 @@
       <c r="P7" s="6"/>
       <c r="Q7" s="6"/>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" s="6"/>
       <c r="B8" s="6"/>
       <c r="C8" s="5"/>
@@ -1663,7 +1675,7 @@
       <c r="P8" s="6"/>
       <c r="Q8" s="6"/>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" s="6"/>
       <c r="B9" s="6"/>
       <c r="C9" s="5"/>
@@ -1686,7 +1698,7 @@
       <c r="P9" s="6"/>
       <c r="Q9" s="6"/>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" s="6"/>
       <c r="B10" s="6"/>
       <c r="C10" s="5"/>
@@ -1708,7 +1720,7 @@
       <c r="P10" s="6"/>
       <c r="Q10" s="6"/>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" s="6"/>
       <c r="B11" s="6"/>
       <c r="C11" s="5"/>
@@ -1730,7 +1742,7 @@
       <c r="P11" s="6"/>
       <c r="Q11" s="6"/>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" s="6"/>
       <c r="B12" s="6"/>
       <c r="C12" s="5"/>
@@ -1753,7 +1765,7 @@
       <c r="P12" s="6"/>
       <c r="Q12" s="6"/>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" s="6"/>
       <c r="B13" s="6"/>
       <c r="C13" s="5"/>
@@ -1772,7 +1784,7 @@
       <c r="P13" s="6"/>
       <c r="Q13" s="6"/>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
         <v>180</v>
       </c>
@@ -1793,7 +1805,7 @@
       <c r="P14" s="6"/>
       <c r="Q14" s="6"/>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15" s="6"/>
       <c r="B15" s="6"/>
       <c r="C15" s="5"/>
@@ -1812,7 +1824,7 @@
       <c r="P15" s="6"/>
       <c r="Q15" s="6"/>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" s="6"/>
       <c r="B16" s="6"/>
       <c r="C16" s="5"/>
@@ -1831,7 +1843,7 @@
       <c r="P16" s="6"/>
       <c r="Q16" s="6"/>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17" s="6"/>
       <c r="B17" s="6" t="s">
         <v>181</v>
@@ -1856,7 +1868,7 @@
       <c r="P17" s="6"/>
       <c r="Q17" s="6"/>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A18" s="6"/>
       <c r="B18" s="6"/>
       <c r="C18" s="5"/>
@@ -1879,7 +1891,7 @@
       <c r="P18" s="6"/>
       <c r="Q18" s="6"/>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A19" s="6"/>
       <c r="B19" s="6"/>
       <c r="C19" s="5"/>
@@ -1898,7 +1910,7 @@
       <c r="P19" s="6"/>
       <c r="Q19" s="6"/>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A20" s="6"/>
       <c r="B20" s="6" t="s">
         <v>30</v>
@@ -1927,7 +1939,7 @@
       <c r="P20" s="6"/>
       <c r="Q20" s="6"/>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A21" s="6"/>
       <c r="B21" s="6"/>
       <c r="C21" s="5"/>
@@ -1952,7 +1964,7 @@
       <c r="P21" s="6"/>
       <c r="Q21" s="6"/>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A22" s="6"/>
       <c r="D22" s="6"/>
       <c r="E22" s="6"/>
@@ -1973,7 +1985,7 @@
       <c r="P22" s="6"/>
       <c r="Q22" s="6"/>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A23" s="6"/>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
@@ -1991,7 +2003,7 @@
       <c r="P23" s="6"/>
       <c r="Q23" s="6"/>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A24" s="6"/>
       <c r="B24" s="6"/>
       <c r="C24" s="6"/>
@@ -2014,7 +2026,7 @@
       <c r="P24" s="6"/>
       <c r="Q24" s="6"/>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A25" s="6"/>
       <c r="D25" s="6"/>
       <c r="E25" s="6"/>
@@ -2035,7 +2047,7 @@
       <c r="P25" s="6"/>
       <c r="Q25" s="6"/>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A26" s="6"/>
       <c r="B26" s="6"/>
       <c r="C26" s="6"/>
@@ -2060,7 +2072,7 @@
       <c r="P26" s="6"/>
       <c r="Q26" s="6"/>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A27" s="6"/>
       <c r="B27" s="6"/>
       <c r="C27" s="6"/>
@@ -2085,7 +2097,7 @@
       <c r="P27" s="7"/>
       <c r="Q27" s="7"/>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A28" s="6"/>
       <c r="K28" s="5" t="s">
         <v>60</v>
@@ -2101,7 +2113,7 @@
       <c r="P28" s="6"/>
       <c r="Q28" s="6"/>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A29" s="6"/>
       <c r="K29" s="1" t="s">
         <v>143</v>
@@ -2115,7 +2127,7 @@
       <c r="P29" s="6"/>
       <c r="Q29" s="6"/>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A30" s="6"/>
       <c r="K30" s="1" t="s">
         <v>150</v>
@@ -2129,7 +2141,7 @@
       <c r="P30" s="6"/>
       <c r="Q30" s="6"/>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A31" s="6"/>
       <c r="K31" s="1" t="s">
         <v>95</v>
@@ -2142,11 +2154,11 @@
       </c>
       <c r="Q31" s="6"/>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A32" s="6"/>
       <c r="Q32" s="6"/>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A33" s="6"/>
       <c r="B33" s="6" t="s">
         <v>45</v>
@@ -2175,7 +2187,7 @@
       <c r="P33" s="6"/>
       <c r="Q33" s="6"/>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A34" s="6"/>
       <c r="B34" s="6"/>
       <c r="C34" s="6"/>
@@ -2200,7 +2212,7 @@
       <c r="P34" s="6"/>
       <c r="Q34" s="6"/>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A35" s="6"/>
       <c r="B35" s="6"/>
       <c r="C35" s="6"/>
@@ -2223,7 +2235,7 @@
       <c r="P35" s="6"/>
       <c r="Q35" s="6"/>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="6"/>
       <c r="B36" s="5"/>
       <c r="C36" s="6"/>
@@ -2248,9 +2260,9 @@
       <c r="P36" s="6"/>
       <c r="Q36" s="6"/>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="6"/>
-      <c r="B37" s="6"/>
+      <c r="B37" s="5"/>
       <c r="C37" s="6"/>
       <c r="D37" s="6"/>
       <c r="E37" s="6"/>
@@ -2258,227 +2270,239 @@
       <c r="G37" s="6"/>
       <c r="H37" s="6"/>
       <c r="I37" s="6"/>
-      <c r="J37" s="6"/>
+      <c r="J37" s="5"/>
       <c r="K37" s="5" t="s">
-        <v>43</v>
+        <v>243</v>
       </c>
       <c r="L37" s="6"/>
       <c r="M37" s="5" t="s">
-        <v>23</v>
+        <v>112</v>
       </c>
       <c r="N37" s="6"/>
-      <c r="O37" s="6" t="s">
-        <v>132</v>
-      </c>
+      <c r="O37" s="6"/>
       <c r="P37" s="6"/>
       <c r="Q37" s="6"/>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A38" s="6"/>
+      <c r="B38" s="6"/>
+      <c r="C38" s="6"/>
+      <c r="D38" s="6"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="6"/>
+      <c r="G38" s="6"/>
+      <c r="H38" s="6"/>
+      <c r="I38" s="6"/>
+      <c r="J38" s="6"/>
+      <c r="K38" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="L38" s="6"/>
+      <c r="M38" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="N38" s="6"/>
+      <c r="O38" s="6" t="s">
+        <v>132</v>
+      </c>
       <c r="P38" s="6"/>
       <c r="Q38" s="6"/>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A39" s="6"/>
-      <c r="B39" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="G39" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="K39" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="M39" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="O39" s="6" t="s">
-        <v>31</v>
-      </c>
       <c r="P39" s="6"/>
       <c r="Q39" s="6"/>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A40" s="6"/>
+      <c r="B40" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>146</v>
+      </c>
       <c r="K40" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M40" s="5" t="s">
         <v>23</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>148</v>
+        <v>31</v>
       </c>
       <c r="P40" s="6"/>
       <c r="Q40" s="6"/>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A41" s="6"/>
       <c r="K41" s="5" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="M41" s="5" t="s">
         <v>23</v>
       </c>
       <c r="O41" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="P41" s="6"/>
       <c r="Q41" s="6"/>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A42" s="6"/>
       <c r="K42" s="5" t="s">
-        <v>161</v>
+        <v>41</v>
       </c>
       <c r="M42" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="O42" s="6"/>
+      <c r="O42" s="6" t="s">
+        <v>147</v>
+      </c>
       <c r="P42" s="6"/>
       <c r="Q42" s="6"/>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A43" s="6"/>
       <c r="K43" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="M43" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="O43" s="6" t="s">
-        <v>149</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="M43" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="O43" s="6"/>
       <c r="P43" s="6"/>
       <c r="Q43" s="6"/>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A44" s="6"/>
       <c r="K44" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="M44" s="5" t="s">
-        <v>23</v>
+        <v>150</v>
+      </c>
+      <c r="M44" s="1" t="s">
+        <v>103</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="P44" s="6"/>
       <c r="Q44" s="6"/>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A45" s="6"/>
       <c r="K45" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="M45" s="5" t="s">
-        <v>153</v>
+        <v>23</v>
       </c>
       <c r="O45" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="P45" s="6"/>
       <c r="Q45" s="6"/>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A46" s="6"/>
       <c r="K46" s="5" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="M46" s="5" t="s">
         <v>153</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="P46" s="6"/>
       <c r="Q46" s="6"/>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A47" s="6"/>
-    </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K47" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="M47" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="O47" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="P47" s="6"/>
+      <c r="Q47" s="6"/>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A48" s="6"/>
-      <c r="Q48" s="6"/>
-    </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A49" s="6"/>
       <c r="Q49" s="6"/>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A50" s="6"/>
-      <c r="B50" s="6" t="s">
+      <c r="Q50" s="6"/>
+    </row>
+    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A51" s="6"/>
+      <c r="B51" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="C50" s="6"/>
-      <c r="D50" s="6"/>
-      <c r="E50" s="6"/>
-      <c r="F50" s="6"/>
-      <c r="G50" s="6"/>
-      <c r="H50" s="6"/>
-      <c r="I50" s="6"/>
-      <c r="J50" s="6"/>
-      <c r="K50" s="1" t="s">
+      <c r="C51" s="6"/>
+      <c r="D51" s="6"/>
+      <c r="E51" s="6"/>
+      <c r="F51" s="6"/>
+      <c r="G51" s="6"/>
+      <c r="H51" s="6"/>
+      <c r="I51" s="6"/>
+      <c r="J51" s="6"/>
+      <c r="K51" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="M50" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="N50" s="6"/>
-      <c r="O50" s="6" t="s">
+      <c r="M51" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="N51" s="6"/>
+      <c r="O51" s="6" t="s">
         <v>72</v>
-      </c>
-      <c r="P50" s="6"/>
-      <c r="Q50" s="6"/>
-    </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A51" s="6"/>
-      <c r="K51" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="L51" s="6"/>
-      <c r="M51" s="6" t="s">
-        <v>69</v>
       </c>
       <c r="P51" s="6"/>
       <c r="Q51" s="6"/>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A52" s="6"/>
-      <c r="K52" s="5" t="s">
+      <c r="K52" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="L52" s="6"/>
+      <c r="M52" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="P52" s="6"/>
+      <c r="Q52" s="6"/>
+    </row>
+    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A53" s="6"/>
+      <c r="K53" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="M52" s="5" t="s">
+      <c r="M53" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="P52" s="7"/>
-      <c r="Q52" s="6"/>
-    </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A53" s="6"/>
-      <c r="K53" s="5"/>
-      <c r="M53" s="5"/>
       <c r="P53" s="7"/>
       <c r="Q53" s="6"/>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A54" s="6"/>
-      <c r="B54" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="K54" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="M54" s="5" t="s">
-        <v>23</v>
-      </c>
+      <c r="K54" s="5"/>
+      <c r="M54" s="5"/>
       <c r="P54" s="7"/>
       <c r="Q54" s="6"/>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A55" s="6"/>
+      <c r="B55" s="1" t="s">
+        <v>166</v>
+      </c>
       <c r="K55" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="M55" s="5" t="s">
         <v>23</v>
@@ -2486,80 +2510,68 @@
       <c r="P55" s="7"/>
       <c r="Q55" s="6"/>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A56" s="6"/>
       <c r="K56" s="5" t="s">
-        <v>33</v>
+        <v>165</v>
       </c>
       <c r="M56" s="5" t="s">
-        <v>163</v>
+        <v>23</v>
       </c>
       <c r="P56" s="7"/>
       <c r="Q56" s="6"/>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A57" s="6"/>
       <c r="K57" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="M57" s="6" t="s">
-        <v>66</v>
+        <v>33</v>
+      </c>
+      <c r="M57" s="5" t="s">
+        <v>163</v>
       </c>
       <c r="P57" s="7"/>
       <c r="Q57" s="6"/>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A58" s="6"/>
-      <c r="K58" s="5"/>
-      <c r="M58" s="5"/>
+      <c r="K58" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="M58" s="6" t="s">
+        <v>66</v>
+      </c>
       <c r="P58" s="7"/>
       <c r="Q58" s="6"/>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A59" s="6"/>
+      <c r="K59" s="5"/>
+      <c r="M59" s="5"/>
       <c r="P59" s="7"/>
       <c r="Q59" s="6"/>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A60" s="6"/>
-      <c r="B60" s="5" t="s">
+      <c r="P60" s="7"/>
+      <c r="Q60" s="6"/>
+    </row>
+    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A61" s="6"/>
+      <c r="B61" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="C60" s="6"/>
-      <c r="D60" s="6"/>
-      <c r="E60" s="6"/>
-      <c r="F60" s="6"/>
-      <c r="G60" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="H60" s="6"/>
-      <c r="I60" s="6"/>
-      <c r="J60" s="5"/>
-      <c r="K60" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="L60" s="6"/>
-      <c r="M60" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="N60" s="9"/>
-      <c r="O60" s="6"/>
-      <c r="P60" s="6"/>
-      <c r="Q60" s="6"/>
-    </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A61" s="6"/>
-      <c r="B61" s="6"/>
       <c r="C61" s="6"/>
       <c r="D61" s="6"/>
       <c r="E61" s="6"/>
       <c r="F61" s="6"/>
-      <c r="G61" s="6"/>
+      <c r="G61" s="6" t="s">
+        <v>70</v>
+      </c>
       <c r="H61" s="6"/>
       <c r="I61" s="6"/>
-      <c r="J61" s="6"/>
+      <c r="J61" s="5"/>
       <c r="K61" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L61" s="6"/>
       <c r="M61" s="8" t="s">
@@ -2570,7 +2582,7 @@
       <c r="P61" s="6"/>
       <c r="Q61" s="6"/>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A62" s="6"/>
       <c r="B62" s="6"/>
       <c r="C62" s="6"/>
@@ -2579,9 +2591,10 @@
       <c r="F62" s="6"/>
       <c r="G62" s="6"/>
       <c r="H62" s="6"/>
+      <c r="I62" s="6"/>
       <c r="J62" s="6"/>
       <c r="K62" s="8" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="L62" s="6"/>
       <c r="M62" s="8" t="s">
@@ -2592,7 +2605,7 @@
       <c r="P62" s="6"/>
       <c r="Q62" s="6"/>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A63" s="6"/>
       <c r="B63" s="6"/>
       <c r="C63" s="6"/>
@@ -2601,22 +2614,20 @@
       <c r="F63" s="6"/>
       <c r="G63" s="6"/>
       <c r="H63" s="6"/>
-      <c r="I63" s="6"/>
       <c r="J63" s="6"/>
       <c r="K63" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="M63" s="5" t="s">
-        <v>163</v>
+        <v>41</v>
+      </c>
+      <c r="L63" s="6"/>
+      <c r="M63" s="8" t="s">
+        <v>23</v>
       </c>
       <c r="N63" s="9"/>
-      <c r="O63" s="6" t="s">
-        <v>63</v>
-      </c>
+      <c r="O63" s="6"/>
       <c r="P63" s="6"/>
       <c r="Q63" s="6"/>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A64" s="6"/>
       <c r="B64" s="6"/>
       <c r="C64" s="6"/>
@@ -2628,18 +2639,19 @@
       <c r="I64" s="6"/>
       <c r="J64" s="6"/>
       <c r="K64" s="8" t="s">
-        <v>168</v>
-      </c>
-      <c r="L64" s="6"/>
-      <c r="M64" s="8" t="s">
-        <v>167</v>
-      </c>
-      <c r="N64" s="6"/>
-      <c r="O64" s="8"/>
+        <v>33</v>
+      </c>
+      <c r="M64" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="N64" s="9"/>
+      <c r="O64" s="6" t="s">
+        <v>63</v>
+      </c>
       <c r="P64" s="6"/>
       <c r="Q64" s="6"/>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A65" s="6"/>
       <c r="B65" s="6"/>
       <c r="C65" s="6"/>
@@ -2650,14 +2662,21 @@
       <c r="H65" s="6"/>
       <c r="I65" s="6"/>
       <c r="J65" s="6"/>
+      <c r="K65" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="L65" s="6"/>
+      <c r="M65" s="8" t="s">
+        <v>167</v>
+      </c>
       <c r="N65" s="6"/>
-      <c r="O65" s="6"/>
+      <c r="O65" s="8"/>
       <c r="P65" s="6"/>
       <c r="Q65" s="6"/>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A66" s="6"/>
-      <c r="B66" s="5"/>
+      <c r="B66" s="6"/>
       <c r="C66" s="6"/>
       <c r="D66" s="6"/>
       <c r="E66" s="6"/>
@@ -2666,17 +2685,14 @@
       <c r="H66" s="6"/>
       <c r="I66" s="6"/>
       <c r="J66" s="6"/>
-      <c r="K66" s="2"/>
-      <c r="M66" s="2"/>
-      <c r="O66" s="2"/>
+      <c r="N66" s="6"/>
+      <c r="O66" s="6"/>
       <c r="P66" s="6"/>
       <c r="Q66" s="6"/>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A67" s="6"/>
-      <c r="B67" s="6" t="s">
-        <v>79</v>
-      </c>
+      <c r="B67" s="5"/>
       <c r="C67" s="6"/>
       <c r="D67" s="6"/>
       <c r="E67" s="6"/>
@@ -2685,21 +2701,17 @@
       <c r="H67" s="6"/>
       <c r="I67" s="6"/>
       <c r="J67" s="6"/>
-      <c r="K67" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="M67" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="O67" s="11" t="s">
-        <v>81</v>
-      </c>
+      <c r="K67" s="2"/>
+      <c r="M67" s="2"/>
+      <c r="O67" s="2"/>
       <c r="P67" s="6"/>
       <c r="Q67" s="6"/>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A68" s="6"/>
-      <c r="B68" s="6"/>
+      <c r="B68" s="6" t="s">
+        <v>79</v>
+      </c>
       <c r="C68" s="6"/>
       <c r="D68" s="6"/>
       <c r="E68" s="6"/>
@@ -2709,184 +2721,184 @@
       <c r="I68" s="6"/>
       <c r="J68" s="6"/>
       <c r="K68" s="11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M68" s="11" t="s">
         <v>23</v>
       </c>
       <c r="O68" s="11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P68" s="6"/>
       <c r="Q68" s="6"/>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A69" s="6"/>
+      <c r="B69" s="6"/>
+      <c r="C69" s="6"/>
+      <c r="D69" s="6"/>
+      <c r="E69" s="6"/>
+      <c r="F69" s="6"/>
+      <c r="G69" s="6"/>
       <c r="H69" s="6"/>
       <c r="I69" s="6"/>
       <c r="J69" s="6"/>
-      <c r="K69" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="M69" s="1" t="s">
+      <c r="K69" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="M69" s="11" t="s">
         <v>23</v>
       </c>
       <c r="O69" s="11" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="P69" s="6"/>
       <c r="Q69" s="6"/>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A70" s="6"/>
       <c r="H70" s="6"/>
       <c r="I70" s="6"/>
       <c r="J70" s="6"/>
       <c r="K70" s="1" t="s">
-        <v>84</v>
+        <v>41</v>
       </c>
       <c r="M70" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="N70" s="6"/>
-      <c r="O70" s="6" t="s">
-        <v>85</v>
+      <c r="O70" s="11" t="s">
+        <v>86</v>
       </c>
       <c r="P70" s="6"/>
       <c r="Q70" s="6"/>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A71" s="6"/>
-      <c r="K71" s="11" t="s">
-        <v>144</v>
+      <c r="H71" s="6"/>
+      <c r="I71" s="6"/>
+      <c r="J71" s="6"/>
+      <c r="K71" s="1" t="s">
+        <v>84</v>
       </c>
       <c r="M71" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="O71" s="11" t="s">
-        <v>61</v>
+      <c r="N71" s="6"/>
+      <c r="O71" s="6" t="s">
+        <v>85</v>
       </c>
       <c r="P71" s="6"/>
       <c r="Q71" s="6"/>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A72" s="6"/>
-      <c r="B72" s="6"/>
-      <c r="C72" s="6"/>
-      <c r="D72" s="6"/>
-      <c r="E72" s="6"/>
-      <c r="F72" s="6"/>
-      <c r="G72" s="6"/>
       <c r="K72" s="11" t="s">
-        <v>83</v>
+        <v>144</v>
       </c>
       <c r="M72" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="O72" s="11"/>
+        <v>23</v>
+      </c>
+      <c r="O72" s="11" t="s">
+        <v>61</v>
+      </c>
       <c r="P72" s="6"/>
       <c r="Q72" s="6"/>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A73" s="6"/>
-      <c r="K73" s="11"/>
-      <c r="M73" s="11"/>
+      <c r="B73" s="6"/>
+      <c r="C73" s="6"/>
+      <c r="D73" s="6"/>
+      <c r="E73" s="6"/>
+      <c r="F73" s="6"/>
+      <c r="G73" s="6"/>
+      <c r="K73" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="M73" s="1" t="s">
+        <v>87</v>
+      </c>
       <c r="O73" s="11"/>
       <c r="P73" s="6"/>
-      <c r="Q73" s="7"/>
-    </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="6"/>
+    </row>
+    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A74" s="6"/>
+      <c r="K74" s="11"/>
+      <c r="M74" s="11"/>
+      <c r="O74" s="11"/>
       <c r="P74" s="6"/>
-      <c r="Q74" s="6"/>
-    </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="7"/>
+    </row>
+    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A75" s="6"/>
-      <c r="B75" s="6"/>
-      <c r="C75" s="6"/>
-      <c r="D75" s="6"/>
-      <c r="E75" s="6"/>
-      <c r="F75" s="6"/>
-      <c r="G75" s="6"/>
-      <c r="K75" s="1"/>
-      <c r="M75" s="1"/>
-      <c r="O75" s="1"/>
-      <c r="P75" s="7"/>
+      <c r="P75" s="6"/>
       <c r="Q75" s="6"/>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A76" s="6"/>
-      <c r="B76" s="1" t="s">
+      <c r="B76" s="6"/>
+      <c r="C76" s="6"/>
+      <c r="D76" s="6"/>
+      <c r="E76" s="6"/>
+      <c r="F76" s="6"/>
+      <c r="G76" s="6"/>
+      <c r="K76" s="1"/>
+      <c r="M76" s="1"/>
+      <c r="O76" s="1"/>
+      <c r="P76" s="7"/>
+      <c r="Q76" s="6"/>
+    </row>
+    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A77" s="6"/>
+      <c r="B77" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="K76" s="11" t="s">
+      <c r="K77" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="M76" s="1" t="s">
+      <c r="M77" s="1" t="s">
         <v>112</v>
-      </c>
-      <c r="P76" s="6"/>
-      <c r="Q76" s="6"/>
-    </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A77" s="5"/>
-      <c r="B77" s="6"/>
-      <c r="C77" s="6"/>
-      <c r="K77" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="M77" s="1" t="s">
-        <v>66</v>
       </c>
       <c r="P77" s="6"/>
       <c r="Q77" s="6"/>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A78" s="6"/>
+    <row r="78" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A78" s="5"/>
+      <c r="B78" s="6"/>
       <c r="C78" s="6"/>
-      <c r="D78" s="6"/>
-      <c r="E78" s="6"/>
-      <c r="F78" s="6"/>
-      <c r="G78" s="6"/>
-      <c r="H78" s="6"/>
-      <c r="I78" s="6"/>
-      <c r="J78" s="6"/>
-      <c r="K78" s="6"/>
-      <c r="L78" s="6"/>
-      <c r="M78" s="6"/>
-      <c r="N78" s="6"/>
-      <c r="O78" s="6"/>
+      <c r="K78" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="M78" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="P78" s="6"/>
       <c r="Q78" s="6"/>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A79" s="6"/>
-      <c r="B79" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="C79" s="5"/>
+      <c r="C79" s="6"/>
       <c r="D79" s="6"/>
       <c r="E79" s="6"/>
       <c r="F79" s="6"/>
       <c r="G79" s="6"/>
       <c r="H79" s="6"/>
       <c r="I79" s="6"/>
-      <c r="J79" s="8"/>
-      <c r="K79" s="6" t="s">
-        <v>25</v>
-      </c>
+      <c r="J79" s="6"/>
+      <c r="K79" s="6"/>
       <c r="L79" s="6"/>
-      <c r="M79" s="6" t="s">
-        <v>23</v>
-      </c>
+      <c r="M79" s="6"/>
       <c r="N79" s="6"/>
       <c r="O79" s="6"/>
       <c r="P79" s="6"/>
       <c r="Q79" s="6"/>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A80" s="6"/>
-      <c r="B80" s="8"/>
+      <c r="B80" s="8" t="s">
+        <v>89</v>
+      </c>
       <c r="C80" s="5"/>
       <c r="D80" s="6"/>
       <c r="E80" s="6"/>
@@ -2895,42 +2907,42 @@
       <c r="H80" s="6"/>
       <c r="I80" s="6"/>
       <c r="J80" s="8"/>
-      <c r="K80" s="5" t="s">
-        <v>26</v>
+      <c r="K80" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="L80" s="6"/>
-      <c r="M80" s="5" t="s">
+      <c r="M80" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N80" s="6"/>
-      <c r="O80" s="5"/>
+      <c r="O80" s="6"/>
       <c r="P80" s="6"/>
       <c r="Q80" s="6"/>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A81" s="6"/>
-      <c r="B81" s="6"/>
-      <c r="C81" s="6"/>
+      <c r="B81" s="8"/>
+      <c r="C81" s="5"/>
       <c r="D81" s="6"/>
       <c r="E81" s="6"/>
       <c r="F81" s="6"/>
       <c r="G81" s="6"/>
       <c r="H81" s="6"/>
       <c r="I81" s="6"/>
-      <c r="J81" s="6"/>
+      <c r="J81" s="8"/>
       <c r="K81" s="5" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="L81" s="6"/>
       <c r="M81" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="N81" s="7"/>
+      <c r="N81" s="6"/>
       <c r="O81" s="5"/>
-      <c r="P81" s="7"/>
+      <c r="P81" s="6"/>
       <c r="Q81" s="6"/>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A82" s="6"/>
       <c r="B82" s="6"/>
       <c r="C82" s="6"/>
@@ -2942,37 +2954,40 @@
       <c r="I82" s="6"/>
       <c r="J82" s="6"/>
       <c r="K82" s="5" t="s">
-        <v>93</v>
+        <v>41</v>
       </c>
       <c r="L82" s="6"/>
       <c r="M82" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="N82" s="6"/>
-      <c r="P82" s="6"/>
+        <v>23</v>
+      </c>
+      <c r="N82" s="7"/>
+      <c r="O82" s="5"/>
+      <c r="P82" s="7"/>
       <c r="Q82" s="6"/>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B83" s="8"/>
-      <c r="C83" s="5"/>
+    <row r="83" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A83" s="6"/>
+      <c r="B83" s="6"/>
+      <c r="C83" s="6"/>
       <c r="D83" s="6"/>
       <c r="E83" s="6"/>
       <c r="F83" s="6"/>
       <c r="G83" s="6"/>
       <c r="H83" s="6"/>
       <c r="I83" s="6"/>
-      <c r="J83" s="8"/>
-      <c r="K83" s="6" t="s">
-        <v>95</v>
+      <c r="J83" s="6"/>
+      <c r="K83" s="5" t="s">
+        <v>93</v>
       </c>
       <c r="L83" s="6"/>
-      <c r="M83" s="6" t="s">
-        <v>96</v>
-      </c>
+      <c r="M83" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="N83" s="6"/>
       <c r="P83" s="6"/>
       <c r="Q83" s="6"/>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B84" s="8"/>
       <c r="C84" s="5"/>
       <c r="D84" s="6"/>
@@ -2982,102 +2997,107 @@
       <c r="H84" s="6"/>
       <c r="I84" s="6"/>
       <c r="J84" s="8"/>
-      <c r="K84" s="5" t="s">
-        <v>102</v>
+      <c r="K84" s="6" t="s">
+        <v>95</v>
       </c>
       <c r="L84" s="6"/>
-      <c r="M84" s="5" t="s">
-        <v>103</v>
+      <c r="M84" s="6" t="s">
+        <v>96</v>
       </c>
       <c r="P84" s="6"/>
       <c r="Q84" s="6"/>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B85" s="1"/>
-      <c r="G85" s="1"/>
+    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="B85" s="8"/>
+      <c r="C85" s="5"/>
+      <c r="D85" s="6"/>
+      <c r="E85" s="6"/>
+      <c r="F85" s="6"/>
+      <c r="G85" s="6"/>
       <c r="H85" s="6"/>
       <c r="I85" s="6"/>
       <c r="J85" s="8"/>
-      <c r="K85" s="5"/>
+      <c r="K85" s="5" t="s">
+        <v>102</v>
+      </c>
       <c r="L85" s="6"/>
-      <c r="M85" s="5"/>
-      <c r="P85" s="7"/>
+      <c r="M85" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="P85" s="6"/>
       <c r="Q85" s="6"/>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="B86" s="1"/>
+      <c r="G86" s="1"/>
       <c r="H86" s="6"/>
       <c r="I86" s="6"/>
       <c r="J86" s="8"/>
       <c r="K86" s="5"/>
       <c r="L86" s="6"/>
       <c r="M86" s="5"/>
-      <c r="O86" s="5"/>
       <c r="P86" s="7"/>
       <c r="Q86" s="6"/>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B87" s="1" t="s">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="H87" s="6"/>
+      <c r="I87" s="6"/>
+      <c r="J87" s="8"/>
+      <c r="K87" s="5"/>
+      <c r="L87" s="6"/>
+      <c r="M87" s="5"/>
+      <c r="O87" s="5"/>
+      <c r="P87" s="7"/>
+      <c r="Q87" s="6"/>
+    </row>
+    <row r="88" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="B88" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="K87" s="1"/>
-      <c r="M87" s="1"/>
-      <c r="P87" s="7"/>
-      <c r="Q87" s="7"/>
-    </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B88" s="1" t="s">
+      <c r="K88" s="1"/>
+      <c r="M88" s="1"/>
+      <c r="P88" s="7"/>
+      <c r="Q88" s="7"/>
+    </row>
+    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="B89" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C88" s="1" t="s">
+      <c r="C89" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="K88" s="1" t="s">
+      <c r="K89" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="M88" s="1" t="s">
+      <c r="M89" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="P88" s="7"/>
-      <c r="Q88" s="6"/>
-    </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="K89" s="1" t="s">
+      <c r="P89" s="7"/>
+      <c r="Q89" s="6"/>
+    </row>
+    <row r="90" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="K90" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="M89" s="1" t="s">
+      <c r="M90" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="O89" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="P89" s="6"/>
-      <c r="Q89" s="6"/>
-    </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A90" s="6"/>
-      <c r="B90" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="C90" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="K90" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="M90" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="N90" s="6"/>
       <c r="O90" s="1" t="s">
         <v>98</v>
       </c>
       <c r="P90" s="6"/>
       <c r="Q90" s="6"/>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A91" s="6"/>
+      <c r="B91" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>97</v>
+      </c>
       <c r="K91" s="1" t="s">
-        <v>101</v>
+        <v>205</v>
       </c>
       <c r="M91" s="1" t="s">
         <v>62</v>
@@ -3089,66 +3109,62 @@
       <c r="P91" s="6"/>
       <c r="Q91" s="6"/>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A92" s="6"/>
+      <c r="K92" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="M92" s="1" t="s">
+        <v>62</v>
+      </c>
       <c r="N92" s="6"/>
-      <c r="P92" s="7"/>
+      <c r="O92" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="P92" s="6"/>
       <c r="Q92" s="6"/>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A93" s="6"/>
       <c r="N93" s="6"/>
-      <c r="O93" s="5"/>
-      <c r="P93" s="6"/>
+      <c r="P93" s="7"/>
       <c r="Q93" s="6"/>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A94" s="6"/>
-      <c r="H94" s="6"/>
-      <c r="I94" s="6"/>
-      <c r="J94" s="6"/>
-      <c r="K94" s="5"/>
-      <c r="L94" s="6"/>
-      <c r="M94" s="5"/>
       <c r="N94" s="6"/>
       <c r="O94" s="5"/>
       <c r="P94" s="6"/>
       <c r="Q94" s="6"/>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A95" s="6"/>
       <c r="H95" s="6"/>
       <c r="I95" s="6"/>
       <c r="J95" s="6"/>
-      <c r="K95" s="6"/>
+      <c r="K95" s="5"/>
       <c r="L95" s="6"/>
-      <c r="M95" s="6"/>
+      <c r="M95" s="5"/>
       <c r="N95" s="6"/>
-      <c r="O95" s="6"/>
+      <c r="O95" s="5"/>
       <c r="P95" s="6"/>
       <c r="Q95" s="6"/>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A96" s="6"/>
-      <c r="D96" s="6"/>
-      <c r="E96" s="6"/>
-      <c r="F96" s="6"/>
-      <c r="G96" s="6"/>
       <c r="H96" s="6"/>
       <c r="I96" s="6"/>
-      <c r="J96" s="8"/>
-      <c r="K96" s="5"/>
+      <c r="J96" s="6"/>
+      <c r="K96" s="6"/>
       <c r="L96" s="6"/>
-      <c r="M96" s="5"/>
+      <c r="M96" s="6"/>
       <c r="N96" s="6"/>
       <c r="O96" s="6"/>
       <c r="P96" s="6"/>
       <c r="Q96" s="6"/>
     </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A97" s="6"/>
-      <c r="B97" s="8"/>
-      <c r="C97" s="5"/>
       <c r="D97" s="6"/>
       <c r="E97" s="6"/>
       <c r="F97" s="6"/>
@@ -3164,48 +3180,47 @@
       <c r="P97" s="6"/>
       <c r="Q97" s="6"/>
     </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A98" s="6"/>
+      <c r="B98" s="8"/>
+      <c r="C98" s="5"/>
+      <c r="D98" s="6"/>
+      <c r="E98" s="6"/>
+      <c r="F98" s="6"/>
+      <c r="G98" s="6"/>
+      <c r="H98" s="6"/>
+      <c r="I98" s="6"/>
+      <c r="J98" s="8"/>
+      <c r="K98" s="5"/>
+      <c r="L98" s="6"/>
+      <c r="M98" s="5"/>
+      <c r="N98" s="6"/>
       <c r="O98" s="6"/>
       <c r="P98" s="6"/>
       <c r="Q98" s="6"/>
     </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A99" s="6"/>
       <c r="O99" s="6"/>
       <c r="P99" s="6"/>
       <c r="Q99" s="6"/>
     </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A100" s="6"/>
       <c r="O100" s="6"/>
       <c r="P100" s="6"/>
       <c r="Q100" s="6"/>
     </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A101" s="6"/>
-      <c r="B101" s="8"/>
-      <c r="C101" s="5"/>
-      <c r="D101" s="6"/>
-      <c r="E101" s="6"/>
-      <c r="F101" s="6"/>
-      <c r="G101" s="6"/>
-      <c r="H101" s="6"/>
-      <c r="I101" s="6"/>
-      <c r="J101" s="6"/>
-      <c r="K101" s="5"/>
-      <c r="L101" s="6"/>
-      <c r="M101" s="5"/>
-      <c r="N101" s="6"/>
       <c r="O101" s="6"/>
       <c r="P101" s="6"/>
       <c r="Q101" s="6"/>
     </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A102" s="6"/>
-      <c r="B102" s="1" t="s">
-        <v>119</v>
-      </c>
+      <c r="B102" s="8"/>
+      <c r="C102" s="5"/>
       <c r="D102" s="6"/>
       <c r="E102" s="6"/>
       <c r="F102" s="6"/>
@@ -3221,47 +3236,40 @@
       <c r="P102" s="6"/>
       <c r="Q102" s="6"/>
     </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A103" s="6"/>
-      <c r="B103" s="1"/>
-      <c r="C103" s="1"/>
+      <c r="B103" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D103" s="6"/>
+      <c r="E103" s="6"/>
+      <c r="F103" s="6"/>
+      <c r="G103" s="6"/>
+      <c r="H103" s="6"/>
+      <c r="I103" s="6"/>
+      <c r="J103" s="6"/>
       <c r="K103" s="5"/>
+      <c r="L103" s="6"/>
+      <c r="M103" s="5"/>
       <c r="N103" s="6"/>
       <c r="O103" s="6"/>
       <c r="P103" s="6"/>
       <c r="Q103" s="6"/>
     </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A104" s="6"/>
-      <c r="B104" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="C104" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="D104" s="6"/>
-      <c r="E104" s="6"/>
-      <c r="F104" s="6"/>
-      <c r="G104" s="6"/>
-      <c r="H104" s="6"/>
-      <c r="I104" s="6"/>
-      <c r="J104" s="6"/>
-      <c r="K104" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="L104" s="6"/>
-      <c r="M104" s="5" t="s">
-        <v>23</v>
-      </c>
+      <c r="B104" s="1"/>
+      <c r="C104" s="1"/>
+      <c r="K104" s="5"/>
       <c r="N104" s="6"/>
       <c r="O104" s="6"/>
       <c r="P104" s="6"/>
       <c r="Q104" s="6"/>
     </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A105" s="6"/>
       <c r="B105" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>119</v>
@@ -3272,23 +3280,23 @@
       <c r="G105" s="6"/>
       <c r="H105" s="6"/>
       <c r="I105" s="6"/>
-      <c r="J105" s="8"/>
+      <c r="J105" s="6"/>
       <c r="K105" s="5" t="s">
-        <v>122</v>
+        <v>174</v>
       </c>
       <c r="L105" s="6"/>
       <c r="M105" s="5" t="s">
-        <v>112</v>
+        <v>23</v>
       </c>
       <c r="N105" s="6"/>
       <c r="O105" s="6"/>
       <c r="P105" s="6"/>
       <c r="Q105" s="6"/>
     </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A106" s="6"/>
       <c r="B106" s="1" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>119</v>
@@ -3299,26 +3307,34 @@
       <c r="G106" s="6"/>
       <c r="H106" s="6"/>
       <c r="I106" s="6"/>
-      <c r="J106" s="5"/>
-      <c r="K106" s="5"/>
+      <c r="J106" s="8"/>
+      <c r="K106" s="5" t="s">
+        <v>122</v>
+      </c>
       <c r="L106" s="6"/>
-      <c r="M106" s="5"/>
+      <c r="M106" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="N106" s="6"/>
       <c r="O106" s="6"/>
       <c r="P106" s="6"/>
       <c r="Q106" s="6"/>
     </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A107" s="6"/>
-      <c r="B107" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="C107" s="6" t="s">
+      <c r="B107" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C107" s="1" t="s">
         <v>119</v>
       </c>
+      <c r="D107" s="6"/>
+      <c r="E107" s="6"/>
+      <c r="F107" s="6"/>
+      <c r="G107" s="6"/>
       <c r="H107" s="6"/>
       <c r="I107" s="6"/>
-      <c r="J107" s="6"/>
+      <c r="J107" s="5"/>
       <c r="K107" s="5"/>
       <c r="L107" s="6"/>
       <c r="M107" s="5"/>
@@ -3327,35 +3343,29 @@
       <c r="P107" s="6"/>
       <c r="Q107" s="6"/>
     </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A108" s="6"/>
       <c r="B108" s="6" t="s">
-        <v>160</v>
+        <v>131</v>
       </c>
       <c r="C108" s="6" t="s">
         <v>119</v>
-      </c>
-      <c r="D108" s="6"/>
-      <c r="E108" s="6"/>
-      <c r="F108" s="6"/>
-      <c r="G108" s="6" t="s">
-        <v>130</v>
       </c>
       <c r="H108" s="6"/>
       <c r="I108" s="6"/>
       <c r="J108" s="6"/>
-      <c r="K108" s="6"/>
+      <c r="K108" s="5"/>
       <c r="L108" s="6"/>
-      <c r="M108" s="6"/>
+      <c r="M108" s="5"/>
       <c r="N108" s="6"/>
       <c r="O108" s="6"/>
       <c r="P108" s="6"/>
       <c r="Q108" s="6"/>
     </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A109" s="6"/>
       <c r="B109" s="6" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C109" s="6" t="s">
         <v>119</v>
@@ -3363,22 +3373,24 @@
       <c r="D109" s="6"/>
       <c r="E109" s="6"/>
       <c r="F109" s="6"/>
-      <c r="G109" s="6"/>
+      <c r="G109" s="6" t="s">
+        <v>130</v>
+      </c>
       <c r="H109" s="6"/>
       <c r="I109" s="6"/>
-      <c r="J109" s="5"/>
-      <c r="K109" s="5"/>
+      <c r="J109" s="6"/>
+      <c r="K109" s="6"/>
       <c r="L109" s="6"/>
-      <c r="M109" s="5"/>
+      <c r="M109" s="6"/>
       <c r="N109" s="6"/>
-      <c r="O109" s="1"/>
+      <c r="O109" s="6"/>
       <c r="P109" s="6"/>
       <c r="Q109" s="6"/>
     </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A110" s="6"/>
       <c r="B110" s="6" t="s">
-        <v>231</v>
+        <v>162</v>
       </c>
       <c r="C110" s="6" t="s">
         <v>119</v>
@@ -3389,35 +3401,39 @@
       <c r="G110" s="6"/>
       <c r="H110" s="6"/>
       <c r="I110" s="6"/>
-      <c r="J110" s="6"/>
-      <c r="K110" s="6"/>
+      <c r="J110" s="5"/>
+      <c r="K110" s="5"/>
       <c r="L110" s="6"/>
-      <c r="M110" s="6"/>
+      <c r="M110" s="5"/>
       <c r="N110" s="6"/>
-      <c r="O110" s="6"/>
+      <c r="O110" s="1"/>
       <c r="P110" s="6"/>
       <c r="Q110" s="6"/>
     </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A111" s="6"/>
-      <c r="B111" s="5"/>
-      <c r="C111" s="5"/>
+      <c r="B111" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="C111" s="6" t="s">
+        <v>119</v>
+      </c>
       <c r="D111" s="6"/>
       <c r="E111" s="6"/>
       <c r="F111" s="6"/>
       <c r="G111" s="6"/>
       <c r="H111" s="6"/>
       <c r="I111" s="6"/>
-      <c r="J111" s="5"/>
-      <c r="K111" s="5"/>
+      <c r="J111" s="6"/>
+      <c r="K111" s="6"/>
       <c r="L111" s="6"/>
-      <c r="M111" s="5"/>
+      <c r="M111" s="6"/>
       <c r="N111" s="6"/>
       <c r="O111" s="6"/>
       <c r="P111" s="6"/>
       <c r="Q111" s="6"/>
     </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A112" s="6"/>
       <c r="B112" s="5"/>
       <c r="C112" s="5"/>
@@ -3436,11 +3452,9 @@
       <c r="P112" s="6"/>
       <c r="Q112" s="6"/>
     </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A113" s="6"/>
-      <c r="B113" s="5" t="s">
-        <v>239</v>
-      </c>
+      <c r="B113" s="5"/>
       <c r="C113" s="5"/>
       <c r="D113" s="6"/>
       <c r="E113" s="6"/>
@@ -3449,21 +3463,19 @@
       <c r="H113" s="6"/>
       <c r="I113" s="6"/>
       <c r="J113" s="5"/>
-      <c r="K113" s="5" t="s">
-        <v>25</v>
-      </c>
+      <c r="K113" s="5"/>
       <c r="L113" s="6"/>
-      <c r="M113" s="5" t="s">
-        <v>23</v>
-      </c>
+      <c r="M113" s="5"/>
       <c r="N113" s="6"/>
       <c r="O113" s="6"/>
       <c r="P113" s="6"/>
       <c r="Q113" s="6"/>
     </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A114" s="6"/>
-      <c r="B114" s="5"/>
+      <c r="B114" s="5" t="s">
+        <v>239</v>
+      </c>
       <c r="C114" s="5"/>
       <c r="D114" s="6"/>
       <c r="E114" s="6"/>
@@ -3473,7 +3485,7 @@
       <c r="I114" s="6"/>
       <c r="J114" s="5"/>
       <c r="K114" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L114" s="6"/>
       <c r="M114" s="5" t="s">
@@ -3484,7 +3496,7 @@
       <c r="P114" s="6"/>
       <c r="Q114" s="6"/>
     </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A115" s="6"/>
       <c r="B115" s="5"/>
       <c r="C115" s="5"/>
@@ -3496,7 +3508,7 @@
       <c r="I115" s="6"/>
       <c r="J115" s="5"/>
       <c r="K115" s="5" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="L115" s="6"/>
       <c r="M115" s="5" t="s">
@@ -3507,7 +3519,7 @@
       <c r="P115" s="6"/>
       <c r="Q115" s="6"/>
     </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A116" s="6"/>
       <c r="B116" s="5"/>
       <c r="C116" s="5"/>
@@ -3519,7 +3531,7 @@
       <c r="I116" s="6"/>
       <c r="J116" s="5"/>
       <c r="K116" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="L116" s="6"/>
       <c r="M116" s="5" t="s">
@@ -3530,19 +3542,19 @@
       <c r="P116" s="6"/>
       <c r="Q116" s="6"/>
     </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A117" s="6"/>
-      <c r="B117" s="6"/>
-      <c r="C117" s="6"/>
+      <c r="B117" s="5"/>
+      <c r="C117" s="5"/>
       <c r="D117" s="6"/>
       <c r="E117" s="6"/>
       <c r="F117" s="6"/>
       <c r="G117" s="6"/>
       <c r="H117" s="6"/>
       <c r="I117" s="6"/>
-      <c r="J117" s="6"/>
+      <c r="J117" s="5"/>
       <c r="K117" s="5" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="L117" s="6"/>
       <c r="M117" s="5" t="s">
@@ -3553,7 +3565,7 @@
       <c r="P117" s="6"/>
       <c r="Q117" s="6"/>
     </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A118" s="6"/>
       <c r="B118" s="6"/>
       <c r="C118" s="6"/>
@@ -3564,40 +3576,41 @@
       <c r="H118" s="6"/>
       <c r="I118" s="6"/>
       <c r="J118" s="6"/>
-      <c r="K118" s="1" t="s">
-        <v>143</v>
-      </c>
+      <c r="K118" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="L118" s="6"/>
       <c r="M118" s="5" t="s">
-        <v>241</v>
+        <v>23</v>
       </c>
       <c r="N118" s="6"/>
       <c r="O118" s="6"/>
       <c r="P118" s="6"/>
       <c r="Q118" s="6"/>
     </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A119" s="5"/>
-      <c r="B119" s="8"/>
-      <c r="C119" s="5"/>
+    <row r="119" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A119" s="6"/>
+      <c r="B119" s="6"/>
+      <c r="C119" s="6"/>
       <c r="D119" s="6"/>
       <c r="E119" s="6"/>
       <c r="F119" s="6"/>
       <c r="G119" s="6"/>
       <c r="H119" s="6"/>
       <c r="I119" s="6"/>
-      <c r="J119" s="8"/>
+      <c r="J119" s="6"/>
       <c r="K119" s="1" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="M119" s="5" t="s">
-        <v>103</v>
+        <v>241</v>
       </c>
       <c r="N119" s="6"/>
-      <c r="O119" s="5"/>
+      <c r="O119" s="6"/>
       <c r="P119" s="6"/>
       <c r="Q119" s="6"/>
     </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A120" s="5"/>
       <c r="B120" s="8"/>
       <c r="C120" s="5"/>
@@ -3608,18 +3621,20 @@
       <c r="H120" s="6"/>
       <c r="I120" s="6"/>
       <c r="J120" s="8"/>
-      <c r="K120" s="1"/>
-      <c r="M120" s="5"/>
+      <c r="K120" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="M120" s="5" t="s">
+        <v>103</v>
+      </c>
       <c r="N120" s="6"/>
       <c r="O120" s="5"/>
       <c r="P120" s="6"/>
       <c r="Q120" s="6"/>
     </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A121" s="5"/>
-      <c r="B121" s="8" t="s">
-        <v>240</v>
-      </c>
+      <c r="B121" s="8"/>
       <c r="C121" s="5"/>
       <c r="D121" s="6"/>
       <c r="E121" s="6"/>
@@ -3628,20 +3643,18 @@
       <c r="H121" s="6"/>
       <c r="I121" s="6"/>
       <c r="J121" s="8"/>
-      <c r="K121" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="M121" s="1" t="s">
-        <v>242</v>
-      </c>
+      <c r="K121" s="1"/>
+      <c r="M121" s="5"/>
       <c r="N121" s="6"/>
       <c r="O121" s="5"/>
       <c r="P121" s="6"/>
       <c r="Q121" s="6"/>
     </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A122" s="5"/>
-      <c r="B122" s="8"/>
+      <c r="B122" s="8" t="s">
+        <v>240</v>
+      </c>
       <c r="C122" s="5"/>
       <c r="D122" s="6"/>
       <c r="E122" s="6"/>
@@ -3651,17 +3664,17 @@
       <c r="I122" s="6"/>
       <c r="J122" s="8"/>
       <c r="K122" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="M122" s="5" t="s">
-        <v>66</v>
+        <v>33</v>
+      </c>
+      <c r="M122" s="1" t="s">
+        <v>242</v>
       </c>
       <c r="N122" s="6"/>
       <c r="O122" s="5"/>
       <c r="P122" s="6"/>
       <c r="Q122" s="6"/>
     </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A123" s="5"/>
       <c r="B123" s="8"/>
       <c r="C123" s="5"/>
@@ -3672,106 +3685,110 @@
       <c r="H123" s="6"/>
       <c r="I123" s="6"/>
       <c r="J123" s="8"/>
-      <c r="K123" s="1"/>
-      <c r="M123" s="5"/>
+      <c r="K123" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="M123" s="5" t="s">
+        <v>66</v>
+      </c>
       <c r="N123" s="6"/>
       <c r="O123" s="5"/>
       <c r="P123" s="6"/>
       <c r="Q123" s="6"/>
     </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A124" s="5"/>
+      <c r="B124" s="8"/>
+      <c r="C124" s="5"/>
+      <c r="D124" s="6"/>
+      <c r="E124" s="6"/>
+      <c r="F124" s="6"/>
+      <c r="G124" s="6"/>
+      <c r="H124" s="6"/>
+      <c r="I124" s="6"/>
+      <c r="J124" s="8"/>
       <c r="K124" s="1"/>
       <c r="M124" s="5"/>
-    </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="C125" s="6"/>
-      <c r="D125" s="6"/>
-      <c r="E125" s="6"/>
-      <c r="F125" s="6"/>
-      <c r="G125" s="6"/>
-      <c r="H125" s="6"/>
-      <c r="I125" s="6"/>
-      <c r="J125" s="6"/>
-      <c r="K125" s="5"/>
-      <c r="L125" s="6"/>
+      <c r="N124" s="6"/>
+      <c r="O124" s="5"/>
+      <c r="P124" s="6"/>
+      <c r="Q124" s="6"/>
+    </row>
+    <row r="125" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="K125" s="1"/>
       <c r="M125" s="5"/>
-      <c r="N125" s="6"/>
-      <c r="O125" s="6"/>
-    </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="126" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="C126" s="6"/>
+      <c r="D126" s="6"/>
+      <c r="E126" s="6"/>
+      <c r="F126" s="6"/>
+      <c r="G126" s="6"/>
+      <c r="H126" s="6"/>
+      <c r="I126" s="6"/>
+      <c r="J126" s="6"/>
+      <c r="K126" s="5"/>
+      <c r="L126" s="6"/>
+      <c r="M126" s="5"/>
       <c r="N126" s="6"/>
       <c r="O126" s="6"/>
     </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B127" s="6" t="s">
+    <row r="127" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="N127" s="6"/>
+      <c r="O127" s="6"/>
+    </row>
+    <row r="128" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="B128" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="N127" s="6"/>
-    </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.2">
       <c r="N128" s="6"/>
-      <c r="O128" s="6"/>
-    </row>
-    <row r="129" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B129" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="C129" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="D129" s="6"/>
-      <c r="E129" s="6"/>
-      <c r="F129" s="6"/>
-      <c r="G129" s="6"/>
-      <c r="H129" s="6"/>
-      <c r="I129" s="6"/>
-      <c r="J129" s="6"/>
-      <c r="K129" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="M129" s="1" t="s">
-        <v>128</v>
-      </c>
+    </row>
+    <row r="129" spans="2:15" x14ac:dyDescent="0.3">
       <c r="N129" s="6"/>
       <c r="O129" s="6"/>
     </row>
-    <row r="130" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="130" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B130" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="C130" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D130" s="6"/>
+      <c r="E130" s="6"/>
+      <c r="F130" s="6"/>
+      <c r="G130" s="6"/>
+      <c r="H130" s="6"/>
+      <c r="I130" s="6"/>
+      <c r="J130" s="6"/>
       <c r="K130" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="M130" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="N130" s="6"/>
+      <c r="O130" s="6"/>
+    </row>
+    <row r="131" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="K131" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="M130" s="1" t="s">
+      <c r="M131" s="1" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="131" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K131" s="1" t="s">
+    <row r="132" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="K132" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="M131" s="1" t="s">
+      <c r="M132" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="133" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B133" s="6" t="s">
+    <row r="134" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B134" s="6" t="s">
         <v>65</v>
-      </c>
-      <c r="C133" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="D133" s="6"/>
-      <c r="E133" s="6"/>
-      <c r="F133" s="6"/>
-      <c r="G133" s="6"/>
-      <c r="H133" s="6"/>
-      <c r="I133" s="6"/>
-      <c r="J133" s="6"/>
-      <c r="K133" s="5"/>
-      <c r="L133" s="6"/>
-      <c r="M133" s="5"/>
-    </row>
-    <row r="134" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B134" s="6" t="s">
-        <v>110</v>
       </c>
       <c r="C134" s="6" t="s">
         <v>64</v>
@@ -3783,373 +3800,391 @@
       <c r="H134" s="6"/>
       <c r="I134" s="6"/>
       <c r="J134" s="6"/>
-      <c r="K134" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="M134" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="135" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="C135" s="6"/>
+      <c r="K134" s="5"/>
+      <c r="L134" s="6"/>
+      <c r="M134" s="5"/>
+    </row>
+    <row r="135" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B135" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="C135" s="6" t="s">
+        <v>64</v>
+      </c>
       <c r="D135" s="6"/>
       <c r="E135" s="6"/>
       <c r="F135" s="6"/>
-      <c r="G135" s="5"/>
+      <c r="G135" s="6"/>
       <c r="H135" s="6"/>
       <c r="I135" s="6"/>
-      <c r="J135" s="5"/>
-      <c r="K135" s="5" t="s">
+      <c r="J135" s="6"/>
+      <c r="K135" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="M135" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="136" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="C136" s="6"/>
+      <c r="D136" s="6"/>
+      <c r="E136" s="6"/>
+      <c r="F136" s="6"/>
+      <c r="G136" s="5"/>
+      <c r="H136" s="6"/>
+      <c r="I136" s="6"/>
+      <c r="J136" s="5"/>
+      <c r="K136" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="L135" s="6"/>
-      <c r="M135" s="5" t="s">
+      <c r="L136" s="6"/>
+      <c r="M136" s="5" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="138" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B138" s="1" t="s">
+    <row r="139" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B139" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="K138" s="1" t="s">
+      <c r="K139" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="M138" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="139" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K139" s="1" t="s">
+      <c r="M139" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="140" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="K140" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="M139" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="140" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K140" s="1"/>
-    </row>
-    <row r="142" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B142" s="1" t="s">
+      <c r="M140" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="141" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="K141" s="1"/>
+    </row>
+    <row r="143" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B143" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="K142" s="1" t="s">
+      <c r="K143" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="M142" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="O142" s="6"/>
-    </row>
-    <row r="143" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K143" s="1" t="s">
+      <c r="M143" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O143" s="6"/>
+    </row>
+    <row r="144" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="K144" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="M143" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="144" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K144" s="1" t="s">
+      <c r="M144" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="145" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="K145" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="M144" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="145" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K145" s="1" t="s">
+      <c r="M145" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="146" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="K146" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M145" s="1" t="s">
+      <c r="M146" s="1" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="146" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K146" s="1" t="s">
+    <row r="147" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="K147" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="M146" s="1" t="s">
+      <c r="M147" s="1" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="147" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K147" s="1" t="s">
+    <row r="148" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="K148" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="M147" s="5" t="s">
+      <c r="M148" s="5" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="148" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B148" s="1" t="s">
+    <row r="149" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B149" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="K148" s="1" t="s">
+      <c r="K149" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="M148" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="149" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B149" s="1"/>
-      <c r="K149" s="1" t="s">
+      <c r="M149" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="150" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B150" s="1"/>
+      <c r="K150" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="M149" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="150" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K150" s="1" t="s">
+      <c r="M150" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="151" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="K151" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="M150" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="151" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K151" s="1" t="s">
+      <c r="M151" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="152" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="K152" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="M151" s="1" t="s">
+      <c r="M152" s="1" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="152" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K152" s="1"/>
-      <c r="M152" s="1"/>
-    </row>
-    <row r="153" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B153" s="1" t="s">
+    <row r="153" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="K153" s="1"/>
+      <c r="M153" s="1"/>
+    </row>
+    <row r="154" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B154" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="K153" s="1" t="s">
+      <c r="K154" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="M153" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="154" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K154" s="1" t="s">
+      <c r="M154" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="155" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="K155" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="M154" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="155" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K155" s="1" t="s">
+      <c r="M155" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="156" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="K156" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="M155" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="156" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K156" s="1" t="s">
+      <c r="M156" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="157" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="K157" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="M156" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="157" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K157" s="1" t="s">
+      <c r="M157" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="158" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="K158" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="M157" s="1" t="s">
+      <c r="M158" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="158" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K158" s="1"/>
-    </row>
-    <row r="160" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B160" s="1" t="s">
+    <row r="159" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="K159" s="1"/>
+    </row>
+    <row r="161" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B161" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="K160" s="1" t="s">
+      <c r="K161" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="M160" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="O160" s="1" t="s">
+      <c r="M161" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O161" s="1" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="161" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K161" s="1" t="s">
+    <row r="162" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="K162" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="M161" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="O161" s="1" t="s">
+      <c r="M162" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O162" s="1" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="162" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K162" s="1" t="s">
+    <row r="163" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="K163" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="M162" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="O162" s="1" t="s">
+      <c r="M163" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O163" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="163" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K163" s="1"/>
-    </row>
-    <row r="164" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B164" s="1" t="s">
+    <row r="164" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="K164" s="1"/>
+    </row>
+    <row r="165" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B165" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="K164" s="1" t="s">
+      <c r="K165" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="M164" s="1" t="s">
+      <c r="M165" s="1" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="165" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K165" s="1" t="s">
+    <row r="166" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="K166" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="M165" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="166" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K166" s="1" t="s">
+      <c r="M166" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="167" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="K167" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="M166" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="167" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K167" s="1" t="s">
+      <c r="M167" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="168" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="K168" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="M167" s="1" t="s">
+      <c r="M168" s="1" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="168" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K168" s="1" t="s">
+    <row r="169" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="K169" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="M168" s="1" t="s">
+      <c r="M169" s="1" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="170" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B170" s="1" t="s">
+    <row r="171" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B171" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="K170" s="1" t="s">
+      <c r="K171" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="M170" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="171" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K171" s="1" t="s">
+      <c r="M171" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="172" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="K172" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="M171" s="1" t="s">
+      <c r="M172" s="1" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="174" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B174" s="1" t="s">
+    <row r="175" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B175" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="K174" s="1" t="s">
+      <c r="K175" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="M174" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="O174" s="1" t="s">
+      <c r="M175" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O175" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="175" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K175" s="1" t="s">
+    <row r="176" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="K176" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="M175" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="O175" s="1" t="s">
+      <c r="M176" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O176" s="1" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="176" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K176" s="1" t="s">
+    <row r="177" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="K177" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="M176" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="O176" s="1" t="s">
+      <c r="M177" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O177" s="1" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="177" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="K177" s="1" t="s">
+    <row r="178" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="K178" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="M177" s="1" t="s">
+      <c r="M178" s="1" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="178" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B178" s="1" t="s">
+    <row r="179" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B179" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="K178" s="1" t="s">
+      <c r="K179" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M178" s="1" t="s">
+      <c r="M179" s="1" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="179" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="K179" s="1" t="s">
+    <row r="180" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="K180" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="M179" s="1" t="s">
+      <c r="M180" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="183" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B183" s="1" t="s">
+    <row r="184" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B184" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="G183" s="1" t="s">
+      <c r="G184" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="K183" s="1" t="s">
+      <c r="K184" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="M183" s="1" t="s">
+      <c r="M184" s="1" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="184" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="K184" s="1" t="s">
+    <row r="185" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="K185" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="M184" s="1" t="s">
+      <c r="M185" s="1" t="s">
         <v>96</v>
       </c>
     </row>
@@ -4165,13 +4200,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EECC075D-9730-41E5-B97E-C301603D1E48}">
-  <dimension ref="A1:Q63"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:Q65"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="27.375" customWidth="1"/>
+    <col min="2" max="2" width="27.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -4212,7 +4247,7 @@
       <c r="P1" s="12"/>
       <c r="Q1" s="12"/>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -4247,7 +4282,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>11</v>
       </c>
@@ -4284,7 +4319,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B6" s="6" t="s">
         <v>53</v>
       </c>
@@ -4301,7 +4336,7 @@
       <c r="M6" s="5"/>
       <c r="N6" s="6"/>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
         <v>141</v>
       </c>
@@ -4315,7 +4350,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="K9" s="1" t="s">
         <v>134</v>
       </c>
@@ -4326,7 +4361,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B11" s="1" t="s">
         <v>129</v>
       </c>
@@ -4340,7 +4375,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B12" s="6" t="s">
         <v>54</v>
       </c>
@@ -4368,7 +4403,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
@@ -4390,7 +4425,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
       <c r="D14" s="6"/>
@@ -4403,7 +4438,7 @@
       <c r="N14" s="6"/>
       <c r="O14" s="6"/>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B15" s="1" t="s">
         <v>74</v>
       </c>
@@ -4421,7 +4456,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="K16" s="1" t="s">
         <v>75</v>
       </c>
@@ -4432,7 +4467,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B17" s="1" t="s">
         <v>104</v>
       </c>
@@ -4449,7 +4484,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="18" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B18" s="1" t="s">
         <v>115</v>
       </c>
@@ -4463,7 +4498,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="19" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K19" s="5" t="s">
         <v>37</v>
       </c>
@@ -4471,7 +4506,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="20" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K20" s="1" t="s">
         <v>118</v>
       </c>
@@ -4479,7 +4514,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="21" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B21" s="1" t="s">
         <v>127</v>
       </c>
@@ -4493,7 +4528,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="23" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B23" s="1" t="s">
         <v>133</v>
       </c>
@@ -4507,7 +4542,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="24" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K24" s="1" t="s">
         <v>134</v>
       </c>
@@ -4515,7 +4550,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="26" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B26" s="1" t="s">
         <v>139</v>
       </c>
@@ -4529,7 +4564,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="27" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K27" s="1" t="s">
         <v>33</v>
       </c>
@@ -4537,7 +4572,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="28" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K28" s="1" t="s">
         <v>41</v>
       </c>
@@ -4545,7 +4580,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K29" s="1" t="s">
         <v>68</v>
       </c>
@@ -4553,7 +4588,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="31" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B31" s="1" t="s">
         <v>158</v>
       </c>
@@ -4567,7 +4602,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="32" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B32" s="1" t="s">
         <v>173</v>
       </c>
@@ -4581,7 +4616,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="K33" s="1" t="s">
         <v>186</v>
       </c>
@@ -4589,7 +4624,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B34" s="1" t="s">
         <v>222</v>
       </c>
@@ -4603,7 +4638,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="K35" s="1" t="s">
         <v>223</v>
       </c>
@@ -4611,7 +4646,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>180</v>
       </c>
@@ -4622,11 +4657,11 @@
         <v>128</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="K37" s="1"/>
       <c r="M37" s="1"/>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B38" s="1" t="s">
         <v>193</v>
       </c>
@@ -4640,7 +4675,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="K39" s="1" t="s">
         <v>186</v>
       </c>
@@ -4648,7 +4683,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B40" s="1" t="s">
         <v>175</v>
       </c>
@@ -4663,10 +4698,10 @@
       </c>
       <c r="N40" s="6"/>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N41" s="6"/>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B42" s="1" t="s">
         <v>116</v>
       </c>
@@ -4687,7 +4722,7 @@
       </c>
       <c r="N42" s="6"/>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B43" s="6"/>
       <c r="C43" s="5"/>
       <c r="D43" s="6"/>
@@ -4705,7 +4740,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B44" s="8"/>
       <c r="C44" s="5"/>
       <c r="D44" s="6"/>
@@ -4723,7 +4758,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B45" s="1" t="s">
         <v>188</v>
       </c>
@@ -4734,7 +4769,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="K46" s="1" t="s">
         <v>189</v>
       </c>
@@ -4742,7 +4777,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
         <v>178</v>
       </c>
@@ -4750,7 +4785,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B50" s="1" t="s">
         <v>184</v>
       </c>
@@ -4767,7 +4802,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A54" s="1"/>
       <c r="B54" s="1" t="s">
         <v>203</v>
@@ -4785,7 +4820,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
       <c r="K55" s="1" t="s">
         <v>202</v>
       </c>
@@ -4793,7 +4828,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
       <c r="K56" s="1" t="s">
         <v>204</v>
       </c>
@@ -4801,7 +4836,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B58" s="1" t="s">
         <v>232</v>
       </c>
@@ -4815,7 +4850,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
       <c r="K59" s="1" t="s">
         <v>75</v>
       </c>
@@ -4823,7 +4858,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B61" s="1" t="s">
         <v>233</v>
       </c>
@@ -4837,7 +4872,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B63" s="1" t="s">
         <v>237</v>
       </c>
@@ -4848,6 +4883,20 @@
         <v>238</v>
       </c>
       <c r="M63" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B65" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="K65" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="M65" s="1" t="s">
         <v>23</v>
       </c>
     </row>
@@ -4863,7 +4912,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEE0849C-6C30-450E-8369-1D81B45C3886}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Config/Datas/__beans__.xlsx
+++ b/Config/Datas/__beans__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E31E431E-9B47-46FD-A3FC-5477BF62B7FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1232C333-D789-40ED-A63A-990268E1521F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="247">
   <si>
     <t>##var</t>
   </si>
@@ -993,6 +993,10 @@
   </si>
   <si>
     <t>entityID</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GA_获得声望</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1421,23 +1425,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Q185"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="28.75" customWidth="1"/>
     <col min="3" max="3" width="22" customWidth="1"/>
-    <col min="4" max="4" width="9.33203125" customWidth="1"/>
+    <col min="4" max="4" width="9.375" customWidth="1"/>
     <col min="5" max="5" width="9.5" customWidth="1"/>
-    <col min="6" max="6" width="5.83203125" customWidth="1"/>
+    <col min="6" max="6" width="5.875" customWidth="1"/>
     <col min="7" max="7" width="16" customWidth="1"/>
-    <col min="8" max="8" width="6.58203125" customWidth="1"/>
+    <col min="8" max="8" width="6.625" customWidth="1"/>
     <col min="9" max="9" width="6.75" customWidth="1"/>
-    <col min="10" max="10" width="7.33203125" customWidth="1"/>
+    <col min="10" max="10" width="7.375" customWidth="1"/>
     <col min="11" max="12" width="13.5" customWidth="1"/>
-    <col min="13" max="13" width="11.83203125" customWidth="1"/>
+    <col min="13" max="13" width="11.875" customWidth="1"/>
     <col min="14" max="14" width="20.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1478,7 +1482,7 @@
       <c r="P1" s="12"/>
       <c r="Q1" s="12"/>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -1513,7 +1517,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
         <v>11</v>
       </c>
@@ -1550,7 +1554,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
         <v>29</v>
       </c>
@@ -1579,7 +1583,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
         <v>29</v>
       </c>
@@ -1606,7 +1610,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A6" s="6"/>
       <c r="B6" s="6"/>
       <c r="C6" s="5"/>
@@ -1625,7 +1629,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A7" s="6"/>
       <c r="B7" s="6" t="s">
         <v>176</v>
@@ -1652,7 +1656,7 @@
       <c r="P7" s="6"/>
       <c r="Q7" s="6"/>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A8" s="6"/>
       <c r="B8" s="6"/>
       <c r="C8" s="5"/>
@@ -1675,7 +1679,7 @@
       <c r="P8" s="6"/>
       <c r="Q8" s="6"/>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A9" s="6"/>
       <c r="B9" s="6"/>
       <c r="C9" s="5"/>
@@ -1698,7 +1702,7 @@
       <c r="P9" s="6"/>
       <c r="Q9" s="6"/>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A10" s="6"/>
       <c r="B10" s="6"/>
       <c r="C10" s="5"/>
@@ -1720,7 +1724,7 @@
       <c r="P10" s="6"/>
       <c r="Q10" s="6"/>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A11" s="6"/>
       <c r="B11" s="6"/>
       <c r="C11" s="5"/>
@@ -1742,7 +1746,7 @@
       <c r="P11" s="6"/>
       <c r="Q11" s="6"/>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A12" s="6"/>
       <c r="B12" s="6"/>
       <c r="C12" s="5"/>
@@ -1765,7 +1769,7 @@
       <c r="P12" s="6"/>
       <c r="Q12" s="6"/>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A13" s="6"/>
       <c r="B13" s="6"/>
       <c r="C13" s="5"/>
@@ -1784,7 +1788,7 @@
       <c r="P13" s="6"/>
       <c r="Q13" s="6"/>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A14" s="6" t="s">
         <v>180</v>
       </c>
@@ -1805,7 +1809,7 @@
       <c r="P14" s="6"/>
       <c r="Q14" s="6"/>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A15" s="6"/>
       <c r="B15" s="6"/>
       <c r="C15" s="5"/>
@@ -1824,7 +1828,7 @@
       <c r="P15" s="6"/>
       <c r="Q15" s="6"/>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A16" s="6"/>
       <c r="B16" s="6"/>
       <c r="C16" s="5"/>
@@ -1843,7 +1847,7 @@
       <c r="P16" s="6"/>
       <c r="Q16" s="6"/>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A17" s="6"/>
       <c r="B17" s="6" t="s">
         <v>181</v>
@@ -1868,7 +1872,7 @@
       <c r="P17" s="6"/>
       <c r="Q17" s="6"/>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A18" s="6"/>
       <c r="B18" s="6"/>
       <c r="C18" s="5"/>
@@ -1891,7 +1895,7 @@
       <c r="P18" s="6"/>
       <c r="Q18" s="6"/>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A19" s="6"/>
       <c r="B19" s="6"/>
       <c r="C19" s="5"/>
@@ -1910,7 +1914,7 @@
       <c r="P19" s="6"/>
       <c r="Q19" s="6"/>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A20" s="6"/>
       <c r="B20" s="6" t="s">
         <v>30</v>
@@ -1939,7 +1943,7 @@
       <c r="P20" s="6"/>
       <c r="Q20" s="6"/>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A21" s="6"/>
       <c r="B21" s="6"/>
       <c r="C21" s="5"/>
@@ -1964,7 +1968,7 @@
       <c r="P21" s="6"/>
       <c r="Q21" s="6"/>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A22" s="6"/>
       <c r="D22" s="6"/>
       <c r="E22" s="6"/>
@@ -1985,7 +1989,7 @@
       <c r="P22" s="6"/>
       <c r="Q22" s="6"/>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A23" s="6"/>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
@@ -2003,7 +2007,7 @@
       <c r="P23" s="6"/>
       <c r="Q23" s="6"/>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A24" s="6"/>
       <c r="B24" s="6"/>
       <c r="C24" s="6"/>
@@ -2026,7 +2030,7 @@
       <c r="P24" s="6"/>
       <c r="Q24" s="6"/>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A25" s="6"/>
       <c r="D25" s="6"/>
       <c r="E25" s="6"/>
@@ -2047,7 +2051,7 @@
       <c r="P25" s="6"/>
       <c r="Q25" s="6"/>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A26" s="6"/>
       <c r="B26" s="6"/>
       <c r="C26" s="6"/>
@@ -2072,7 +2076,7 @@
       <c r="P26" s="6"/>
       <c r="Q26" s="6"/>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A27" s="6"/>
       <c r="B27" s="6"/>
       <c r="C27" s="6"/>
@@ -2097,7 +2101,7 @@
       <c r="P27" s="7"/>
       <c r="Q27" s="7"/>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A28" s="6"/>
       <c r="K28" s="5" t="s">
         <v>60</v>
@@ -2113,7 +2117,7 @@
       <c r="P28" s="6"/>
       <c r="Q28" s="6"/>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A29" s="6"/>
       <c r="K29" s="1" t="s">
         <v>143</v>
@@ -2127,7 +2131,7 @@
       <c r="P29" s="6"/>
       <c r="Q29" s="6"/>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A30" s="6"/>
       <c r="K30" s="1" t="s">
         <v>150</v>
@@ -2141,7 +2145,7 @@
       <c r="P30" s="6"/>
       <c r="Q30" s="6"/>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A31" s="6"/>
       <c r="K31" s="1" t="s">
         <v>95</v>
@@ -2154,11 +2158,11 @@
       </c>
       <c r="Q31" s="6"/>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A32" s="6"/>
       <c r="Q32" s="6"/>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A33" s="6"/>
       <c r="B33" s="6" t="s">
         <v>45</v>
@@ -2187,7 +2191,7 @@
       <c r="P33" s="6"/>
       <c r="Q33" s="6"/>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A34" s="6"/>
       <c r="B34" s="6"/>
       <c r="C34" s="6"/>
@@ -2212,7 +2216,7 @@
       <c r="P34" s="6"/>
       <c r="Q34" s="6"/>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A35" s="6"/>
       <c r="B35" s="6"/>
       <c r="C35" s="6"/>
@@ -2235,7 +2239,7 @@
       <c r="P35" s="6"/>
       <c r="Q35" s="6"/>
     </row>
-    <row r="36" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="6"/>
       <c r="B36" s="5"/>
       <c r="C36" s="6"/>
@@ -2260,7 +2264,7 @@
       <c r="P36" s="6"/>
       <c r="Q36" s="6"/>
     </row>
-    <row r="37" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="6"/>
       <c r="B37" s="5"/>
       <c r="C37" s="6"/>
@@ -2283,7 +2287,7 @@
       <c r="P37" s="6"/>
       <c r="Q37" s="6"/>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A38" s="6"/>
       <c r="B38" s="6"/>
       <c r="C38" s="6"/>
@@ -2308,12 +2312,12 @@
       <c r="P38" s="6"/>
       <c r="Q38" s="6"/>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A39" s="6"/>
       <c r="P39" s="6"/>
       <c r="Q39" s="6"/>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A40" s="6"/>
       <c r="B40" s="1" t="s">
         <v>145</v>
@@ -2333,7 +2337,7 @@
       <c r="P40" s="6"/>
       <c r="Q40" s="6"/>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A41" s="6"/>
       <c r="K41" s="5" t="s">
         <v>26</v>
@@ -2347,7 +2351,7 @@
       <c r="P41" s="6"/>
       <c r="Q41" s="6"/>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A42" s="6"/>
       <c r="K42" s="5" t="s">
         <v>41</v>
@@ -2361,7 +2365,7 @@
       <c r="P42" s="6"/>
       <c r="Q42" s="6"/>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A43" s="6"/>
       <c r="K43" s="5" t="s">
         <v>161</v>
@@ -2373,7 +2377,7 @@
       <c r="P43" s="6"/>
       <c r="Q43" s="6"/>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A44" s="6"/>
       <c r="K44" s="5" t="s">
         <v>150</v>
@@ -2387,7 +2391,7 @@
       <c r="P44" s="6"/>
       <c r="Q44" s="6"/>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A45" s="6"/>
       <c r="K45" s="5" t="s">
         <v>154</v>
@@ -2401,7 +2405,7 @@
       <c r="P45" s="6"/>
       <c r="Q45" s="6"/>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A46" s="6"/>
       <c r="K46" s="5" t="s">
         <v>155</v>
@@ -2415,7 +2419,7 @@
       <c r="P46" s="6"/>
       <c r="Q46" s="6"/>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A47" s="6"/>
       <c r="K47" s="5" t="s">
         <v>157</v>
@@ -2429,18 +2433,18 @@
       <c r="P47" s="6"/>
       <c r="Q47" s="6"/>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A48" s="6"/>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A49" s="6"/>
       <c r="Q49" s="6"/>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A50" s="6"/>
       <c r="Q50" s="6"/>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A51" s="6"/>
       <c r="B51" s="6" t="s">
         <v>66</v>
@@ -2466,7 +2470,7 @@
       <c r="P51" s="6"/>
       <c r="Q51" s="6"/>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A52" s="6"/>
       <c r="K52" s="6" t="s">
         <v>67</v>
@@ -2478,7 +2482,7 @@
       <c r="P52" s="6"/>
       <c r="Q52" s="6"/>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A53" s="6"/>
       <c r="K53" s="5" t="s">
         <v>68</v>
@@ -2489,14 +2493,14 @@
       <c r="P53" s="7"/>
       <c r="Q53" s="6"/>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A54" s="6"/>
       <c r="K54" s="5"/>
       <c r="M54" s="5"/>
       <c r="P54" s="7"/>
       <c r="Q54" s="6"/>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A55" s="6"/>
       <c r="B55" s="1" t="s">
         <v>166</v>
@@ -2510,7 +2514,7 @@
       <c r="P55" s="7"/>
       <c r="Q55" s="6"/>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A56" s="6"/>
       <c r="K56" s="5" t="s">
         <v>165</v>
@@ -2521,7 +2525,7 @@
       <c r="P56" s="7"/>
       <c r="Q56" s="6"/>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A57" s="6"/>
       <c r="K57" s="5" t="s">
         <v>33</v>
@@ -2532,7 +2536,7 @@
       <c r="P57" s="7"/>
       <c r="Q57" s="6"/>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A58" s="6"/>
       <c r="K58" s="5" t="s">
         <v>169</v>
@@ -2543,19 +2547,19 @@
       <c r="P58" s="7"/>
       <c r="Q58" s="6"/>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A59" s="6"/>
       <c r="K59" s="5"/>
       <c r="M59" s="5"/>
       <c r="P59" s="7"/>
       <c r="Q59" s="6"/>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A60" s="6"/>
       <c r="P60" s="7"/>
       <c r="Q60" s="6"/>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A61" s="6"/>
       <c r="B61" s="5" t="s">
         <v>73</v>
@@ -2582,7 +2586,7 @@
       <c r="P61" s="6"/>
       <c r="Q61" s="6"/>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A62" s="6"/>
       <c r="B62" s="6"/>
       <c r="C62" s="6"/>
@@ -2605,7 +2609,7 @@
       <c r="P62" s="6"/>
       <c r="Q62" s="6"/>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A63" s="6"/>
       <c r="B63" s="6"/>
       <c r="C63" s="6"/>
@@ -2627,7 +2631,7 @@
       <c r="P63" s="6"/>
       <c r="Q63" s="6"/>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A64" s="6"/>
       <c r="B64" s="6"/>
       <c r="C64" s="6"/>
@@ -2651,7 +2655,7 @@
       <c r="P64" s="6"/>
       <c r="Q64" s="6"/>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A65" s="6"/>
       <c r="B65" s="6"/>
       <c r="C65" s="6"/>
@@ -2674,7 +2678,7 @@
       <c r="P65" s="6"/>
       <c r="Q65" s="6"/>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A66" s="6"/>
       <c r="B66" s="6"/>
       <c r="C66" s="6"/>
@@ -2690,7 +2694,7 @@
       <c r="P66" s="6"/>
       <c r="Q66" s="6"/>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A67" s="6"/>
       <c r="B67" s="5"/>
       <c r="C67" s="6"/>
@@ -2707,7 +2711,7 @@
       <c r="P67" s="6"/>
       <c r="Q67" s="6"/>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A68" s="6"/>
       <c r="B68" s="6" t="s">
         <v>79</v>
@@ -2732,7 +2736,7 @@
       <c r="P68" s="6"/>
       <c r="Q68" s="6"/>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A69" s="6"/>
       <c r="B69" s="6"/>
       <c r="C69" s="6"/>
@@ -2755,7 +2759,7 @@
       <c r="P69" s="6"/>
       <c r="Q69" s="6"/>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A70" s="6"/>
       <c r="H70" s="6"/>
       <c r="I70" s="6"/>
@@ -2772,7 +2776,7 @@
       <c r="P70" s="6"/>
       <c r="Q70" s="6"/>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A71" s="6"/>
       <c r="H71" s="6"/>
       <c r="I71" s="6"/>
@@ -2790,7 +2794,7 @@
       <c r="P71" s="6"/>
       <c r="Q71" s="6"/>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A72" s="6"/>
       <c r="K72" s="11" t="s">
         <v>144</v>
@@ -2804,7 +2808,7 @@
       <c r="P72" s="6"/>
       <c r="Q72" s="6"/>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A73" s="6"/>
       <c r="B73" s="6"/>
       <c r="C73" s="6"/>
@@ -2822,7 +2826,7 @@
       <c r="P73" s="6"/>
       <c r="Q73" s="6"/>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A74" s="6"/>
       <c r="K74" s="11"/>
       <c r="M74" s="11"/>
@@ -2830,12 +2834,12 @@
       <c r="P74" s="6"/>
       <c r="Q74" s="7"/>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A75" s="6"/>
       <c r="P75" s="6"/>
       <c r="Q75" s="6"/>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A76" s="6"/>
       <c r="B76" s="6"/>
       <c r="C76" s="6"/>
@@ -2849,7 +2853,7 @@
       <c r="P76" s="7"/>
       <c r="Q76" s="6"/>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A77" s="6"/>
       <c r="B77" s="1" t="s">
         <v>82</v>
@@ -2863,7 +2867,7 @@
       <c r="P77" s="6"/>
       <c r="Q77" s="6"/>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A78" s="5"/>
       <c r="B78" s="6"/>
       <c r="C78" s="6"/>
@@ -2876,7 +2880,7 @@
       <c r="P78" s="6"/>
       <c r="Q78" s="6"/>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A79" s="6"/>
       <c r="C79" s="6"/>
       <c r="D79" s="6"/>
@@ -2894,7 +2898,7 @@
       <c r="P79" s="6"/>
       <c r="Q79" s="6"/>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A80" s="6"/>
       <c r="B80" s="8" t="s">
         <v>89</v>
@@ -2919,7 +2923,7 @@
       <c r="P80" s="6"/>
       <c r="Q80" s="6"/>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A81" s="6"/>
       <c r="B81" s="8"/>
       <c r="C81" s="5"/>
@@ -2942,7 +2946,7 @@
       <c r="P81" s="6"/>
       <c r="Q81" s="6"/>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A82" s="6"/>
       <c r="B82" s="6"/>
       <c r="C82" s="6"/>
@@ -2965,7 +2969,7 @@
       <c r="P82" s="7"/>
       <c r="Q82" s="6"/>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A83" s="6"/>
       <c r="B83" s="6"/>
       <c r="C83" s="6"/>
@@ -2987,7 +2991,7 @@
       <c r="P83" s="6"/>
       <c r="Q83" s="6"/>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B84" s="8"/>
       <c r="C84" s="5"/>
       <c r="D84" s="6"/>
@@ -3007,7 +3011,7 @@
       <c r="P84" s="6"/>
       <c r="Q84" s="6"/>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B85" s="8"/>
       <c r="C85" s="5"/>
       <c r="D85" s="6"/>
@@ -3027,7 +3031,7 @@
       <c r="P85" s="6"/>
       <c r="Q85" s="6"/>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B86" s="1"/>
       <c r="G86" s="1"/>
       <c r="H86" s="6"/>
@@ -3039,7 +3043,7 @@
       <c r="P86" s="7"/>
       <c r="Q86" s="6"/>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.2">
       <c r="H87" s="6"/>
       <c r="I87" s="6"/>
       <c r="J87" s="8"/>
@@ -3050,7 +3054,7 @@
       <c r="P87" s="7"/>
       <c r="Q87" s="6"/>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B88" s="1" t="s">
         <v>97</v>
       </c>
@@ -3059,7 +3063,7 @@
       <c r="P88" s="7"/>
       <c r="Q88" s="7"/>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B89" s="1" t="s">
         <v>107</v>
       </c>
@@ -3075,7 +3079,7 @@
       <c r="P89" s="7"/>
       <c r="Q89" s="6"/>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.2">
       <c r="K90" s="1" t="s">
         <v>68</v>
       </c>
@@ -3088,7 +3092,7 @@
       <c r="P90" s="6"/>
       <c r="Q90" s="6"/>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A91" s="6"/>
       <c r="B91" s="1" t="s">
         <v>100</v>
@@ -3109,7 +3113,7 @@
       <c r="P91" s="6"/>
       <c r="Q91" s="6"/>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A92" s="6"/>
       <c r="K92" s="1" t="s">
         <v>101</v>
@@ -3124,20 +3128,20 @@
       <c r="P92" s="6"/>
       <c r="Q92" s="6"/>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A93" s="6"/>
       <c r="N93" s="6"/>
       <c r="P93" s="7"/>
       <c r="Q93" s="6"/>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A94" s="6"/>
       <c r="N94" s="6"/>
       <c r="O94" s="5"/>
       <c r="P94" s="6"/>
       <c r="Q94" s="6"/>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A95" s="6"/>
       <c r="H95" s="6"/>
       <c r="I95" s="6"/>
@@ -3150,7 +3154,7 @@
       <c r="P95" s="6"/>
       <c r="Q95" s="6"/>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A96" s="6"/>
       <c r="H96" s="6"/>
       <c r="I96" s="6"/>
@@ -3163,7 +3167,7 @@
       <c r="P96" s="6"/>
       <c r="Q96" s="6"/>
     </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A97" s="6"/>
       <c r="D97" s="6"/>
       <c r="E97" s="6"/>
@@ -3180,7 +3184,7 @@
       <c r="P97" s="6"/>
       <c r="Q97" s="6"/>
     </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A98" s="6"/>
       <c r="B98" s="8"/>
       <c r="C98" s="5"/>
@@ -3199,25 +3203,25 @@
       <c r="P98" s="6"/>
       <c r="Q98" s="6"/>
     </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A99" s="6"/>
       <c r="O99" s="6"/>
       <c r="P99" s="6"/>
       <c r="Q99" s="6"/>
     </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A100" s="6"/>
       <c r="O100" s="6"/>
       <c r="P100" s="6"/>
       <c r="Q100" s="6"/>
     </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A101" s="6"/>
       <c r="O101" s="6"/>
       <c r="P101" s="6"/>
       <c r="Q101" s="6"/>
     </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A102" s="6"/>
       <c r="B102" s="8"/>
       <c r="C102" s="5"/>
@@ -3236,7 +3240,7 @@
       <c r="P102" s="6"/>
       <c r="Q102" s="6"/>
     </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A103" s="6"/>
       <c r="B103" s="1" t="s">
         <v>119</v>
@@ -3256,7 +3260,7 @@
       <c r="P103" s="6"/>
       <c r="Q103" s="6"/>
     </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A104" s="6"/>
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
@@ -3266,7 +3270,7 @@
       <c r="P104" s="6"/>
       <c r="Q104" s="6"/>
     </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A105" s="6"/>
       <c r="B105" s="1" t="s">
         <v>120</v>
@@ -3293,7 +3297,7 @@
       <c r="P105" s="6"/>
       <c r="Q105" s="6"/>
     </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A106" s="6"/>
       <c r="B106" s="1" t="s">
         <v>121</v>
@@ -3320,7 +3324,7 @@
       <c r="P106" s="6"/>
       <c r="Q106" s="6"/>
     </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A107" s="6"/>
       <c r="B107" s="1" t="s">
         <v>126</v>
@@ -3343,7 +3347,7 @@
       <c r="P107" s="6"/>
       <c r="Q107" s="6"/>
     </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A108" s="6"/>
       <c r="B108" s="6" t="s">
         <v>131</v>
@@ -3362,7 +3366,7 @@
       <c r="P108" s="6"/>
       <c r="Q108" s="6"/>
     </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A109" s="6"/>
       <c r="B109" s="6" t="s">
         <v>160</v>
@@ -3387,7 +3391,7 @@
       <c r="P109" s="6"/>
       <c r="Q109" s="6"/>
     </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A110" s="6"/>
       <c r="B110" s="6" t="s">
         <v>162</v>
@@ -3410,7 +3414,7 @@
       <c r="P110" s="6"/>
       <c r="Q110" s="6"/>
     </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A111" s="6"/>
       <c r="B111" s="6" t="s">
         <v>231</v>
@@ -3433,7 +3437,7 @@
       <c r="P111" s="6"/>
       <c r="Q111" s="6"/>
     </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A112" s="6"/>
       <c r="B112" s="5"/>
       <c r="C112" s="5"/>
@@ -3452,7 +3456,7 @@
       <c r="P112" s="6"/>
       <c r="Q112" s="6"/>
     </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A113" s="6"/>
       <c r="B113" s="5"/>
       <c r="C113" s="5"/>
@@ -3471,7 +3475,7 @@
       <c r="P113" s="6"/>
       <c r="Q113" s="6"/>
     </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A114" s="6"/>
       <c r="B114" s="5" t="s">
         <v>239</v>
@@ -3496,7 +3500,7 @@
       <c r="P114" s="6"/>
       <c r="Q114" s="6"/>
     </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A115" s="6"/>
       <c r="B115" s="5"/>
       <c r="C115" s="5"/>
@@ -3519,7 +3523,7 @@
       <c r="P115" s="6"/>
       <c r="Q115" s="6"/>
     </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A116" s="6"/>
       <c r="B116" s="5"/>
       <c r="C116" s="5"/>
@@ -3542,7 +3546,7 @@
       <c r="P116" s="6"/>
       <c r="Q116" s="6"/>
     </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A117" s="6"/>
       <c r="B117" s="5"/>
       <c r="C117" s="5"/>
@@ -3565,7 +3569,7 @@
       <c r="P117" s="6"/>
       <c r="Q117" s="6"/>
     </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A118" s="6"/>
       <c r="B118" s="6"/>
       <c r="C118" s="6"/>
@@ -3588,7 +3592,7 @@
       <c r="P118" s="6"/>
       <c r="Q118" s="6"/>
     </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A119" s="6"/>
       <c r="B119" s="6"/>
       <c r="C119" s="6"/>
@@ -3610,7 +3614,7 @@
       <c r="P119" s="6"/>
       <c r="Q119" s="6"/>
     </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A120" s="5"/>
       <c r="B120" s="8"/>
       <c r="C120" s="5"/>
@@ -3632,7 +3636,7 @@
       <c r="P120" s="6"/>
       <c r="Q120" s="6"/>
     </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A121" s="5"/>
       <c r="B121" s="8"/>
       <c r="C121" s="5"/>
@@ -3650,7 +3654,7 @@
       <c r="P121" s="6"/>
       <c r="Q121" s="6"/>
     </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A122" s="5"/>
       <c r="B122" s="8" t="s">
         <v>240</v>
@@ -3674,7 +3678,7 @@
       <c r="P122" s="6"/>
       <c r="Q122" s="6"/>
     </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A123" s="5"/>
       <c r="B123" s="8"/>
       <c r="C123" s="5"/>
@@ -3696,7 +3700,7 @@
       <c r="P123" s="6"/>
       <c r="Q123" s="6"/>
     </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A124" s="5"/>
       <c r="B124" s="8"/>
       <c r="C124" s="5"/>
@@ -3714,11 +3718,11 @@
       <c r="P124" s="6"/>
       <c r="Q124" s="6"/>
     </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:17" x14ac:dyDescent="0.2">
       <c r="K125" s="1"/>
       <c r="M125" s="5"/>
     </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C126" s="6"/>
       <c r="D126" s="6"/>
       <c r="E126" s="6"/>
@@ -3733,21 +3737,21 @@
       <c r="N126" s="6"/>
       <c r="O126" s="6"/>
     </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:17" x14ac:dyDescent="0.2">
       <c r="N127" s="6"/>
       <c r="O127" s="6"/>
     </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B128" s="6" t="s">
         <v>64</v>
       </c>
       <c r="N128" s="6"/>
     </row>
-    <row r="129" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="129" spans="2:15" x14ac:dyDescent="0.2">
       <c r="N129" s="6"/>
       <c r="O129" s="6"/>
     </row>
-    <row r="130" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="130" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B130" s="5" t="s">
         <v>123</v>
       </c>
@@ -3770,7 +3774,7 @@
       <c r="N130" s="6"/>
       <c r="O130" s="6"/>
     </row>
-    <row r="131" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="131" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K131" s="1" t="s">
         <v>113</v>
       </c>
@@ -3778,7 +3782,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="132" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="132" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K132" s="1" t="s">
         <v>125</v>
       </c>
@@ -3786,7 +3790,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="134" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="134" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B134" s="6" t="s">
         <v>65</v>
       </c>
@@ -3804,7 +3808,7 @@
       <c r="L134" s="6"/>
       <c r="M134" s="5"/>
     </row>
-    <row r="135" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="135" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B135" s="6" t="s">
         <v>110</v>
       </c>
@@ -3825,7 +3829,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="136" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="136" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C136" s="6"/>
       <c r="D136" s="6"/>
       <c r="E136" s="6"/>
@@ -3842,7 +3846,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="139" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="139" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B139" s="1" t="s">
         <v>195</v>
       </c>
@@ -3853,7 +3857,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="140" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="140" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K140" s="1" t="s">
         <v>197</v>
       </c>
@@ -3861,10 +3865,10 @@
         <v>23</v>
       </c>
     </row>
-    <row r="141" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="141" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K141" s="1"/>
     </row>
-    <row r="143" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="143" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B143" s="1" t="s">
         <v>206</v>
       </c>
@@ -3876,7 +3880,7 @@
       </c>
       <c r="O143" s="6"/>
     </row>
-    <row r="144" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="144" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K144" s="1" t="s">
         <v>26</v>
       </c>
@@ -3884,7 +3888,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="145" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="145" spans="2:13" x14ac:dyDescent="0.2">
       <c r="K145" s="1" t="s">
         <v>41</v>
       </c>
@@ -3892,7 +3896,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="146" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="146" spans="2:13" x14ac:dyDescent="0.2">
       <c r="K146" s="1" t="s">
         <v>33</v>
       </c>
@@ -3900,7 +3904,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="147" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="147" spans="2:13" x14ac:dyDescent="0.2">
       <c r="K147" s="1" t="s">
         <v>199</v>
       </c>
@@ -3908,7 +3912,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="148" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="148" spans="2:13" x14ac:dyDescent="0.2">
       <c r="K148" s="1" t="s">
         <v>150</v>
       </c>
@@ -3916,7 +3920,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="149" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="149" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B149" s="1" t="s">
         <v>227</v>
       </c>
@@ -3927,7 +3931,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="150" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="150" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B150" s="1"/>
       <c r="K150" s="1" t="s">
         <v>26</v>
@@ -3936,7 +3940,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="151" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="151" spans="2:13" x14ac:dyDescent="0.2">
       <c r="K151" s="1" t="s">
         <v>41</v>
       </c>
@@ -3944,7 +3948,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="152" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="152" spans="2:13" x14ac:dyDescent="0.2">
       <c r="K152" s="1" t="s">
         <v>228</v>
       </c>
@@ -3952,11 +3956,11 @@
         <v>229</v>
       </c>
     </row>
-    <row r="153" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="153" spans="2:13" x14ac:dyDescent="0.2">
       <c r="K153" s="1"/>
       <c r="M153" s="1"/>
     </row>
-    <row r="154" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="154" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B154" s="1" t="s">
         <v>230</v>
       </c>
@@ -3967,7 +3971,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="155" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="155" spans="2:13" x14ac:dyDescent="0.2">
       <c r="K155" s="1" t="s">
         <v>26</v>
       </c>
@@ -3975,7 +3979,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="156" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="156" spans="2:13" x14ac:dyDescent="0.2">
       <c r="K156" s="1" t="s">
         <v>41</v>
       </c>
@@ -3983,7 +3987,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="157" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="157" spans="2:13" x14ac:dyDescent="0.2">
       <c r="K157" s="1" t="s">
         <v>60</v>
       </c>
@@ -3991,7 +3995,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="158" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="158" spans="2:13" x14ac:dyDescent="0.2">
       <c r="K158" s="1" t="s">
         <v>134</v>
       </c>
@@ -3999,10 +4003,10 @@
         <v>66</v>
       </c>
     </row>
-    <row r="159" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="159" spans="2:13" x14ac:dyDescent="0.2">
       <c r="K159" s="1"/>
     </row>
-    <row r="161" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="161" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B161" s="1" t="s">
         <v>207</v>
       </c>
@@ -4016,7 +4020,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="162" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="162" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K162" s="1" t="s">
         <v>26</v>
       </c>
@@ -4027,7 +4031,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="163" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="163" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K163" s="1" t="s">
         <v>41</v>
       </c>
@@ -4038,10 +4042,10 @@
         <v>211</v>
       </c>
     </row>
-    <row r="164" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="164" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K164" s="1"/>
     </row>
-    <row r="165" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="165" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B165" s="1" t="s">
         <v>208</v>
       </c>
@@ -4052,7 +4056,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="166" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="166" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K166" s="1" t="s">
         <v>26</v>
       </c>
@@ -4060,7 +4064,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="167" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="167" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K167" s="1" t="s">
         <v>41</v>
       </c>
@@ -4068,7 +4072,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="168" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="168" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K168" s="1" t="s">
         <v>216</v>
       </c>
@@ -4076,7 +4080,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="169" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="169" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K169" s="1" t="s">
         <v>218</v>
       </c>
@@ -4084,7 +4088,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="171" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="171" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B171" s="1" t="s">
         <v>213</v>
       </c>
@@ -4095,7 +4099,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="172" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="172" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K172" s="1" t="s">
         <v>215</v>
       </c>
@@ -4103,7 +4107,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="175" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="175" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B175" s="1" t="s">
         <v>219</v>
       </c>
@@ -4117,7 +4121,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="176" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="176" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K176" s="1" t="s">
         <v>26</v>
       </c>
@@ -4128,7 +4132,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="177" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="177" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K177" s="1" t="s">
         <v>41</v>
       </c>
@@ -4139,7 +4143,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="178" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="178" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K178" s="1" t="s">
         <v>143</v>
       </c>
@@ -4147,7 +4151,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="179" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="179" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B179" s="1" t="s">
         <v>234</v>
       </c>
@@ -4158,7 +4162,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="180" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="180" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K180" s="1" t="s">
         <v>134</v>
       </c>
@@ -4166,7 +4170,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="184" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="184" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B184" s="1" t="s">
         <v>226</v>
       </c>
@@ -4180,7 +4184,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="185" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="185" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K185" s="1" t="s">
         <v>95</v>
       </c>
@@ -4200,13 +4204,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EECC075D-9730-41E5-B97E-C301603D1E48}">
-  <dimension ref="A1:Q65"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:Q68"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="27.33203125" customWidth="1"/>
+    <col min="2" max="2" width="27.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -4247,7 +4251,7 @@
       <c r="P1" s="12"/>
       <c r="Q1" s="12"/>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -4282,7 +4286,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
         <v>11</v>
       </c>
@@ -4319,7 +4323,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="6" t="s">
         <v>53</v>
       </c>
@@ -4336,7 +4340,7 @@
       <c r="M6" s="5"/>
       <c r="N6" s="6"/>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B8" s="1" t="s">
         <v>141</v>
       </c>
@@ -4350,7 +4354,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="K9" s="1" t="s">
         <v>134</v>
       </c>
@@ -4361,7 +4365,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B11" s="1" t="s">
         <v>129</v>
       </c>
@@ -4375,7 +4379,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B12" s="6" t="s">
         <v>54</v>
       </c>
@@ -4403,7 +4407,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
@@ -4425,7 +4429,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
       <c r="D14" s="6"/>
@@ -4438,7 +4442,7 @@
       <c r="N14" s="6"/>
       <c r="O14" s="6"/>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B15" s="1" t="s">
         <v>74</v>
       </c>
@@ -4456,7 +4460,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="K16" s="1" t="s">
         <v>75</v>
       </c>
@@ -4467,7 +4471,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B17" s="1" t="s">
         <v>104</v>
       </c>
@@ -4484,7 +4488,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="18" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B18" s="1" t="s">
         <v>115</v>
       </c>
@@ -4498,7 +4502,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="19" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K19" s="5" t="s">
         <v>37</v>
       </c>
@@ -4506,7 +4510,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="20" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K20" s="1" t="s">
         <v>118</v>
       </c>
@@ -4514,7 +4518,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="21" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B21" s="1" t="s">
         <v>127</v>
       </c>
@@ -4528,7 +4532,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="23" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B23" s="1" t="s">
         <v>133</v>
       </c>
@@ -4542,7 +4546,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="24" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K24" s="1" t="s">
         <v>134</v>
       </c>
@@ -4550,7 +4554,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="26" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B26" s="1" t="s">
         <v>139</v>
       </c>
@@ -4564,7 +4568,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="27" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K27" s="1" t="s">
         <v>33</v>
       </c>
@@ -4572,7 +4576,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="28" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K28" s="1" t="s">
         <v>41</v>
       </c>
@@ -4580,7 +4584,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K29" s="1" t="s">
         <v>68</v>
       </c>
@@ -4588,7 +4592,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="31" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B31" s="1" t="s">
         <v>158</v>
       </c>
@@ -4602,7 +4606,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="32" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B32" s="1" t="s">
         <v>173</v>
       </c>
@@ -4616,7 +4620,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
       <c r="K33" s="1" t="s">
         <v>186</v>
       </c>
@@ -4624,7 +4628,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B34" s="1" t="s">
         <v>222</v>
       </c>
@@ -4638,7 +4642,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
       <c r="K35" s="1" t="s">
         <v>223</v>
       </c>
@@ -4646,7 +4650,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>180</v>
       </c>
@@ -4657,11 +4661,11 @@
         <v>128</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
       <c r="K37" s="1"/>
       <c r="M37" s="1"/>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B38" s="1" t="s">
         <v>193</v>
       </c>
@@ -4675,7 +4679,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
       <c r="K39" s="1" t="s">
         <v>186</v>
       </c>
@@ -4683,7 +4687,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B40" s="1" t="s">
         <v>175</v>
       </c>
@@ -4698,10 +4702,10 @@
       </c>
       <c r="N40" s="6"/>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.2">
       <c r="N41" s="6"/>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B42" s="1" t="s">
         <v>116</v>
       </c>
@@ -4722,7 +4726,7 @@
       </c>
       <c r="N42" s="6"/>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B43" s="6"/>
       <c r="C43" s="5"/>
       <c r="D43" s="6"/>
@@ -4740,7 +4744,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B44" s="8"/>
       <c r="C44" s="5"/>
       <c r="D44" s="6"/>
@@ -4758,7 +4762,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B45" s="1" t="s">
         <v>188</v>
       </c>
@@ -4769,7 +4773,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.2">
       <c r="K46" s="1" t="s">
         <v>189</v>
       </c>
@@ -4777,7 +4781,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
         <v>178</v>
       </c>
@@ -4785,7 +4789,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B50" s="1" t="s">
         <v>184</v>
       </c>
@@ -4802,7 +4806,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A54" s="1"/>
       <c r="B54" s="1" t="s">
         <v>203</v>
@@ -4820,7 +4824,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.2">
       <c r="K55" s="1" t="s">
         <v>202</v>
       </c>
@@ -4828,7 +4832,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.2">
       <c r="K56" s="1" t="s">
         <v>204</v>
       </c>
@@ -4836,7 +4840,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B58" s="1" t="s">
         <v>232</v>
       </c>
@@ -4850,7 +4854,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.2">
       <c r="K59" s="1" t="s">
         <v>75</v>
       </c>
@@ -4858,7 +4862,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B61" s="1" t="s">
         <v>233</v>
       </c>
@@ -4872,7 +4876,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B63" s="1" t="s">
         <v>237</v>
       </c>
@@ -4886,7 +4890,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B65" s="1" t="s">
         <v>244</v>
       </c>
@@ -4899,6 +4903,26 @@
       <c r="M65" s="1" t="s">
         <v>23</v>
       </c>
+    </row>
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B67" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="K67" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="M67" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B68" s="1"/>
+      <c r="C68" s="1"/>
+      <c r="K68" s="1"/>
+      <c r="M68" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -4912,7 +4936,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEE0849C-6C30-450E-8369-1D81B45C3886}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Config/Datas/__beans__.xlsx
+++ b/Config/Datas/__beans__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1232C333-D789-40ED-A63A-990268E1521F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{013C9223-C6E3-411C-9157-F3B1BB815266}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="248">
   <si>
     <t>##var</t>
   </si>
@@ -997,6 +997,10 @@
   </si>
   <si>
     <t>GA_获得声望</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Condition_位于首尾</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1424,7 +1428,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q185"/>
+  <dimension ref="A1:Q187"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="28.75" customWidth="1"/>
@@ -3809,12 +3813,8 @@
       <c r="M134" s="5"/>
     </row>
     <row r="135" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B135" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="C135" s="6" t="s">
-        <v>64</v>
-      </c>
+      <c r="B135" s="6"/>
+      <c r="C135" s="6"/>
       <c r="D135" s="6"/>
       <c r="E135" s="6"/>
       <c r="F135" s="6"/>
@@ -3822,373 +3822,416 @@
       <c r="H135" s="6"/>
       <c r="I135" s="6"/>
       <c r="J135" s="6"/>
-      <c r="K135" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="M135" s="1" t="s">
-        <v>114</v>
-      </c>
+      <c r="K135" s="5"/>
+      <c r="L135" s="6"/>
+      <c r="M135" s="5"/>
     </row>
     <row r="136" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="C136" s="6"/>
+      <c r="B136" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="C136" s="6" t="s">
+        <v>64</v>
+      </c>
       <c r="D136" s="6"/>
       <c r="E136" s="6"/>
       <c r="F136" s="6"/>
-      <c r="G136" s="5"/>
+      <c r="G136" s="6"/>
       <c r="H136" s="6"/>
       <c r="I136" s="6"/>
-      <c r="J136" s="5"/>
-      <c r="K136" s="5" t="s">
+      <c r="J136" s="6"/>
+      <c r="K136" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="M136" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="137" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="D137" s="6"/>
+      <c r="E137" s="6"/>
+      <c r="F137" s="6"/>
+      <c r="G137" s="5"/>
+      <c r="H137" s="6"/>
+      <c r="I137" s="6"/>
+      <c r="J137" s="5"/>
+      <c r="K137" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="L136" s="6"/>
-      <c r="M136" s="5" t="s">
+      <c r="L137" s="6"/>
+      <c r="M137" s="5" t="s">
         <v>112</v>
       </c>
+    </row>
+    <row r="138" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="D138" s="6"/>
+      <c r="E138" s="6"/>
+      <c r="F138" s="6"/>
+      <c r="G138" s="5"/>
+      <c r="H138" s="6"/>
+      <c r="I138" s="6"/>
+      <c r="J138" s="5"/>
+      <c r="K138" s="5"/>
+      <c r="L138" s="6"/>
+      <c r="M138" s="5"/>
     </row>
     <row r="139" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B139" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="C139" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="K139" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M139" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="141" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B141" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="K139" s="1" t="s">
+      <c r="K141" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="M139" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="140" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K140" s="1" t="s">
+      <c r="M141" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="142" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K142" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="M140" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="141" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K141" s="1"/>
+      <c r="M142" s="1" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="143" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B143" s="1" t="s">
+      <c r="K143" s="1"/>
+    </row>
+    <row r="145" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B145" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="K143" s="1" t="s">
+      <c r="K145" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="M143" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="O143" s="6"/>
-    </row>
-    <row r="144" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K144" s="1" t="s">
+      <c r="M145" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O145" s="6"/>
+    </row>
+    <row r="146" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K146" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="M144" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="145" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="K145" s="1" t="s">
+      <c r="M146" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="147" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K147" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="M145" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="146" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="K146" s="1" t="s">
+      <c r="M147" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="148" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K148" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M146" s="1" t="s">
+      <c r="M148" s="1" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="147" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="K147" s="1" t="s">
+    <row r="149" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K149" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="M147" s="1" t="s">
+      <c r="M149" s="1" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="148" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="K148" s="1" t="s">
+    <row r="150" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K150" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="M148" s="5" t="s">
+      <c r="M150" s="5" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="149" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B149" s="1" t="s">
+    <row r="151" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B151" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="K149" s="1" t="s">
+      <c r="K151" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="M149" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="150" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B150" s="1"/>
-      <c r="K150" s="1" t="s">
+      <c r="M151" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="152" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B152" s="1"/>
+      <c r="K152" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="M150" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="151" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="K151" s="1" t="s">
+      <c r="M152" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="153" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K153" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="M151" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="152" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="K152" s="1" t="s">
+      <c r="M153" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="154" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K154" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="M152" s="1" t="s">
+      <c r="M154" s="1" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="153" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="K153" s="1"/>
-      <c r="M153" s="1"/>
-    </row>
-    <row r="154" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B154" s="1" t="s">
+    <row r="155" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K155" s="1"/>
+      <c r="M155" s="1"/>
+    </row>
+    <row r="156" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B156" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="K154" s="1" t="s">
+      <c r="K156" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="M154" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="155" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="K155" s="1" t="s">
+      <c r="M156" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="157" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K157" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="M155" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="156" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="K156" s="1" t="s">
+      <c r="M157" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="158" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K158" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="M156" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="157" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="K157" s="1" t="s">
+      <c r="M158" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="159" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K159" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="M157" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="158" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="K158" s="1" t="s">
+      <c r="M159" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="160" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K160" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="M158" s="1" t="s">
+      <c r="M160" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="159" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="K159" s="1"/>
-    </row>
     <row r="161" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B161" s="1" t="s">
+      <c r="K161" s="1"/>
+    </row>
+    <row r="163" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B163" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="K161" s="1" t="s">
+      <c r="K163" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="M161" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="O161" s="1" t="s">
+      <c r="M163" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O163" s="1" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="162" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K162" s="1" t="s">
+    <row r="164" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K164" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="M162" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="O162" s="1" t="s">
+      <c r="M164" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O164" s="1" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="163" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K163" s="1" t="s">
+    <row r="165" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K165" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="M163" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="O163" s="1" t="s">
+      <c r="M165" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O165" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="164" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K164" s="1"/>
-    </row>
-    <row r="165" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B165" s="1" t="s">
+    <row r="166" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K166" s="1"/>
+    </row>
+    <row r="167" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B167" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="K165" s="1" t="s">
+      <c r="K167" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="M165" s="1" t="s">
+      <c r="M167" s="1" t="s">
         <v>112</v>
-      </c>
-    </row>
-    <row r="166" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K166" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="M166" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="167" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K167" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="M167" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="168" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K168" s="1" t="s">
-        <v>216</v>
+        <v>26</v>
       </c>
       <c r="M168" s="1" t="s">
-        <v>103</v>
+        <v>23</v>
       </c>
     </row>
     <row r="169" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K169" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M169" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="170" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K170" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="M170" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="171" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K171" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="M169" s="1" t="s">
+      <c r="M171" s="1" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="171" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B171" s="1" t="s">
+    <row r="173" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B173" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="K171" s="1" t="s">
+      <c r="K173" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="M171" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="172" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K172" s="1" t="s">
+      <c r="M173" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="174" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K174" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="M172" s="1" t="s">
+      <c r="M174" s="1" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="175" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B175" s="1" t="s">
+    <row r="177" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B177" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="K175" s="1" t="s">
+      <c r="K177" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="M175" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="O175" s="1" t="s">
+      <c r="M177" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O177" s="1" t="s">
         <v>31</v>
-      </c>
-    </row>
-    <row r="176" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K176" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="M176" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="O176" s="1" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="177" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K177" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="M177" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="O177" s="1" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="178" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K178" s="1" t="s">
-        <v>143</v>
+        <v>26</v>
       </c>
       <c r="M178" s="1" t="s">
-        <v>236</v>
+        <v>23</v>
+      </c>
+      <c r="O178" s="1" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="179" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B179" s="1" t="s">
-        <v>234</v>
-      </c>
       <c r="K179" s="1" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="M179" s="1" t="s">
-        <v>235</v>
+        <v>23</v>
+      </c>
+      <c r="O179" s="1" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="180" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K180" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="M180" s="1" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="181" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B181" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="K181" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M181" s="1" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="182" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K182" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="M180" s="1" t="s">
+      <c r="M182" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="184" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B184" s="1" t="s">
+    <row r="186" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B186" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="G184" s="1" t="s">
+      <c r="G186" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="K184" s="1" t="s">
+      <c r="K186" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="M184" s="1" t="s">
+      <c r="M186" s="1" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="185" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K185" s="1" t="s">
+    <row r="187" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K187" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="M185" s="1" t="s">
+      <c r="M187" s="1" t="s">
         <v>96</v>
       </c>
     </row>

--- a/Config/Datas/__beans__.xlsx
+++ b/Config/Datas/__beans__.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{013C9223-C6E3-411C-9157-F3B1BB815266}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECAC5806-CD99-4B7A-A071-AFE071828FB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4040,10 +4040,10 @@
     </row>
     <row r="160" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K160" s="1" t="s">
-        <v>134</v>
+        <v>68</v>
       </c>
       <c r="M160" s="1" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
     </row>
     <row r="161" spans="2:15" x14ac:dyDescent="0.2">

--- a/Config/Datas/__beans__.xlsx
+++ b/Config/Datas/__beans__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECAC5806-CD99-4B7A-A071-AFE071828FB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3AFDDF7-99C8-4CC9-91E3-EC05B75A7DAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="254">
   <si>
     <t>##var</t>
   </si>
@@ -1001,6 +1001,30 @@
   </si>
   <si>
     <t>Condition_位于首尾</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>BuffData</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>costEvent</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>isStackable</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GA_获得Buff</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>buffID</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GA_减少Buff</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1428,7 +1452,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q187"/>
+  <dimension ref="A1:Q194"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="28.75" customWidth="1"/>
@@ -4235,6 +4259,49 @@
         <v>96</v>
       </c>
     </row>
+    <row r="190" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B190" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="K190" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="M190" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="191" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K191" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M191" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="192" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K192" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M192" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="193" spans="11:13" x14ac:dyDescent="0.2">
+      <c r="K193" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="M193" s="6" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="194" spans="11:13" x14ac:dyDescent="0.2">
+      <c r="K194" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="M194" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="K1:Q1"/>
@@ -4247,7 +4314,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EECC075D-9730-41E5-B97E-C301603D1E48}">
-  <dimension ref="A1:Q68"/>
+  <dimension ref="A1:Q72"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="27.375" customWidth="1"/>
@@ -4966,6 +5033,50 @@
       <c r="C68" s="1"/>
       <c r="K68" s="1"/>
       <c r="M68" s="1"/>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B69" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="K69" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="M69" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="K70" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="M70" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B71" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="K71" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="M71" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="K72" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="M72" s="1" t="s">
+        <v>128</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/Config/Datas/__beans__.xlsx
+++ b/Config/Datas/__beans__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3AFDDF7-99C8-4CC9-91E3-EC05B75A7DAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{168469D7-EA84-4E52-9678-311B4AD7F1A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="256">
   <si>
     <t>##var</t>
   </si>
@@ -1025,6 +1025,14 @@
   </si>
   <si>
     <t>GA_减少Buff</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>timeCost</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>时间消耗</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1452,7 +1460,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q194"/>
+  <dimension ref="A1:Q198"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="28.75" customWidth="1"/>
@@ -2188,130 +2196,68 @@
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A32" s="6"/>
+      <c r="K32" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="M32" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="O32" s="6" t="s">
+        <v>255</v>
+      </c>
       <c r="Q32" s="6"/>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A33" s="6"/>
-      <c r="B33" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="C33" s="6"/>
-      <c r="D33" s="6"/>
-      <c r="E33" s="6"/>
-      <c r="F33" s="6"/>
-      <c r="G33" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="H33" s="6"/>
-      <c r="I33" s="6"/>
-      <c r="J33" s="6"/>
-      <c r="K33" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L33" s="6"/>
-      <c r="M33" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="N33" s="6"/>
-      <c r="O33" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="P33" s="6"/>
+      <c r="K33" s="1"/>
+      <c r="M33" s="5"/>
+      <c r="O33" s="6"/>
       <c r="Q33" s="6"/>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A34" s="6"/>
-      <c r="B34" s="6"/>
-      <c r="C34" s="6"/>
-      <c r="D34" s="6"/>
-      <c r="E34" s="6"/>
-      <c r="F34" s="6"/>
-      <c r="G34" s="6"/>
-      <c r="H34" s="6"/>
-      <c r="I34" s="6"/>
-      <c r="J34" s="6"/>
-      <c r="K34" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="L34" s="6"/>
-      <c r="M34" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="N34" s="6"/>
-      <c r="O34" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="P34" s="6"/>
+      <c r="K34" s="1"/>
+      <c r="M34" s="5"/>
+      <c r="O34" s="6"/>
       <c r="Q34" s="6"/>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A35" s="6"/>
-      <c r="B35" s="6"/>
-      <c r="C35" s="6"/>
-      <c r="D35" s="6"/>
-      <c r="E35" s="6"/>
-      <c r="F35" s="6"/>
-      <c r="G35" s="6"/>
-      <c r="H35" s="6"/>
-      <c r="I35" s="6"/>
-      <c r="J35" s="6"/>
-      <c r="K35" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="M35" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="O35" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="P35" s="6"/>
+      <c r="K35" s="1"/>
+      <c r="M35" s="5"/>
+      <c r="O35" s="6"/>
       <c r="Q35" s="6"/>
     </row>
-    <row r="36" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A36" s="6"/>
-      <c r="B36" s="5"/>
-      <c r="C36" s="6"/>
-      <c r="D36" s="6"/>
-      <c r="E36" s="6"/>
-      <c r="F36" s="6"/>
-      <c r="G36" s="6"/>
-      <c r="H36" s="6"/>
-      <c r="I36" s="6"/>
-      <c r="J36" s="5"/>
-      <c r="K36" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="L36" s="6"/>
-      <c r="M36" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="N36" s="6"/>
-      <c r="O36" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="P36" s="6"/>
       <c r="Q36" s="6"/>
     </row>
-    <row r="37" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A37" s="6"/>
-      <c r="B37" s="5"/>
+      <c r="B37" s="6" t="s">
+        <v>45</v>
+      </c>
       <c r="C37" s="6"/>
       <c r="D37" s="6"/>
       <c r="E37" s="6"/>
       <c r="F37" s="6"/>
-      <c r="G37" s="6"/>
+      <c r="G37" s="6" t="s">
+        <v>48</v>
+      </c>
       <c r="H37" s="6"/>
       <c r="I37" s="6"/>
-      <c r="J37" s="5"/>
+      <c r="J37" s="6"/>
       <c r="K37" s="5" t="s">
-        <v>243</v>
+        <v>25</v>
       </c>
       <c r="L37" s="6"/>
       <c r="M37" s="5" t="s">
-        <v>112</v>
+        <v>23</v>
       </c>
       <c r="N37" s="6"/>
-      <c r="O37" s="6"/>
+      <c r="O37" s="6" t="s">
+        <v>31</v>
+      </c>
       <c r="P37" s="6"/>
       <c r="Q37" s="6"/>
     </row>
@@ -2327,7 +2273,7 @@
       <c r="I38" s="6"/>
       <c r="J38" s="6"/>
       <c r="K38" s="5" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="L38" s="6"/>
       <c r="M38" s="5" t="s">
@@ -2335,86 +2281,128 @@
       </c>
       <c r="N38" s="6"/>
       <c r="O38" s="6" t="s">
-        <v>132</v>
+        <v>46</v>
       </c>
       <c r="P38" s="6"/>
       <c r="Q38" s="6"/>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A39" s="6"/>
+      <c r="B39" s="6"/>
+      <c r="C39" s="6"/>
+      <c r="D39" s="6"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="6"/>
+      <c r="G39" s="6"/>
+      <c r="H39" s="6"/>
+      <c r="I39" s="6"/>
+      <c r="J39" s="6"/>
+      <c r="K39" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="M39" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="O39" s="6" t="s">
+        <v>47</v>
+      </c>
       <c r="P39" s="6"/>
       <c r="Q39" s="6"/>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="6"/>
-      <c r="B40" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="G40" s="1" t="s">
-        <v>146</v>
-      </c>
+      <c r="B40" s="5"/>
+      <c r="C40" s="6"/>
+      <c r="D40" s="6"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="6"/>
+      <c r="G40" s="6"/>
+      <c r="H40" s="6"/>
+      <c r="I40" s="6"/>
+      <c r="J40" s="5"/>
       <c r="K40" s="5" t="s">
-        <v>25</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="L40" s="6"/>
       <c r="M40" s="5" t="s">
-        <v>23</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="N40" s="6"/>
       <c r="O40" s="6" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="P40" s="6"/>
       <c r="Q40" s="6"/>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="6"/>
+      <c r="B41" s="5"/>
+      <c r="C41" s="6"/>
+      <c r="D41" s="6"/>
+      <c r="E41" s="6"/>
+      <c r="F41" s="6"/>
+      <c r="G41" s="6"/>
+      <c r="H41" s="6"/>
+      <c r="I41" s="6"/>
+      <c r="J41" s="5"/>
       <c r="K41" s="5" t="s">
-        <v>26</v>
-      </c>
+        <v>243</v>
+      </c>
+      <c r="L41" s="6"/>
       <c r="M41" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="O41" s="6" t="s">
-        <v>148</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="N41" s="6"/>
+      <c r="O41" s="6"/>
       <c r="P41" s="6"/>
       <c r="Q41" s="6"/>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A42" s="6"/>
+      <c r="B42" s="6"/>
+      <c r="C42" s="6"/>
+      <c r="D42" s="6"/>
+      <c r="E42" s="6"/>
+      <c r="F42" s="6"/>
+      <c r="G42" s="6"/>
+      <c r="H42" s="6"/>
+      <c r="I42" s="6"/>
+      <c r="J42" s="6"/>
       <c r="K42" s="5" t="s">
-        <v>41</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="L42" s="6"/>
       <c r="M42" s="5" t="s">
         <v>23</v>
       </c>
+      <c r="N42" s="6"/>
       <c r="O42" s="6" t="s">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="P42" s="6"/>
       <c r="Q42" s="6"/>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A43" s="6"/>
-      <c r="K43" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="M43" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="O43" s="6"/>
       <c r="P43" s="6"/>
       <c r="Q43" s="6"/>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A44" s="6"/>
+      <c r="B44" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>146</v>
+      </c>
       <c r="K44" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="M44" s="1" t="s">
-        <v>103</v>
+        <v>25</v>
+      </c>
+      <c r="M44" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>149</v>
+        <v>31</v>
       </c>
       <c r="P44" s="6"/>
       <c r="Q44" s="6"/>
@@ -2422,13 +2410,13 @@
     <row r="45" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A45" s="6"/>
       <c r="K45" s="5" t="s">
-        <v>154</v>
+        <v>26</v>
       </c>
       <c r="M45" s="5" t="s">
         <v>23</v>
       </c>
       <c r="O45" s="6" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="P45" s="6"/>
       <c r="Q45" s="6"/>
@@ -2436,13 +2424,13 @@
     <row r="46" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A46" s="6"/>
       <c r="K46" s="5" t="s">
-        <v>155</v>
+        <v>41</v>
       </c>
       <c r="M46" s="5" t="s">
-        <v>153</v>
+        <v>23</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="P46" s="6"/>
       <c r="Q46" s="6"/>
@@ -2450,259 +2438,221 @@
     <row r="47" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A47" s="6"/>
       <c r="K47" s="5" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="M47" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="O47" s="6" t="s">
-        <v>156</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="O47" s="6"/>
       <c r="P47" s="6"/>
       <c r="Q47" s="6"/>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A48" s="6"/>
+      <c r="K48" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="M48" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="O48" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="P48" s="6"/>
+      <c r="Q48" s="6"/>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A49" s="6"/>
+      <c r="K49" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="M49" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="O49" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="P49" s="6"/>
       <c r="Q49" s="6"/>
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A50" s="6"/>
+      <c r="K50" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="M50" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="O50" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="P50" s="6"/>
       <c r="Q50" s="6"/>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A51" s="6"/>
-      <c r="B51" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C51" s="6"/>
-      <c r="D51" s="6"/>
-      <c r="E51" s="6"/>
-      <c r="F51" s="6"/>
-      <c r="G51" s="6"/>
-      <c r="H51" s="6"/>
-      <c r="I51" s="6"/>
-      <c r="J51" s="6"/>
-      <c r="K51" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="M51" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="N51" s="6"/>
+      <c r="K51" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="M51" s="5" t="s">
+        <v>153</v>
+      </c>
       <c r="O51" s="6" t="s">
-        <v>72</v>
+        <v>156</v>
       </c>
       <c r="P51" s="6"/>
       <c r="Q51" s="6"/>
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A52" s="6"/>
-      <c r="K52" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="L52" s="6"/>
-      <c r="M52" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="P52" s="6"/>
-      <c r="Q52" s="6"/>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A53" s="6"/>
-      <c r="K53" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="M53" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="P53" s="7"/>
       <c r="Q53" s="6"/>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A54" s="6"/>
-      <c r="K54" s="5"/>
-      <c r="M54" s="5"/>
-      <c r="P54" s="7"/>
       <c r="Q54" s="6"/>
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A55" s="6"/>
-      <c r="B55" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="K55" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="M55" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="P55" s="7"/>
+      <c r="B55" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C55" s="6"/>
+      <c r="D55" s="6"/>
+      <c r="E55" s="6"/>
+      <c r="F55" s="6"/>
+      <c r="G55" s="6"/>
+      <c r="H55" s="6"/>
+      <c r="I55" s="6"/>
+      <c r="J55" s="6"/>
+      <c r="K55" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="M55" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="N55" s="6"/>
+      <c r="O55" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="P55" s="6"/>
       <c r="Q55" s="6"/>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A56" s="6"/>
-      <c r="K56" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="M56" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="P56" s="7"/>
+      <c r="K56" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="L56" s="6"/>
+      <c r="M56" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="P56" s="6"/>
       <c r="Q56" s="6"/>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A57" s="6"/>
       <c r="K57" s="5" t="s">
-        <v>33</v>
+        <v>68</v>
       </c>
       <c r="M57" s="5" t="s">
-        <v>163</v>
+        <v>62</v>
       </c>
       <c r="P57" s="7"/>
       <c r="Q57" s="6"/>
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A58" s="6"/>
-      <c r="K58" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="M58" s="6" t="s">
-        <v>66</v>
-      </c>
+      <c r="K58" s="5"/>
+      <c r="M58" s="5"/>
       <c r="P58" s="7"/>
       <c r="Q58" s="6"/>
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A59" s="6"/>
-      <c r="K59" s="5"/>
-      <c r="M59" s="5"/>
+      <c r="B59" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="K59" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="M59" s="5" t="s">
+        <v>23</v>
+      </c>
       <c r="P59" s="7"/>
       <c r="Q59" s="6"/>
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A60" s="6"/>
+      <c r="K60" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="M60" s="5" t="s">
+        <v>23</v>
+      </c>
       <c r="P60" s="7"/>
       <c r="Q60" s="6"/>
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A61" s="6"/>
-      <c r="B61" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="C61" s="6"/>
-      <c r="D61" s="6"/>
-      <c r="E61" s="6"/>
-      <c r="F61" s="6"/>
-      <c r="G61" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="H61" s="6"/>
-      <c r="I61" s="6"/>
-      <c r="J61" s="5"/>
-      <c r="K61" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="L61" s="6"/>
-      <c r="M61" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="N61" s="9"/>
-      <c r="O61" s="6"/>
-      <c r="P61" s="6"/>
+      <c r="K61" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="M61" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="P61" s="7"/>
       <c r="Q61" s="6"/>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A62" s="6"/>
-      <c r="B62" s="6"/>
-      <c r="C62" s="6"/>
-      <c r="D62" s="6"/>
-      <c r="E62" s="6"/>
-      <c r="F62" s="6"/>
-      <c r="G62" s="6"/>
-      <c r="H62" s="6"/>
-      <c r="I62" s="6"/>
-      <c r="J62" s="6"/>
-      <c r="K62" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="L62" s="6"/>
-      <c r="M62" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="N62" s="9"/>
-      <c r="O62" s="6"/>
-      <c r="P62" s="6"/>
+      <c r="K62" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="M62" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="P62" s="7"/>
       <c r="Q62" s="6"/>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A63" s="6"/>
-      <c r="B63" s="6"/>
-      <c r="C63" s="6"/>
-      <c r="D63" s="6"/>
-      <c r="E63" s="6"/>
-      <c r="F63" s="6"/>
-      <c r="G63" s="6"/>
-      <c r="H63" s="6"/>
-      <c r="J63" s="6"/>
-      <c r="K63" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="L63" s="6"/>
-      <c r="M63" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="N63" s="9"/>
-      <c r="O63" s="6"/>
-      <c r="P63" s="6"/>
+      <c r="K63" s="5"/>
+      <c r="M63" s="5"/>
+      <c r="P63" s="7"/>
       <c r="Q63" s="6"/>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A64" s="6"/>
-      <c r="B64" s="6"/>
-      <c r="C64" s="6"/>
-      <c r="D64" s="6"/>
-      <c r="E64" s="6"/>
-      <c r="F64" s="6"/>
-      <c r="G64" s="6"/>
-      <c r="H64" s="6"/>
-      <c r="I64" s="6"/>
-      <c r="J64" s="6"/>
-      <c r="K64" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="M64" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="N64" s="9"/>
-      <c r="O64" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="P64" s="6"/>
+      <c r="P64" s="7"/>
       <c r="Q64" s="6"/>
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A65" s="6"/>
-      <c r="B65" s="6"/>
+      <c r="B65" s="5" t="s">
+        <v>73</v>
+      </c>
       <c r="C65" s="6"/>
       <c r="D65" s="6"/>
       <c r="E65" s="6"/>
       <c r="F65" s="6"/>
-      <c r="G65" s="6"/>
+      <c r="G65" s="6" t="s">
+        <v>70</v>
+      </c>
       <c r="H65" s="6"/>
       <c r="I65" s="6"/>
-      <c r="J65" s="6"/>
+      <c r="J65" s="5"/>
       <c r="K65" s="8" t="s">
-        <v>168</v>
+        <v>25</v>
       </c>
       <c r="L65" s="6"/>
       <c r="M65" s="8" t="s">
-        <v>167</v>
-      </c>
-      <c r="N65" s="6"/>
-      <c r="O65" s="8"/>
+        <v>23</v>
+      </c>
+      <c r="N65" s="9"/>
+      <c r="O65" s="6"/>
       <c r="P65" s="6"/>
       <c r="Q65" s="6"/>
     </row>
@@ -2717,33 +2667,43 @@
       <c r="H66" s="6"/>
       <c r="I66" s="6"/>
       <c r="J66" s="6"/>
-      <c r="N66" s="6"/>
+      <c r="K66" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="L66" s="6"/>
+      <c r="M66" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="N66" s="9"/>
       <c r="O66" s="6"/>
       <c r="P66" s="6"/>
       <c r="Q66" s="6"/>
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A67" s="6"/>
-      <c r="B67" s="5"/>
+      <c r="B67" s="6"/>
       <c r="C67" s="6"/>
       <c r="D67" s="6"/>
       <c r="E67" s="6"/>
       <c r="F67" s="6"/>
       <c r="G67" s="6"/>
       <c r="H67" s="6"/>
-      <c r="I67" s="6"/>
       <c r="J67" s="6"/>
-      <c r="K67" s="2"/>
-      <c r="M67" s="2"/>
-      <c r="O67" s="2"/>
+      <c r="K67" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="L67" s="6"/>
+      <c r="M67" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="N67" s="9"/>
+      <c r="O67" s="6"/>
       <c r="P67" s="6"/>
       <c r="Q67" s="6"/>
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A68" s="6"/>
-      <c r="B68" s="6" t="s">
-        <v>79</v>
-      </c>
+      <c r="B68" s="6"/>
       <c r="C68" s="6"/>
       <c r="D68" s="6"/>
       <c r="E68" s="6"/>
@@ -2752,14 +2712,15 @@
       <c r="H68" s="6"/>
       <c r="I68" s="6"/>
       <c r="J68" s="6"/>
-      <c r="K68" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="M68" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="O68" s="11" t="s">
-        <v>81</v>
+      <c r="K68" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="M68" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="N68" s="9"/>
+      <c r="O68" s="6" t="s">
+        <v>63</v>
       </c>
       <c r="P68" s="6"/>
       <c r="Q68" s="6"/>
@@ -2775,63 +2736,72 @@
       <c r="H69" s="6"/>
       <c r="I69" s="6"/>
       <c r="J69" s="6"/>
-      <c r="K69" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="M69" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="O69" s="11" t="s">
-        <v>80</v>
-      </c>
+      <c r="K69" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="L69" s="6"/>
+      <c r="M69" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="N69" s="6"/>
+      <c r="O69" s="8"/>
       <c r="P69" s="6"/>
       <c r="Q69" s="6"/>
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A70" s="6"/>
+      <c r="B70" s="6"/>
+      <c r="C70" s="6"/>
+      <c r="D70" s="6"/>
+      <c r="E70" s="6"/>
+      <c r="F70" s="6"/>
+      <c r="G70" s="6"/>
       <c r="H70" s="6"/>
       <c r="I70" s="6"/>
       <c r="J70" s="6"/>
-      <c r="K70" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="M70" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="O70" s="11" t="s">
-        <v>86</v>
-      </c>
+      <c r="N70" s="6"/>
+      <c r="O70" s="6"/>
       <c r="P70" s="6"/>
       <c r="Q70" s="6"/>
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A71" s="6"/>
+      <c r="B71" s="5"/>
+      <c r="C71" s="6"/>
+      <c r="D71" s="6"/>
+      <c r="E71" s="6"/>
+      <c r="F71" s="6"/>
+      <c r="G71" s="6"/>
       <c r="H71" s="6"/>
       <c r="I71" s="6"/>
       <c r="J71" s="6"/>
-      <c r="K71" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="M71" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="N71" s="6"/>
-      <c r="O71" s="6" t="s">
-        <v>85</v>
-      </c>
+      <c r="K71" s="2"/>
+      <c r="M71" s="2"/>
+      <c r="O71" s="2"/>
       <c r="P71" s="6"/>
       <c r="Q71" s="6"/>
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A72" s="6"/>
+      <c r="B72" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C72" s="6"/>
+      <c r="D72" s="6"/>
+      <c r="E72" s="6"/>
+      <c r="F72" s="6"/>
+      <c r="G72" s="6"/>
+      <c r="H72" s="6"/>
+      <c r="I72" s="6"/>
+      <c r="J72" s="6"/>
       <c r="K72" s="11" t="s">
-        <v>144</v>
-      </c>
-      <c r="M72" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="M72" s="11" t="s">
         <v>23</v>
       </c>
       <c r="O72" s="11" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="P72" s="6"/>
       <c r="Q72" s="6"/>
@@ -2844,162 +2814,144 @@
       <c r="E73" s="6"/>
       <c r="F73" s="6"/>
       <c r="G73" s="6"/>
+      <c r="H73" s="6"/>
+      <c r="I73" s="6"/>
+      <c r="J73" s="6"/>
       <c r="K73" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="M73" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="O73" s="11"/>
+        <v>26</v>
+      </c>
+      <c r="M73" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="O73" s="11" t="s">
+        <v>80</v>
+      </c>
       <c r="P73" s="6"/>
       <c r="Q73" s="6"/>
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A74" s="6"/>
-      <c r="K74" s="11"/>
-      <c r="M74" s="11"/>
-      <c r="O74" s="11"/>
+      <c r="H74" s="6"/>
+      <c r="I74" s="6"/>
+      <c r="J74" s="6"/>
+      <c r="K74" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M74" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O74" s="11" t="s">
+        <v>86</v>
+      </c>
       <c r="P74" s="6"/>
-      <c r="Q74" s="7"/>
+      <c r="Q74" s="6"/>
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A75" s="6"/>
+      <c r="H75" s="6"/>
+      <c r="I75" s="6"/>
+      <c r="J75" s="6"/>
+      <c r="K75" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="M75" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="N75" s="6"/>
+      <c r="O75" s="6" t="s">
+        <v>85</v>
+      </c>
       <c r="P75" s="6"/>
       <c r="Q75" s="6"/>
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A76" s="6"/>
-      <c r="B76" s="6"/>
-      <c r="C76" s="6"/>
-      <c r="D76" s="6"/>
-      <c r="E76" s="6"/>
-      <c r="F76" s="6"/>
-      <c r="G76" s="6"/>
-      <c r="K76" s="1"/>
-      <c r="M76" s="1"/>
-      <c r="O76" s="1"/>
-      <c r="P76" s="7"/>
+      <c r="K76" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="M76" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O76" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="P76" s="6"/>
       <c r="Q76" s="6"/>
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A77" s="6"/>
-      <c r="B77" s="1" t="s">
-        <v>82</v>
-      </c>
+      <c r="B77" s="6"/>
+      <c r="C77" s="6"/>
+      <c r="D77" s="6"/>
+      <c r="E77" s="6"/>
+      <c r="F77" s="6"/>
+      <c r="G77" s="6"/>
       <c r="K77" s="11" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="M77" s="1" t="s">
-        <v>112</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="O77" s="11"/>
       <c r="P77" s="6"/>
       <c r="Q77" s="6"/>
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A78" s="5"/>
-      <c r="B78" s="6"/>
-      <c r="C78" s="6"/>
-      <c r="K78" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="M78" s="1" t="s">
-        <v>66</v>
-      </c>
+      <c r="A78" s="6"/>
+      <c r="K78" s="11"/>
+      <c r="M78" s="11"/>
+      <c r="O78" s="11"/>
       <c r="P78" s="6"/>
-      <c r="Q78" s="6"/>
+      <c r="Q78" s="7"/>
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A79" s="6"/>
-      <c r="C79" s="6"/>
-      <c r="D79" s="6"/>
-      <c r="E79" s="6"/>
-      <c r="F79" s="6"/>
-      <c r="G79" s="6"/>
-      <c r="H79" s="6"/>
-      <c r="I79" s="6"/>
-      <c r="J79" s="6"/>
-      <c r="K79" s="6"/>
-      <c r="L79" s="6"/>
-      <c r="M79" s="6"/>
-      <c r="N79" s="6"/>
-      <c r="O79" s="6"/>
       <c r="P79" s="6"/>
       <c r="Q79" s="6"/>
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A80" s="6"/>
-      <c r="B80" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="C80" s="5"/>
+      <c r="B80" s="6"/>
+      <c r="C80" s="6"/>
       <c r="D80" s="6"/>
       <c r="E80" s="6"/>
       <c r="F80" s="6"/>
       <c r="G80" s="6"/>
-      <c r="H80" s="6"/>
-      <c r="I80" s="6"/>
-      <c r="J80" s="8"/>
-      <c r="K80" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L80" s="6"/>
-      <c r="M80" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N80" s="6"/>
-      <c r="O80" s="6"/>
-      <c r="P80" s="6"/>
+      <c r="K80" s="1"/>
+      <c r="M80" s="1"/>
+      <c r="O80" s="1"/>
+      <c r="P80" s="7"/>
       <c r="Q80" s="6"/>
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A81" s="6"/>
-      <c r="B81" s="8"/>
-      <c r="C81" s="5"/>
-      <c r="D81" s="6"/>
-      <c r="E81" s="6"/>
-      <c r="F81" s="6"/>
-      <c r="G81" s="6"/>
-      <c r="H81" s="6"/>
-      <c r="I81" s="6"/>
-      <c r="J81" s="8"/>
-      <c r="K81" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="L81" s="6"/>
-      <c r="M81" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="N81" s="6"/>
-      <c r="O81" s="5"/>
+      <c r="B81" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="K81" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="M81" s="1" t="s">
+        <v>112</v>
+      </c>
       <c r="P81" s="6"/>
       <c r="Q81" s="6"/>
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A82" s="6"/>
+      <c r="A82" s="5"/>
       <c r="B82" s="6"/>
       <c r="C82" s="6"/>
-      <c r="D82" s="6"/>
-      <c r="E82" s="6"/>
-      <c r="F82" s="6"/>
-      <c r="G82" s="6"/>
-      <c r="H82" s="6"/>
-      <c r="I82" s="6"/>
-      <c r="J82" s="6"/>
-      <c r="K82" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="L82" s="6"/>
-      <c r="M82" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="N82" s="7"/>
-      <c r="O82" s="5"/>
-      <c r="P82" s="7"/>
+      <c r="K82" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="M82" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="P82" s="6"/>
       <c r="Q82" s="6"/>
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A83" s="6"/>
-      <c r="B83" s="6"/>
       <c r="C83" s="6"/>
       <c r="D83" s="6"/>
       <c r="E83" s="6"/>
@@ -3008,19 +2960,19 @@
       <c r="H83" s="6"/>
       <c r="I83" s="6"/>
       <c r="J83" s="6"/>
-      <c r="K83" s="5" t="s">
-        <v>93</v>
-      </c>
+      <c r="K83" s="6"/>
       <c r="L83" s="6"/>
-      <c r="M83" s="5" t="s">
-        <v>94</v>
-      </c>
+      <c r="M83" s="6"/>
       <c r="N83" s="6"/>
+      <c r="O83" s="6"/>
       <c r="P83" s="6"/>
       <c r="Q83" s="6"/>
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B84" s="8"/>
+      <c r="A84" s="6"/>
+      <c r="B84" s="8" t="s">
+        <v>89</v>
+      </c>
       <c r="C84" s="5"/>
       <c r="D84" s="6"/>
       <c r="E84" s="6"/>
@@ -3030,16 +2982,19 @@
       <c r="I84" s="6"/>
       <c r="J84" s="8"/>
       <c r="K84" s="6" t="s">
-        <v>95</v>
+        <v>25</v>
       </c>
       <c r="L84" s="6"/>
       <c r="M84" s="6" t="s">
-        <v>96</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="N84" s="6"/>
+      <c r="O84" s="6"/>
       <c r="P84" s="6"/>
       <c r="Q84" s="6"/>
     </row>
     <row r="85" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A85" s="6"/>
       <c r="B85" s="8"/>
       <c r="C85" s="5"/>
       <c r="D85" s="6"/>
@@ -3050,201 +3005,251 @@
       <c r="I85" s="6"/>
       <c r="J85" s="8"/>
       <c r="K85" s="5" t="s">
-        <v>102</v>
+        <v>26</v>
       </c>
       <c r="L85" s="6"/>
       <c r="M85" s="5" t="s">
-        <v>103</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="N85" s="6"/>
+      <c r="O85" s="5"/>
       <c r="P85" s="6"/>
       <c r="Q85" s="6"/>
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B86" s="1"/>
-      <c r="G86" s="1"/>
+      <c r="A86" s="6"/>
+      <c r="B86" s="6"/>
+      <c r="C86" s="6"/>
+      <c r="D86" s="6"/>
+      <c r="E86" s="6"/>
+      <c r="F86" s="6"/>
+      <c r="G86" s="6"/>
       <c r="H86" s="6"/>
       <c r="I86" s="6"/>
-      <c r="J86" s="8"/>
-      <c r="K86" s="5"/>
+      <c r="J86" s="6"/>
+      <c r="K86" s="5" t="s">
+        <v>41</v>
+      </c>
       <c r="L86" s="6"/>
-      <c r="M86" s="5"/>
+      <c r="M86" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="N86" s="7"/>
+      <c r="O86" s="5"/>
       <c r="P86" s="7"/>
       <c r="Q86" s="6"/>
     </row>
     <row r="87" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A87" s="6"/>
+      <c r="B87" s="6"/>
+      <c r="C87" s="6"/>
+      <c r="D87" s="6"/>
+      <c r="E87" s="6"/>
+      <c r="F87" s="6"/>
+      <c r="G87" s="6"/>
       <c r="H87" s="6"/>
       <c r="I87" s="6"/>
-      <c r="J87" s="8"/>
-      <c r="K87" s="5"/>
+      <c r="J87" s="6"/>
+      <c r="K87" s="5" t="s">
+        <v>93</v>
+      </c>
       <c r="L87" s="6"/>
-      <c r="M87" s="5"/>
-      <c r="O87" s="5"/>
-      <c r="P87" s="7"/>
+      <c r="M87" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="N87" s="6"/>
+      <c r="P87" s="6"/>
       <c r="Q87" s="6"/>
     </row>
     <row r="88" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B88" s="1" t="s">
+      <c r="B88" s="8"/>
+      <c r="C88" s="5"/>
+      <c r="D88" s="6"/>
+      <c r="E88" s="6"/>
+      <c r="F88" s="6"/>
+      <c r="G88" s="6"/>
+      <c r="H88" s="6"/>
+      <c r="I88" s="6"/>
+      <c r="J88" s="8"/>
+      <c r="K88" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="L88" s="6"/>
+      <c r="M88" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="P88" s="6"/>
+      <c r="Q88" s="6"/>
+    </row>
+    <row r="89" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="B89" s="8"/>
+      <c r="C89" s="5"/>
+      <c r="D89" s="6"/>
+      <c r="E89" s="6"/>
+      <c r="F89" s="6"/>
+      <c r="G89" s="6"/>
+      <c r="H89" s="6"/>
+      <c r="I89" s="6"/>
+      <c r="J89" s="8"/>
+      <c r="K89" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="L89" s="6"/>
+      <c r="M89" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="P89" s="6"/>
+      <c r="Q89" s="6"/>
+    </row>
+    <row r="90" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="B90" s="1"/>
+      <c r="G90" s="1"/>
+      <c r="H90" s="6"/>
+      <c r="I90" s="6"/>
+      <c r="J90" s="8"/>
+      <c r="K90" s="5"/>
+      <c r="L90" s="6"/>
+      <c r="M90" s="5"/>
+      <c r="P90" s="7"/>
+      <c r="Q90" s="6"/>
+    </row>
+    <row r="91" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="H91" s="6"/>
+      <c r="I91" s="6"/>
+      <c r="J91" s="8"/>
+      <c r="K91" s="5"/>
+      <c r="L91" s="6"/>
+      <c r="M91" s="5"/>
+      <c r="O91" s="5"/>
+      <c r="P91" s="7"/>
+      <c r="Q91" s="6"/>
+    </row>
+    <row r="92" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="B92" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="K88" s="1"/>
-      <c r="M88" s="1"/>
-      <c r="P88" s="7"/>
-      <c r="Q88" s="7"/>
-    </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B89" s="1" t="s">
+      <c r="K92" s="1"/>
+      <c r="M92" s="1"/>
+      <c r="P92" s="7"/>
+      <c r="Q92" s="7"/>
+    </row>
+    <row r="93" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="B93" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C89" s="1" t="s">
+      <c r="C93" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="K89" s="1" t="s">
+      <c r="K93" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="M89" s="1" t="s">
+      <c r="M93" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="P89" s="7"/>
-      <c r="Q89" s="6"/>
-    </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="K90" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="M90" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="O90" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="P90" s="6"/>
-      <c r="Q90" s="6"/>
-    </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A91" s="6"/>
-      <c r="B91" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="C91" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="K91" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="M91" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="N91" s="6"/>
-      <c r="O91" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="P91" s="6"/>
-      <c r="Q91" s="6"/>
-    </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A92" s="6"/>
-      <c r="K92" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="M92" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="N92" s="6"/>
-      <c r="O92" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="P92" s="6"/>
-      <c r="Q92" s="6"/>
-    </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A93" s="6"/>
-      <c r="N93" s="6"/>
       <c r="P93" s="7"/>
       <c r="Q93" s="6"/>
     </row>
     <row r="94" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A94" s="6"/>
-      <c r="N94" s="6"/>
-      <c r="O94" s="5"/>
+      <c r="K94" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="M94" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="O94" s="1" t="s">
+        <v>98</v>
+      </c>
       <c r="P94" s="6"/>
       <c r="Q94" s="6"/>
     </row>
     <row r="95" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A95" s="6"/>
-      <c r="H95" s="6"/>
-      <c r="I95" s="6"/>
-      <c r="J95" s="6"/>
-      <c r="K95" s="5"/>
-      <c r="L95" s="6"/>
-      <c r="M95" s="5"/>
+      <c r="B95" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="K95" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="M95" s="1" t="s">
+        <v>62</v>
+      </c>
       <c r="N95" s="6"/>
-      <c r="O95" s="5"/>
+      <c r="O95" s="1" t="s">
+        <v>98</v>
+      </c>
       <c r="P95" s="6"/>
       <c r="Q95" s="6"/>
     </row>
     <row r="96" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A96" s="6"/>
-      <c r="H96" s="6"/>
-      <c r="I96" s="6"/>
-      <c r="J96" s="6"/>
-      <c r="K96" s="6"/>
-      <c r="L96" s="6"/>
-      <c r="M96" s="6"/>
+      <c r="K96" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="M96" s="1" t="s">
+        <v>62</v>
+      </c>
       <c r="N96" s="6"/>
-      <c r="O96" s="6"/>
+      <c r="O96" s="1" t="s">
+        <v>98</v>
+      </c>
       <c r="P96" s="6"/>
       <c r="Q96" s="6"/>
     </row>
     <row r="97" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A97" s="6"/>
-      <c r="D97" s="6"/>
-      <c r="E97" s="6"/>
-      <c r="F97" s="6"/>
-      <c r="G97" s="6"/>
-      <c r="H97" s="6"/>
-      <c r="I97" s="6"/>
-      <c r="J97" s="8"/>
-      <c r="K97" s="5"/>
-      <c r="L97" s="6"/>
-      <c r="M97" s="5"/>
       <c r="N97" s="6"/>
-      <c r="O97" s="6"/>
-      <c r="P97" s="6"/>
+      <c r="P97" s="7"/>
       <c r="Q97" s="6"/>
     </row>
     <row r="98" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A98" s="6"/>
-      <c r="B98" s="8"/>
-      <c r="C98" s="5"/>
-      <c r="D98" s="6"/>
-      <c r="E98" s="6"/>
-      <c r="F98" s="6"/>
-      <c r="G98" s="6"/>
-      <c r="H98" s="6"/>
-      <c r="I98" s="6"/>
-      <c r="J98" s="8"/>
-      <c r="K98" s="5"/>
-      <c r="L98" s="6"/>
-      <c r="M98" s="5"/>
       <c r="N98" s="6"/>
-      <c r="O98" s="6"/>
+      <c r="O98" s="5"/>
       <c r="P98" s="6"/>
       <c r="Q98" s="6"/>
     </row>
     <row r="99" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A99" s="6"/>
-      <c r="O99" s="6"/>
+      <c r="H99" s="6"/>
+      <c r="I99" s="6"/>
+      <c r="J99" s="6"/>
+      <c r="K99" s="5"/>
+      <c r="L99" s="6"/>
+      <c r="M99" s="5"/>
+      <c r="N99" s="6"/>
+      <c r="O99" s="5"/>
       <c r="P99" s="6"/>
       <c r="Q99" s="6"/>
     </row>
     <row r="100" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A100" s="6"/>
+      <c r="H100" s="6"/>
+      <c r="I100" s="6"/>
+      <c r="J100" s="6"/>
+      <c r="K100" s="6"/>
+      <c r="L100" s="6"/>
+      <c r="M100" s="6"/>
+      <c r="N100" s="6"/>
       <c r="O100" s="6"/>
       <c r="P100" s="6"/>
       <c r="Q100" s="6"/>
     </row>
     <row r="101" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A101" s="6"/>
+      <c r="D101" s="6"/>
+      <c r="E101" s="6"/>
+      <c r="F101" s="6"/>
+      <c r="G101" s="6"/>
+      <c r="H101" s="6"/>
+      <c r="I101" s="6"/>
+      <c r="J101" s="8"/>
+      <c r="K101" s="5"/>
+      <c r="L101" s="6"/>
+      <c r="M101" s="5"/>
+      <c r="N101" s="6"/>
       <c r="O101" s="6"/>
       <c r="P101" s="6"/>
       <c r="Q101" s="6"/>
@@ -3259,7 +3264,7 @@
       <c r="G102" s="6"/>
       <c r="H102" s="6"/>
       <c r="I102" s="6"/>
-      <c r="J102" s="6"/>
+      <c r="J102" s="8"/>
       <c r="K102" s="5"/>
       <c r="L102" s="6"/>
       <c r="M102" s="5"/>
@@ -3270,83 +3275,36 @@
     </row>
     <row r="103" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A103" s="6"/>
-      <c r="B103" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="D103" s="6"/>
-      <c r="E103" s="6"/>
-      <c r="F103" s="6"/>
-      <c r="G103" s="6"/>
-      <c r="H103" s="6"/>
-      <c r="I103" s="6"/>
-      <c r="J103" s="6"/>
-      <c r="K103" s="5"/>
-      <c r="L103" s="6"/>
-      <c r="M103" s="5"/>
-      <c r="N103" s="6"/>
       <c r="O103" s="6"/>
       <c r="P103" s="6"/>
       <c r="Q103" s="6"/>
     </row>
     <row r="104" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A104" s="6"/>
-      <c r="B104" s="1"/>
-      <c r="C104" s="1"/>
-      <c r="K104" s="5"/>
-      <c r="N104" s="6"/>
       <c r="O104" s="6"/>
       <c r="P104" s="6"/>
       <c r="Q104" s="6"/>
     </row>
     <row r="105" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A105" s="6"/>
-      <c r="B105" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="C105" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="D105" s="6"/>
-      <c r="E105" s="6"/>
-      <c r="F105" s="6"/>
-      <c r="G105" s="6"/>
-      <c r="H105" s="6"/>
-      <c r="I105" s="6"/>
-      <c r="J105" s="6"/>
-      <c r="K105" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="L105" s="6"/>
-      <c r="M105" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="N105" s="6"/>
       <c r="O105" s="6"/>
       <c r="P105" s="6"/>
       <c r="Q105" s="6"/>
     </row>
     <row r="106" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A106" s="6"/>
-      <c r="B106" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="C106" s="1" t="s">
-        <v>119</v>
-      </c>
+      <c r="B106" s="8"/>
+      <c r="C106" s="5"/>
       <c r="D106" s="6"/>
       <c r="E106" s="6"/>
       <c r="F106" s="6"/>
       <c r="G106" s="6"/>
       <c r="H106" s="6"/>
       <c r="I106" s="6"/>
-      <c r="J106" s="8"/>
-      <c r="K106" s="5" t="s">
-        <v>122</v>
-      </c>
+      <c r="J106" s="6"/>
+      <c r="K106" s="5"/>
       <c r="L106" s="6"/>
-      <c r="M106" s="5" t="s">
-        <v>112</v>
-      </c>
+      <c r="M106" s="5"/>
       <c r="N106" s="6"/>
       <c r="O106" s="6"/>
       <c r="P106" s="6"/>
@@ -3355,9 +3313,6 @@
     <row r="107" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A107" s="6"/>
       <c r="B107" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="C107" s="1" t="s">
         <v>119</v>
       </c>
       <c r="D107" s="6"/>
@@ -3366,7 +3321,7 @@
       <c r="G107" s="6"/>
       <c r="H107" s="6"/>
       <c r="I107" s="6"/>
-      <c r="J107" s="5"/>
+      <c r="J107" s="6"/>
       <c r="K107" s="5"/>
       <c r="L107" s="6"/>
       <c r="M107" s="5"/>
@@ -3377,18 +3332,9 @@
     </row>
     <row r="108" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A108" s="6"/>
-      <c r="B108" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="C108" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="H108" s="6"/>
-      <c r="I108" s="6"/>
-      <c r="J108" s="6"/>
+      <c r="B108" s="1"/>
+      <c r="C108" s="1"/>
       <c r="K108" s="5"/>
-      <c r="L108" s="6"/>
-      <c r="M108" s="5"/>
       <c r="N108" s="6"/>
       <c r="O108" s="6"/>
       <c r="P108" s="6"/>
@@ -3396,24 +3342,26 @@
     </row>
     <row r="109" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A109" s="6"/>
-      <c r="B109" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="C109" s="6" t="s">
+      <c r="B109" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C109" s="1" t="s">
         <v>119</v>
       </c>
       <c r="D109" s="6"/>
       <c r="E109" s="6"/>
       <c r="F109" s="6"/>
-      <c r="G109" s="6" t="s">
-        <v>130</v>
-      </c>
+      <c r="G109" s="6"/>
       <c r="H109" s="6"/>
       <c r="I109" s="6"/>
       <c r="J109" s="6"/>
-      <c r="K109" s="6"/>
+      <c r="K109" s="5" t="s">
+        <v>174</v>
+      </c>
       <c r="L109" s="6"/>
-      <c r="M109" s="6"/>
+      <c r="M109" s="5" t="s">
+        <v>23</v>
+      </c>
       <c r="N109" s="6"/>
       <c r="O109" s="6"/>
       <c r="P109" s="6"/>
@@ -3421,10 +3369,10 @@
     </row>
     <row r="110" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A110" s="6"/>
-      <c r="B110" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="C110" s="6" t="s">
+      <c r="B110" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C110" s="1" t="s">
         <v>119</v>
       </c>
       <c r="D110" s="6"/>
@@ -3433,21 +3381,25 @@
       <c r="G110" s="6"/>
       <c r="H110" s="6"/>
       <c r="I110" s="6"/>
-      <c r="J110" s="5"/>
-      <c r="K110" s="5"/>
+      <c r="J110" s="8"/>
+      <c r="K110" s="5" t="s">
+        <v>122</v>
+      </c>
       <c r="L110" s="6"/>
-      <c r="M110" s="5"/>
+      <c r="M110" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="N110" s="6"/>
-      <c r="O110" s="1"/>
+      <c r="O110" s="6"/>
       <c r="P110" s="6"/>
       <c r="Q110" s="6"/>
     </row>
     <row r="111" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A111" s="6"/>
-      <c r="B111" s="6" t="s">
-        <v>231</v>
-      </c>
-      <c r="C111" s="6" t="s">
+      <c r="B111" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C111" s="1" t="s">
         <v>119</v>
       </c>
       <c r="D111" s="6"/>
@@ -3456,10 +3408,10 @@
       <c r="G111" s="6"/>
       <c r="H111" s="6"/>
       <c r="I111" s="6"/>
-      <c r="J111" s="6"/>
-      <c r="K111" s="6"/>
+      <c r="J111" s="5"/>
+      <c r="K111" s="5"/>
       <c r="L111" s="6"/>
-      <c r="M111" s="6"/>
+      <c r="M111" s="5"/>
       <c r="N111" s="6"/>
       <c r="O111" s="6"/>
       <c r="P111" s="6"/>
@@ -3467,15 +3419,15 @@
     </row>
     <row r="112" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A112" s="6"/>
-      <c r="B112" s="5"/>
-      <c r="C112" s="5"/>
-      <c r="D112" s="6"/>
-      <c r="E112" s="6"/>
-      <c r="F112" s="6"/>
-      <c r="G112" s="6"/>
+      <c r="B112" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="C112" s="6" t="s">
+        <v>119</v>
+      </c>
       <c r="H112" s="6"/>
       <c r="I112" s="6"/>
-      <c r="J112" s="5"/>
+      <c r="J112" s="6"/>
       <c r="K112" s="5"/>
       <c r="L112" s="6"/>
       <c r="M112" s="5"/>
@@ -3486,18 +3438,24 @@
     </row>
     <row r="113" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A113" s="6"/>
-      <c r="B113" s="5"/>
-      <c r="C113" s="5"/>
+      <c r="B113" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="C113" s="6" t="s">
+        <v>119</v>
+      </c>
       <c r="D113" s="6"/>
       <c r="E113" s="6"/>
       <c r="F113" s="6"/>
-      <c r="G113" s="6"/>
+      <c r="G113" s="6" t="s">
+        <v>130</v>
+      </c>
       <c r="H113" s="6"/>
       <c r="I113" s="6"/>
-      <c r="J113" s="5"/>
-      <c r="K113" s="5"/>
+      <c r="J113" s="6"/>
+      <c r="K113" s="6"/>
       <c r="L113" s="6"/>
-      <c r="M113" s="5"/>
+      <c r="M113" s="6"/>
       <c r="N113" s="6"/>
       <c r="O113" s="6"/>
       <c r="P113" s="6"/>
@@ -3505,10 +3463,12 @@
     </row>
     <row r="114" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A114" s="6"/>
-      <c r="B114" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="C114" s="5"/>
+      <c r="B114" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="C114" s="6" t="s">
+        <v>119</v>
+      </c>
       <c r="D114" s="6"/>
       <c r="E114" s="6"/>
       <c r="F114" s="6"/>
@@ -3516,36 +3476,32 @@
       <c r="H114" s="6"/>
       <c r="I114" s="6"/>
       <c r="J114" s="5"/>
-      <c r="K114" s="5" t="s">
-        <v>25</v>
-      </c>
+      <c r="K114" s="5"/>
       <c r="L114" s="6"/>
-      <c r="M114" s="5" t="s">
-        <v>23</v>
-      </c>
+      <c r="M114" s="5"/>
       <c r="N114" s="6"/>
-      <c r="O114" s="6"/>
+      <c r="O114" s="1"/>
       <c r="P114" s="6"/>
       <c r="Q114" s="6"/>
     </row>
     <row r="115" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A115" s="6"/>
-      <c r="B115" s="5"/>
-      <c r="C115" s="5"/>
+      <c r="B115" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="C115" s="6" t="s">
+        <v>119</v>
+      </c>
       <c r="D115" s="6"/>
       <c r="E115" s="6"/>
       <c r="F115" s="6"/>
       <c r="G115" s="6"/>
       <c r="H115" s="6"/>
       <c r="I115" s="6"/>
-      <c r="J115" s="5"/>
-      <c r="K115" s="5" t="s">
-        <v>26</v>
-      </c>
+      <c r="J115" s="6"/>
+      <c r="K115" s="6"/>
       <c r="L115" s="6"/>
-      <c r="M115" s="5" t="s">
-        <v>23</v>
-      </c>
+      <c r="M115" s="6"/>
       <c r="N115" s="6"/>
       <c r="O115" s="6"/>
       <c r="P115" s="6"/>
@@ -3562,13 +3518,9 @@
       <c r="H116" s="6"/>
       <c r="I116" s="6"/>
       <c r="J116" s="5"/>
-      <c r="K116" s="5" t="s">
-        <v>41</v>
-      </c>
+      <c r="K116" s="5"/>
       <c r="L116" s="6"/>
-      <c r="M116" s="5" t="s">
-        <v>23</v>
-      </c>
+      <c r="M116" s="5"/>
       <c r="N116" s="6"/>
       <c r="O116" s="6"/>
       <c r="P116" s="6"/>
@@ -3585,13 +3537,9 @@
       <c r="H117" s="6"/>
       <c r="I117" s="6"/>
       <c r="J117" s="5"/>
-      <c r="K117" s="5" t="s">
-        <v>43</v>
-      </c>
+      <c r="K117" s="5"/>
       <c r="L117" s="6"/>
-      <c r="M117" s="5" t="s">
-        <v>23</v>
-      </c>
+      <c r="M117" s="5"/>
       <c r="N117" s="6"/>
       <c r="O117" s="6"/>
       <c r="P117" s="6"/>
@@ -3599,17 +3547,19 @@
     </row>
     <row r="118" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A118" s="6"/>
-      <c r="B118" s="6"/>
-      <c r="C118" s="6"/>
+      <c r="B118" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="C118" s="5"/>
       <c r="D118" s="6"/>
       <c r="E118" s="6"/>
       <c r="F118" s="6"/>
       <c r="G118" s="6"/>
       <c r="H118" s="6"/>
       <c r="I118" s="6"/>
-      <c r="J118" s="6"/>
+      <c r="J118" s="5"/>
       <c r="K118" s="5" t="s">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="L118" s="6"/>
       <c r="M118" s="5" t="s">
@@ -3622,20 +3572,21 @@
     </row>
     <row r="119" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A119" s="6"/>
-      <c r="B119" s="6"/>
-      <c r="C119" s="6"/>
+      <c r="B119" s="5"/>
+      <c r="C119" s="5"/>
       <c r="D119" s="6"/>
       <c r="E119" s="6"/>
       <c r="F119" s="6"/>
       <c r="G119" s="6"/>
       <c r="H119" s="6"/>
       <c r="I119" s="6"/>
-      <c r="J119" s="6"/>
-      <c r="K119" s="1" t="s">
-        <v>143</v>
-      </c>
+      <c r="J119" s="5"/>
+      <c r="K119" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="L119" s="6"/>
       <c r="M119" s="5" t="s">
-        <v>241</v>
+        <v>23</v>
       </c>
       <c r="N119" s="6"/>
       <c r="O119" s="6"/>
@@ -3643,8 +3594,8 @@
       <c r="Q119" s="6"/>
     </row>
     <row r="120" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A120" s="5"/>
-      <c r="B120" s="8"/>
+      <c r="A120" s="6"/>
+      <c r="B120" s="5"/>
       <c r="C120" s="5"/>
       <c r="D120" s="6"/>
       <c r="E120" s="6"/>
@@ -3652,21 +3603,22 @@
       <c r="G120" s="6"/>
       <c r="H120" s="6"/>
       <c r="I120" s="6"/>
-      <c r="J120" s="8"/>
-      <c r="K120" s="1" t="s">
-        <v>150</v>
-      </c>
+      <c r="J120" s="5"/>
+      <c r="K120" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="L120" s="6"/>
       <c r="M120" s="5" t="s">
-        <v>103</v>
+        <v>23</v>
       </c>
       <c r="N120" s="6"/>
-      <c r="O120" s="5"/>
+      <c r="O120" s="6"/>
       <c r="P120" s="6"/>
       <c r="Q120" s="6"/>
     </row>
     <row r="121" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A121" s="5"/>
-      <c r="B121" s="8"/>
+      <c r="A121" s="6"/>
+      <c r="B121" s="5"/>
       <c r="C121" s="5"/>
       <c r="D121" s="6"/>
       <c r="E121" s="6"/>
@@ -3674,57 +3626,61 @@
       <c r="G121" s="6"/>
       <c r="H121" s="6"/>
       <c r="I121" s="6"/>
-      <c r="J121" s="8"/>
-      <c r="K121" s="1"/>
-      <c r="M121" s="5"/>
+      <c r="J121" s="5"/>
+      <c r="K121" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="L121" s="6"/>
+      <c r="M121" s="5" t="s">
+        <v>23</v>
+      </c>
       <c r="N121" s="6"/>
-      <c r="O121" s="5"/>
+      <c r="O121" s="6"/>
       <c r="P121" s="6"/>
       <c r="Q121" s="6"/>
     </row>
     <row r="122" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A122" s="5"/>
-      <c r="B122" s="8" t="s">
-        <v>240</v>
-      </c>
-      <c r="C122" s="5"/>
+      <c r="A122" s="6"/>
+      <c r="B122" s="6"/>
+      <c r="C122" s="6"/>
       <c r="D122" s="6"/>
       <c r="E122" s="6"/>
       <c r="F122" s="6"/>
       <c r="G122" s="6"/>
       <c r="H122" s="6"/>
       <c r="I122" s="6"/>
-      <c r="J122" s="8"/>
-      <c r="K122" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="M122" s="1" t="s">
-        <v>242</v>
+      <c r="J122" s="6"/>
+      <c r="K122" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="L122" s="6"/>
+      <c r="M122" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="N122" s="6"/>
-      <c r="O122" s="5"/>
+      <c r="O122" s="6"/>
       <c r="P122" s="6"/>
       <c r="Q122" s="6"/>
     </row>
     <row r="123" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A123" s="5"/>
-      <c r="B123" s="8"/>
-      <c r="C123" s="5"/>
+      <c r="A123" s="6"/>
+      <c r="B123" s="6"/>
+      <c r="C123" s="6"/>
       <c r="D123" s="6"/>
       <c r="E123" s="6"/>
       <c r="F123" s="6"/>
       <c r="G123" s="6"/>
       <c r="H123" s="6"/>
       <c r="I123" s="6"/>
-      <c r="J123" s="8"/>
+      <c r="J123" s="6"/>
       <c r="K123" s="1" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="M123" s="5" t="s">
-        <v>66</v>
+        <v>241</v>
       </c>
       <c r="N123" s="6"/>
-      <c r="O123" s="5"/>
+      <c r="O123" s="6"/>
       <c r="P123" s="6"/>
       <c r="Q123" s="6"/>
     </row>
@@ -3739,53 +3695,105 @@
       <c r="H124" s="6"/>
       <c r="I124" s="6"/>
       <c r="J124" s="8"/>
-      <c r="K124" s="1"/>
-      <c r="M124" s="5"/>
+      <c r="K124" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="M124" s="5" t="s">
+        <v>103</v>
+      </c>
       <c r="N124" s="6"/>
       <c r="O124" s="5"/>
       <c r="P124" s="6"/>
       <c r="Q124" s="6"/>
     </row>
     <row r="125" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A125" s="5"/>
+      <c r="B125" s="8"/>
+      <c r="C125" s="5"/>
+      <c r="D125" s="6"/>
+      <c r="E125" s="6"/>
+      <c r="F125" s="6"/>
+      <c r="G125" s="6"/>
+      <c r="H125" s="6"/>
+      <c r="I125" s="6"/>
+      <c r="J125" s="8"/>
       <c r="K125" s="1"/>
       <c r="M125" s="5"/>
+      <c r="N125" s="6"/>
+      <c r="O125" s="5"/>
+      <c r="P125" s="6"/>
+      <c r="Q125" s="6"/>
     </row>
     <row r="126" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="C126" s="6"/>
+      <c r="A126" s="5"/>
+      <c r="B126" s="8" t="s">
+        <v>240</v>
+      </c>
+      <c r="C126" s="5"/>
       <c r="D126" s="6"/>
       <c r="E126" s="6"/>
       <c r="F126" s="6"/>
       <c r="G126" s="6"/>
       <c r="H126" s="6"/>
       <c r="I126" s="6"/>
-      <c r="J126" s="6"/>
-      <c r="K126" s="5"/>
-      <c r="L126" s="6"/>
-      <c r="M126" s="5"/>
+      <c r="J126" s="8"/>
+      <c r="K126" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M126" s="1" t="s">
+        <v>242</v>
+      </c>
       <c r="N126" s="6"/>
-      <c r="O126" s="6"/>
+      <c r="O126" s="5"/>
+      <c r="P126" s="6"/>
+      <c r="Q126" s="6"/>
     </row>
     <row r="127" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A127" s="5"/>
+      <c r="B127" s="8"/>
+      <c r="C127" s="5"/>
+      <c r="D127" s="6"/>
+      <c r="E127" s="6"/>
+      <c r="F127" s="6"/>
+      <c r="G127" s="6"/>
+      <c r="H127" s="6"/>
+      <c r="I127" s="6"/>
+      <c r="J127" s="8"/>
+      <c r="K127" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="M127" s="5" t="s">
+        <v>66</v>
+      </c>
       <c r="N127" s="6"/>
-      <c r="O127" s="6"/>
+      <c r="O127" s="5"/>
+      <c r="P127" s="6"/>
+      <c r="Q127" s="6"/>
     </row>
     <row r="128" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B128" s="6" t="s">
-        <v>64</v>
-      </c>
+      <c r="A128" s="5"/>
+      <c r="B128" s="8"/>
+      <c r="C128" s="5"/>
+      <c r="D128" s="6"/>
+      <c r="E128" s="6"/>
+      <c r="F128" s="6"/>
+      <c r="G128" s="6"/>
+      <c r="H128" s="6"/>
+      <c r="I128" s="6"/>
+      <c r="J128" s="8"/>
+      <c r="K128" s="1"/>
+      <c r="M128" s="5"/>
       <c r="N128" s="6"/>
+      <c r="O128" s="5"/>
+      <c r="P128" s="6"/>
+      <c r="Q128" s="6"/>
     </row>
     <row r="129" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="N129" s="6"/>
-      <c r="O129" s="6"/>
+      <c r="K129" s="1"/>
+      <c r="M129" s="5"/>
     </row>
     <row r="130" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B130" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="C130" s="6" t="s">
-        <v>64</v>
-      </c>
+      <c r="C130" s="6"/>
       <c r="D130" s="6"/>
       <c r="E130" s="6"/>
       <c r="F130" s="6"/>
@@ -3793,34 +3801,29 @@
       <c r="H130" s="6"/>
       <c r="I130" s="6"/>
       <c r="J130" s="6"/>
-      <c r="K130" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="M130" s="1" t="s">
-        <v>128</v>
-      </c>
+      <c r="K130" s="5"/>
+      <c r="L130" s="6"/>
+      <c r="M130" s="5"/>
       <c r="N130" s="6"/>
       <c r="O130" s="6"/>
     </row>
     <row r="131" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K131" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="M131" s="1" t="s">
-        <v>114</v>
-      </c>
+      <c r="N131" s="6"/>
+      <c r="O131" s="6"/>
     </row>
     <row r="132" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K132" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="M132" s="1" t="s">
-        <v>128</v>
-      </c>
+      <c r="B132" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="N132" s="6"/>
+    </row>
+    <row r="133" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="N133" s="6"/>
+      <c r="O133" s="6"/>
     </row>
     <row r="134" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B134" s="6" t="s">
-        <v>65</v>
+      <c r="B134" s="5" t="s">
+        <v>123</v>
       </c>
       <c r="C134" s="6" t="s">
         <v>64</v>
@@ -3832,207 +3835,215 @@
       <c r="H134" s="6"/>
       <c r="I134" s="6"/>
       <c r="J134" s="6"/>
-      <c r="K134" s="5"/>
-      <c r="L134" s="6"/>
-      <c r="M134" s="5"/>
+      <c r="K134" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="M134" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="N134" s="6"/>
+      <c r="O134" s="6"/>
     </row>
     <row r="135" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B135" s="6"/>
-      <c r="C135" s="6"/>
-      <c r="D135" s="6"/>
-      <c r="E135" s="6"/>
-      <c r="F135" s="6"/>
-      <c r="G135" s="6"/>
-      <c r="H135" s="6"/>
-      <c r="I135" s="6"/>
-      <c r="J135" s="6"/>
-      <c r="K135" s="5"/>
-      <c r="L135" s="6"/>
-      <c r="M135" s="5"/>
+      <c r="K135" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="M135" s="1" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="136" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B136" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="C136" s="6" t="s">
+      <c r="K136" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="M136" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="138" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B138" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C138" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="D136" s="6"/>
-      <c r="E136" s="6"/>
-      <c r="F136" s="6"/>
-      <c r="G136" s="6"/>
-      <c r="H136" s="6"/>
-      <c r="I136" s="6"/>
-      <c r="J136" s="6"/>
-      <c r="K136" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="M136" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="137" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="D137" s="6"/>
-      <c r="E137" s="6"/>
-      <c r="F137" s="6"/>
-      <c r="G137" s="5"/>
-      <c r="H137" s="6"/>
-      <c r="I137" s="6"/>
-      <c r="J137" s="5"/>
-      <c r="K137" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="L137" s="6"/>
-      <c r="M137" s="5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="138" spans="2:15" x14ac:dyDescent="0.2">
       <c r="D138" s="6"/>
       <c r="E138" s="6"/>
       <c r="F138" s="6"/>
-      <c r="G138" s="5"/>
+      <c r="G138" s="6"/>
       <c r="H138" s="6"/>
       <c r="I138" s="6"/>
-      <c r="J138" s="5"/>
+      <c r="J138" s="6"/>
       <c r="K138" s="5"/>
       <c r="L138" s="6"/>
       <c r="M138" s="5"/>
     </row>
     <row r="139" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B139" s="1" t="s">
+      <c r="B139" s="6"/>
+      <c r="C139" s="6"/>
+      <c r="D139" s="6"/>
+      <c r="E139" s="6"/>
+      <c r="F139" s="6"/>
+      <c r="G139" s="6"/>
+      <c r="H139" s="6"/>
+      <c r="I139" s="6"/>
+      <c r="J139" s="6"/>
+      <c r="K139" s="5"/>
+      <c r="L139" s="6"/>
+      <c r="M139" s="5"/>
+    </row>
+    <row r="140" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B140" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="C140" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D140" s="6"/>
+      <c r="E140" s="6"/>
+      <c r="F140" s="6"/>
+      <c r="G140" s="6"/>
+      <c r="H140" s="6"/>
+      <c r="I140" s="6"/>
+      <c r="J140" s="6"/>
+      <c r="K140" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="M140" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="141" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="D141" s="6"/>
+      <c r="E141" s="6"/>
+      <c r="F141" s="6"/>
+      <c r="G141" s="5"/>
+      <c r="H141" s="6"/>
+      <c r="I141" s="6"/>
+      <c r="J141" s="5"/>
+      <c r="K141" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="L141" s="6"/>
+      <c r="M141" s="5" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="142" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="D142" s="6"/>
+      <c r="E142" s="6"/>
+      <c r="F142" s="6"/>
+      <c r="G142" s="5"/>
+      <c r="H142" s="6"/>
+      <c r="I142" s="6"/>
+      <c r="J142" s="5"/>
+      <c r="K142" s="5"/>
+      <c r="L142" s="6"/>
+      <c r="M142" s="5"/>
+    </row>
+    <row r="143" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B143" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="C139" s="6" t="s">
+      <c r="C143" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="K139" s="1" t="s">
+      <c r="K143" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M139" s="1" t="s">
+      <c r="M143" s="1" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="141" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B141" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="K141" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="M141" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="142" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K142" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="M142" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="143" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K143" s="1"/>
     </row>
     <row r="145" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B145" s="1" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="K145" s="1" t="s">
-        <v>25</v>
+        <v>196</v>
       </c>
       <c r="M145" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="O145" s="6"/>
     </row>
     <row r="146" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K146" s="1" t="s">
-        <v>26</v>
+        <v>197</v>
       </c>
       <c r="M146" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="147" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K147" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="M147" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="148" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K148" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="M148" s="1" t="s">
-        <v>198</v>
-      </c>
+      <c r="K147" s="1"/>
     </row>
     <row r="149" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B149" s="1" t="s">
+        <v>206</v>
+      </c>
       <c r="K149" s="1" t="s">
-        <v>199</v>
+        <v>25</v>
       </c>
       <c r="M149" s="1" t="s">
-        <v>112</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="O149" s="6"/>
     </row>
     <row r="150" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K150" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="M150" s="5" t="s">
-        <v>103</v>
+        <v>26</v>
+      </c>
+      <c r="M150" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="151" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B151" s="1" t="s">
-        <v>227</v>
-      </c>
       <c r="K151" s="1" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="M151" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="152" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B152" s="1"/>
       <c r="K152" s="1" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="M152" s="1" t="s">
-        <v>23</v>
+        <v>198</v>
       </c>
     </row>
     <row r="153" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K153" s="1" t="s">
-        <v>41</v>
+        <v>199</v>
       </c>
       <c r="M153" s="1" t="s">
-        <v>23</v>
+        <v>112</v>
       </c>
     </row>
     <row r="154" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K154" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="M154" s="1" t="s">
-        <v>229</v>
+        <v>150</v>
+      </c>
+      <c r="M154" s="5" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="155" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K155" s="1"/>
-      <c r="M155" s="1"/>
+      <c r="B155" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="K155" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="M155" s="1" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="156" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B156" s="1" t="s">
-        <v>230</v>
-      </c>
+      <c r="B156" s="1"/>
       <c r="K156" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M156" s="1" t="s">
         <v>23</v>
@@ -4040,7 +4051,7 @@
     </row>
     <row r="157" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K157" s="1" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="M157" s="1" t="s">
         <v>23</v>
@@ -4048,79 +4059,74 @@
     </row>
     <row r="158" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K158" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="M158" s="1" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="159" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K159" s="1"/>
+      <c r="M159" s="1"/>
+    </row>
+    <row r="160" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B160" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="K160" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="M160" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="161" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K161" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M161" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="162" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K162" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="M158" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="159" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K159" s="1" t="s">
+      <c r="M162" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="163" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K163" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="M159" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="160" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K160" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="M160" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="161" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K161" s="1"/>
-    </row>
-    <row r="163" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B163" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="K163" s="1" t="s">
-        <v>25</v>
-      </c>
       <c r="M163" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="O163" s="1" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="164" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K164" s="1" t="s">
-        <v>26</v>
+        <v>68</v>
       </c>
       <c r="M164" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="O164" s="1" t="s">
-        <v>210</v>
+        <v>71</v>
       </c>
     </row>
     <row r="165" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K165" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="M165" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="O165" s="1" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="166" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K166" s="1"/>
+      <c r="K165" s="1"/>
     </row>
     <row r="167" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B167" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="K167" s="1" t="s">
-        <v>212</v>
+        <v>25</v>
       </c>
       <c r="M167" s="1" t="s">
-        <v>112</v>
+        <v>23</v>
+      </c>
+      <c r="O167" s="1" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="168" spans="2:15" x14ac:dyDescent="0.2">
@@ -4130,6 +4136,9 @@
       <c r="M168" s="1" t="s">
         <v>23</v>
       </c>
+      <c r="O168" s="1" t="s">
+        <v>210</v>
+      </c>
     </row>
     <row r="169" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K169" s="1" t="s">
@@ -4138,29 +4147,35 @@
       <c r="M169" s="1" t="s">
         <v>23</v>
       </c>
+      <c r="O169" s="1" t="s">
+        <v>211</v>
+      </c>
     </row>
     <row r="170" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K170" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="M170" s="1" t="s">
-        <v>103</v>
-      </c>
+      <c r="K170" s="1"/>
     </row>
     <row r="171" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B171" s="1" t="s">
+        <v>208</v>
+      </c>
       <c r="K171" s="1" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="M171" s="1" t="s">
-        <v>217</v>
+        <v>112</v>
+      </c>
+    </row>
+    <row r="172" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K172" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M172" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="173" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B173" s="1" t="s">
-        <v>213</v>
-      </c>
       <c r="K173" s="1" t="s">
-        <v>214</v>
+        <v>41</v>
       </c>
       <c r="M173" s="1" t="s">
         <v>23</v>
@@ -4168,137 +4183,164 @@
     </row>
     <row r="174" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K174" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="M174" s="1" t="s">
         <v>103</v>
       </c>
     </row>
+    <row r="175" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K175" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="M175" s="1" t="s">
+        <v>217</v>
+      </c>
+    </row>
     <row r="177" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B177" s="1" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="K177" s="1" t="s">
-        <v>25</v>
+        <v>214</v>
       </c>
       <c r="M177" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="O177" s="1" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="178" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K178" s="1" t="s">
-        <v>26</v>
+        <v>215</v>
       </c>
       <c r="M178" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="O178" s="1" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="179" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K179" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="M179" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="O179" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="180" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K180" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="M180" s="1" t="s">
-        <v>236</v>
+        <v>103</v>
       </c>
     </row>
     <row r="181" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B181" s="1" t="s">
-        <v>234</v>
+        <v>219</v>
       </c>
       <c r="K181" s="1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="M181" s="1" t="s">
-        <v>235</v>
+        <v>23</v>
+      </c>
+      <c r="O181" s="1" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="182" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K182" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M182" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O182" s="1" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="183" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K183" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M183" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O183" s="1" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="184" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K184" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="M184" s="1" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="185" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B185" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="K185" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M185" s="1" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="186" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K186" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="M182" s="1" t="s">
+      <c r="M186" s="1" t="s">
         <v>66</v>
-      </c>
-    </row>
-    <row r="186" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B186" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="G186" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="K186" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="M186" s="1" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="187" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K187" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="M187" s="1" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="190" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B190" s="1" t="s">
-        <v>248</v>
+        <v>226</v>
+      </c>
+      <c r="G190" s="1" t="s">
+        <v>225</v>
       </c>
       <c r="K190" s="1" t="s">
-        <v>25</v>
+        <v>111</v>
       </c>
       <c r="M190" s="1" t="s">
-        <v>23</v>
+        <v>112</v>
       </c>
     </row>
     <row r="191" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K191" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="M191" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="194" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B194" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="K194" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="M194" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="195" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="K195" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="M191" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="192" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K192" s="1" t="s">
+      <c r="M195" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="196" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="K196" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="M192" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="193" spans="11:13" x14ac:dyDescent="0.2">
-      <c r="K193" s="1" t="s">
+      <c r="M196" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="197" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="K197" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="M193" s="6" t="s">
+      <c r="M197" s="6" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="194" spans="11:13" x14ac:dyDescent="0.2">
-      <c r="K194" s="1" t="s">
+    <row r="198" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="K198" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="M194" s="1" t="s">
+      <c r="M198" s="1" t="s">
         <v>94</v>
       </c>
     </row>

--- a/Config/Datas/__beans__.xlsx
+++ b/Config/Datas/__beans__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{168469D7-EA84-4E52-9678-311B4AD7F1A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBCE11E1-4F86-4E01-A563-73C314668132}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/Config/Datas/__beans__.xlsx
+++ b/Config/Datas/__beans__.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBCE11E1-4F86-4E01-A563-73C314668132}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17DC48FA-B2F1-4D9C-8784-91994E60F751}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="259">
   <si>
     <t>##var</t>
   </si>
@@ -1033,6 +1033,18 @@
   </si>
   <si>
     <t>时间消耗</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>signedValue</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Condition_当前顾客要求全满足</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GA_获得金币</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1460,7 +1472,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q198"/>
+  <dimension ref="A1:Q201"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="28.75" customWidth="1"/>
@@ -2713,14 +2725,10 @@
       <c r="I68" s="6"/>
       <c r="J68" s="6"/>
       <c r="K68" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="M68" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="N68" s="9"/>
-      <c r="O68" s="6" t="s">
-        <v>63</v>
+        <v>256</v>
+      </c>
+      <c r="M68" s="8" t="s">
+        <v>112</v>
       </c>
       <c r="P68" s="6"/>
       <c r="Q68" s="6"/>
@@ -2737,14 +2745,15 @@
       <c r="I69" s="6"/>
       <c r="J69" s="6"/>
       <c r="K69" s="8" t="s">
-        <v>168</v>
-      </c>
-      <c r="L69" s="6"/>
-      <c r="M69" s="8" t="s">
-        <v>167</v>
-      </c>
-      <c r="N69" s="6"/>
-      <c r="O69" s="8"/>
+        <v>33</v>
+      </c>
+      <c r="M69" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="N69" s="9"/>
+      <c r="O69" s="6" t="s">
+        <v>63</v>
+      </c>
       <c r="P69" s="6"/>
       <c r="Q69" s="6"/>
     </row>
@@ -2759,8 +2768,15 @@
       <c r="H70" s="6"/>
       <c r="I70" s="6"/>
       <c r="J70" s="6"/>
+      <c r="K70" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="L70" s="6"/>
+      <c r="M70" s="8" t="s">
+        <v>167</v>
+      </c>
       <c r="N70" s="6"/>
-      <c r="O70" s="6"/>
+      <c r="O70" s="8"/>
       <c r="P70" s="6"/>
       <c r="Q70" s="6"/>
     </row>
@@ -3955,126 +3971,124 @@
         <v>112</v>
       </c>
     </row>
-    <row r="145" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B145" s="1" t="s">
+    <row r="144" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B144" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="145" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A145" s="1"/>
+      <c r="B145" s="1"/>
+      <c r="C145" s="1"/>
+    </row>
+    <row r="146" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B146" s="1"/>
+      <c r="C146" s="1"/>
+    </row>
+    <row r="147" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B147" s="1"/>
+      <c r="C147" s="1"/>
+    </row>
+    <row r="148" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B148" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="K145" s="1" t="s">
+      <c r="K148" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="M145" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="146" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K146" s="1" t="s">
+      <c r="M148" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="149" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="K149" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="M146" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="147" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K147" s="1"/>
-    </row>
-    <row r="149" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B149" s="1" t="s">
+      <c r="M149" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="150" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="K150" s="1"/>
+    </row>
+    <row r="152" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B152" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="K149" s="1" t="s">
+      <c r="K152" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="M149" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="O149" s="6"/>
-    </row>
-    <row r="150" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K150" s="1" t="s">
+      <c r="M152" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O152" s="6"/>
+    </row>
+    <row r="153" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="K153" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="M150" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="151" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K151" s="1" t="s">
+      <c r="M153" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="154" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="K154" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="M151" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="152" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K152" s="1" t="s">
+      <c r="M154" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="155" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="K155" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M152" s="1" t="s">
+      <c r="M155" s="1" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="153" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K153" s="1" t="s">
+    <row r="156" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="K156" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="M153" s="1" t="s">
+      <c r="M156" s="1" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="154" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K154" s="1" t="s">
+    <row r="157" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="K157" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="M154" s="5" t="s">
+      <c r="M157" s="5" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="155" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B155" s="1" t="s">
+    <row r="158" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B158" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="K155" s="1" t="s">
+      <c r="K158" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="M155" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="156" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B156" s="1"/>
-      <c r="K156" s="1" t="s">
+      <c r="M158" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="159" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B159" s="1"/>
+      <c r="K159" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="M156" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="157" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K157" s="1" t="s">
+      <c r="M159" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="160" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="K160" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="M157" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="158" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K158" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="M158" s="1" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="159" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K159" s="1"/>
-      <c r="M159" s="1"/>
-    </row>
-    <row r="160" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B160" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="K160" s="1" t="s">
-        <v>25</v>
       </c>
       <c r="M160" s="1" t="s">
         <v>23</v>
@@ -4082,23 +4096,22 @@
     </row>
     <row r="161" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K161" s="1" t="s">
-        <v>26</v>
+        <v>228</v>
       </c>
       <c r="M161" s="1" t="s">
-        <v>23</v>
+        <v>229</v>
       </c>
     </row>
     <row r="162" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K162" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="M162" s="1" t="s">
-        <v>23</v>
-      </c>
+      <c r="K162" s="1"/>
+      <c r="M162" s="1"/>
     </row>
     <row r="163" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B163" s="1" t="s">
+        <v>230</v>
+      </c>
       <c r="K163" s="1" t="s">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="M163" s="1" t="s">
         <v>23</v>
@@ -4106,241 +4119,265 @@
     </row>
     <row r="164" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K164" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M164" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="165" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K165" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M165" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="166" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K166" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="M166" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="167" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K167" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="M164" s="1" t="s">
+      <c r="M167" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="165" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K165" s="1"/>
-    </row>
-    <row r="167" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B167" s="1" t="s">
+    <row r="168" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K168" s="1"/>
+    </row>
+    <row r="170" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B170" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="K167" s="1" t="s">
+      <c r="K170" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="M167" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="O167" s="1" t="s">
+      <c r="M170" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O170" s="1" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="168" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K168" s="1" t="s">
+    <row r="171" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K171" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="M168" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="O168" s="1" t="s">
+      <c r="M171" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O171" s="1" t="s">
         <v>210</v>
-      </c>
-    </row>
-    <row r="169" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K169" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="M169" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="O169" s="1" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="170" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K170" s="1"/>
-    </row>
-    <row r="171" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B171" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="K171" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="M171" s="1" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="172" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K172" s="1" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="M172" s="1" t="s">
         <v>23</v>
       </c>
+      <c r="O172" s="1" t="s">
+        <v>211</v>
+      </c>
     </row>
     <row r="173" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K173" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="M173" s="1" t="s">
-        <v>23</v>
-      </c>
+      <c r="K173" s="1"/>
     </row>
     <row r="174" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B174" s="1" t="s">
+        <v>208</v>
+      </c>
       <c r="K174" s="1" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="M174" s="1" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
     </row>
     <row r="175" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K175" s="1" t="s">
-        <v>218</v>
+        <v>26</v>
       </c>
       <c r="M175" s="1" t="s">
-        <v>217</v>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="176" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K176" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M176" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="177" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B177" s="1" t="s">
-        <v>213</v>
-      </c>
       <c r="K177" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="M177" s="1" t="s">
-        <v>23</v>
+        <v>103</v>
       </c>
     </row>
     <row r="178" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K178" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="M178" s="1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="180" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B180" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="K180" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="M180" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="181" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K181" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="M178" s="1" t="s">
+      <c r="M181" s="1" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="181" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B181" s="1" t="s">
+    <row r="184" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B184" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="K181" s="1" t="s">
+      <c r="K184" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="M181" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="O181" s="1" t="s">
+      <c r="M184" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O184" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="182" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K182" s="1" t="s">
+    <row r="185" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K185" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="M182" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="O182" s="1" t="s">
+      <c r="M185" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O185" s="1" t="s">
         <v>220</v>
-      </c>
-    </row>
-    <row r="183" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K183" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="M183" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="O183" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="184" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K184" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="M184" s="1" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="185" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B185" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="K185" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="M185" s="1" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="186" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K186" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M186" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O186" s="1" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="187" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K187" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="M187" s="1" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="188" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B188" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="K188" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M188" s="1" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="189" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K189" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="M186" s="1" t="s">
+      <c r="M189" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="190" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B190" s="1" t="s">
+    <row r="193" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B193" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="G190" s="1" t="s">
+      <c r="G193" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="K190" s="1" t="s">
+      <c r="K193" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="M190" s="1" t="s">
+      <c r="M193" s="1" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="191" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K191" s="1" t="s">
+    <row r="194" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="K194" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="M191" s="1" t="s">
+      <c r="M194" s="1" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="194" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B194" s="1" t="s">
+    <row r="197" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B197" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="K194" s="1" t="s">
+      <c r="K197" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="M194" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="195" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="K195" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="M195" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="196" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="K196" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="M196" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="197" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="K197" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="M197" s="6" t="s">
-        <v>99</v>
+      <c r="M197" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="198" spans="2:13" x14ac:dyDescent="0.2">
       <c r="K198" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M198" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="199" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="K199" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M199" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="200" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="K200" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="M200" s="6" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="201" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="K201" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="M198" s="1" t="s">
+      <c r="M201" s="1" t="s">
         <v>94</v>
       </c>
     </row>
@@ -5071,10 +5108,18 @@
       </c>
     </row>
     <row r="68" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B68" s="1"/>
-      <c r="C68" s="1"/>
-      <c r="K68" s="1"/>
-      <c r="M68" s="1"/>
+      <c r="B68" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="K68" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="M68" s="1" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B69" s="1" t="s">

--- a/Config/Datas/__beans__.xlsx
+++ b/Config/Datas/__beans__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17DC48FA-B2F1-4D9C-8784-91994E60F751}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77B128A6-AF9F-4AC9-AF4A-0F4A3CDF67AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="260">
   <si>
     <t>##var</t>
   </si>
@@ -1045,6 +1045,10 @@
   </si>
   <si>
     <t>GA_获得金币</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>originCost</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1472,7 +1476,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q201"/>
+  <dimension ref="A1:Q204"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="28.75" customWidth="1"/>
@@ -2369,9 +2373,9 @@
       <c r="P41" s="6"/>
       <c r="Q41" s="6"/>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="6"/>
-      <c r="B42" s="6"/>
+      <c r="B42" s="5"/>
       <c r="C42" s="6"/>
       <c r="D42" s="6"/>
       <c r="E42" s="6"/>
@@ -2379,96 +2383,114 @@
       <c r="G42" s="6"/>
       <c r="H42" s="6"/>
       <c r="I42" s="6"/>
-      <c r="J42" s="6"/>
+      <c r="J42" s="5"/>
       <c r="K42" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="L42" s="6"/>
+        <v>60</v>
+      </c>
       <c r="M42" s="5" t="s">
         <v>23</v>
       </c>
       <c r="N42" s="6"/>
-      <c r="O42" s="6" t="s">
-        <v>132</v>
-      </c>
+      <c r="O42" s="6"/>
       <c r="P42" s="6"/>
       <c r="Q42" s="6"/>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="6"/>
+      <c r="B43" s="5"/>
+      <c r="C43" s="6"/>
+      <c r="D43" s="6"/>
+      <c r="E43" s="6"/>
+      <c r="F43" s="6"/>
+      <c r="G43" s="6"/>
+      <c r="H43" s="6"/>
+      <c r="I43" s="6"/>
+      <c r="J43" s="5"/>
+      <c r="K43" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="M43" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="N43" s="6"/>
+      <c r="O43" s="6"/>
       <c r="P43" s="6"/>
       <c r="Q43" s="6"/>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="6"/>
-      <c r="B44" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="G44" s="1" t="s">
-        <v>146</v>
-      </c>
+      <c r="B44" s="5"/>
+      <c r="C44" s="6"/>
+      <c r="D44" s="6"/>
+      <c r="E44" s="6"/>
+      <c r="F44" s="6"/>
+      <c r="G44" s="6"/>
+      <c r="H44" s="6"/>
+      <c r="I44" s="6"/>
+      <c r="J44" s="5"/>
       <c r="K44" s="5" t="s">
-        <v>25</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="L44" s="6"/>
       <c r="M44" s="5" t="s">
         <v>23</v>
       </c>
+      <c r="N44" s="6"/>
       <c r="O44" s="6" t="s">
-        <v>31</v>
+        <v>132</v>
       </c>
       <c r="P44" s="6"/>
       <c r="Q44" s="6"/>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A45" s="6"/>
-      <c r="K45" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="M45" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="O45" s="6" t="s">
-        <v>148</v>
-      </c>
+      <c r="B45" s="6"/>
+      <c r="C45" s="6"/>
+      <c r="D45" s="6"/>
+      <c r="E45" s="6"/>
+      <c r="F45" s="6"/>
+      <c r="G45" s="6"/>
+      <c r="H45" s="6"/>
+      <c r="I45" s="6"/>
+      <c r="J45" s="6"/>
       <c r="P45" s="6"/>
       <c r="Q45" s="6"/>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A46" s="6"/>
-      <c r="K46" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="M46" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="O46" s="6" t="s">
-        <v>147</v>
-      </c>
       <c r="P46" s="6"/>
       <c r="Q46" s="6"/>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A47" s="6"/>
+      <c r="B47" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>146</v>
+      </c>
       <c r="K47" s="5" t="s">
-        <v>161</v>
+        <v>25</v>
       </c>
       <c r="M47" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="O47" s="6"/>
+      <c r="O47" s="6" t="s">
+        <v>31</v>
+      </c>
       <c r="P47" s="6"/>
       <c r="Q47" s="6"/>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A48" s="6"/>
       <c r="K48" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="M48" s="1" t="s">
-        <v>103</v>
+        <v>26</v>
+      </c>
+      <c r="M48" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P48" s="6"/>
       <c r="Q48" s="6"/>
@@ -2476,13 +2498,13 @@
     <row r="49" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A49" s="6"/>
       <c r="K49" s="5" t="s">
-        <v>154</v>
+        <v>41</v>
       </c>
       <c r="M49" s="5" t="s">
         <v>23</v>
       </c>
       <c r="O49" s="6" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="P49" s="6"/>
       <c r="Q49" s="6"/>
@@ -2490,246 +2512,221 @@
     <row r="50" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A50" s="6"/>
       <c r="K50" s="5" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="M50" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="O50" s="6" t="s">
-        <v>152</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="O50" s="6"/>
       <c r="P50" s="6"/>
       <c r="Q50" s="6"/>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A51" s="6"/>
       <c r="K51" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="M51" s="5" t="s">
-        <v>153</v>
+        <v>150</v>
+      </c>
+      <c r="M51" s="1" t="s">
+        <v>103</v>
       </c>
       <c r="O51" s="6" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="P51" s="6"/>
       <c r="Q51" s="6"/>
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A52" s="6"/>
+      <c r="K52" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="M52" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="O52" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="P52" s="6"/>
+      <c r="Q52" s="6"/>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A53" s="6"/>
+      <c r="K53" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="M53" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="O53" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="P53" s="6"/>
       <c r="Q53" s="6"/>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A54" s="6"/>
+      <c r="K54" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="M54" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="O54" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="P54" s="6"/>
       <c r="Q54" s="6"/>
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A55" s="6"/>
-      <c r="B55" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C55" s="6"/>
-      <c r="D55" s="6"/>
-      <c r="E55" s="6"/>
-      <c r="F55" s="6"/>
-      <c r="G55" s="6"/>
-      <c r="H55" s="6"/>
-      <c r="I55" s="6"/>
-      <c r="J55" s="6"/>
-      <c r="K55" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="M55" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="N55" s="6"/>
-      <c r="O55" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="P55" s="6"/>
-      <c r="Q55" s="6"/>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A56" s="6"/>
-      <c r="K56" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="L56" s="6"/>
-      <c r="M56" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="P56" s="6"/>
       <c r="Q56" s="6"/>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A57" s="6"/>
-      <c r="K57" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="M57" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="P57" s="7"/>
       <c r="Q57" s="6"/>
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A58" s="6"/>
-      <c r="K58" s="5"/>
-      <c r="M58" s="5"/>
-      <c r="P58" s="7"/>
+      <c r="B58" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C58" s="6"/>
+      <c r="D58" s="6"/>
+      <c r="E58" s="6"/>
+      <c r="F58" s="6"/>
+      <c r="G58" s="6"/>
+      <c r="H58" s="6"/>
+      <c r="I58" s="6"/>
+      <c r="J58" s="6"/>
+      <c r="K58" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="M58" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="N58" s="6"/>
+      <c r="O58" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="P58" s="6"/>
       <c r="Q58" s="6"/>
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A59" s="6"/>
-      <c r="B59" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="K59" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="M59" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="P59" s="7"/>
+      <c r="K59" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="L59" s="6"/>
+      <c r="M59" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="P59" s="6"/>
       <c r="Q59" s="6"/>
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A60" s="6"/>
       <c r="K60" s="5" t="s">
-        <v>165</v>
+        <v>68</v>
       </c>
       <c r="M60" s="5" t="s">
-        <v>23</v>
+        <v>62</v>
       </c>
       <c r="P60" s="7"/>
       <c r="Q60" s="6"/>
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A61" s="6"/>
-      <c r="K61" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="M61" s="5" t="s">
-        <v>163</v>
-      </c>
+      <c r="K61" s="5"/>
+      <c r="M61" s="5"/>
       <c r="P61" s="7"/>
       <c r="Q61" s="6"/>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A62" s="6"/>
+      <c r="B62" s="1" t="s">
+        <v>166</v>
+      </c>
       <c r="K62" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="M62" s="6" t="s">
-        <v>66</v>
+        <v>164</v>
+      </c>
+      <c r="M62" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="P62" s="7"/>
       <c r="Q62" s="6"/>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A63" s="6"/>
-      <c r="K63" s="5"/>
-      <c r="M63" s="5"/>
+      <c r="K63" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="M63" s="5" t="s">
+        <v>23</v>
+      </c>
       <c r="P63" s="7"/>
       <c r="Q63" s="6"/>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A64" s="6"/>
+      <c r="K64" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="M64" s="5" t="s">
+        <v>163</v>
+      </c>
       <c r="P64" s="7"/>
       <c r="Q64" s="6"/>
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A65" s="6"/>
-      <c r="B65" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="C65" s="6"/>
-      <c r="D65" s="6"/>
-      <c r="E65" s="6"/>
-      <c r="F65" s="6"/>
-      <c r="G65" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="H65" s="6"/>
-      <c r="I65" s="6"/>
-      <c r="J65" s="5"/>
-      <c r="K65" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="L65" s="6"/>
-      <c r="M65" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="N65" s="9"/>
-      <c r="O65" s="6"/>
-      <c r="P65" s="6"/>
+      <c r="K65" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="M65" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="P65" s="7"/>
       <c r="Q65" s="6"/>
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A66" s="6"/>
-      <c r="B66" s="6"/>
-      <c r="C66" s="6"/>
-      <c r="D66" s="6"/>
-      <c r="E66" s="6"/>
-      <c r="F66" s="6"/>
-      <c r="G66" s="6"/>
-      <c r="H66" s="6"/>
-      <c r="I66" s="6"/>
-      <c r="J66" s="6"/>
-      <c r="K66" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="L66" s="6"/>
-      <c r="M66" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="N66" s="9"/>
-      <c r="O66" s="6"/>
-      <c r="P66" s="6"/>
+      <c r="K66" s="5"/>
+      <c r="M66" s="5"/>
+      <c r="P66" s="7"/>
       <c r="Q66" s="6"/>
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A67" s="6"/>
-      <c r="B67" s="6"/>
-      <c r="C67" s="6"/>
-      <c r="D67" s="6"/>
-      <c r="E67" s="6"/>
-      <c r="F67" s="6"/>
-      <c r="G67" s="6"/>
-      <c r="H67" s="6"/>
-      <c r="J67" s="6"/>
-      <c r="K67" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="L67" s="6"/>
-      <c r="M67" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="N67" s="9"/>
-      <c r="O67" s="6"/>
-      <c r="P67" s="6"/>
+      <c r="P67" s="7"/>
       <c r="Q67" s="6"/>
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A68" s="6"/>
-      <c r="B68" s="6"/>
+      <c r="B68" s="5" t="s">
+        <v>73</v>
+      </c>
       <c r="C68" s="6"/>
       <c r="D68" s="6"/>
       <c r="E68" s="6"/>
       <c r="F68" s="6"/>
-      <c r="G68" s="6"/>
+      <c r="G68" s="6" t="s">
+        <v>70</v>
+      </c>
       <c r="H68" s="6"/>
       <c r="I68" s="6"/>
-      <c r="J68" s="6"/>
+      <c r="J68" s="5"/>
       <c r="K68" s="8" t="s">
-        <v>256</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="L68" s="6"/>
       <c r="M68" s="8" t="s">
-        <v>112</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="N68" s="9"/>
+      <c r="O68" s="6"/>
       <c r="P68" s="6"/>
       <c r="Q68" s="6"/>
     </row>
@@ -2745,15 +2742,14 @@
       <c r="I69" s="6"/>
       <c r="J69" s="6"/>
       <c r="K69" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="M69" s="5" t="s">
-        <v>163</v>
+        <v>26</v>
+      </c>
+      <c r="L69" s="6"/>
+      <c r="M69" s="8" t="s">
+        <v>23</v>
       </c>
       <c r="N69" s="9"/>
-      <c r="O69" s="6" t="s">
-        <v>63</v>
-      </c>
+      <c r="O69" s="6"/>
       <c r="P69" s="6"/>
       <c r="Q69" s="6"/>
     </row>
@@ -2766,23 +2762,22 @@
       <c r="F70" s="6"/>
       <c r="G70" s="6"/>
       <c r="H70" s="6"/>
-      <c r="I70" s="6"/>
       <c r="J70" s="6"/>
       <c r="K70" s="8" t="s">
-        <v>168</v>
+        <v>41</v>
       </c>
       <c r="L70" s="6"/>
       <c r="M70" s="8" t="s">
-        <v>167</v>
-      </c>
-      <c r="N70" s="6"/>
-      <c r="O70" s="8"/>
+        <v>23</v>
+      </c>
+      <c r="N70" s="9"/>
+      <c r="O70" s="6"/>
       <c r="P70" s="6"/>
       <c r="Q70" s="6"/>
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A71" s="6"/>
-      <c r="B71" s="5"/>
+      <c r="B71" s="6"/>
       <c r="C71" s="6"/>
       <c r="D71" s="6"/>
       <c r="E71" s="6"/>
@@ -2791,17 +2786,18 @@
       <c r="H71" s="6"/>
       <c r="I71" s="6"/>
       <c r="J71" s="6"/>
-      <c r="K71" s="2"/>
-      <c r="M71" s="2"/>
-      <c r="O71" s="2"/>
+      <c r="K71" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="M71" s="8" t="s">
+        <v>112</v>
+      </c>
       <c r="P71" s="6"/>
       <c r="Q71" s="6"/>
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A72" s="6"/>
-      <c r="B72" s="6" t="s">
-        <v>79</v>
-      </c>
+      <c r="B72" s="6"/>
       <c r="C72" s="6"/>
       <c r="D72" s="6"/>
       <c r="E72" s="6"/>
@@ -2810,14 +2806,15 @@
       <c r="H72" s="6"/>
       <c r="I72" s="6"/>
       <c r="J72" s="6"/>
-      <c r="K72" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="M72" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="O72" s="11" t="s">
-        <v>81</v>
+      <c r="K72" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="M72" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="N72" s="9"/>
+      <c r="O72" s="6" t="s">
+        <v>63</v>
       </c>
       <c r="P72" s="6"/>
       <c r="Q72" s="6"/>
@@ -2833,95 +2830,129 @@
       <c r="H73" s="6"/>
       <c r="I73" s="6"/>
       <c r="J73" s="6"/>
-      <c r="K73" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="M73" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="O73" s="11" t="s">
-        <v>80</v>
-      </c>
+      <c r="K73" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="L73" s="6"/>
+      <c r="M73" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="N73" s="6"/>
+      <c r="O73" s="8"/>
       <c r="P73" s="6"/>
       <c r="Q73" s="6"/>
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A74" s="6"/>
+      <c r="B74" s="5"/>
+      <c r="C74" s="6"/>
+      <c r="D74" s="6"/>
+      <c r="E74" s="6"/>
+      <c r="F74" s="6"/>
+      <c r="G74" s="6"/>
       <c r="H74" s="6"/>
       <c r="I74" s="6"/>
       <c r="J74" s="6"/>
-      <c r="K74" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="M74" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="O74" s="11" t="s">
-        <v>86</v>
-      </c>
+      <c r="K74" s="2"/>
+      <c r="M74" s="2"/>
+      <c r="O74" s="2"/>
       <c r="P74" s="6"/>
       <c r="Q74" s="6"/>
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A75" s="6"/>
+      <c r="B75" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C75" s="6"/>
+      <c r="D75" s="6"/>
+      <c r="E75" s="6"/>
+      <c r="F75" s="6"/>
+      <c r="G75" s="6"/>
       <c r="H75" s="6"/>
       <c r="I75" s="6"/>
       <c r="J75" s="6"/>
-      <c r="K75" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="M75" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="N75" s="6"/>
-      <c r="O75" s="6" t="s">
-        <v>85</v>
+      <c r="K75" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="M75" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="O75" s="11" t="s">
+        <v>81</v>
       </c>
       <c r="P75" s="6"/>
       <c r="Q75" s="6"/>
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A76" s="6"/>
+      <c r="B76" s="6"/>
+      <c r="C76" s="6"/>
+      <c r="D76" s="6"/>
+      <c r="E76" s="6"/>
+      <c r="F76" s="6"/>
+      <c r="G76" s="6"/>
+      <c r="H76" s="6"/>
+      <c r="I76" s="6"/>
+      <c r="J76" s="6"/>
       <c r="K76" s="11" t="s">
-        <v>144</v>
-      </c>
-      <c r="M76" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M76" s="11" t="s">
         <v>23</v>
       </c>
       <c r="O76" s="11" t="s">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="P76" s="6"/>
       <c r="Q76" s="6"/>
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A77" s="6"/>
-      <c r="B77" s="6"/>
-      <c r="C77" s="6"/>
-      <c r="D77" s="6"/>
-      <c r="E77" s="6"/>
-      <c r="F77" s="6"/>
-      <c r="G77" s="6"/>
-      <c r="K77" s="11" t="s">
-        <v>83</v>
+      <c r="H77" s="6"/>
+      <c r="I77" s="6"/>
+      <c r="J77" s="6"/>
+      <c r="K77" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="M77" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="O77" s="11"/>
+        <v>23</v>
+      </c>
+      <c r="O77" s="11" t="s">
+        <v>86</v>
+      </c>
       <c r="P77" s="6"/>
       <c r="Q77" s="6"/>
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A78" s="6"/>
-      <c r="K78" s="11"/>
-      <c r="M78" s="11"/>
-      <c r="O78" s="11"/>
+      <c r="H78" s="6"/>
+      <c r="I78" s="6"/>
+      <c r="J78" s="6"/>
+      <c r="K78" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="M78" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="N78" s="6"/>
+      <c r="O78" s="6" t="s">
+        <v>85</v>
+      </c>
       <c r="P78" s="6"/>
-      <c r="Q78" s="7"/>
+      <c r="Q78" s="6"/>
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A79" s="6"/>
+      <c r="K79" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="M79" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O79" s="11" t="s">
+        <v>61</v>
+      </c>
       <c r="P79" s="6"/>
       <c r="Q79" s="6"/>
     </row>
@@ -2933,108 +2964,72 @@
       <c r="E80" s="6"/>
       <c r="F80" s="6"/>
       <c r="G80" s="6"/>
-      <c r="K80" s="1"/>
-      <c r="M80" s="1"/>
-      <c r="O80" s="1"/>
-      <c r="P80" s="7"/>
+      <c r="K80" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="M80" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="O80" s="11"/>
+      <c r="P80" s="6"/>
       <c r="Q80" s="6"/>
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A81" s="6"/>
-      <c r="B81" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="K81" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="M81" s="1" t="s">
-        <v>112</v>
-      </c>
+      <c r="K81" s="11"/>
+      <c r="M81" s="11"/>
+      <c r="O81" s="11"/>
       <c r="P81" s="6"/>
-      <c r="Q81" s="6"/>
+      <c r="Q81" s="7"/>
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A82" s="5"/>
-      <c r="B82" s="6"/>
-      <c r="C82" s="6"/>
-      <c r="K82" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="M82" s="1" t="s">
-        <v>66</v>
-      </c>
+      <c r="A82" s="6"/>
       <c r="P82" s="6"/>
       <c r="Q82" s="6"/>
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A83" s="6"/>
+      <c r="B83" s="6"/>
       <c r="C83" s="6"/>
       <c r="D83" s="6"/>
       <c r="E83" s="6"/>
       <c r="F83" s="6"/>
       <c r="G83" s="6"/>
-      <c r="H83" s="6"/>
-      <c r="I83" s="6"/>
-      <c r="J83" s="6"/>
-      <c r="K83" s="6"/>
-      <c r="L83" s="6"/>
-      <c r="M83" s="6"/>
-      <c r="N83" s="6"/>
-      <c r="O83" s="6"/>
-      <c r="P83" s="6"/>
+      <c r="K83" s="1"/>
+      <c r="M83" s="1"/>
+      <c r="O83" s="1"/>
+      <c r="P83" s="7"/>
       <c r="Q83" s="6"/>
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A84" s="6"/>
-      <c r="B84" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="C84" s="5"/>
-      <c r="D84" s="6"/>
-      <c r="E84" s="6"/>
-      <c r="F84" s="6"/>
-      <c r="G84" s="6"/>
-      <c r="H84" s="6"/>
-      <c r="I84" s="6"/>
-      <c r="J84" s="8"/>
-      <c r="K84" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L84" s="6"/>
-      <c r="M84" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N84" s="6"/>
-      <c r="O84" s="6"/>
+      <c r="B84" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="K84" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="M84" s="1" t="s">
+        <v>112</v>
+      </c>
       <c r="P84" s="6"/>
       <c r="Q84" s="6"/>
     </row>
     <row r="85" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A85" s="6"/>
-      <c r="B85" s="8"/>
-      <c r="C85" s="5"/>
-      <c r="D85" s="6"/>
-      <c r="E85" s="6"/>
-      <c r="F85" s="6"/>
-      <c r="G85" s="6"/>
-      <c r="H85" s="6"/>
-      <c r="I85" s="6"/>
-      <c r="J85" s="8"/>
-      <c r="K85" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="L85" s="6"/>
-      <c r="M85" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="N85" s="6"/>
-      <c r="O85" s="5"/>
+      <c r="A85" s="5"/>
+      <c r="B85" s="6"/>
+      <c r="C85" s="6"/>
+      <c r="K85" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="M85" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="P85" s="6"/>
       <c r="Q85" s="6"/>
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A86" s="6"/>
-      <c r="B86" s="6"/>
       <c r="C86" s="6"/>
       <c r="D86" s="6"/>
       <c r="E86" s="6"/>
@@ -3043,41 +3038,41 @@
       <c r="H86" s="6"/>
       <c r="I86" s="6"/>
       <c r="J86" s="6"/>
-      <c r="K86" s="5" t="s">
-        <v>41</v>
-      </c>
+      <c r="K86" s="6"/>
       <c r="L86" s="6"/>
-      <c r="M86" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="N86" s="7"/>
-      <c r="O86" s="5"/>
-      <c r="P86" s="7"/>
+      <c r="M86" s="6"/>
+      <c r="N86" s="6"/>
+      <c r="O86" s="6"/>
+      <c r="P86" s="6"/>
       <c r="Q86" s="6"/>
     </row>
     <row r="87" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A87" s="6"/>
-      <c r="B87" s="6"/>
-      <c r="C87" s="6"/>
+      <c r="B87" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="C87" s="5"/>
       <c r="D87" s="6"/>
       <c r="E87" s="6"/>
       <c r="F87" s="6"/>
       <c r="G87" s="6"/>
       <c r="H87" s="6"/>
       <c r="I87" s="6"/>
-      <c r="J87" s="6"/>
-      <c r="K87" s="5" t="s">
-        <v>93</v>
+      <c r="J87" s="8"/>
+      <c r="K87" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="L87" s="6"/>
-      <c r="M87" s="5" t="s">
-        <v>94</v>
+      <c r="M87" s="6" t="s">
+        <v>23</v>
       </c>
       <c r="N87" s="6"/>
+      <c r="O87" s="6"/>
       <c r="P87" s="6"/>
       <c r="Q87" s="6"/>
     </row>
     <row r="88" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A88" s="6"/>
       <c r="B88" s="8"/>
       <c r="C88" s="5"/>
       <c r="D88" s="6"/>
@@ -3087,283 +3082,297 @@
       <c r="H88" s="6"/>
       <c r="I88" s="6"/>
       <c r="J88" s="8"/>
-      <c r="K88" s="6" t="s">
-        <v>95</v>
+      <c r="K88" s="5" t="s">
+        <v>26</v>
       </c>
       <c r="L88" s="6"/>
-      <c r="M88" s="6" t="s">
-        <v>96</v>
-      </c>
+      <c r="M88" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="N88" s="6"/>
+      <c r="O88" s="5"/>
       <c r="P88" s="6"/>
       <c r="Q88" s="6"/>
     </row>
     <row r="89" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B89" s="8"/>
-      <c r="C89" s="5"/>
+      <c r="A89" s="6"/>
+      <c r="B89" s="6"/>
+      <c r="C89" s="6"/>
       <c r="D89" s="6"/>
       <c r="E89" s="6"/>
       <c r="F89" s="6"/>
       <c r="G89" s="6"/>
       <c r="H89" s="6"/>
       <c r="I89" s="6"/>
-      <c r="J89" s="8"/>
+      <c r="J89" s="6"/>
       <c r="K89" s="5" t="s">
-        <v>102</v>
+        <v>41</v>
       </c>
       <c r="L89" s="6"/>
       <c r="M89" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="P89" s="6"/>
+        <v>23</v>
+      </c>
+      <c r="N89" s="7"/>
+      <c r="O89" s="5"/>
+      <c r="P89" s="7"/>
       <c r="Q89" s="6"/>
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B90" s="1"/>
-      <c r="G90" s="1"/>
+      <c r="A90" s="6"/>
+      <c r="B90" s="6"/>
+      <c r="C90" s="6"/>
+      <c r="D90" s="6"/>
+      <c r="E90" s="6"/>
+      <c r="F90" s="6"/>
+      <c r="G90" s="6"/>
       <c r="H90" s="6"/>
       <c r="I90" s="6"/>
-      <c r="J90" s="8"/>
-      <c r="K90" s="5"/>
+      <c r="J90" s="6"/>
+      <c r="K90" s="5" t="s">
+        <v>93</v>
+      </c>
       <c r="L90" s="6"/>
-      <c r="M90" s="5"/>
-      <c r="P90" s="7"/>
+      <c r="M90" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="N90" s="6"/>
+      <c r="P90" s="6"/>
       <c r="Q90" s="6"/>
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="B91" s="8"/>
+      <c r="C91" s="5"/>
+      <c r="D91" s="6"/>
+      <c r="E91" s="6"/>
+      <c r="F91" s="6"/>
+      <c r="G91" s="6"/>
       <c r="H91" s="6"/>
       <c r="I91" s="6"/>
       <c r="J91" s="8"/>
-      <c r="K91" s="5"/>
+      <c r="K91" s="6" t="s">
+        <v>95</v>
+      </c>
       <c r="L91" s="6"/>
-      <c r="M91" s="5"/>
-      <c r="O91" s="5"/>
-      <c r="P91" s="7"/>
+      <c r="M91" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="P91" s="6"/>
       <c r="Q91" s="6"/>
     </row>
     <row r="92" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B92" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="K92" s="1"/>
-      <c r="M92" s="1"/>
-      <c r="P92" s="7"/>
-      <c r="Q92" s="7"/>
+      <c r="B92" s="8"/>
+      <c r="C92" s="5"/>
+      <c r="D92" s="6"/>
+      <c r="E92" s="6"/>
+      <c r="F92" s="6"/>
+      <c r="G92" s="6"/>
+      <c r="H92" s="6"/>
+      <c r="I92" s="6"/>
+      <c r="J92" s="8"/>
+      <c r="K92" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="L92" s="6"/>
+      <c r="M92" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="P92" s="6"/>
+      <c r="Q92" s="6"/>
     </row>
     <row r="93" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B93" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="C93" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="K93" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="M93" s="1" t="s">
-        <v>99</v>
-      </c>
+      <c r="B93" s="1"/>
+      <c r="G93" s="1"/>
+      <c r="H93" s="6"/>
+      <c r="I93" s="6"/>
+      <c r="J93" s="8"/>
+      <c r="K93" s="5"/>
+      <c r="L93" s="6"/>
+      <c r="M93" s="5"/>
       <c r="P93" s="7"/>
       <c r="Q93" s="6"/>
     </row>
     <row r="94" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="K94" s="1" t="s">
+      <c r="H94" s="6"/>
+      <c r="I94" s="6"/>
+      <c r="J94" s="8"/>
+      <c r="K94" s="5"/>
+      <c r="L94" s="6"/>
+      <c r="M94" s="5"/>
+      <c r="O94" s="5"/>
+      <c r="P94" s="7"/>
+      <c r="Q94" s="6"/>
+    </row>
+    <row r="95" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="B95" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="K95" s="1"/>
+      <c r="M95" s="1"/>
+      <c r="P95" s="7"/>
+      <c r="Q95" s="7"/>
+    </row>
+    <row r="96" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="B96" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="K96" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="M96" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="P96" s="7"/>
+      <c r="Q96" s="6"/>
+    </row>
+    <row r="97" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K97" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="M94" s="1" t="s">
+      <c r="M97" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="O94" s="1" t="s">
+      <c r="O97" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="P94" s="6"/>
-      <c r="Q94" s="6"/>
-    </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A95" s="6"/>
-      <c r="B95" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="C95" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="K95" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="M95" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="N95" s="6"/>
-      <c r="O95" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="P95" s="6"/>
-      <c r="Q95" s="6"/>
-    </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A96" s="6"/>
-      <c r="K96" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="M96" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="N96" s="6"/>
-      <c r="O96" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="P96" s="6"/>
-      <c r="Q96" s="6"/>
-    </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A97" s="6"/>
-      <c r="N97" s="6"/>
-      <c r="P97" s="7"/>
+      <c r="P97" s="6"/>
       <c r="Q97" s="6"/>
     </row>
     <row r="98" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A98" s="6"/>
+      <c r="B98" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="K98" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="M98" s="1" t="s">
+        <v>62</v>
+      </c>
       <c r="N98" s="6"/>
-      <c r="O98" s="5"/>
+      <c r="O98" s="1" t="s">
+        <v>98</v>
+      </c>
       <c r="P98" s="6"/>
       <c r="Q98" s="6"/>
     </row>
     <row r="99" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A99" s="6"/>
-      <c r="H99" s="6"/>
-      <c r="I99" s="6"/>
-      <c r="J99" s="6"/>
-      <c r="K99" s="5"/>
-      <c r="L99" s="6"/>
-      <c r="M99" s="5"/>
+      <c r="K99" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="M99" s="1" t="s">
+        <v>62</v>
+      </c>
       <c r="N99" s="6"/>
-      <c r="O99" s="5"/>
+      <c r="O99" s="1" t="s">
+        <v>98</v>
+      </c>
       <c r="P99" s="6"/>
       <c r="Q99" s="6"/>
     </row>
     <row r="100" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A100" s="6"/>
-      <c r="H100" s="6"/>
-      <c r="I100" s="6"/>
-      <c r="J100" s="6"/>
-      <c r="K100" s="6"/>
-      <c r="L100" s="6"/>
-      <c r="M100" s="6"/>
       <c r="N100" s="6"/>
-      <c r="O100" s="6"/>
-      <c r="P100" s="6"/>
+      <c r="P100" s="7"/>
       <c r="Q100" s="6"/>
     </row>
     <row r="101" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A101" s="6"/>
-      <c r="D101" s="6"/>
-      <c r="E101" s="6"/>
-      <c r="F101" s="6"/>
-      <c r="G101" s="6"/>
-      <c r="H101" s="6"/>
-      <c r="I101" s="6"/>
-      <c r="J101" s="8"/>
-      <c r="K101" s="5"/>
-      <c r="L101" s="6"/>
-      <c r="M101" s="5"/>
       <c r="N101" s="6"/>
-      <c r="O101" s="6"/>
+      <c r="O101" s="5"/>
       <c r="P101" s="6"/>
       <c r="Q101" s="6"/>
     </row>
     <row r="102" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A102" s="6"/>
-      <c r="B102" s="8"/>
-      <c r="C102" s="5"/>
-      <c r="D102" s="6"/>
-      <c r="E102" s="6"/>
-      <c r="F102" s="6"/>
-      <c r="G102" s="6"/>
       <c r="H102" s="6"/>
       <c r="I102" s="6"/>
-      <c r="J102" s="8"/>
+      <c r="J102" s="6"/>
       <c r="K102" s="5"/>
       <c r="L102" s="6"/>
       <c r="M102" s="5"/>
       <c r="N102" s="6"/>
-      <c r="O102" s="6"/>
+      <c r="O102" s="5"/>
       <c r="P102" s="6"/>
       <c r="Q102" s="6"/>
     </row>
     <row r="103" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A103" s="6"/>
+      <c r="H103" s="6"/>
+      <c r="I103" s="6"/>
+      <c r="J103" s="6"/>
+      <c r="K103" s="6"/>
+      <c r="L103" s="6"/>
+      <c r="M103" s="6"/>
+      <c r="N103" s="6"/>
       <c r="O103" s="6"/>
       <c r="P103" s="6"/>
       <c r="Q103" s="6"/>
     </row>
     <row r="104" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A104" s="6"/>
+      <c r="D104" s="6"/>
+      <c r="E104" s="6"/>
+      <c r="F104" s="6"/>
+      <c r="G104" s="6"/>
+      <c r="H104" s="6"/>
+      <c r="I104" s="6"/>
+      <c r="J104" s="8"/>
+      <c r="K104" s="5"/>
+      <c r="L104" s="6"/>
+      <c r="M104" s="5"/>
+      <c r="N104" s="6"/>
       <c r="O104" s="6"/>
       <c r="P104" s="6"/>
       <c r="Q104" s="6"/>
     </row>
     <row r="105" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A105" s="6"/>
+      <c r="B105" s="8"/>
+      <c r="C105" s="5"/>
+      <c r="D105" s="6"/>
+      <c r="E105" s="6"/>
+      <c r="F105" s="6"/>
+      <c r="G105" s="6"/>
+      <c r="H105" s="6"/>
+      <c r="I105" s="6"/>
+      <c r="J105" s="8"/>
+      <c r="K105" s="5"/>
+      <c r="L105" s="6"/>
+      <c r="M105" s="5"/>
+      <c r="N105" s="6"/>
       <c r="O105" s="6"/>
       <c r="P105" s="6"/>
       <c r="Q105" s="6"/>
     </row>
     <row r="106" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A106" s="6"/>
-      <c r="B106" s="8"/>
-      <c r="C106" s="5"/>
-      <c r="D106" s="6"/>
-      <c r="E106" s="6"/>
-      <c r="F106" s="6"/>
-      <c r="G106" s="6"/>
-      <c r="H106" s="6"/>
-      <c r="I106" s="6"/>
-      <c r="J106" s="6"/>
-      <c r="K106" s="5"/>
-      <c r="L106" s="6"/>
-      <c r="M106" s="5"/>
-      <c r="N106" s="6"/>
       <c r="O106" s="6"/>
       <c r="P106" s="6"/>
       <c r="Q106" s="6"/>
     </row>
     <row r="107" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A107" s="6"/>
-      <c r="B107" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="D107" s="6"/>
-      <c r="E107" s="6"/>
-      <c r="F107" s="6"/>
-      <c r="G107" s="6"/>
-      <c r="H107" s="6"/>
-      <c r="I107" s="6"/>
-      <c r="J107" s="6"/>
-      <c r="K107" s="5"/>
-      <c r="L107" s="6"/>
-      <c r="M107" s="5"/>
-      <c r="N107" s="6"/>
       <c r="O107" s="6"/>
       <c r="P107" s="6"/>
       <c r="Q107" s="6"/>
     </row>
     <row r="108" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A108" s="6"/>
-      <c r="B108" s="1"/>
-      <c r="C108" s="1"/>
-      <c r="K108" s="5"/>
-      <c r="N108" s="6"/>
       <c r="O108" s="6"/>
       <c r="P108" s="6"/>
       <c r="Q108" s="6"/>
     </row>
     <row r="109" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A109" s="6"/>
-      <c r="B109" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="C109" s="1" t="s">
-        <v>119</v>
-      </c>
+      <c r="B109" s="8"/>
+      <c r="C109" s="5"/>
       <c r="D109" s="6"/>
       <c r="E109" s="6"/>
       <c r="F109" s="6"/>
@@ -3371,13 +3380,9 @@
       <c r="H109" s="6"/>
       <c r="I109" s="6"/>
       <c r="J109" s="6"/>
-      <c r="K109" s="5" t="s">
-        <v>174</v>
-      </c>
+      <c r="K109" s="5"/>
       <c r="L109" s="6"/>
-      <c r="M109" s="5" t="s">
-        <v>23</v>
-      </c>
+      <c r="M109" s="5"/>
       <c r="N109" s="6"/>
       <c r="O109" s="6"/>
       <c r="P109" s="6"/>
@@ -3386,9 +3391,6 @@
     <row r="110" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A110" s="6"/>
       <c r="B110" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="C110" s="1" t="s">
         <v>119</v>
       </c>
       <c r="D110" s="6"/>
@@ -3397,14 +3399,10 @@
       <c r="G110" s="6"/>
       <c r="H110" s="6"/>
       <c r="I110" s="6"/>
-      <c r="J110" s="8"/>
-      <c r="K110" s="5" t="s">
-        <v>122</v>
-      </c>
+      <c r="J110" s="6"/>
+      <c r="K110" s="5"/>
       <c r="L110" s="6"/>
-      <c r="M110" s="5" t="s">
-        <v>112</v>
-      </c>
+      <c r="M110" s="5"/>
       <c r="N110" s="6"/>
       <c r="O110" s="6"/>
       <c r="P110" s="6"/>
@@ -3412,22 +3410,9 @@
     </row>
     <row r="111" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A111" s="6"/>
-      <c r="B111" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="C111" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="D111" s="6"/>
-      <c r="E111" s="6"/>
-      <c r="F111" s="6"/>
-      <c r="G111" s="6"/>
-      <c r="H111" s="6"/>
-      <c r="I111" s="6"/>
-      <c r="J111" s="5"/>
+      <c r="B111" s="1"/>
+      <c r="C111" s="1"/>
       <c r="K111" s="5"/>
-      <c r="L111" s="6"/>
-      <c r="M111" s="5"/>
       <c r="N111" s="6"/>
       <c r="O111" s="6"/>
       <c r="P111" s="6"/>
@@ -3435,18 +3420,26 @@
     </row>
     <row r="112" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A112" s="6"/>
-      <c r="B112" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="C112" s="6" t="s">
+      <c r="B112" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C112" s="1" t="s">
         <v>119</v>
       </c>
+      <c r="D112" s="6"/>
+      <c r="E112" s="6"/>
+      <c r="F112" s="6"/>
+      <c r="G112" s="6"/>
       <c r="H112" s="6"/>
       <c r="I112" s="6"/>
       <c r="J112" s="6"/>
-      <c r="K112" s="5"/>
+      <c r="K112" s="5" t="s">
+        <v>174</v>
+      </c>
       <c r="L112" s="6"/>
-      <c r="M112" s="5"/>
+      <c r="M112" s="5" t="s">
+        <v>23</v>
+      </c>
       <c r="N112" s="6"/>
       <c r="O112" s="6"/>
       <c r="P112" s="6"/>
@@ -3454,24 +3447,26 @@
     </row>
     <row r="113" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A113" s="6"/>
-      <c r="B113" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="C113" s="6" t="s">
+      <c r="B113" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C113" s="1" t="s">
         <v>119</v>
       </c>
       <c r="D113" s="6"/>
       <c r="E113" s="6"/>
       <c r="F113" s="6"/>
-      <c r="G113" s="6" t="s">
-        <v>130</v>
-      </c>
+      <c r="G113" s="6"/>
       <c r="H113" s="6"/>
       <c r="I113" s="6"/>
-      <c r="J113" s="6"/>
-      <c r="K113" s="6"/>
+      <c r="J113" s="8"/>
+      <c r="K113" s="5" t="s">
+        <v>122</v>
+      </c>
       <c r="L113" s="6"/>
-      <c r="M113" s="6"/>
+      <c r="M113" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="N113" s="6"/>
       <c r="O113" s="6"/>
       <c r="P113" s="6"/>
@@ -3479,10 +3474,10 @@
     </row>
     <row r="114" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A114" s="6"/>
-      <c r="B114" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="C114" s="6" t="s">
+      <c r="B114" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C114" s="1" t="s">
         <v>119</v>
       </c>
       <c r="D114" s="6"/>
@@ -3496,28 +3491,24 @@
       <c r="L114" s="6"/>
       <c r="M114" s="5"/>
       <c r="N114" s="6"/>
-      <c r="O114" s="1"/>
+      <c r="O114" s="6"/>
       <c r="P114" s="6"/>
       <c r="Q114" s="6"/>
     </row>
     <row r="115" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A115" s="6"/>
       <c r="B115" s="6" t="s">
-        <v>231</v>
+        <v>131</v>
       </c>
       <c r="C115" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="D115" s="6"/>
-      <c r="E115" s="6"/>
-      <c r="F115" s="6"/>
-      <c r="G115" s="6"/>
       <c r="H115" s="6"/>
       <c r="I115" s="6"/>
       <c r="J115" s="6"/>
-      <c r="K115" s="6"/>
+      <c r="K115" s="5"/>
       <c r="L115" s="6"/>
-      <c r="M115" s="6"/>
+      <c r="M115" s="5"/>
       <c r="N115" s="6"/>
       <c r="O115" s="6"/>
       <c r="P115" s="6"/>
@@ -3525,18 +3516,24 @@
     </row>
     <row r="116" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A116" s="6"/>
-      <c r="B116" s="5"/>
-      <c r="C116" s="5"/>
+      <c r="B116" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="C116" s="6" t="s">
+        <v>119</v>
+      </c>
       <c r="D116" s="6"/>
       <c r="E116" s="6"/>
       <c r="F116" s="6"/>
-      <c r="G116" s="6"/>
+      <c r="G116" s="6" t="s">
+        <v>130</v>
+      </c>
       <c r="H116" s="6"/>
       <c r="I116" s="6"/>
-      <c r="J116" s="5"/>
-      <c r="K116" s="5"/>
+      <c r="J116" s="6"/>
+      <c r="K116" s="6"/>
       <c r="L116" s="6"/>
-      <c r="M116" s="5"/>
+      <c r="M116" s="6"/>
       <c r="N116" s="6"/>
       <c r="O116" s="6"/>
       <c r="P116" s="6"/>
@@ -3544,8 +3541,12 @@
     </row>
     <row r="117" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A117" s="6"/>
-      <c r="B117" s="5"/>
-      <c r="C117" s="5"/>
+      <c r="B117" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="C117" s="6" t="s">
+        <v>119</v>
+      </c>
       <c r="D117" s="6"/>
       <c r="E117" s="6"/>
       <c r="F117" s="6"/>
@@ -3557,30 +3558,28 @@
       <c r="L117" s="6"/>
       <c r="M117" s="5"/>
       <c r="N117" s="6"/>
-      <c r="O117" s="6"/>
+      <c r="O117" s="1"/>
       <c r="P117" s="6"/>
       <c r="Q117" s="6"/>
     </row>
     <row r="118" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A118" s="6"/>
-      <c r="B118" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="C118" s="5"/>
+      <c r="B118" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="C118" s="6" t="s">
+        <v>119</v>
+      </c>
       <c r="D118" s="6"/>
       <c r="E118" s="6"/>
       <c r="F118" s="6"/>
       <c r="G118" s="6"/>
       <c r="H118" s="6"/>
       <c r="I118" s="6"/>
-      <c r="J118" s="5"/>
-      <c r="K118" s="5" t="s">
-        <v>25</v>
-      </c>
+      <c r="J118" s="6"/>
+      <c r="K118" s="6"/>
       <c r="L118" s="6"/>
-      <c r="M118" s="5" t="s">
-        <v>23</v>
-      </c>
+      <c r="M118" s="6"/>
       <c r="N118" s="6"/>
       <c r="O118" s="6"/>
       <c r="P118" s="6"/>
@@ -3597,13 +3596,9 @@
       <c r="H119" s="6"/>
       <c r="I119" s="6"/>
       <c r="J119" s="5"/>
-      <c r="K119" s="5" t="s">
-        <v>26</v>
-      </c>
+      <c r="K119" s="5"/>
       <c r="L119" s="6"/>
-      <c r="M119" s="5" t="s">
-        <v>23</v>
-      </c>
+      <c r="M119" s="5"/>
       <c r="N119" s="6"/>
       <c r="O119" s="6"/>
       <c r="P119" s="6"/>
@@ -3620,13 +3615,9 @@
       <c r="H120" s="6"/>
       <c r="I120" s="6"/>
       <c r="J120" s="5"/>
-      <c r="K120" s="5" t="s">
-        <v>41</v>
-      </c>
+      <c r="K120" s="5"/>
       <c r="L120" s="6"/>
-      <c r="M120" s="5" t="s">
-        <v>23</v>
-      </c>
+      <c r="M120" s="5"/>
       <c r="N120" s="6"/>
       <c r="O120" s="6"/>
       <c r="P120" s="6"/>
@@ -3634,7 +3625,9 @@
     </row>
     <row r="121" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A121" s="6"/>
-      <c r="B121" s="5"/>
+      <c r="B121" s="5" t="s">
+        <v>239</v>
+      </c>
       <c r="C121" s="5"/>
       <c r="D121" s="6"/>
       <c r="E121" s="6"/>
@@ -3644,7 +3637,7 @@
       <c r="I121" s="6"/>
       <c r="J121" s="5"/>
       <c r="K121" s="5" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="L121" s="6"/>
       <c r="M121" s="5" t="s">
@@ -3657,17 +3650,17 @@
     </row>
     <row r="122" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A122" s="6"/>
-      <c r="B122" s="6"/>
-      <c r="C122" s="6"/>
+      <c r="B122" s="5"/>
+      <c r="C122" s="5"/>
       <c r="D122" s="6"/>
       <c r="E122" s="6"/>
       <c r="F122" s="6"/>
       <c r="G122" s="6"/>
       <c r="H122" s="6"/>
       <c r="I122" s="6"/>
-      <c r="J122" s="6"/>
+      <c r="J122" s="5"/>
       <c r="K122" s="5" t="s">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="L122" s="6"/>
       <c r="M122" s="5" t="s">
@@ -3680,20 +3673,21 @@
     </row>
     <row r="123" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A123" s="6"/>
-      <c r="B123" s="6"/>
-      <c r="C123" s="6"/>
+      <c r="B123" s="5"/>
+      <c r="C123" s="5"/>
       <c r="D123" s="6"/>
       <c r="E123" s="6"/>
       <c r="F123" s="6"/>
       <c r="G123" s="6"/>
       <c r="H123" s="6"/>
       <c r="I123" s="6"/>
-      <c r="J123" s="6"/>
-      <c r="K123" s="1" t="s">
-        <v>143</v>
-      </c>
+      <c r="J123" s="5"/>
+      <c r="K123" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="L123" s="6"/>
       <c r="M123" s="5" t="s">
-        <v>241</v>
+        <v>23</v>
       </c>
       <c r="N123" s="6"/>
       <c r="O123" s="6"/>
@@ -3701,8 +3695,8 @@
       <c r="Q123" s="6"/>
     </row>
     <row r="124" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A124" s="5"/>
-      <c r="B124" s="8"/>
+      <c r="A124" s="6"/>
+      <c r="B124" s="5"/>
       <c r="C124" s="5"/>
       <c r="D124" s="6"/>
       <c r="E124" s="6"/>
@@ -3710,57 +3704,61 @@
       <c r="G124" s="6"/>
       <c r="H124" s="6"/>
       <c r="I124" s="6"/>
-      <c r="J124" s="8"/>
-      <c r="K124" s="1" t="s">
-        <v>150</v>
-      </c>
+      <c r="J124" s="5"/>
+      <c r="K124" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="L124" s="6"/>
       <c r="M124" s="5" t="s">
-        <v>103</v>
+        <v>23</v>
       </c>
       <c r="N124" s="6"/>
-      <c r="O124" s="5"/>
+      <c r="O124" s="6"/>
       <c r="P124" s="6"/>
       <c r="Q124" s="6"/>
     </row>
     <row r="125" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A125" s="5"/>
-      <c r="B125" s="8"/>
-      <c r="C125" s="5"/>
+      <c r="A125" s="6"/>
+      <c r="B125" s="6"/>
+      <c r="C125" s="6"/>
       <c r="D125" s="6"/>
       <c r="E125" s="6"/>
       <c r="F125" s="6"/>
       <c r="G125" s="6"/>
       <c r="H125" s="6"/>
       <c r="I125" s="6"/>
-      <c r="J125" s="8"/>
-      <c r="K125" s="1"/>
-      <c r="M125" s="5"/>
+      <c r="J125" s="6"/>
+      <c r="K125" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="L125" s="6"/>
+      <c r="M125" s="5" t="s">
+        <v>23</v>
+      </c>
       <c r="N125" s="6"/>
-      <c r="O125" s="5"/>
+      <c r="O125" s="6"/>
       <c r="P125" s="6"/>
       <c r="Q125" s="6"/>
     </row>
     <row r="126" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A126" s="5"/>
-      <c r="B126" s="8" t="s">
-        <v>240</v>
-      </c>
-      <c r="C126" s="5"/>
+      <c r="A126" s="6"/>
+      <c r="B126" s="6"/>
+      <c r="C126" s="6"/>
       <c r="D126" s="6"/>
       <c r="E126" s="6"/>
       <c r="F126" s="6"/>
       <c r="G126" s="6"/>
       <c r="H126" s="6"/>
       <c r="I126" s="6"/>
-      <c r="J126" s="8"/>
+      <c r="J126" s="6"/>
       <c r="K126" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="M126" s="1" t="s">
-        <v>242</v>
+        <v>143</v>
+      </c>
+      <c r="M126" s="5" t="s">
+        <v>241</v>
       </c>
       <c r="N126" s="6"/>
-      <c r="O126" s="5"/>
+      <c r="O126" s="6"/>
       <c r="P126" s="6"/>
       <c r="Q126" s="6"/>
     </row>
@@ -3776,10 +3774,10 @@
       <c r="I127" s="6"/>
       <c r="J127" s="8"/>
       <c r="K127" s="1" t="s">
-        <v>134</v>
+        <v>150</v>
       </c>
       <c r="M127" s="5" t="s">
-        <v>66</v>
+        <v>103</v>
       </c>
       <c r="N127" s="6"/>
       <c r="O127" s="5"/>
@@ -3804,314 +3802,355 @@
       <c r="P128" s="6"/>
       <c r="Q128" s="6"/>
     </row>
-    <row r="129" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K129" s="1"/>
-      <c r="M129" s="5"/>
-    </row>
-    <row r="130" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="C130" s="6"/>
+    <row r="129" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A129" s="5"/>
+      <c r="B129" s="8" t="s">
+        <v>240</v>
+      </c>
+      <c r="C129" s="5"/>
+      <c r="D129" s="6"/>
+      <c r="E129" s="6"/>
+      <c r="F129" s="6"/>
+      <c r="G129" s="6"/>
+      <c r="H129" s="6"/>
+      <c r="I129" s="6"/>
+      <c r="J129" s="8"/>
+      <c r="K129" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M129" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="N129" s="6"/>
+      <c r="O129" s="5"/>
+      <c r="P129" s="6"/>
+      <c r="Q129" s="6"/>
+    </row>
+    <row r="130" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A130" s="5"/>
+      <c r="B130" s="8"/>
+      <c r="C130" s="5"/>
       <c r="D130" s="6"/>
       <c r="E130" s="6"/>
       <c r="F130" s="6"/>
       <c r="G130" s="6"/>
       <c r="H130" s="6"/>
       <c r="I130" s="6"/>
-      <c r="J130" s="6"/>
-      <c r="K130" s="5"/>
-      <c r="L130" s="6"/>
-      <c r="M130" s="5"/>
+      <c r="J130" s="8"/>
+      <c r="K130" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="M130" s="5" t="s">
+        <v>66</v>
+      </c>
       <c r="N130" s="6"/>
-      <c r="O130" s="6"/>
-    </row>
-    <row r="131" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O130" s="5"/>
+      <c r="P130" s="6"/>
+      <c r="Q130" s="6"/>
+    </row>
+    <row r="131" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A131" s="5"/>
+      <c r="B131" s="8"/>
+      <c r="C131" s="5"/>
+      <c r="D131" s="6"/>
+      <c r="E131" s="6"/>
+      <c r="F131" s="6"/>
+      <c r="G131" s="6"/>
+      <c r="H131" s="6"/>
+      <c r="I131" s="6"/>
+      <c r="J131" s="8"/>
+      <c r="K131" s="1"/>
+      <c r="M131" s="5"/>
       <c r="N131" s="6"/>
-      <c r="O131" s="6"/>
-    </row>
-    <row r="132" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B132" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="N132" s="6"/>
-    </row>
-    <row r="133" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O131" s="5"/>
+      <c r="P131" s="6"/>
+      <c r="Q131" s="6"/>
+    </row>
+    <row r="132" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K132" s="1"/>
+      <c r="M132" s="5"/>
+    </row>
+    <row r="133" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="C133" s="6"/>
+      <c r="D133" s="6"/>
+      <c r="E133" s="6"/>
+      <c r="F133" s="6"/>
+      <c r="G133" s="6"/>
+      <c r="H133" s="6"/>
+      <c r="I133" s="6"/>
+      <c r="J133" s="6"/>
+      <c r="K133" s="5"/>
+      <c r="L133" s="6"/>
+      <c r="M133" s="5"/>
       <c r="N133" s="6"/>
       <c r="O133" s="6"/>
     </row>
-    <row r="134" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B134" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="C134" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="D134" s="6"/>
-      <c r="E134" s="6"/>
-      <c r="F134" s="6"/>
-      <c r="G134" s="6"/>
-      <c r="H134" s="6"/>
-      <c r="I134" s="6"/>
-      <c r="J134" s="6"/>
-      <c r="K134" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="M134" s="1" t="s">
-        <v>128</v>
-      </c>
+    <row r="134" spans="1:17" x14ac:dyDescent="0.2">
       <c r="N134" s="6"/>
       <c r="O134" s="6"/>
     </row>
-    <row r="135" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K135" s="1" t="s">
+    <row r="135" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="B135" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="N135" s="6"/>
+    </row>
+    <row r="136" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="N136" s="6"/>
+      <c r="O136" s="6"/>
+    </row>
+    <row r="137" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="B137" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="C137" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D137" s="6"/>
+      <c r="E137" s="6"/>
+      <c r="F137" s="6"/>
+      <c r="G137" s="6"/>
+      <c r="H137" s="6"/>
+      <c r="I137" s="6"/>
+      <c r="J137" s="6"/>
+      <c r="K137" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="M137" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="N137" s="6"/>
+      <c r="O137" s="6"/>
+    </row>
+    <row r="138" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K138" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="M135" s="1" t="s">
+      <c r="M138" s="1" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="136" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K136" s="1" t="s">
+    <row r="139" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K139" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="M136" s="1" t="s">
+      <c r="M139" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="138" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B138" s="6" t="s">
+    <row r="141" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="B141" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="C138" s="6" t="s">
+      <c r="C141" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="D138" s="6"/>
-      <c r="E138" s="6"/>
-      <c r="F138" s="6"/>
-      <c r="G138" s="6"/>
-      <c r="H138" s="6"/>
-      <c r="I138" s="6"/>
-      <c r="J138" s="6"/>
-      <c r="K138" s="5"/>
-      <c r="L138" s="6"/>
-      <c r="M138" s="5"/>
-    </row>
-    <row r="139" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B139" s="6"/>
-      <c r="C139" s="6"/>
-      <c r="D139" s="6"/>
-      <c r="E139" s="6"/>
-      <c r="F139" s="6"/>
-      <c r="G139" s="6"/>
-      <c r="H139" s="6"/>
-      <c r="I139" s="6"/>
-      <c r="J139" s="6"/>
-      <c r="K139" s="5"/>
-      <c r="L139" s="6"/>
-      <c r="M139" s="5"/>
-    </row>
-    <row r="140" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B140" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="C140" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="D140" s="6"/>
-      <c r="E140" s="6"/>
-      <c r="F140" s="6"/>
-      <c r="G140" s="6"/>
-      <c r="H140" s="6"/>
-      <c r="I140" s="6"/>
-      <c r="J140" s="6"/>
-      <c r="K140" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="M140" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="141" spans="2:15" x14ac:dyDescent="0.2">
       <c r="D141" s="6"/>
       <c r="E141" s="6"/>
       <c r="F141" s="6"/>
-      <c r="G141" s="5"/>
+      <c r="G141" s="6"/>
       <c r="H141" s="6"/>
       <c r="I141" s="6"/>
-      <c r="J141" s="5"/>
-      <c r="K141" s="5" t="s">
-        <v>111</v>
-      </c>
+      <c r="J141" s="6"/>
+      <c r="K141" s="5"/>
       <c r="L141" s="6"/>
-      <c r="M141" s="5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="142" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="M141" s="5"/>
+    </row>
+    <row r="142" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="B142" s="6"/>
+      <c r="C142" s="6"/>
       <c r="D142" s="6"/>
       <c r="E142" s="6"/>
       <c r="F142" s="6"/>
-      <c r="G142" s="5"/>
+      <c r="G142" s="6"/>
       <c r="H142" s="6"/>
       <c r="I142" s="6"/>
-      <c r="J142" s="5"/>
+      <c r="J142" s="6"/>
       <c r="K142" s="5"/>
       <c r="L142" s="6"/>
       <c r="M142" s="5"/>
     </row>
-    <row r="143" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B143" s="1" t="s">
-        <v>247</v>
+    <row r="143" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="B143" s="6" t="s">
+        <v>110</v>
       </c>
       <c r="C143" s="6" t="s">
         <v>64</v>
       </c>
+      <c r="D143" s="6"/>
+      <c r="E143" s="6"/>
+      <c r="F143" s="6"/>
+      <c r="G143" s="6"/>
+      <c r="H143" s="6"/>
+      <c r="I143" s="6"/>
+      <c r="J143" s="6"/>
       <c r="K143" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="M143" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="144" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="D144" s="6"/>
+      <c r="E144" s="6"/>
+      <c r="F144" s="6"/>
+      <c r="G144" s="5"/>
+      <c r="H144" s="6"/>
+      <c r="I144" s="6"/>
+      <c r="J144" s="5"/>
+      <c r="K144" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="L144" s="6"/>
+      <c r="M144" s="5" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="145" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="D145" s="6"/>
+      <c r="E145" s="6"/>
+      <c r="F145" s="6"/>
+      <c r="G145" s="5"/>
+      <c r="H145" s="6"/>
+      <c r="I145" s="6"/>
+      <c r="J145" s="5"/>
+      <c r="K145" s="5"/>
+      <c r="L145" s="6"/>
+      <c r="M145" s="5"/>
+    </row>
+    <row r="146" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B146" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="C146" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="K146" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M143" s="1" t="s">
+      <c r="M146" s="1" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="144" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B144" s="1" t="s">
+    <row r="147" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B147" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="C144" s="1" t="s">
+      <c r="C147" s="1" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="145" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A145" s="1"/>
-      <c r="B145" s="1"/>
-      <c r="C145" s="1"/>
-    </row>
-    <row r="146" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="B146" s="1"/>
-      <c r="C146" s="1"/>
-    </row>
-    <row r="147" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="B147" s="1"/>
-      <c r="C147" s="1"/>
-    </row>
     <row r="148" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="B148" s="1" t="s">
+      <c r="A148" s="1"/>
+      <c r="B148" s="1"/>
+      <c r="C148" s="1"/>
+    </row>
+    <row r="149" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B149" s="1"/>
+      <c r="C149" s="1"/>
+    </row>
+    <row r="150" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B150" s="1"/>
+      <c r="C150" s="1"/>
+    </row>
+    <row r="151" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B151" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="K148" s="1" t="s">
+      <c r="K151" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="M148" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="149" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="K149" s="1" t="s">
+      <c r="M151" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="152" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="K152" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="M149" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="150" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="K150" s="1"/>
-    </row>
-    <row r="152" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="B152" s="1" t="s">
+      <c r="M152" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="153" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="K153" s="1"/>
+    </row>
+    <row r="155" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B155" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="K152" s="1" t="s">
+      <c r="K155" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="M152" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="O152" s="6"/>
-    </row>
-    <row r="153" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="K153" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="M153" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="154" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="K154" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="M154" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="155" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="K155" s="1" t="s">
-        <v>33</v>
-      </c>
       <c r="M155" s="1" t="s">
-        <v>198</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="O155" s="6"/>
     </row>
     <row r="156" spans="1:15" x14ac:dyDescent="0.2">
       <c r="K156" s="1" t="s">
-        <v>199</v>
+        <v>26</v>
       </c>
       <c r="M156" s="1" t="s">
-        <v>112</v>
+        <v>23</v>
       </c>
     </row>
     <row r="157" spans="1:15" x14ac:dyDescent="0.2">
       <c r="K157" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="M157" s="5" t="s">
-        <v>103</v>
+        <v>41</v>
+      </c>
+      <c r="M157" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="158" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="B158" s="1" t="s">
-        <v>227</v>
-      </c>
       <c r="K158" s="1" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="M158" s="1" t="s">
-        <v>23</v>
+        <v>198</v>
       </c>
     </row>
     <row r="159" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="B159" s="1"/>
       <c r="K159" s="1" t="s">
-        <v>26</v>
+        <v>199</v>
       </c>
       <c r="M159" s="1" t="s">
-        <v>23</v>
+        <v>112</v>
       </c>
     </row>
     <row r="160" spans="1:15" x14ac:dyDescent="0.2">
       <c r="K160" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="M160" s="5" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="161" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B161" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="K161" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="M161" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="162" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B162" s="1"/>
+      <c r="K162" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M162" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="163" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K163" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="M160" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="161" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K161" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="M161" s="1" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="162" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K162" s="1"/>
-      <c r="M162" s="1"/>
-    </row>
-    <row r="163" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B163" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="K163" s="1" t="s">
-        <v>25</v>
       </c>
       <c r="M163" s="1" t="s">
         <v>23</v>
@@ -4119,23 +4158,22 @@
     </row>
     <row r="164" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K164" s="1" t="s">
-        <v>26</v>
+        <v>228</v>
       </c>
       <c r="M164" s="1" t="s">
-        <v>23</v>
+        <v>229</v>
       </c>
     </row>
     <row r="165" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K165" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="M165" s="1" t="s">
-        <v>23</v>
-      </c>
+      <c r="K165" s="1"/>
+      <c r="M165" s="1"/>
     </row>
     <row r="166" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B166" s="1" t="s">
+        <v>230</v>
+      </c>
       <c r="K166" s="1" t="s">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="M166" s="1" t="s">
         <v>23</v>
@@ -4143,241 +4181,265 @@
     </row>
     <row r="167" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K167" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M167" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="168" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K168" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M168" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="169" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K169" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="M169" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="170" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K170" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="M167" s="1" t="s">
+      <c r="M170" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="168" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K168" s="1"/>
-    </row>
-    <row r="170" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B170" s="1" t="s">
+    <row r="171" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K171" s="1"/>
+    </row>
+    <row r="173" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B173" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="K170" s="1" t="s">
+      <c r="K173" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="M170" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="O170" s="1" t="s">
+      <c r="M173" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O173" s="1" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="171" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K171" s="1" t="s">
+    <row r="174" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K174" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="M171" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="O171" s="1" t="s">
+      <c r="M174" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O174" s="1" t="s">
         <v>210</v>
-      </c>
-    </row>
-    <row r="172" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K172" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="M172" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="O172" s="1" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="173" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K173" s="1"/>
-    </row>
-    <row r="174" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B174" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="K174" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="M174" s="1" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="175" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K175" s="1" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="M175" s="1" t="s">
         <v>23</v>
       </c>
+      <c r="O175" s="1" t="s">
+        <v>211</v>
+      </c>
     </row>
     <row r="176" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K176" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="M176" s="1" t="s">
-        <v>23</v>
-      </c>
+      <c r="K176" s="1"/>
     </row>
     <row r="177" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B177" s="1" t="s">
+        <v>208</v>
+      </c>
       <c r="K177" s="1" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="M177" s="1" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
     </row>
     <row r="178" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K178" s="1" t="s">
-        <v>218</v>
+        <v>26</v>
       </c>
       <c r="M178" s="1" t="s">
-        <v>217</v>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="179" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K179" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M179" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="180" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B180" s="1" t="s">
-        <v>213</v>
-      </c>
       <c r="K180" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="M180" s="1" t="s">
-        <v>23</v>
+        <v>103</v>
       </c>
     </row>
     <row r="181" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K181" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="M181" s="1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="183" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B183" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="K183" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="M183" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="184" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K184" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="M181" s="1" t="s">
+      <c r="M184" s="1" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="184" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B184" s="1" t="s">
+    <row r="187" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B187" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="K184" s="1" t="s">
+      <c r="K187" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="M184" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="O184" s="1" t="s">
+      <c r="M187" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O187" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="185" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K185" s="1" t="s">
+    <row r="188" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K188" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="M185" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="O185" s="1" t="s">
+      <c r="M188" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O188" s="1" t="s">
         <v>220</v>
-      </c>
-    </row>
-    <row r="186" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K186" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="M186" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="O186" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="187" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K187" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="M187" s="1" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="188" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B188" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="K188" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="M188" s="1" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="189" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K189" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M189" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O189" s="1" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="190" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K190" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="M190" s="1" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="191" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B191" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="K191" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M191" s="1" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="192" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K192" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="M189" s="1" t="s">
+      <c r="M192" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="193" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B193" s="1" t="s">
+    <row r="196" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B196" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="G193" s="1" t="s">
+      <c r="G196" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="K193" s="1" t="s">
+      <c r="K196" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="M193" s="1" t="s">
+      <c r="M196" s="1" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="194" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="K194" s="1" t="s">
+    <row r="197" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="K197" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="M194" s="1" t="s">
+      <c r="M197" s="1" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="197" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B197" s="1" t="s">
+    <row r="200" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B200" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="K197" s="1" t="s">
+      <c r="K200" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="M197" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="198" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="K198" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="M198" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="199" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="K199" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="M199" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="200" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="K200" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="M200" s="6" t="s">
-        <v>99</v>
+      <c r="M200" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="201" spans="2:13" x14ac:dyDescent="0.2">
       <c r="K201" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M201" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="202" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="K202" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M202" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="203" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="K203" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="M203" s="6" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="204" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="K204" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="M201" s="1" t="s">
+      <c r="M204" s="1" t="s">
         <v>94</v>
       </c>
     </row>

--- a/Config/Datas/__beans__.xlsx
+++ b/Config/Datas/__beans__.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77B128A6-AF9F-4AC9-AF4A-0F4A3CDF67AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55AB2BAD-8451-4E0F-B9FB-D92CF73BB5C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="260">
   <si>
     <t>##var</t>
   </si>
@@ -1476,7 +1476,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q204"/>
+  <dimension ref="A1:Q205"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="28.75" customWidth="1"/>
@@ -4421,7 +4421,7 @@
     </row>
     <row r="202" spans="2:13" x14ac:dyDescent="0.2">
       <c r="K202" s="1" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="M202" s="1" t="s">
         <v>23</v>
@@ -4429,17 +4429,25 @@
     </row>
     <row r="203" spans="2:13" x14ac:dyDescent="0.2">
       <c r="K203" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="M203" s="6" t="s">
-        <v>99</v>
+        <v>41</v>
+      </c>
+      <c r="M203" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="204" spans="2:13" x14ac:dyDescent="0.2">
       <c r="K204" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="M204" s="6" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="205" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="K205" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="M204" s="1" t="s">
+      <c r="M205" s="1" t="s">
         <v>94</v>
       </c>
     </row>

--- a/Config/Datas/__beans__.xlsx
+++ b/Config/Datas/__beans__.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55AB2BAD-8451-4E0F-B9FB-D92CF73BB5C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92D07897-5E17-4E42-A885-DEFA9BB2BC37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="269">
   <si>
     <t>##var</t>
   </si>
@@ -1049,6 +1049,42 @@
   </si>
   <si>
     <t>originCost</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GA_增加顾客等待值</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GetCustomerInfo</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GetCustomerStrategy</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>(DynamicValue#sep=-)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GetCustomerInfo#sep=,</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CustomerCGA</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CustomerActionType</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>actionCGAs</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>list,CustomerCGA</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1476,7 +1512,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q205"/>
+  <dimension ref="A1:Q213"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="28.75" customWidth="1"/>
@@ -2694,176 +2730,98 @@
     <row r="66" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A66" s="6"/>
       <c r="K66" s="5"/>
-      <c r="M66" s="5"/>
+      <c r="M66" s="6"/>
       <c r="P66" s="7"/>
       <c r="Q66" s="6"/>
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A67" s="6"/>
+      <c r="B67" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="K67" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="M67" s="5" t="s">
+        <v>266</v>
+      </c>
       <c r="P67" s="7"/>
       <c r="Q67" s="6"/>
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A68" s="6"/>
-      <c r="B68" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="C68" s="6"/>
-      <c r="D68" s="6"/>
-      <c r="E68" s="6"/>
-      <c r="F68" s="6"/>
-      <c r="G68" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="H68" s="6"/>
-      <c r="I68" s="6"/>
-      <c r="J68" s="5"/>
-      <c r="K68" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="L68" s="6"/>
-      <c r="M68" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="N68" s="9"/>
-      <c r="O68" s="6"/>
-      <c r="P68" s="6"/>
+      <c r="K68" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="M68" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="P68" s="7"/>
       <c r="Q68" s="6"/>
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A69" s="6"/>
-      <c r="B69" s="6"/>
-      <c r="C69" s="6"/>
-      <c r="D69" s="6"/>
-      <c r="E69" s="6"/>
-      <c r="F69" s="6"/>
-      <c r="G69" s="6"/>
-      <c r="H69" s="6"/>
-      <c r="I69" s="6"/>
-      <c r="J69" s="6"/>
-      <c r="K69" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="L69" s="6"/>
-      <c r="M69" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="N69" s="9"/>
-      <c r="O69" s="6"/>
-      <c r="P69" s="6"/>
+      <c r="K69" s="5"/>
+      <c r="M69" s="6"/>
+      <c r="P69" s="7"/>
       <c r="Q69" s="6"/>
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A70" s="6"/>
-      <c r="B70" s="6"/>
-      <c r="C70" s="6"/>
-      <c r="D70" s="6"/>
-      <c r="E70" s="6"/>
-      <c r="F70" s="6"/>
-      <c r="G70" s="6"/>
-      <c r="H70" s="6"/>
-      <c r="J70" s="6"/>
-      <c r="K70" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="L70" s="6"/>
-      <c r="M70" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="N70" s="9"/>
-      <c r="O70" s="6"/>
-      <c r="P70" s="6"/>
+      <c r="K70" s="5"/>
+      <c r="M70" s="6"/>
+      <c r="P70" s="7"/>
       <c r="Q70" s="6"/>
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A71" s="6"/>
-      <c r="B71" s="6"/>
-      <c r="C71" s="6"/>
-      <c r="D71" s="6"/>
-      <c r="E71" s="6"/>
-      <c r="F71" s="6"/>
-      <c r="G71" s="6"/>
-      <c r="H71" s="6"/>
-      <c r="I71" s="6"/>
-      <c r="J71" s="6"/>
-      <c r="K71" s="8" t="s">
-        <v>256</v>
-      </c>
-      <c r="M71" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="P71" s="6"/>
+      <c r="K71" s="5"/>
+      <c r="M71" s="6"/>
+      <c r="P71" s="7"/>
       <c r="Q71" s="6"/>
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A72" s="6"/>
-      <c r="B72" s="6"/>
-      <c r="C72" s="6"/>
-      <c r="D72" s="6"/>
-      <c r="E72" s="6"/>
-      <c r="F72" s="6"/>
-      <c r="G72" s="6"/>
-      <c r="H72" s="6"/>
-      <c r="I72" s="6"/>
-      <c r="J72" s="6"/>
-      <c r="K72" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="M72" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="N72" s="9"/>
-      <c r="O72" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="P72" s="6"/>
+      <c r="K72" s="5"/>
+      <c r="M72" s="5"/>
+      <c r="P72" s="7"/>
       <c r="Q72" s="6"/>
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A73" s="6"/>
-      <c r="B73" s="6"/>
-      <c r="C73" s="6"/>
-      <c r="D73" s="6"/>
-      <c r="E73" s="6"/>
-      <c r="F73" s="6"/>
-      <c r="G73" s="6"/>
-      <c r="H73" s="6"/>
-      <c r="I73" s="6"/>
-      <c r="J73" s="6"/>
-      <c r="K73" s="8" t="s">
-        <v>168</v>
-      </c>
-      <c r="L73" s="6"/>
-      <c r="M73" s="8" t="s">
-        <v>167</v>
-      </c>
-      <c r="N73" s="6"/>
-      <c r="O73" s="8"/>
-      <c r="P73" s="6"/>
+      <c r="P73" s="7"/>
       <c r="Q73" s="6"/>
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A74" s="6"/>
-      <c r="B74" s="5"/>
+      <c r="B74" s="5" t="s">
+        <v>73</v>
+      </c>
       <c r="C74" s="6"/>
       <c r="D74" s="6"/>
       <c r="E74" s="6"/>
       <c r="F74" s="6"/>
-      <c r="G74" s="6"/>
+      <c r="G74" s="6" t="s">
+        <v>70</v>
+      </c>
       <c r="H74" s="6"/>
       <c r="I74" s="6"/>
-      <c r="J74" s="6"/>
-      <c r="K74" s="2"/>
-      <c r="M74" s="2"/>
-      <c r="O74" s="2"/>
+      <c r="J74" s="5"/>
+      <c r="K74" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="L74" s="6"/>
+      <c r="M74" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="N74" s="9"/>
+      <c r="O74" s="6"/>
       <c r="P74" s="6"/>
       <c r="Q74" s="6"/>
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A75" s="6"/>
-      <c r="B75" s="6" t="s">
-        <v>79</v>
-      </c>
+      <c r="B75" s="6"/>
       <c r="C75" s="6"/>
       <c r="D75" s="6"/>
       <c r="E75" s="6"/>
@@ -2872,15 +2830,15 @@
       <c r="H75" s="6"/>
       <c r="I75" s="6"/>
       <c r="J75" s="6"/>
-      <c r="K75" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="M75" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="O75" s="11" t="s">
-        <v>81</v>
-      </c>
+      <c r="K75" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="L75" s="6"/>
+      <c r="M75" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="N75" s="9"/>
+      <c r="O75" s="6"/>
       <c r="P75" s="6"/>
       <c r="Q75" s="6"/>
     </row>
@@ -2893,66 +2851,83 @@
       <c r="F76" s="6"/>
       <c r="G76" s="6"/>
       <c r="H76" s="6"/>
-      <c r="I76" s="6"/>
       <c r="J76" s="6"/>
-      <c r="K76" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="M76" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="O76" s="11" t="s">
-        <v>80</v>
-      </c>
+      <c r="K76" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="L76" s="6"/>
+      <c r="M76" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="N76" s="9"/>
+      <c r="O76" s="6"/>
       <c r="P76" s="6"/>
       <c r="Q76" s="6"/>
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A77" s="6"/>
+      <c r="B77" s="6"/>
+      <c r="C77" s="6"/>
+      <c r="D77" s="6"/>
+      <c r="E77" s="6"/>
+      <c r="F77" s="6"/>
+      <c r="G77" s="6"/>
       <c r="H77" s="6"/>
       <c r="I77" s="6"/>
       <c r="J77" s="6"/>
-      <c r="K77" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="M77" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="O77" s="11" t="s">
-        <v>86</v>
+      <c r="K77" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="M77" s="8" t="s">
+        <v>112</v>
       </c>
       <c r="P77" s="6"/>
       <c r="Q77" s="6"/>
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A78" s="6"/>
+      <c r="B78" s="6"/>
+      <c r="C78" s="6"/>
+      <c r="D78" s="6"/>
+      <c r="E78" s="6"/>
+      <c r="F78" s="6"/>
+      <c r="G78" s="6"/>
       <c r="H78" s="6"/>
       <c r="I78" s="6"/>
       <c r="J78" s="6"/>
-      <c r="K78" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="M78" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="N78" s="6"/>
+      <c r="K78" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="M78" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="N78" s="9"/>
       <c r="O78" s="6" t="s">
-        <v>85</v>
+        <v>63</v>
       </c>
       <c r="P78" s="6"/>
       <c r="Q78" s="6"/>
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A79" s="6"/>
-      <c r="K79" s="11" t="s">
-        <v>144</v>
-      </c>
-      <c r="M79" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="O79" s="11" t="s">
-        <v>61</v>
-      </c>
+      <c r="B79" s="6"/>
+      <c r="C79" s="6"/>
+      <c r="D79" s="6"/>
+      <c r="E79" s="6"/>
+      <c r="F79" s="6"/>
+      <c r="G79" s="6"/>
+      <c r="H79" s="6"/>
+      <c r="I79" s="6"/>
+      <c r="J79" s="6"/>
+      <c r="K79" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="L79" s="6"/>
+      <c r="M79" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="N79" s="6"/>
+      <c r="O79" s="8"/>
       <c r="P79" s="6"/>
       <c r="Q79" s="6"/>
     </row>
@@ -2964,439 +2939,488 @@
       <c r="E80" s="6"/>
       <c r="F80" s="6"/>
       <c r="G80" s="6"/>
-      <c r="K80" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="M80" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="O80" s="11"/>
+      <c r="H80" s="6"/>
+      <c r="I80" s="6"/>
+      <c r="J80" s="6"/>
+      <c r="K80" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="M80" s="8" t="s">
+        <v>268</v>
+      </c>
+      <c r="N80" s="6"/>
+      <c r="O80" s="8"/>
       <c r="P80" s="6"/>
       <c r="Q80" s="6"/>
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A81" s="6"/>
-      <c r="K81" s="11"/>
-      <c r="M81" s="11"/>
-      <c r="O81" s="11"/>
+      <c r="B81" s="6"/>
+      <c r="C81" s="6"/>
+      <c r="D81" s="6"/>
+      <c r="E81" s="6"/>
+      <c r="F81" s="6"/>
+      <c r="G81" s="6"/>
+      <c r="H81" s="6"/>
+      <c r="I81" s="6"/>
+      <c r="J81" s="6"/>
+      <c r="K81" s="8"/>
+      <c r="L81" s="6"/>
+      <c r="M81" s="8"/>
+      <c r="N81" s="6"/>
+      <c r="O81" s="8"/>
       <c r="P81" s="6"/>
-      <c r="Q81" s="7"/>
+      <c r="Q81" s="6"/>
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A82" s="6"/>
+      <c r="B82" s="5"/>
+      <c r="C82" s="6"/>
+      <c r="D82" s="6"/>
+      <c r="E82" s="6"/>
+      <c r="F82" s="6"/>
+      <c r="G82" s="6"/>
+      <c r="H82" s="6"/>
+      <c r="I82" s="6"/>
+      <c r="J82" s="6"/>
+      <c r="K82" s="2"/>
+      <c r="M82" s="2"/>
+      <c r="O82" s="2"/>
       <c r="P82" s="6"/>
       <c r="Q82" s="6"/>
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A83" s="6"/>
-      <c r="B83" s="6"/>
+      <c r="B83" s="6" t="s">
+        <v>79</v>
+      </c>
       <c r="C83" s="6"/>
       <c r="D83" s="6"/>
       <c r="E83" s="6"/>
       <c r="F83" s="6"/>
       <c r="G83" s="6"/>
-      <c r="K83" s="1"/>
-      <c r="M83" s="1"/>
-      <c r="O83" s="1"/>
-      <c r="P83" s="7"/>
+      <c r="H83" s="6"/>
+      <c r="I83" s="6"/>
+      <c r="J83" s="6"/>
+      <c r="K83" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="M83" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="O83" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="P83" s="6"/>
       <c r="Q83" s="6"/>
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A84" s="6"/>
-      <c r="B84" s="1" t="s">
-        <v>82</v>
-      </c>
+      <c r="B84" s="6"/>
+      <c r="C84" s="6"/>
+      <c r="D84" s="6"/>
+      <c r="E84" s="6"/>
+      <c r="F84" s="6"/>
+      <c r="G84" s="6"/>
+      <c r="H84" s="6"/>
+      <c r="I84" s="6"/>
+      <c r="J84" s="6"/>
       <c r="K84" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="M84" s="1" t="s">
-        <v>112</v>
+        <v>26</v>
+      </c>
+      <c r="M84" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="O84" s="11" t="s">
+        <v>80</v>
       </c>
       <c r="P84" s="6"/>
       <c r="Q84" s="6"/>
     </row>
     <row r="85" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A85" s="5"/>
-      <c r="B85" s="6"/>
-      <c r="C85" s="6"/>
+      <c r="A85" s="6"/>
+      <c r="H85" s="6"/>
+      <c r="I85" s="6"/>
+      <c r="J85" s="6"/>
       <c r="K85" s="1" t="s">
-        <v>134</v>
+        <v>41</v>
       </c>
       <c r="M85" s="1" t="s">
-        <v>66</v>
+        <v>23</v>
+      </c>
+      <c r="O85" s="11" t="s">
+        <v>86</v>
       </c>
       <c r="P85" s="6"/>
       <c r="Q85" s="6"/>
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A86" s="6"/>
-      <c r="C86" s="6"/>
-      <c r="D86" s="6"/>
-      <c r="E86" s="6"/>
-      <c r="F86" s="6"/>
-      <c r="G86" s="6"/>
       <c r="H86" s="6"/>
       <c r="I86" s="6"/>
       <c r="J86" s="6"/>
-      <c r="K86" s="6"/>
-      <c r="L86" s="6"/>
-      <c r="M86" s="6"/>
+      <c r="K86" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="M86" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="N86" s="6"/>
-      <c r="O86" s="6"/>
+      <c r="O86" s="6" t="s">
+        <v>85</v>
+      </c>
       <c r="P86" s="6"/>
       <c r="Q86" s="6"/>
     </row>
     <row r="87" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A87" s="6"/>
-      <c r="B87" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="C87" s="5"/>
-      <c r="D87" s="6"/>
-      <c r="E87" s="6"/>
-      <c r="F87" s="6"/>
-      <c r="G87" s="6"/>
-      <c r="H87" s="6"/>
-      <c r="I87" s="6"/>
-      <c r="J87" s="8"/>
-      <c r="K87" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L87" s="6"/>
-      <c r="M87" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N87" s="6"/>
-      <c r="O87" s="6"/>
+      <c r="K87" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="M87" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O87" s="11" t="s">
+        <v>61</v>
+      </c>
       <c r="P87" s="6"/>
       <c r="Q87" s="6"/>
     </row>
     <row r="88" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A88" s="6"/>
-      <c r="B88" s="8"/>
-      <c r="C88" s="5"/>
+      <c r="B88" s="6"/>
+      <c r="C88" s="6"/>
       <c r="D88" s="6"/>
       <c r="E88" s="6"/>
       <c r="F88" s="6"/>
       <c r="G88" s="6"/>
-      <c r="H88" s="6"/>
-      <c r="I88" s="6"/>
-      <c r="J88" s="8"/>
-      <c r="K88" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="L88" s="6"/>
-      <c r="M88" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="N88" s="6"/>
-      <c r="O88" s="5"/>
+      <c r="K88" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="M88" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="O88" s="11"/>
       <c r="P88" s="6"/>
       <c r="Q88" s="6"/>
     </row>
     <row r="89" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A89" s="6"/>
-      <c r="B89" s="6"/>
-      <c r="C89" s="6"/>
-      <c r="D89" s="6"/>
-      <c r="E89" s="6"/>
-      <c r="F89" s="6"/>
-      <c r="G89" s="6"/>
-      <c r="H89" s="6"/>
-      <c r="I89" s="6"/>
-      <c r="J89" s="6"/>
-      <c r="K89" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="L89" s="6"/>
-      <c r="M89" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="N89" s="7"/>
-      <c r="O89" s="5"/>
-      <c r="P89" s="7"/>
-      <c r="Q89" s="6"/>
+      <c r="K89" s="11"/>
+      <c r="M89" s="11"/>
+      <c r="O89" s="11"/>
+      <c r="P89" s="6"/>
+      <c r="Q89" s="7"/>
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A90" s="6"/>
-      <c r="B90" s="6"/>
-      <c r="C90" s="6"/>
-      <c r="D90" s="6"/>
-      <c r="E90" s="6"/>
-      <c r="F90" s="6"/>
-      <c r="G90" s="6"/>
-      <c r="H90" s="6"/>
-      <c r="I90" s="6"/>
-      <c r="J90" s="6"/>
-      <c r="K90" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="L90" s="6"/>
-      <c r="M90" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="N90" s="6"/>
       <c r="P90" s="6"/>
       <c r="Q90" s="6"/>
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B91" s="8"/>
-      <c r="C91" s="5"/>
+      <c r="A91" s="6"/>
+      <c r="B91" s="6"/>
+      <c r="C91" s="6"/>
       <c r="D91" s="6"/>
       <c r="E91" s="6"/>
       <c r="F91" s="6"/>
       <c r="G91" s="6"/>
-      <c r="H91" s="6"/>
-      <c r="I91" s="6"/>
-      <c r="J91" s="8"/>
-      <c r="K91" s="6" t="s">
+      <c r="K91" s="1"/>
+      <c r="M91" s="1"/>
+      <c r="O91" s="1"/>
+      <c r="P91" s="7"/>
+      <c r="Q91" s="6"/>
+    </row>
+    <row r="92" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A92" s="6"/>
+      <c r="B92" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="K92" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="L91" s="6"/>
-      <c r="M91" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="P91" s="6"/>
-      <c r="Q91" s="6"/>
-    </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B92" s="8"/>
-      <c r="C92" s="5"/>
-      <c r="D92" s="6"/>
-      <c r="E92" s="6"/>
-      <c r="F92" s="6"/>
-      <c r="G92" s="6"/>
-      <c r="H92" s="6"/>
-      <c r="I92" s="6"/>
-      <c r="J92" s="8"/>
-      <c r="K92" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="L92" s="6"/>
-      <c r="M92" s="5" t="s">
-        <v>103</v>
+      <c r="M92" s="1" t="s">
+        <v>112</v>
       </c>
       <c r="P92" s="6"/>
       <c r="Q92" s="6"/>
     </row>
     <row r="93" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B93" s="1"/>
-      <c r="G93" s="1"/>
-      <c r="H93" s="6"/>
-      <c r="I93" s="6"/>
-      <c r="J93" s="8"/>
-      <c r="K93" s="5"/>
-      <c r="L93" s="6"/>
-      <c r="M93" s="5"/>
-      <c r="P93" s="7"/>
+      <c r="A93" s="5"/>
+      <c r="B93" s="6"/>
+      <c r="C93" s="6"/>
+      <c r="K93" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="M93" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="P93" s="6"/>
       <c r="Q93" s="6"/>
     </row>
     <row r="94" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A94" s="6"/>
+      <c r="C94" s="6"/>
+      <c r="D94" s="6"/>
+      <c r="E94" s="6"/>
+      <c r="F94" s="6"/>
+      <c r="G94" s="6"/>
       <c r="H94" s="6"/>
       <c r="I94" s="6"/>
-      <c r="J94" s="8"/>
-      <c r="K94" s="5"/>
+      <c r="J94" s="6"/>
+      <c r="K94" s="6"/>
       <c r="L94" s="6"/>
-      <c r="M94" s="5"/>
-      <c r="O94" s="5"/>
-      <c r="P94" s="7"/>
+      <c r="M94" s="6"/>
+      <c r="N94" s="6"/>
+      <c r="O94" s="6"/>
+      <c r="P94" s="6"/>
       <c r="Q94" s="6"/>
     </row>
     <row r="95" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B95" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="K95" s="1"/>
-      <c r="M95" s="1"/>
-      <c r="P95" s="7"/>
-      <c r="Q95" s="7"/>
+      <c r="A95" s="6"/>
+      <c r="B95" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="C95" s="5"/>
+      <c r="D95" s="6"/>
+      <c r="E95" s="6"/>
+      <c r="F95" s="6"/>
+      <c r="G95" s="6"/>
+      <c r="H95" s="6"/>
+      <c r="I95" s="6"/>
+      <c r="J95" s="8"/>
+      <c r="K95" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L95" s="6"/>
+      <c r="M95" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N95" s="6"/>
+      <c r="O95" s="6"/>
+      <c r="P95" s="6"/>
+      <c r="Q95" s="6"/>
     </row>
     <row r="96" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B96" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="C96" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="K96" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="M96" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="P96" s="7"/>
+      <c r="A96" s="6"/>
+      <c r="B96" s="8"/>
+      <c r="C96" s="5"/>
+      <c r="D96" s="6"/>
+      <c r="E96" s="6"/>
+      <c r="F96" s="6"/>
+      <c r="G96" s="6"/>
+      <c r="H96" s="6"/>
+      <c r="I96" s="6"/>
+      <c r="J96" s="8"/>
+      <c r="K96" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="L96" s="6"/>
+      <c r="M96" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="N96" s="6"/>
+      <c r="O96" s="5"/>
+      <c r="P96" s="6"/>
       <c r="Q96" s="6"/>
     </row>
     <row r="97" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="K97" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="M97" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="O97" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="P97" s="6"/>
+      <c r="A97" s="6"/>
+      <c r="B97" s="6"/>
+      <c r="C97" s="6"/>
+      <c r="D97" s="6"/>
+      <c r="E97" s="6"/>
+      <c r="F97" s="6"/>
+      <c r="G97" s="6"/>
+      <c r="H97" s="6"/>
+      <c r="I97" s="6"/>
+      <c r="J97" s="6"/>
+      <c r="K97" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="L97" s="6"/>
+      <c r="M97" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="N97" s="7"/>
+      <c r="O97" s="5"/>
+      <c r="P97" s="7"/>
       <c r="Q97" s="6"/>
     </row>
     <row r="98" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A98" s="6"/>
-      <c r="B98" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="C98" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="K98" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="M98" s="1" t="s">
-        <v>62</v>
+      <c r="B98" s="6"/>
+      <c r="C98" s="6"/>
+      <c r="D98" s="6"/>
+      <c r="E98" s="6"/>
+      <c r="F98" s="6"/>
+      <c r="G98" s="6"/>
+      <c r="H98" s="6"/>
+      <c r="I98" s="6"/>
+      <c r="J98" s="6"/>
+      <c r="K98" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="L98" s="6"/>
+      <c r="M98" s="5" t="s">
+        <v>94</v>
       </c>
       <c r="N98" s="6"/>
-      <c r="O98" s="1" t="s">
-        <v>98</v>
-      </c>
       <c r="P98" s="6"/>
       <c r="Q98" s="6"/>
     </row>
     <row r="99" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A99" s="6"/>
-      <c r="K99" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="M99" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="N99" s="6"/>
-      <c r="O99" s="1" t="s">
-        <v>98</v>
+      <c r="B99" s="8"/>
+      <c r="C99" s="5"/>
+      <c r="D99" s="6"/>
+      <c r="E99" s="6"/>
+      <c r="F99" s="6"/>
+      <c r="G99" s="6"/>
+      <c r="H99" s="6"/>
+      <c r="I99" s="6"/>
+      <c r="J99" s="8"/>
+      <c r="K99" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="L99" s="6"/>
+      <c r="M99" s="6" t="s">
+        <v>96</v>
       </c>
       <c r="P99" s="6"/>
       <c r="Q99" s="6"/>
     </row>
     <row r="100" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A100" s="6"/>
-      <c r="N100" s="6"/>
-      <c r="P100" s="7"/>
+      <c r="B100" s="8"/>
+      <c r="C100" s="5"/>
+      <c r="D100" s="6"/>
+      <c r="E100" s="6"/>
+      <c r="F100" s="6"/>
+      <c r="G100" s="6"/>
+      <c r="H100" s="6"/>
+      <c r="I100" s="6"/>
+      <c r="J100" s="8"/>
+      <c r="K100" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="L100" s="6"/>
+      <c r="M100" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="P100" s="6"/>
       <c r="Q100" s="6"/>
     </row>
     <row r="101" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A101" s="6"/>
-      <c r="N101" s="6"/>
-      <c r="O101" s="5"/>
-      <c r="P101" s="6"/>
+      <c r="B101" s="1"/>
+      <c r="G101" s="1"/>
+      <c r="H101" s="6"/>
+      <c r="I101" s="6"/>
+      <c r="J101" s="8"/>
+      <c r="K101" s="5"/>
+      <c r="L101" s="6"/>
+      <c r="M101" s="5"/>
+      <c r="P101" s="7"/>
       <c r="Q101" s="6"/>
     </row>
     <row r="102" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A102" s="6"/>
       <c r="H102" s="6"/>
       <c r="I102" s="6"/>
-      <c r="J102" s="6"/>
+      <c r="J102" s="8"/>
       <c r="K102" s="5"/>
       <c r="L102" s="6"/>
       <c r="M102" s="5"/>
-      <c r="N102" s="6"/>
       <c r="O102" s="5"/>
-      <c r="P102" s="6"/>
+      <c r="P102" s="7"/>
       <c r="Q102" s="6"/>
     </row>
     <row r="103" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A103" s="6"/>
-      <c r="H103" s="6"/>
-      <c r="I103" s="6"/>
-      <c r="J103" s="6"/>
-      <c r="K103" s="6"/>
-      <c r="L103" s="6"/>
-      <c r="M103" s="6"/>
-      <c r="N103" s="6"/>
-      <c r="O103" s="6"/>
-      <c r="P103" s="6"/>
-      <c r="Q103" s="6"/>
+      <c r="B103" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="K103" s="1"/>
+      <c r="M103" s="1"/>
+      <c r="P103" s="7"/>
+      <c r="Q103" s="7"/>
     </row>
     <row r="104" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A104" s="6"/>
-      <c r="D104" s="6"/>
-      <c r="E104" s="6"/>
-      <c r="F104" s="6"/>
-      <c r="G104" s="6"/>
-      <c r="H104" s="6"/>
-      <c r="I104" s="6"/>
-      <c r="J104" s="8"/>
-      <c r="K104" s="5"/>
-      <c r="L104" s="6"/>
-      <c r="M104" s="5"/>
-      <c r="N104" s="6"/>
-      <c r="O104" s="6"/>
-      <c r="P104" s="6"/>
+      <c r="B104" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="K104" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="M104" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="P104" s="7"/>
       <c r="Q104" s="6"/>
     </row>
     <row r="105" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A105" s="6"/>
-      <c r="B105" s="8"/>
-      <c r="C105" s="5"/>
-      <c r="D105" s="6"/>
-      <c r="E105" s="6"/>
-      <c r="F105" s="6"/>
-      <c r="G105" s="6"/>
-      <c r="H105" s="6"/>
-      <c r="I105" s="6"/>
-      <c r="J105" s="8"/>
-      <c r="K105" s="5"/>
-      <c r="L105" s="6"/>
-      <c r="M105" s="5"/>
-      <c r="N105" s="6"/>
-      <c r="O105" s="6"/>
+      <c r="K105" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="M105" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="O105" s="1" t="s">
+        <v>98</v>
+      </c>
       <c r="P105" s="6"/>
       <c r="Q105" s="6"/>
     </row>
     <row r="106" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A106" s="6"/>
-      <c r="O106" s="6"/>
+      <c r="B106" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="K106" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="M106" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="N106" s="6"/>
+      <c r="O106" s="1" t="s">
+        <v>98</v>
+      </c>
       <c r="P106" s="6"/>
       <c r="Q106" s="6"/>
     </row>
     <row r="107" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A107" s="6"/>
-      <c r="O107" s="6"/>
+      <c r="K107" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="M107" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="N107" s="6"/>
+      <c r="O107" s="1" t="s">
+        <v>98</v>
+      </c>
       <c r="P107" s="6"/>
       <c r="Q107" s="6"/>
     </row>
     <row r="108" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A108" s="6"/>
-      <c r="O108" s="6"/>
-      <c r="P108" s="6"/>
+      <c r="N108" s="6"/>
+      <c r="P108" s="7"/>
       <c r="Q108" s="6"/>
     </row>
     <row r="109" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A109" s="6"/>
-      <c r="B109" s="8"/>
-      <c r="C109" s="5"/>
-      <c r="D109" s="6"/>
-      <c r="E109" s="6"/>
-      <c r="F109" s="6"/>
-      <c r="G109" s="6"/>
-      <c r="H109" s="6"/>
-      <c r="I109" s="6"/>
-      <c r="J109" s="6"/>
-      <c r="K109" s="5"/>
-      <c r="L109" s="6"/>
-      <c r="M109" s="5"/>
       <c r="N109" s="6"/>
-      <c r="O109" s="6"/>
+      <c r="O109" s="5"/>
       <c r="P109" s="6"/>
       <c r="Q109" s="6"/>
     </row>
     <row r="110" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A110" s="6"/>
-      <c r="B110" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="D110" s="6"/>
-      <c r="E110" s="6"/>
-      <c r="F110" s="6"/>
-      <c r="G110" s="6"/>
       <c r="H110" s="6"/>
       <c r="I110" s="6"/>
       <c r="J110" s="6"/>
@@ -3404,15 +3428,18 @@
       <c r="L110" s="6"/>
       <c r="M110" s="5"/>
       <c r="N110" s="6"/>
-      <c r="O110" s="6"/>
+      <c r="O110" s="5"/>
       <c r="P110" s="6"/>
       <c r="Q110" s="6"/>
     </row>
     <row r="111" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A111" s="6"/>
-      <c r="B111" s="1"/>
-      <c r="C111" s="1"/>
-      <c r="K111" s="5"/>
+      <c r="H111" s="6"/>
+      <c r="I111" s="6"/>
+      <c r="J111" s="6"/>
+      <c r="K111" s="6"/>
+      <c r="L111" s="6"/>
+      <c r="M111" s="6"/>
       <c r="N111" s="6"/>
       <c r="O111" s="6"/>
       <c r="P111" s="6"/>
@@ -3420,26 +3447,16 @@
     </row>
     <row r="112" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A112" s="6"/>
-      <c r="B112" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="C112" s="1" t="s">
-        <v>119</v>
-      </c>
       <c r="D112" s="6"/>
       <c r="E112" s="6"/>
       <c r="F112" s="6"/>
       <c r="G112" s="6"/>
       <c r="H112" s="6"/>
       <c r="I112" s="6"/>
-      <c r="J112" s="6"/>
-      <c r="K112" s="5" t="s">
-        <v>174</v>
-      </c>
+      <c r="J112" s="8"/>
+      <c r="K112" s="5"/>
       <c r="L112" s="6"/>
-      <c r="M112" s="5" t="s">
-        <v>23</v>
-      </c>
+      <c r="M112" s="5"/>
       <c r="N112" s="6"/>
       <c r="O112" s="6"/>
       <c r="P112" s="6"/>
@@ -3447,12 +3464,8 @@
     </row>
     <row r="113" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A113" s="6"/>
-      <c r="B113" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="C113" s="1" t="s">
-        <v>119</v>
-      </c>
+      <c r="B113" s="8"/>
+      <c r="C113" s="5"/>
       <c r="D113" s="6"/>
       <c r="E113" s="6"/>
       <c r="F113" s="6"/>
@@ -3460,13 +3473,9 @@
       <c r="H113" s="6"/>
       <c r="I113" s="6"/>
       <c r="J113" s="8"/>
-      <c r="K113" s="5" t="s">
-        <v>122</v>
-      </c>
+      <c r="K113" s="5"/>
       <c r="L113" s="6"/>
-      <c r="M113" s="5" t="s">
-        <v>112</v>
-      </c>
+      <c r="M113" s="5"/>
       <c r="N113" s="6"/>
       <c r="O113" s="6"/>
       <c r="P113" s="6"/>
@@ -3474,100 +3483,44 @@
     </row>
     <row r="114" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A114" s="6"/>
-      <c r="B114" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="C114" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="D114" s="6"/>
-      <c r="E114" s="6"/>
-      <c r="F114" s="6"/>
-      <c r="G114" s="6"/>
-      <c r="H114" s="6"/>
-      <c r="I114" s="6"/>
-      <c r="J114" s="5"/>
-      <c r="K114" s="5"/>
-      <c r="L114" s="6"/>
-      <c r="M114" s="5"/>
-      <c r="N114" s="6"/>
       <c r="O114" s="6"/>
       <c r="P114" s="6"/>
       <c r="Q114" s="6"/>
     </row>
     <row r="115" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A115" s="6"/>
-      <c r="B115" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="C115" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="H115" s="6"/>
-      <c r="I115" s="6"/>
-      <c r="J115" s="6"/>
-      <c r="K115" s="5"/>
-      <c r="L115" s="6"/>
-      <c r="M115" s="5"/>
-      <c r="N115" s="6"/>
       <c r="O115" s="6"/>
       <c r="P115" s="6"/>
       <c r="Q115" s="6"/>
     </row>
     <row r="116" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A116" s="6"/>
-      <c r="B116" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="C116" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="D116" s="6"/>
-      <c r="E116" s="6"/>
-      <c r="F116" s="6"/>
-      <c r="G116" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="H116" s="6"/>
-      <c r="I116" s="6"/>
-      <c r="J116" s="6"/>
-      <c r="K116" s="6"/>
-      <c r="L116" s="6"/>
-      <c r="M116" s="6"/>
-      <c r="N116" s="6"/>
       <c r="O116" s="6"/>
       <c r="P116" s="6"/>
       <c r="Q116" s="6"/>
     </row>
     <row r="117" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A117" s="6"/>
-      <c r="B117" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="C117" s="6" t="s">
-        <v>119</v>
-      </c>
+      <c r="B117" s="8"/>
+      <c r="C117" s="5"/>
       <c r="D117" s="6"/>
       <c r="E117" s="6"/>
       <c r="F117" s="6"/>
       <c r="G117" s="6"/>
       <c r="H117" s="6"/>
       <c r="I117" s="6"/>
-      <c r="J117" s="5"/>
+      <c r="J117" s="6"/>
       <c r="K117" s="5"/>
       <c r="L117" s="6"/>
       <c r="M117" s="5"/>
       <c r="N117" s="6"/>
-      <c r="O117" s="1"/>
+      <c r="O117" s="6"/>
       <c r="P117" s="6"/>
       <c r="Q117" s="6"/>
     </row>
     <row r="118" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A118" s="6"/>
-      <c r="B118" s="6" t="s">
-        <v>231</v>
-      </c>
-      <c r="C118" s="6" t="s">
+      <c r="B118" s="1" t="s">
         <v>119</v>
       </c>
       <c r="D118" s="6"/>
@@ -3577,9 +3530,9 @@
       <c r="H118" s="6"/>
       <c r="I118" s="6"/>
       <c r="J118" s="6"/>
-      <c r="K118" s="6"/>
+      <c r="K118" s="5"/>
       <c r="L118" s="6"/>
-      <c r="M118" s="6"/>
+      <c r="M118" s="5"/>
       <c r="N118" s="6"/>
       <c r="O118" s="6"/>
       <c r="P118" s="6"/>
@@ -3587,18 +3540,9 @@
     </row>
     <row r="119" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A119" s="6"/>
-      <c r="B119" s="5"/>
-      <c r="C119" s="5"/>
-      <c r="D119" s="6"/>
-      <c r="E119" s="6"/>
-      <c r="F119" s="6"/>
-      <c r="G119" s="6"/>
-      <c r="H119" s="6"/>
-      <c r="I119" s="6"/>
-      <c r="J119" s="5"/>
+      <c r="B119" s="1"/>
+      <c r="C119" s="1"/>
       <c r="K119" s="5"/>
-      <c r="L119" s="6"/>
-      <c r="M119" s="5"/>
       <c r="N119" s="6"/>
       <c r="O119" s="6"/>
       <c r="P119" s="6"/>
@@ -3606,18 +3550,26 @@
     </row>
     <row r="120" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A120" s="6"/>
-      <c r="B120" s="5"/>
-      <c r="C120" s="5"/>
+      <c r="B120" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>119</v>
+      </c>
       <c r="D120" s="6"/>
       <c r="E120" s="6"/>
       <c r="F120" s="6"/>
       <c r="G120" s="6"/>
       <c r="H120" s="6"/>
       <c r="I120" s="6"/>
-      <c r="J120" s="5"/>
-      <c r="K120" s="5"/>
+      <c r="J120" s="6"/>
+      <c r="K120" s="5" t="s">
+        <v>174</v>
+      </c>
       <c r="L120" s="6"/>
-      <c r="M120" s="5"/>
+      <c r="M120" s="5" t="s">
+        <v>23</v>
+      </c>
       <c r="N120" s="6"/>
       <c r="O120" s="6"/>
       <c r="P120" s="6"/>
@@ -3625,23 +3577,25 @@
     </row>
     <row r="121" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A121" s="6"/>
-      <c r="B121" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="C121" s="5"/>
+      <c r="B121" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>119</v>
+      </c>
       <c r="D121" s="6"/>
       <c r="E121" s="6"/>
       <c r="F121" s="6"/>
       <c r="G121" s="6"/>
       <c r="H121" s="6"/>
       <c r="I121" s="6"/>
-      <c r="J121" s="5"/>
+      <c r="J121" s="8"/>
       <c r="K121" s="5" t="s">
-        <v>25</v>
+        <v>122</v>
       </c>
       <c r="L121" s="6"/>
       <c r="M121" s="5" t="s">
-        <v>23</v>
+        <v>112</v>
       </c>
       <c r="N121" s="6"/>
       <c r="O121" s="6"/>
@@ -3650,8 +3604,12 @@
     </row>
     <row r="122" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A122" s="6"/>
-      <c r="B122" s="5"/>
-      <c r="C122" s="5"/>
+      <c r="B122" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>119</v>
+      </c>
       <c r="D122" s="6"/>
       <c r="E122" s="6"/>
       <c r="F122" s="6"/>
@@ -3659,13 +3617,9 @@
       <c r="H122" s="6"/>
       <c r="I122" s="6"/>
       <c r="J122" s="5"/>
-      <c r="K122" s="5" t="s">
-        <v>26</v>
-      </c>
+      <c r="K122" s="5"/>
       <c r="L122" s="6"/>
-      <c r="M122" s="5" t="s">
-        <v>23</v>
-      </c>
+      <c r="M122" s="5"/>
       <c r="N122" s="6"/>
       <c r="O122" s="6"/>
       <c r="P122" s="6"/>
@@ -3673,22 +3627,18 @@
     </row>
     <row r="123" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A123" s="6"/>
-      <c r="B123" s="5"/>
-      <c r="C123" s="5"/>
-      <c r="D123" s="6"/>
-      <c r="E123" s="6"/>
-      <c r="F123" s="6"/>
-      <c r="G123" s="6"/>
+      <c r="B123" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="C123" s="6" t="s">
+        <v>119</v>
+      </c>
       <c r="H123" s="6"/>
       <c r="I123" s="6"/>
-      <c r="J123" s="5"/>
-      <c r="K123" s="5" t="s">
-        <v>41</v>
-      </c>
+      <c r="J123" s="6"/>
+      <c r="K123" s="5"/>
       <c r="L123" s="6"/>
-      <c r="M123" s="5" t="s">
-        <v>23</v>
-      </c>
+      <c r="M123" s="5"/>
       <c r="N123" s="6"/>
       <c r="O123" s="6"/>
       <c r="P123" s="6"/>
@@ -3696,22 +3646,24 @@
     </row>
     <row r="124" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A124" s="6"/>
-      <c r="B124" s="5"/>
-      <c r="C124" s="5"/>
+      <c r="B124" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="C124" s="6" t="s">
+        <v>119</v>
+      </c>
       <c r="D124" s="6"/>
       <c r="E124" s="6"/>
       <c r="F124" s="6"/>
-      <c r="G124" s="6"/>
+      <c r="G124" s="6" t="s">
+        <v>130</v>
+      </c>
       <c r="H124" s="6"/>
       <c r="I124" s="6"/>
-      <c r="J124" s="5"/>
-      <c r="K124" s="5" t="s">
-        <v>43</v>
-      </c>
+      <c r="J124" s="6"/>
+      <c r="K124" s="6"/>
       <c r="L124" s="6"/>
-      <c r="M124" s="5" t="s">
-        <v>23</v>
-      </c>
+      <c r="M124" s="6"/>
       <c r="N124" s="6"/>
       <c r="O124" s="6"/>
       <c r="P124" s="6"/>
@@ -3719,31 +3671,35 @@
     </row>
     <row r="125" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A125" s="6"/>
-      <c r="B125" s="6"/>
-      <c r="C125" s="6"/>
+      <c r="B125" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="C125" s="6" t="s">
+        <v>119</v>
+      </c>
       <c r="D125" s="6"/>
       <c r="E125" s="6"/>
       <c r="F125" s="6"/>
       <c r="G125" s="6"/>
       <c r="H125" s="6"/>
       <c r="I125" s="6"/>
-      <c r="J125" s="6"/>
-      <c r="K125" s="5" t="s">
-        <v>60</v>
-      </c>
+      <c r="J125" s="5"/>
+      <c r="K125" s="5"/>
       <c r="L125" s="6"/>
-      <c r="M125" s="5" t="s">
-        <v>23</v>
-      </c>
+      <c r="M125" s="5"/>
       <c r="N125" s="6"/>
-      <c r="O125" s="6"/>
+      <c r="O125" s="1"/>
       <c r="P125" s="6"/>
       <c r="Q125" s="6"/>
     </row>
     <row r="126" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A126" s="6"/>
-      <c r="B126" s="6"/>
-      <c r="C126" s="6"/>
+      <c r="B126" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="C126" s="6" t="s">
+        <v>119</v>
+      </c>
       <c r="D126" s="6"/>
       <c r="E126" s="6"/>
       <c r="F126" s="6"/>
@@ -3751,20 +3707,17 @@
       <c r="H126" s="6"/>
       <c r="I126" s="6"/>
       <c r="J126" s="6"/>
-      <c r="K126" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="M126" s="5" t="s">
-        <v>241</v>
-      </c>
+      <c r="K126" s="6"/>
+      <c r="L126" s="6"/>
+      <c r="M126" s="6"/>
       <c r="N126" s="6"/>
       <c r="O126" s="6"/>
       <c r="P126" s="6"/>
       <c r="Q126" s="6"/>
     </row>
     <row r="127" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A127" s="5"/>
-      <c r="B127" s="8"/>
+      <c r="A127" s="6"/>
+      <c r="B127" s="5"/>
       <c r="C127" s="5"/>
       <c r="D127" s="6"/>
       <c r="E127" s="6"/>
@@ -3772,21 +3725,18 @@
       <c r="G127" s="6"/>
       <c r="H127" s="6"/>
       <c r="I127" s="6"/>
-      <c r="J127" s="8"/>
-      <c r="K127" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="M127" s="5" t="s">
-        <v>103</v>
-      </c>
+      <c r="J127" s="5"/>
+      <c r="K127" s="5"/>
+      <c r="L127" s="6"/>
+      <c r="M127" s="5"/>
       <c r="N127" s="6"/>
-      <c r="O127" s="5"/>
+      <c r="O127" s="6"/>
       <c r="P127" s="6"/>
       <c r="Q127" s="6"/>
     </row>
     <row r="128" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A128" s="5"/>
-      <c r="B128" s="8"/>
+      <c r="A128" s="6"/>
+      <c r="B128" s="5"/>
       <c r="C128" s="5"/>
       <c r="D128" s="6"/>
       <c r="E128" s="6"/>
@@ -3794,18 +3744,19 @@
       <c r="G128" s="6"/>
       <c r="H128" s="6"/>
       <c r="I128" s="6"/>
-      <c r="J128" s="8"/>
-      <c r="K128" s="1"/>
+      <c r="J128" s="5"/>
+      <c r="K128" s="5"/>
+      <c r="L128" s="6"/>
       <c r="M128" s="5"/>
       <c r="N128" s="6"/>
-      <c r="O128" s="5"/>
+      <c r="O128" s="6"/>
       <c r="P128" s="6"/>
       <c r="Q128" s="6"/>
     </row>
     <row r="129" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A129" s="5"/>
-      <c r="B129" s="8" t="s">
-        <v>240</v>
+      <c r="A129" s="6"/>
+      <c r="B129" s="5" t="s">
+        <v>239</v>
       </c>
       <c r="C129" s="5"/>
       <c r="D129" s="6"/>
@@ -3814,21 +3765,22 @@
       <c r="G129" s="6"/>
       <c r="H129" s="6"/>
       <c r="I129" s="6"/>
-      <c r="J129" s="8"/>
-      <c r="K129" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="M129" s="1" t="s">
-        <v>242</v>
+      <c r="J129" s="5"/>
+      <c r="K129" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L129" s="6"/>
+      <c r="M129" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="N129" s="6"/>
-      <c r="O129" s="5"/>
+      <c r="O129" s="6"/>
       <c r="P129" s="6"/>
       <c r="Q129" s="6"/>
     </row>
     <row r="130" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A130" s="5"/>
-      <c r="B130" s="8"/>
+      <c r="A130" s="6"/>
+      <c r="B130" s="5"/>
       <c r="C130" s="5"/>
       <c r="D130" s="6"/>
       <c r="E130" s="6"/>
@@ -3836,21 +3788,22 @@
       <c r="G130" s="6"/>
       <c r="H130" s="6"/>
       <c r="I130" s="6"/>
-      <c r="J130" s="8"/>
-      <c r="K130" s="1" t="s">
-        <v>134</v>
-      </c>
+      <c r="J130" s="5"/>
+      <c r="K130" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="L130" s="6"/>
       <c r="M130" s="5" t="s">
-        <v>66</v>
+        <v>23</v>
       </c>
       <c r="N130" s="6"/>
-      <c r="O130" s="5"/>
+      <c r="O130" s="6"/>
       <c r="P130" s="6"/>
       <c r="Q130" s="6"/>
     </row>
     <row r="131" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A131" s="5"/>
-      <c r="B131" s="8"/>
+      <c r="A131" s="6"/>
+      <c r="B131" s="5"/>
       <c r="C131" s="5"/>
       <c r="D131" s="6"/>
       <c r="E131" s="6"/>
@@ -3858,19 +3811,45 @@
       <c r="G131" s="6"/>
       <c r="H131" s="6"/>
       <c r="I131" s="6"/>
-      <c r="J131" s="8"/>
-      <c r="K131" s="1"/>
-      <c r="M131" s="5"/>
+      <c r="J131" s="5"/>
+      <c r="K131" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="L131" s="6"/>
+      <c r="M131" s="5" t="s">
+        <v>23</v>
+      </c>
       <c r="N131" s="6"/>
-      <c r="O131" s="5"/>
+      <c r="O131" s="6"/>
       <c r="P131" s="6"/>
       <c r="Q131" s="6"/>
     </row>
     <row r="132" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="K132" s="1"/>
-      <c r="M132" s="5"/>
+      <c r="A132" s="6"/>
+      <c r="B132" s="5"/>
+      <c r="C132" s="5"/>
+      <c r="D132" s="6"/>
+      <c r="E132" s="6"/>
+      <c r="F132" s="6"/>
+      <c r="G132" s="6"/>
+      <c r="H132" s="6"/>
+      <c r="I132" s="6"/>
+      <c r="J132" s="5"/>
+      <c r="K132" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="L132" s="6"/>
+      <c r="M132" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="N132" s="6"/>
+      <c r="O132" s="6"/>
+      <c r="P132" s="6"/>
+      <c r="Q132" s="6"/>
     </row>
     <row r="133" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A133" s="6"/>
+      <c r="B133" s="6"/>
       <c r="C133" s="6"/>
       <c r="D133" s="6"/>
       <c r="E133" s="6"/>
@@ -3879,72 +3858,150 @@
       <c r="H133" s="6"/>
       <c r="I133" s="6"/>
       <c r="J133" s="6"/>
-      <c r="K133" s="5"/>
+      <c r="K133" s="5" t="s">
+        <v>60</v>
+      </c>
       <c r="L133" s="6"/>
-      <c r="M133" s="5"/>
+      <c r="M133" s="5" t="s">
+        <v>23</v>
+      </c>
       <c r="N133" s="6"/>
       <c r="O133" s="6"/>
+      <c r="P133" s="6"/>
+      <c r="Q133" s="6"/>
     </row>
     <row r="134" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A134" s="6"/>
+      <c r="B134" s="6"/>
+      <c r="C134" s="6"/>
+      <c r="D134" s="6"/>
+      <c r="E134" s="6"/>
+      <c r="F134" s="6"/>
+      <c r="G134" s="6"/>
+      <c r="H134" s="6"/>
+      <c r="I134" s="6"/>
+      <c r="J134" s="6"/>
+      <c r="K134" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="M134" s="5" t="s">
+        <v>241</v>
+      </c>
       <c r="N134" s="6"/>
       <c r="O134" s="6"/>
+      <c r="P134" s="6"/>
+      <c r="Q134" s="6"/>
     </row>
     <row r="135" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B135" s="6" t="s">
-        <v>64</v>
+      <c r="A135" s="5"/>
+      <c r="B135" s="8"/>
+      <c r="C135" s="5"/>
+      <c r="D135" s="6"/>
+      <c r="E135" s="6"/>
+      <c r="F135" s="6"/>
+      <c r="G135" s="6"/>
+      <c r="H135" s="6"/>
+      <c r="I135" s="6"/>
+      <c r="J135" s="8"/>
+      <c r="K135" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="M135" s="5" t="s">
+        <v>103</v>
       </c>
       <c r="N135" s="6"/>
+      <c r="O135" s="5"/>
+      <c r="P135" s="6"/>
+      <c r="Q135" s="6"/>
     </row>
     <row r="136" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A136" s="5"/>
+      <c r="B136" s="8"/>
+      <c r="C136" s="5"/>
+      <c r="D136" s="6"/>
+      <c r="E136" s="6"/>
+      <c r="F136" s="6"/>
+      <c r="G136" s="6"/>
+      <c r="H136" s="6"/>
+      <c r="I136" s="6"/>
+      <c r="J136" s="8"/>
+      <c r="K136" s="1"/>
+      <c r="M136" s="5"/>
       <c r="N136" s="6"/>
-      <c r="O136" s="6"/>
+      <c r="O136" s="5"/>
+      <c r="P136" s="6"/>
+      <c r="Q136" s="6"/>
     </row>
     <row r="137" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B137" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="C137" s="6" t="s">
-        <v>64</v>
-      </c>
+      <c r="A137" s="5"/>
+      <c r="B137" s="8" t="s">
+        <v>240</v>
+      </c>
+      <c r="C137" s="5"/>
       <c r="D137" s="6"/>
       <c r="E137" s="6"/>
       <c r="F137" s="6"/>
       <c r="G137" s="6"/>
       <c r="H137" s="6"/>
       <c r="I137" s="6"/>
-      <c r="J137" s="6"/>
+      <c r="J137" s="8"/>
       <c r="K137" s="1" t="s">
-        <v>124</v>
+        <v>33</v>
       </c>
       <c r="M137" s="1" t="s">
-        <v>128</v>
+        <v>242</v>
       </c>
       <c r="N137" s="6"/>
-      <c r="O137" s="6"/>
+      <c r="O137" s="5"/>
+      <c r="P137" s="6"/>
+      <c r="Q137" s="6"/>
     </row>
     <row r="138" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A138" s="5"/>
+      <c r="B138" s="8"/>
+      <c r="C138" s="5"/>
+      <c r="D138" s="6"/>
+      <c r="E138" s="6"/>
+      <c r="F138" s="6"/>
+      <c r="G138" s="6"/>
+      <c r="H138" s="6"/>
+      <c r="I138" s="6"/>
+      <c r="J138" s="8"/>
       <c r="K138" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="M138" s="1" t="s">
-        <v>114</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="M138" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="N138" s="6"/>
+      <c r="O138" s="5"/>
+      <c r="P138" s="6"/>
+      <c r="Q138" s="6"/>
     </row>
     <row r="139" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="K139" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="M139" s="1" t="s">
-        <v>128</v>
-      </c>
+      <c r="A139" s="5"/>
+      <c r="B139" s="8"/>
+      <c r="C139" s="5"/>
+      <c r="D139" s="6"/>
+      <c r="E139" s="6"/>
+      <c r="F139" s="6"/>
+      <c r="G139" s="6"/>
+      <c r="H139" s="6"/>
+      <c r="I139" s="6"/>
+      <c r="J139" s="8"/>
+      <c r="K139" s="1"/>
+      <c r="M139" s="5"/>
+      <c r="N139" s="6"/>
+      <c r="O139" s="5"/>
+      <c r="P139" s="6"/>
+      <c r="Q139" s="6"/>
+    </row>
+    <row r="140" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K140" s="1"/>
+      <c r="M140" s="5"/>
     </row>
     <row r="141" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B141" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="C141" s="6" t="s">
-        <v>64</v>
-      </c>
+      <c r="C141" s="6"/>
       <c r="D141" s="6"/>
       <c r="E141" s="6"/>
       <c r="F141" s="6"/>
@@ -3955,499 +4012,572 @@
       <c r="K141" s="5"/>
       <c r="L141" s="6"/>
       <c r="M141" s="5"/>
+      <c r="N141" s="6"/>
+      <c r="O141" s="6"/>
     </row>
     <row r="142" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B142" s="6"/>
-      <c r="C142" s="6"/>
-      <c r="D142" s="6"/>
-      <c r="E142" s="6"/>
-      <c r="F142" s="6"/>
-      <c r="G142" s="6"/>
-      <c r="H142" s="6"/>
-      <c r="I142" s="6"/>
-      <c r="J142" s="6"/>
-      <c r="K142" s="5"/>
-      <c r="L142" s="6"/>
-      <c r="M142" s="5"/>
+      <c r="N142" s="6"/>
+      <c r="O142" s="6"/>
     </row>
     <row r="143" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B143" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="C143" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="D143" s="6"/>
-      <c r="E143" s="6"/>
-      <c r="F143" s="6"/>
-      <c r="G143" s="6"/>
-      <c r="H143" s="6"/>
-      <c r="I143" s="6"/>
-      <c r="J143" s="6"/>
-      <c r="K143" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="M143" s="1" t="s">
-        <v>114</v>
-      </c>
+      <c r="N143" s="6"/>
     </row>
     <row r="144" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="D144" s="6"/>
-      <c r="E144" s="6"/>
-      <c r="F144" s="6"/>
-      <c r="G144" s="5"/>
-      <c r="H144" s="6"/>
-      <c r="I144" s="6"/>
-      <c r="J144" s="5"/>
-      <c r="K144" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="L144" s="6"/>
-      <c r="M144" s="5" t="s">
-        <v>112</v>
-      </c>
+      <c r="N144" s="6"/>
+      <c r="O144" s="6"/>
     </row>
     <row r="145" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B145" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="C145" s="6" t="s">
+        <v>64</v>
+      </c>
       <c r="D145" s="6"/>
       <c r="E145" s="6"/>
       <c r="F145" s="6"/>
-      <c r="G145" s="5"/>
+      <c r="G145" s="6"/>
       <c r="H145" s="6"/>
       <c r="I145" s="6"/>
-      <c r="J145" s="5"/>
-      <c r="K145" s="5"/>
-      <c r="L145" s="6"/>
-      <c r="M145" s="5"/>
+      <c r="J145" s="6"/>
+      <c r="K145" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="M145" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="N145" s="6"/>
+      <c r="O145" s="6"/>
     </row>
     <row r="146" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="B146" s="1" t="s">
+      <c r="K146" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="M146" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="147" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="K147" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="M147" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="149" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B149" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C149" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D149" s="6"/>
+      <c r="E149" s="6"/>
+      <c r="F149" s="6"/>
+      <c r="G149" s="6"/>
+      <c r="H149" s="6"/>
+      <c r="I149" s="6"/>
+      <c r="J149" s="6"/>
+      <c r="K149" s="5"/>
+      <c r="L149" s="6"/>
+      <c r="M149" s="5"/>
+    </row>
+    <row r="150" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B150" s="6"/>
+      <c r="C150" s="6"/>
+      <c r="D150" s="6"/>
+      <c r="E150" s="6"/>
+      <c r="F150" s="6"/>
+      <c r="G150" s="6"/>
+      <c r="H150" s="6"/>
+      <c r="I150" s="6"/>
+      <c r="J150" s="6"/>
+      <c r="K150" s="5"/>
+      <c r="L150" s="6"/>
+      <c r="M150" s="5"/>
+    </row>
+    <row r="151" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B151" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="C151" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D151" s="6"/>
+      <c r="E151" s="6"/>
+      <c r="F151" s="6"/>
+      <c r="G151" s="6"/>
+      <c r="H151" s="6"/>
+      <c r="I151" s="6"/>
+      <c r="J151" s="6"/>
+      <c r="K151" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="M151" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="152" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="D152" s="6"/>
+      <c r="E152" s="6"/>
+      <c r="F152" s="6"/>
+      <c r="G152" s="5"/>
+      <c r="H152" s="6"/>
+      <c r="I152" s="6"/>
+      <c r="J152" s="5"/>
+      <c r="K152" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="L152" s="6"/>
+      <c r="M152" s="5" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="153" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="D153" s="6"/>
+      <c r="E153" s="6"/>
+      <c r="F153" s="6"/>
+      <c r="G153" s="5"/>
+      <c r="H153" s="6"/>
+      <c r="I153" s="6"/>
+      <c r="J153" s="5"/>
+      <c r="K153" s="5"/>
+      <c r="L153" s="6"/>
+      <c r="M153" s="5"/>
+    </row>
+    <row r="154" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B154" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="C146" s="6" t="s">
+      <c r="C154" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="K146" s="1" t="s">
+      <c r="K154" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M146" s="1" t="s">
+      <c r="M154" s="1" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="147" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="B147" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="C147" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="148" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A148" s="1"/>
-      <c r="B148" s="1"/>
-      <c r="C148" s="1"/>
-    </row>
-    <row r="149" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="B149" s="1"/>
-      <c r="C149" s="1"/>
-    </row>
-    <row r="150" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="B150" s="1"/>
-      <c r="C150" s="1"/>
-    </row>
-    <row r="151" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="B151" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="K151" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="M151" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="152" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="K152" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="M152" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="153" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="K153" s="1"/>
     </row>
     <row r="155" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B155" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="K155" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="M155" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="O155" s="6"/>
+        <v>257</v>
+      </c>
+      <c r="C155" s="1" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="156" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="K156" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="M156" s="1" t="s">
-        <v>23</v>
-      </c>
+      <c r="A156" s="1"/>
+      <c r="B156" s="1"/>
+      <c r="C156" s="1"/>
     </row>
     <row r="157" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="K157" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="M157" s="1" t="s">
-        <v>23</v>
-      </c>
+      <c r="B157" s="1"/>
+      <c r="C157" s="1"/>
     </row>
     <row r="158" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="K158" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="M158" s="1" t="s">
-        <v>198</v>
-      </c>
+      <c r="B158" s="1"/>
+      <c r="C158" s="1"/>
     </row>
     <row r="159" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B159" s="1" t="s">
+        <v>195</v>
+      </c>
       <c r="K159" s="1" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="M159" s="1" t="s">
-        <v>112</v>
+        <v>23</v>
       </c>
     </row>
     <row r="160" spans="1:15" x14ac:dyDescent="0.2">
       <c r="K160" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="M160" s="5" t="s">
-        <v>103</v>
+        <v>197</v>
+      </c>
+      <c r="M160" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="161" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B161" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="K161" s="1" t="s">
+      <c r="K161" s="1"/>
+    </row>
+    <row r="163" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B163" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="K163" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="M161" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="162" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B162" s="1"/>
-      <c r="K162" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="M162" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="163" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K163" s="1" t="s">
-        <v>41</v>
-      </c>
       <c r="M163" s="1" t="s">
         <v>23</v>
       </c>
+      <c r="O163" s="6"/>
     </row>
     <row r="164" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K164" s="1" t="s">
-        <v>228</v>
+        <v>26</v>
       </c>
       <c r="M164" s="1" t="s">
-        <v>229</v>
+        <v>23</v>
       </c>
     </row>
     <row r="165" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K165" s="1"/>
-      <c r="M165" s="1"/>
+      <c r="K165" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M165" s="1" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="166" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B166" s="1" t="s">
-        <v>230</v>
-      </c>
       <c r="K166" s="1" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="M166" s="1" t="s">
-        <v>23</v>
+        <v>198</v>
       </c>
     </row>
     <row r="167" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K167" s="1" t="s">
-        <v>26</v>
+        <v>199</v>
       </c>
       <c r="M167" s="1" t="s">
-        <v>23</v>
+        <v>112</v>
       </c>
     </row>
     <row r="168" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K168" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="M168" s="5" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="169" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B169" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="K169" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="M169" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="170" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B170" s="1"/>
+      <c r="K170" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M170" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="171" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K171" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="M168" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="169" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K169" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="M169" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="170" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K170" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="M170" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="171" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K171" s="1"/>
+      <c r="M171" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="172" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K172" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="M172" s="1" t="s">
+        <v>229</v>
+      </c>
     </row>
     <row r="173" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B173" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="K173" s="1" t="s">
+      <c r="K173" s="1"/>
+      <c r="M173" s="1"/>
+    </row>
+    <row r="174" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B174" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="K174" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="M173" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="O173" s="1" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="174" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K174" s="1" t="s">
-        <v>26</v>
-      </c>
       <c r="M174" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="O174" s="1" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="175" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K175" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M175" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="176" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K176" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="M175" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="O175" s="1" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="176" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K176" s="1"/>
+      <c r="M176" s="1" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="177" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B177" s="1" t="s">
-        <v>208</v>
-      </c>
       <c r="K177" s="1" t="s">
-        <v>212</v>
+        <v>60</v>
       </c>
       <c r="M177" s="1" t="s">
-        <v>112</v>
+        <v>23</v>
       </c>
     </row>
     <row r="178" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K178" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="M178" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="179" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K179" s="1"/>
+    </row>
+    <row r="181" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B181" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="K181" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="M181" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O181" s="1" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="182" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K182" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="M178" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="179" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K179" s="1" t="s">
+      <c r="M182" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O182" s="1" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="183" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K183" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="M179" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="180" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K180" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="M180" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="181" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K181" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="M181" s="1" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="183" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B183" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="K183" s="1" t="s">
-        <v>214</v>
-      </c>
       <c r="M183" s="1" t="s">
         <v>23</v>
       </c>
+      <c r="O183" s="1" t="s">
+        <v>211</v>
+      </c>
     </row>
     <row r="184" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K184" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="M184" s="1" t="s">
-        <v>103</v>
+      <c r="K184" s="1"/>
+    </row>
+    <row r="185" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B185" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="K185" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="M185" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="186" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K186" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M186" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="187" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B187" s="1" t="s">
-        <v>219</v>
-      </c>
       <c r="K187" s="1" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="M187" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="O187" s="1" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="188" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K188" s="1" t="s">
-        <v>26</v>
+        <v>216</v>
       </c>
       <c r="M188" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="O188" s="1" t="s">
-        <v>220</v>
+        <v>103</v>
       </c>
     </row>
     <row r="189" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K189" s="1" t="s">
-        <v>41</v>
+        <v>218</v>
       </c>
       <c r="M189" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="O189" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="190" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="K190" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="M190" s="1" t="s">
-        <v>236</v>
+        <v>217</v>
       </c>
     </row>
     <row r="191" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B191" s="1" t="s">
-        <v>234</v>
+        <v>213</v>
       </c>
       <c r="K191" s="1" t="s">
-        <v>33</v>
+        <v>214</v>
       </c>
       <c r="M191" s="1" t="s">
-        <v>235</v>
+        <v>23</v>
       </c>
     </row>
     <row r="192" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K192" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="M192" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="195" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B195" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="K195" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="M195" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O195" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="196" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K196" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M196" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O196" s="1" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="197" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K197" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M197" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O197" s="1" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="198" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K198" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="M198" s="1" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="199" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B199" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="K199" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M199" s="1" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="200" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K200" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="M192" s="1" t="s">
+      <c r="M200" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="196" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B196" s="1" t="s">
+    <row r="204" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B204" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="G196" s="1" t="s">
+      <c r="G204" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="K196" s="1" t="s">
+      <c r="K204" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="M196" s="1" t="s">
+      <c r="M204" s="1" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="197" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="K197" s="1" t="s">
+    <row r="205" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K205" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="M197" s="1" t="s">
+      <c r="M205" s="1" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="200" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B200" s="1" t="s">
+    <row r="208" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B208" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="K200" s="1" t="s">
+      <c r="K208" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="M200" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="201" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="K201" s="1" t="s">
+      <c r="M208" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="209" spans="11:13" x14ac:dyDescent="0.2">
+      <c r="K209" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="M201" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="202" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="K202" s="1" t="s">
+      <c r="M209" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="210" spans="11:13" x14ac:dyDescent="0.2">
+      <c r="K210" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="M202" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="203" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="K203" s="1" t="s">
+      <c r="M210" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="211" spans="11:13" x14ac:dyDescent="0.2">
+      <c r="K211" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="M203" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="204" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="K204" s="1" t="s">
+      <c r="M211" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="212" spans="11:13" x14ac:dyDescent="0.2">
+      <c r="K212" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="M204" s="6" t="s">
+      <c r="M212" s="6" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="205" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="K205" s="1" t="s">
+    <row r="213" spans="11:13" x14ac:dyDescent="0.2">
+      <c r="K213" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="M205" s="1" t="s">
+      <c r="M213" s="1" t="s">
         <v>94</v>
       </c>
     </row>
@@ -4463,7 +4593,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EECC075D-9730-41E5-B97E-C301603D1E48}">
-  <dimension ref="A1:Q72"/>
+  <dimension ref="A1:Q78"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="27.375" customWidth="1"/>
@@ -5233,6 +5363,47 @@
       </c>
       <c r="M72" s="1" t="s">
         <v>128</v>
+      </c>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B74" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="K74" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="M74" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="K75" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="M75" s="1" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B77" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="K77" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="M77" s="1" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="78" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="K78" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="M78" s="1" t="s">
+        <v>263</v>
       </c>
     </row>
   </sheetData>

--- a/Config/Datas/__beans__.xlsx
+++ b/Config/Datas/__beans__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92D07897-5E17-4E42-A885-DEFA9BB2BC37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8ACF422-6AF5-4D03-A2C6-3A729910642F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="272">
   <si>
     <t>##var</t>
   </si>
@@ -1085,6 +1085,18 @@
   </si>
   <si>
     <t>list,CustomerCGA</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GA_触发遭遇</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GA_触发瞬时遭遇</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GA_定点爆破</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -4593,7 +4605,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EECC075D-9730-41E5-B97E-C301603D1E48}">
-  <dimension ref="A1:Q78"/>
+  <dimension ref="A1:Q84"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="27.375" customWidth="1"/>
@@ -5273,9 +5285,17 @@
         <v>53</v>
       </c>
       <c r="K63" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="M63" s="1" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="K64" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="M63" s="1" t="s">
+      <c r="M64" s="1" t="s">
         <v>23</v>
       </c>
     </row>
@@ -5404,6 +5424,54 @@
       </c>
       <c r="M78" s="1" t="s">
         <v>263</v>
+      </c>
+    </row>
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B80" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="K80" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="M80" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="81" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B81" s="1"/>
+      <c r="C81" s="1"/>
+      <c r="K81" s="1"/>
+      <c r="M81" s="1"/>
+    </row>
+    <row r="82" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B82" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="K82" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="M82" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="84" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B84" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="K84" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="M84" s="1" t="s">
+        <v>187</v>
       </c>
     </row>
   </sheetData>

--- a/Config/Datas/__beans__.xlsx
+++ b/Config/Datas/__beans__.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8ACF422-6AF5-4D03-A2C6-3A729910642F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{171B10D8-F03A-40FE-B999-46720884BBA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="274">
   <si>
     <t>##var</t>
   </si>
@@ -1097,6 +1097,14 @@
   </si>
   <si>
     <t>GA_定点爆破</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GA_使顾客离开</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GA_效果选择</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -4605,7 +4613,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EECC075D-9730-41E5-B97E-C301603D1E48}">
-  <dimension ref="A1:Q84"/>
+  <dimension ref="A1:Q88"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="27.375" customWidth="1"/>
@@ -5472,6 +5480,34 @@
       </c>
       <c r="M84" s="1" t="s">
         <v>187</v>
+      </c>
+    </row>
+    <row r="86" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B86" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="K86" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="M86" s="1" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="88" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B88" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="K88" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="M88" s="1" t="s">
+        <v>153</v>
       </c>
     </row>
   </sheetData>

--- a/Config/Datas/__beans__.xlsx
+++ b/Config/Datas/__beans__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{171B10D8-F03A-40FE-B999-46720884BBA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EADBC029-B785-426E-8C4A-61DECA7BC800}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="277">
   <si>
     <t>##var</t>
   </si>
@@ -1105,6 +1105,18 @@
   </si>
   <si>
     <t>GA_效果选择</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>list,string</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ReputationData</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>totalReputation</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1532,7 +1544,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q213"/>
+  <dimension ref="A1:Q221"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="28.75" customWidth="1"/>
@@ -4561,7 +4573,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="209" spans="11:13" x14ac:dyDescent="0.2">
+    <row r="209" spans="2:13" x14ac:dyDescent="0.2">
       <c r="K209" s="1" t="s">
         <v>26</v>
       </c>
@@ -4569,7 +4581,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="210" spans="11:13" x14ac:dyDescent="0.2">
+    <row r="210" spans="2:13" x14ac:dyDescent="0.2">
       <c r="K210" s="1" t="s">
         <v>60</v>
       </c>
@@ -4577,7 +4589,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="211" spans="11:13" x14ac:dyDescent="0.2">
+    <row r="211" spans="2:13" x14ac:dyDescent="0.2">
       <c r="K211" s="1" t="s">
         <v>41</v>
       </c>
@@ -4585,7 +4597,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="212" spans="11:13" x14ac:dyDescent="0.2">
+    <row r="212" spans="2:13" x14ac:dyDescent="0.2">
       <c r="K212" s="1" t="s">
         <v>249</v>
       </c>
@@ -4593,12 +4605,71 @@
         <v>99</v>
       </c>
     </row>
-    <row r="213" spans="11:13" x14ac:dyDescent="0.2">
+    <row r="213" spans="2:13" x14ac:dyDescent="0.2">
       <c r="K213" s="1" t="s">
         <v>250</v>
       </c>
       <c r="M213" s="1" t="s">
         <v>94</v>
+      </c>
+    </row>
+    <row r="215" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B215" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="K215" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="M215" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="216" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="K216" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M216" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="217" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="K217" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="M217" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="218" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="K218" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M218" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="219" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="K219" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="M219" s="1" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="220" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="K220" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="M220" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="221" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="K221" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="M221" s="1" t="s">
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -4613,7 +4684,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EECC075D-9730-41E5-B97E-C301603D1E48}">
-  <dimension ref="A1:Q88"/>
+  <dimension ref="A1:Q87"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="27.375" customWidth="1"/>
@@ -5434,79 +5505,79 @@
         <v>263</v>
       </c>
     </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B79" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="K79" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="M79" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
     <row r="80" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B80" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="C80" s="1" t="s">
+      <c r="B80" s="1"/>
+      <c r="C80" s="1"/>
+      <c r="K80" s="1"/>
+      <c r="M80" s="1"/>
+    </row>
+    <row r="81" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B81" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="C81" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="K80" s="1" t="s">
+      <c r="K81" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="M80" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="81" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B81" s="1"/>
-      <c r="C81" s="1"/>
-      <c r="K81" s="1"/>
-      <c r="M81" s="1"/>
-    </row>
-    <row r="82" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B82" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="C82" s="1" t="s">
+      <c r="M81" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="83" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B83" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="C83" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="K82" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="M82" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="84" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B84" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="C84" s="1" t="s">
+      <c r="K83" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="M83" s="1" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="85" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B85" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="C85" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="K84" s="1" t="s">
+      <c r="K85" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="M84" s="1" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="86" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B86" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="C86" s="1" t="s">
+      <c r="M85" s="1" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="87" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B87" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="C87" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="K86" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="M86" s="1" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="88" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B88" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="C88" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="K88" s="1" t="s">
+      <c r="K87" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="M88" s="1" t="s">
+      <c r="M87" s="1" t="s">
         <v>153</v>
       </c>
     </row>

--- a/Config/Datas/__beans__.xlsx
+++ b/Config/Datas/__beans__.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EADBC029-B785-426E-8C4A-61DECA7BC800}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93EFF309-AF19-4E34-816F-D1BE742546AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="650" uniqueCount="286">
   <si>
     <t>##var</t>
   </si>
@@ -1117,6 +1117,42 @@
   </si>
   <si>
     <t>totalReputation</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>RankProbability</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>probability_普通</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>probability_稀有</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>probability_史诗</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>probability_传说</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GA_修改稀有度概率</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>RankProbability#sep=|</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>probs</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GA_获得收入</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1544,24 +1580,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q221"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:Q225"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="28.75" customWidth="1"/>
     <col min="3" max="3" width="22" customWidth="1"/>
-    <col min="4" max="4" width="9.375" customWidth="1"/>
+    <col min="4" max="4" width="9.33203125" customWidth="1"/>
     <col min="5" max="5" width="9.5" customWidth="1"/>
-    <col min="6" max="6" width="5.875" customWidth="1"/>
+    <col min="6" max="6" width="5.83203125" customWidth="1"/>
     <col min="7" max="7" width="16" customWidth="1"/>
-    <col min="8" max="8" width="6.625" customWidth="1"/>
+    <col min="8" max="8" width="6.58203125" customWidth="1"/>
     <col min="9" max="9" width="6.75" customWidth="1"/>
-    <col min="10" max="10" width="7.375" customWidth="1"/>
+    <col min="10" max="10" width="7.33203125" customWidth="1"/>
     <col min="11" max="12" width="13.5" customWidth="1"/>
-    <col min="13" max="13" width="11.875" customWidth="1"/>
+    <col min="13" max="13" width="11.83203125" customWidth="1"/>
     <col min="14" max="14" width="20.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1602,7 +1638,7 @@
       <c r="P1" s="12"/>
       <c r="Q1" s="12"/>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -1637,7 +1673,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>11</v>
       </c>
@@ -1674,7 +1710,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
         <v>29</v>
       </c>
@@ -1703,7 +1739,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
         <v>29</v>
       </c>
@@ -1730,7 +1766,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" s="6"/>
       <c r="B6" s="6"/>
       <c r="C6" s="5"/>
@@ -1749,7 +1785,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" s="6"/>
       <c r="B7" s="6" t="s">
         <v>176</v>
@@ -1776,7 +1812,7 @@
       <c r="P7" s="6"/>
       <c r="Q7" s="6"/>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" s="6"/>
       <c r="B8" s="6"/>
       <c r="C8" s="5"/>
@@ -1799,7 +1835,7 @@
       <c r="P8" s="6"/>
       <c r="Q8" s="6"/>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" s="6"/>
       <c r="B9" s="6"/>
       <c r="C9" s="5"/>
@@ -1822,7 +1858,7 @@
       <c r="P9" s="6"/>
       <c r="Q9" s="6"/>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" s="6"/>
       <c r="B10" s="6"/>
       <c r="C10" s="5"/>
@@ -1844,7 +1880,7 @@
       <c r="P10" s="6"/>
       <c r="Q10" s="6"/>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" s="6"/>
       <c r="B11" s="6"/>
       <c r="C11" s="5"/>
@@ -1866,7 +1902,7 @@
       <c r="P11" s="6"/>
       <c r="Q11" s="6"/>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" s="6"/>
       <c r="B12" s="6"/>
       <c r="C12" s="5"/>
@@ -1889,7 +1925,7 @@
       <c r="P12" s="6"/>
       <c r="Q12" s="6"/>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" s="6"/>
       <c r="B13" s="6"/>
       <c r="C13" s="5"/>
@@ -1908,7 +1944,7 @@
       <c r="P13" s="6"/>
       <c r="Q13" s="6"/>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
         <v>180</v>
       </c>
@@ -1929,7 +1965,7 @@
       <c r="P14" s="6"/>
       <c r="Q14" s="6"/>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15" s="6"/>
       <c r="B15" s="6"/>
       <c r="C15" s="5"/>
@@ -1948,7 +1984,7 @@
       <c r="P15" s="6"/>
       <c r="Q15" s="6"/>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" s="6"/>
       <c r="B16" s="6"/>
       <c r="C16" s="5"/>
@@ -1967,7 +2003,7 @@
       <c r="P16" s="6"/>
       <c r="Q16" s="6"/>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17" s="6"/>
       <c r="B17" s="6" t="s">
         <v>181</v>
@@ -1992,7 +2028,7 @@
       <c r="P17" s="6"/>
       <c r="Q17" s="6"/>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A18" s="6"/>
       <c r="B18" s="6"/>
       <c r="C18" s="5"/>
@@ -2015,7 +2051,7 @@
       <c r="P18" s="6"/>
       <c r="Q18" s="6"/>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A19" s="6"/>
       <c r="B19" s="6"/>
       <c r="C19" s="5"/>
@@ -2034,7 +2070,7 @@
       <c r="P19" s="6"/>
       <c r="Q19" s="6"/>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A20" s="6"/>
       <c r="B20" s="6" t="s">
         <v>30</v>
@@ -2063,7 +2099,7 @@
       <c r="P20" s="6"/>
       <c r="Q20" s="6"/>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A21" s="6"/>
       <c r="B21" s="6"/>
       <c r="C21" s="5"/>
@@ -2088,7 +2124,7 @@
       <c r="P21" s="6"/>
       <c r="Q21" s="6"/>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A22" s="6"/>
       <c r="D22" s="6"/>
       <c r="E22" s="6"/>
@@ -2109,7 +2145,7 @@
       <c r="P22" s="6"/>
       <c r="Q22" s="6"/>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A23" s="6"/>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
@@ -2127,7 +2163,7 @@
       <c r="P23" s="6"/>
       <c r="Q23" s="6"/>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A24" s="6"/>
       <c r="B24" s="6"/>
       <c r="C24" s="6"/>
@@ -2150,7 +2186,7 @@
       <c r="P24" s="6"/>
       <c r="Q24" s="6"/>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A25" s="6"/>
       <c r="D25" s="6"/>
       <c r="E25" s="6"/>
@@ -2171,7 +2207,7 @@
       <c r="P25" s="6"/>
       <c r="Q25" s="6"/>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A26" s="6"/>
       <c r="B26" s="6"/>
       <c r="C26" s="6"/>
@@ -2196,7 +2232,7 @@
       <c r="P26" s="6"/>
       <c r="Q26" s="6"/>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A27" s="6"/>
       <c r="B27" s="6"/>
       <c r="C27" s="6"/>
@@ -2221,7 +2257,7 @@
       <c r="P27" s="7"/>
       <c r="Q27" s="7"/>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A28" s="6"/>
       <c r="K28" s="5" t="s">
         <v>60</v>
@@ -2237,7 +2273,7 @@
       <c r="P28" s="6"/>
       <c r="Q28" s="6"/>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A29" s="6"/>
       <c r="K29" s="1" t="s">
         <v>143</v>
@@ -2251,7 +2287,7 @@
       <c r="P29" s="6"/>
       <c r="Q29" s="6"/>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A30" s="6"/>
       <c r="K30" s="1" t="s">
         <v>150</v>
@@ -2265,7 +2301,7 @@
       <c r="P30" s="6"/>
       <c r="Q30" s="6"/>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A31" s="6"/>
       <c r="K31" s="1" t="s">
         <v>95</v>
@@ -2278,7 +2314,7 @@
       </c>
       <c r="Q31" s="6"/>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A32" s="6"/>
       <c r="K32" s="1" t="s">
         <v>254</v>
@@ -2291,32 +2327,32 @@
       </c>
       <c r="Q32" s="6"/>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A33" s="6"/>
       <c r="K33" s="1"/>
       <c r="M33" s="5"/>
       <c r="O33" s="6"/>
       <c r="Q33" s="6"/>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A34" s="6"/>
       <c r="K34" s="1"/>
       <c r="M34" s="5"/>
       <c r="O34" s="6"/>
       <c r="Q34" s="6"/>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A35" s="6"/>
       <c r="K35" s="1"/>
       <c r="M35" s="5"/>
       <c r="O35" s="6"/>
       <c r="Q35" s="6"/>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A36" s="6"/>
       <c r="Q36" s="6"/>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A37" s="6"/>
       <c r="B37" s="6" t="s">
         <v>45</v>
@@ -2345,7 +2381,7 @@
       <c r="P37" s="6"/>
       <c r="Q37" s="6"/>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A38" s="6"/>
       <c r="B38" s="6"/>
       <c r="C38" s="6"/>
@@ -2370,7 +2406,7 @@
       <c r="P38" s="6"/>
       <c r="Q38" s="6"/>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A39" s="6"/>
       <c r="B39" s="6"/>
       <c r="C39" s="6"/>
@@ -2393,7 +2429,7 @@
       <c r="P39" s="6"/>
       <c r="Q39" s="6"/>
     </row>
-    <row r="40" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="6"/>
       <c r="B40" s="5"/>
       <c r="C40" s="6"/>
@@ -2418,7 +2454,7 @@
       <c r="P40" s="6"/>
       <c r="Q40" s="6"/>
     </row>
-    <row r="41" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="6"/>
       <c r="B41" s="5"/>
       <c r="C41" s="6"/>
@@ -2441,7 +2477,7 @@
       <c r="P41" s="6"/>
       <c r="Q41" s="6"/>
     </row>
-    <row r="42" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="6"/>
       <c r="B42" s="5"/>
       <c r="C42" s="6"/>
@@ -2463,7 +2499,7 @@
       <c r="P42" s="6"/>
       <c r="Q42" s="6"/>
     </row>
-    <row r="43" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="6"/>
       <c r="B43" s="5"/>
       <c r="C43" s="6"/>
@@ -2485,7 +2521,7 @@
       <c r="P43" s="6"/>
       <c r="Q43" s="6"/>
     </row>
-    <row r="44" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="6"/>
       <c r="B44" s="5"/>
       <c r="C44" s="6"/>
@@ -2510,7 +2546,7 @@
       <c r="P44" s="6"/>
       <c r="Q44" s="6"/>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A45" s="6"/>
       <c r="B45" s="6"/>
       <c r="C45" s="6"/>
@@ -2524,12 +2560,12 @@
       <c r="P45" s="6"/>
       <c r="Q45" s="6"/>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A46" s="6"/>
       <c r="P46" s="6"/>
       <c r="Q46" s="6"/>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A47" s="6"/>
       <c r="B47" s="1" t="s">
         <v>145</v>
@@ -2549,7 +2585,7 @@
       <c r="P47" s="6"/>
       <c r="Q47" s="6"/>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A48" s="6"/>
       <c r="K48" s="5" t="s">
         <v>26</v>
@@ -2563,7 +2599,7 @@
       <c r="P48" s="6"/>
       <c r="Q48" s="6"/>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A49" s="6"/>
       <c r="K49" s="5" t="s">
         <v>41</v>
@@ -2577,7 +2613,7 @@
       <c r="P49" s="6"/>
       <c r="Q49" s="6"/>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A50" s="6"/>
       <c r="K50" s="5" t="s">
         <v>161</v>
@@ -2589,7 +2625,7 @@
       <c r="P50" s="6"/>
       <c r="Q50" s="6"/>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A51" s="6"/>
       <c r="K51" s="5" t="s">
         <v>150</v>
@@ -2603,7 +2639,7 @@
       <c r="P51" s="6"/>
       <c r="Q51" s="6"/>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A52" s="6"/>
       <c r="K52" s="5" t="s">
         <v>154</v>
@@ -2617,7 +2653,7 @@
       <c r="P52" s="6"/>
       <c r="Q52" s="6"/>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A53" s="6"/>
       <c r="K53" s="5" t="s">
         <v>155</v>
@@ -2631,7 +2667,7 @@
       <c r="P53" s="6"/>
       <c r="Q53" s="6"/>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A54" s="6"/>
       <c r="K54" s="5" t="s">
         <v>157</v>
@@ -2645,18 +2681,18 @@
       <c r="P54" s="6"/>
       <c r="Q54" s="6"/>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A55" s="6"/>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A56" s="6"/>
       <c r="Q56" s="6"/>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A57" s="6"/>
       <c r="Q57" s="6"/>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A58" s="6"/>
       <c r="B58" s="6" t="s">
         <v>66</v>
@@ -2682,7 +2718,7 @@
       <c r="P58" s="6"/>
       <c r="Q58" s="6"/>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A59" s="6"/>
       <c r="K59" s="6" t="s">
         <v>67</v>
@@ -2694,7 +2730,7 @@
       <c r="P59" s="6"/>
       <c r="Q59" s="6"/>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A60" s="6"/>
       <c r="K60" s="5" t="s">
         <v>68</v>
@@ -2705,14 +2741,14 @@
       <c r="P60" s="7"/>
       <c r="Q60" s="6"/>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A61" s="6"/>
       <c r="K61" s="5"/>
       <c r="M61" s="5"/>
       <c r="P61" s="7"/>
       <c r="Q61" s="6"/>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A62" s="6"/>
       <c r="B62" s="1" t="s">
         <v>166</v>
@@ -2726,7 +2762,7 @@
       <c r="P62" s="7"/>
       <c r="Q62" s="6"/>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A63" s="6"/>
       <c r="K63" s="5" t="s">
         <v>165</v>
@@ -2737,7 +2773,7 @@
       <c r="P63" s="7"/>
       <c r="Q63" s="6"/>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A64" s="6"/>
       <c r="K64" s="5" t="s">
         <v>33</v>
@@ -2748,7 +2784,7 @@
       <c r="P64" s="7"/>
       <c r="Q64" s="6"/>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A65" s="6"/>
       <c r="K65" s="5" t="s">
         <v>169</v>
@@ -2759,14 +2795,14 @@
       <c r="P65" s="7"/>
       <c r="Q65" s="6"/>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A66" s="6"/>
       <c r="K66" s="5"/>
       <c r="M66" s="6"/>
       <c r="P66" s="7"/>
       <c r="Q66" s="6"/>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A67" s="6"/>
       <c r="B67" s="1" t="s">
         <v>265</v>
@@ -2780,7 +2816,7 @@
       <c r="P67" s="7"/>
       <c r="Q67" s="6"/>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A68" s="6"/>
       <c r="K68" s="5" t="s">
         <v>169</v>
@@ -2791,40 +2827,40 @@
       <c r="P68" s="7"/>
       <c r="Q68" s="6"/>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A69" s="6"/>
       <c r="K69" s="5"/>
       <c r="M69" s="6"/>
       <c r="P69" s="7"/>
       <c r="Q69" s="6"/>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A70" s="6"/>
       <c r="K70" s="5"/>
       <c r="M70" s="6"/>
       <c r="P70" s="7"/>
       <c r="Q70" s="6"/>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A71" s="6"/>
       <c r="K71" s="5"/>
       <c r="M71" s="6"/>
       <c r="P71" s="7"/>
       <c r="Q71" s="6"/>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A72" s="6"/>
       <c r="K72" s="5"/>
       <c r="M72" s="5"/>
       <c r="P72" s="7"/>
       <c r="Q72" s="6"/>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A73" s="6"/>
       <c r="P73" s="7"/>
       <c r="Q73" s="6"/>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A74" s="6"/>
       <c r="B74" s="5" t="s">
         <v>73</v>
@@ -2851,7 +2887,7 @@
       <c r="P74" s="6"/>
       <c r="Q74" s="6"/>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A75" s="6"/>
       <c r="B75" s="6"/>
       <c r="C75" s="6"/>
@@ -2874,7 +2910,7 @@
       <c r="P75" s="6"/>
       <c r="Q75" s="6"/>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A76" s="6"/>
       <c r="B76" s="6"/>
       <c r="C76" s="6"/>
@@ -2896,7 +2932,7 @@
       <c r="P76" s="6"/>
       <c r="Q76" s="6"/>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A77" s="6"/>
       <c r="B77" s="6"/>
       <c r="C77" s="6"/>
@@ -2916,7 +2952,7 @@
       <c r="P77" s="6"/>
       <c r="Q77" s="6"/>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A78" s="6"/>
       <c r="B78" s="6"/>
       <c r="C78" s="6"/>
@@ -2940,7 +2976,7 @@
       <c r="P78" s="6"/>
       <c r="Q78" s="6"/>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A79" s="6"/>
       <c r="B79" s="6"/>
       <c r="C79" s="6"/>
@@ -2963,7 +2999,7 @@
       <c r="P79" s="6"/>
       <c r="Q79" s="6"/>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A80" s="6"/>
       <c r="B80" s="6"/>
       <c r="C80" s="6"/>
@@ -2985,7 +3021,7 @@
       <c r="P80" s="6"/>
       <c r="Q80" s="6"/>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A81" s="6"/>
       <c r="B81" s="6"/>
       <c r="C81" s="6"/>
@@ -3004,7 +3040,7 @@
       <c r="P81" s="6"/>
       <c r="Q81" s="6"/>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A82" s="6"/>
       <c r="B82" s="5"/>
       <c r="C82" s="6"/>
@@ -3021,7 +3057,7 @@
       <c r="P82" s="6"/>
       <c r="Q82" s="6"/>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A83" s="6"/>
       <c r="B83" s="6" t="s">
         <v>79</v>
@@ -3046,7 +3082,7 @@
       <c r="P83" s="6"/>
       <c r="Q83" s="6"/>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A84" s="6"/>
       <c r="B84" s="6"/>
       <c r="C84" s="6"/>
@@ -3069,7 +3105,7 @@
       <c r="P84" s="6"/>
       <c r="Q84" s="6"/>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A85" s="6"/>
       <c r="H85" s="6"/>
       <c r="I85" s="6"/>
@@ -3086,7 +3122,7 @@
       <c r="P85" s="6"/>
       <c r="Q85" s="6"/>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A86" s="6"/>
       <c r="H86" s="6"/>
       <c r="I86" s="6"/>
@@ -3104,7 +3140,7 @@
       <c r="P86" s="6"/>
       <c r="Q86" s="6"/>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A87" s="6"/>
       <c r="K87" s="11" t="s">
         <v>144</v>
@@ -3118,7 +3154,7 @@
       <c r="P87" s="6"/>
       <c r="Q87" s="6"/>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A88" s="6"/>
       <c r="B88" s="6"/>
       <c r="C88" s="6"/>
@@ -3136,7 +3172,7 @@
       <c r="P88" s="6"/>
       <c r="Q88" s="6"/>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A89" s="6"/>
       <c r="K89" s="11"/>
       <c r="M89" s="11"/>
@@ -3144,12 +3180,12 @@
       <c r="P89" s="6"/>
       <c r="Q89" s="7"/>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A90" s="6"/>
       <c r="P90" s="6"/>
       <c r="Q90" s="6"/>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A91" s="6"/>
       <c r="B91" s="6"/>
       <c r="C91" s="6"/>
@@ -3163,7 +3199,7 @@
       <c r="P91" s="7"/>
       <c r="Q91" s="6"/>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A92" s="6"/>
       <c r="B92" s="1" t="s">
         <v>82</v>
@@ -3177,7 +3213,7 @@
       <c r="P92" s="6"/>
       <c r="Q92" s="6"/>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A93" s="5"/>
       <c r="B93" s="6"/>
       <c r="C93" s="6"/>
@@ -3190,7 +3226,7 @@
       <c r="P93" s="6"/>
       <c r="Q93" s="6"/>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A94" s="6"/>
       <c r="C94" s="6"/>
       <c r="D94" s="6"/>
@@ -3208,7 +3244,7 @@
       <c r="P94" s="6"/>
       <c r="Q94" s="6"/>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A95" s="6"/>
       <c r="B95" s="8" t="s">
         <v>89</v>
@@ -3233,7 +3269,7 @@
       <c r="P95" s="6"/>
       <c r="Q95" s="6"/>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A96" s="6"/>
       <c r="B96" s="8"/>
       <c r="C96" s="5"/>
@@ -3256,7 +3292,7 @@
       <c r="P96" s="6"/>
       <c r="Q96" s="6"/>
     </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A97" s="6"/>
       <c r="B97" s="6"/>
       <c r="C97" s="6"/>
@@ -3279,7 +3315,7 @@
       <c r="P97" s="7"/>
       <c r="Q97" s="6"/>
     </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A98" s="6"/>
       <c r="B98" s="6"/>
       <c r="C98" s="6"/>
@@ -3301,7 +3337,7 @@
       <c r="P98" s="6"/>
       <c r="Q98" s="6"/>
     </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B99" s="8"/>
       <c r="C99" s="5"/>
       <c r="D99" s="6"/>
@@ -3321,7 +3357,7 @@
       <c r="P99" s="6"/>
       <c r="Q99" s="6"/>
     </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B100" s="8"/>
       <c r="C100" s="5"/>
       <c r="D100" s="6"/>
@@ -3341,7 +3377,7 @@
       <c r="P100" s="6"/>
       <c r="Q100" s="6"/>
     </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B101" s="1"/>
       <c r="G101" s="1"/>
       <c r="H101" s="6"/>
@@ -3353,7 +3389,7 @@
       <c r="P101" s="7"/>
       <c r="Q101" s="6"/>
     </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:17" x14ac:dyDescent="0.3">
       <c r="H102" s="6"/>
       <c r="I102" s="6"/>
       <c r="J102" s="8"/>
@@ -3364,7 +3400,7 @@
       <c r="P102" s="7"/>
       <c r="Q102" s="6"/>
     </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B103" s="1" t="s">
         <v>97</v>
       </c>
@@ -3373,7 +3409,7 @@
       <c r="P103" s="7"/>
       <c r="Q103" s="7"/>
     </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B104" s="1" t="s">
         <v>107</v>
       </c>
@@ -3389,7 +3425,7 @@
       <c r="P104" s="7"/>
       <c r="Q104" s="6"/>
     </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:17" x14ac:dyDescent="0.3">
       <c r="K105" s="1" t="s">
         <v>68</v>
       </c>
@@ -3402,7 +3438,7 @@
       <c r="P105" s="6"/>
       <c r="Q105" s="6"/>
     </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A106" s="6"/>
       <c r="B106" s="1" t="s">
         <v>100</v>
@@ -3423,7 +3459,7 @@
       <c r="P106" s="6"/>
       <c r="Q106" s="6"/>
     </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A107" s="6"/>
       <c r="K107" s="1" t="s">
         <v>101</v>
@@ -3438,20 +3474,20 @@
       <c r="P107" s="6"/>
       <c r="Q107" s="6"/>
     </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A108" s="6"/>
       <c r="N108" s="6"/>
       <c r="P108" s="7"/>
       <c r="Q108" s="6"/>
     </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A109" s="6"/>
       <c r="N109" s="6"/>
       <c r="O109" s="5"/>
       <c r="P109" s="6"/>
       <c r="Q109" s="6"/>
     </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A110" s="6"/>
       <c r="H110" s="6"/>
       <c r="I110" s="6"/>
@@ -3464,7 +3500,7 @@
       <c r="P110" s="6"/>
       <c r="Q110" s="6"/>
     </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A111" s="6"/>
       <c r="H111" s="6"/>
       <c r="I111" s="6"/>
@@ -3477,7 +3513,7 @@
       <c r="P111" s="6"/>
       <c r="Q111" s="6"/>
     </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A112" s="6"/>
       <c r="D112" s="6"/>
       <c r="E112" s="6"/>
@@ -3494,7 +3530,7 @@
       <c r="P112" s="6"/>
       <c r="Q112" s="6"/>
     </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A113" s="6"/>
       <c r="B113" s="8"/>
       <c r="C113" s="5"/>
@@ -3513,25 +3549,25 @@
       <c r="P113" s="6"/>
       <c r="Q113" s="6"/>
     </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A114" s="6"/>
       <c r="O114" s="6"/>
       <c r="P114" s="6"/>
       <c r="Q114" s="6"/>
     </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A115" s="6"/>
       <c r="O115" s="6"/>
       <c r="P115" s="6"/>
       <c r="Q115" s="6"/>
     </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A116" s="6"/>
       <c r="O116" s="6"/>
       <c r="P116" s="6"/>
       <c r="Q116" s="6"/>
     </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A117" s="6"/>
       <c r="B117" s="8"/>
       <c r="C117" s="5"/>
@@ -3550,7 +3586,7 @@
       <c r="P117" s="6"/>
       <c r="Q117" s="6"/>
     </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A118" s="6"/>
       <c r="B118" s="1" t="s">
         <v>119</v>
@@ -3570,7 +3606,7 @@
       <c r="P118" s="6"/>
       <c r="Q118" s="6"/>
     </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A119" s="6"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
@@ -3580,7 +3616,7 @@
       <c r="P119" s="6"/>
       <c r="Q119" s="6"/>
     </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A120" s="6"/>
       <c r="B120" s="1" t="s">
         <v>120</v>
@@ -3607,7 +3643,7 @@
       <c r="P120" s="6"/>
       <c r="Q120" s="6"/>
     </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A121" s="6"/>
       <c r="B121" s="1" t="s">
         <v>121</v>
@@ -3634,7 +3670,7 @@
       <c r="P121" s="6"/>
       <c r="Q121" s="6"/>
     </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A122" s="6"/>
       <c r="B122" s="1" t="s">
         <v>126</v>
@@ -3657,7 +3693,7 @@
       <c r="P122" s="6"/>
       <c r="Q122" s="6"/>
     </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A123" s="6"/>
       <c r="B123" s="6" t="s">
         <v>131</v>
@@ -3676,7 +3712,7 @@
       <c r="P123" s="6"/>
       <c r="Q123" s="6"/>
     </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A124" s="6"/>
       <c r="B124" s="6" t="s">
         <v>160</v>
@@ -3701,7 +3737,7 @@
       <c r="P124" s="6"/>
       <c r="Q124" s="6"/>
     </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A125" s="6"/>
       <c r="B125" s="6" t="s">
         <v>162</v>
@@ -3724,7 +3760,7 @@
       <c r="P125" s="6"/>
       <c r="Q125" s="6"/>
     </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A126" s="6"/>
       <c r="B126" s="6" t="s">
         <v>231</v>
@@ -3747,7 +3783,7 @@
       <c r="P126" s="6"/>
       <c r="Q126" s="6"/>
     </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A127" s="6"/>
       <c r="B127" s="5"/>
       <c r="C127" s="5"/>
@@ -3766,7 +3802,7 @@
       <c r="P127" s="6"/>
       <c r="Q127" s="6"/>
     </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A128" s="6"/>
       <c r="B128" s="5"/>
       <c r="C128" s="5"/>
@@ -3785,7 +3821,7 @@
       <c r="P128" s="6"/>
       <c r="Q128" s="6"/>
     </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A129" s="6"/>
       <c r="B129" s="5" t="s">
         <v>239</v>
@@ -3810,7 +3846,7 @@
       <c r="P129" s="6"/>
       <c r="Q129" s="6"/>
     </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A130" s="6"/>
       <c r="B130" s="5"/>
       <c r="C130" s="5"/>
@@ -3833,7 +3869,7 @@
       <c r="P130" s="6"/>
       <c r="Q130" s="6"/>
     </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A131" s="6"/>
       <c r="B131" s="5"/>
       <c r="C131" s="5"/>
@@ -3856,7 +3892,7 @@
       <c r="P131" s="6"/>
       <c r="Q131" s="6"/>
     </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A132" s="6"/>
       <c r="B132" s="5"/>
       <c r="C132" s="5"/>
@@ -3879,7 +3915,7 @@
       <c r="P132" s="6"/>
       <c r="Q132" s="6"/>
     </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A133" s="6"/>
       <c r="B133" s="6"/>
       <c r="C133" s="6"/>
@@ -3902,7 +3938,7 @@
       <c r="P133" s="6"/>
       <c r="Q133" s="6"/>
     </row>
-    <row r="134" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A134" s="6"/>
       <c r="B134" s="6"/>
       <c r="C134" s="6"/>
@@ -3924,7 +3960,7 @@
       <c r="P134" s="6"/>
       <c r="Q134" s="6"/>
     </row>
-    <row r="135" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A135" s="5"/>
       <c r="B135" s="8"/>
       <c r="C135" s="5"/>
@@ -3946,7 +3982,7 @@
       <c r="P135" s="6"/>
       <c r="Q135" s="6"/>
     </row>
-    <row r="136" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A136" s="5"/>
       <c r="B136" s="8"/>
       <c r="C136" s="5"/>
@@ -3964,7 +4000,7 @@
       <c r="P136" s="6"/>
       <c r="Q136" s="6"/>
     </row>
-    <row r="137" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A137" s="5"/>
       <c r="B137" s="8" t="s">
         <v>240</v>
@@ -3988,7 +4024,7 @@
       <c r="P137" s="6"/>
       <c r="Q137" s="6"/>
     </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A138" s="5"/>
       <c r="B138" s="8"/>
       <c r="C138" s="5"/>
@@ -4010,7 +4046,7 @@
       <c r="P138" s="6"/>
       <c r="Q138" s="6"/>
     </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A139" s="5"/>
       <c r="B139" s="8"/>
       <c r="C139" s="5"/>
@@ -4028,11 +4064,11 @@
       <c r="P139" s="6"/>
       <c r="Q139" s="6"/>
     </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:17" x14ac:dyDescent="0.3">
       <c r="K140" s="1"/>
       <c r="M140" s="5"/>
     </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:17" x14ac:dyDescent="0.3">
       <c r="C141" s="6"/>
       <c r="D141" s="6"/>
       <c r="E141" s="6"/>
@@ -4047,21 +4083,21 @@
       <c r="N141" s="6"/>
       <c r="O141" s="6"/>
     </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:17" x14ac:dyDescent="0.3">
       <c r="N142" s="6"/>
       <c r="O142" s="6"/>
     </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B143" s="6" t="s">
         <v>64</v>
       </c>
       <c r="N143" s="6"/>
     </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:17" x14ac:dyDescent="0.3">
       <c r="N144" s="6"/>
       <c r="O144" s="6"/>
     </row>
-    <row r="145" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B145" s="5" t="s">
         <v>123</v>
       </c>
@@ -4084,7 +4120,7 @@
       <c r="N145" s="6"/>
       <c r="O145" s="6"/>
     </row>
-    <row r="146" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:15" x14ac:dyDescent="0.3">
       <c r="K146" s="1" t="s">
         <v>113</v>
       </c>
@@ -4092,7 +4128,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="147" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:15" x14ac:dyDescent="0.3">
       <c r="K147" s="1" t="s">
         <v>125</v>
       </c>
@@ -4100,7 +4136,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="149" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B149" s="6" t="s">
         <v>65</v>
       </c>
@@ -4118,7 +4154,7 @@
       <c r="L149" s="6"/>
       <c r="M149" s="5"/>
     </row>
-    <row r="150" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B150" s="6"/>
       <c r="C150" s="6"/>
       <c r="D150" s="6"/>
@@ -4132,7 +4168,7 @@
       <c r="L150" s="6"/>
       <c r="M150" s="5"/>
     </row>
-    <row r="151" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B151" s="6" t="s">
         <v>110</v>
       </c>
@@ -4153,7 +4189,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="152" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:15" x14ac:dyDescent="0.3">
       <c r="D152" s="6"/>
       <c r="E152" s="6"/>
       <c r="F152" s="6"/>
@@ -4169,7 +4205,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="153" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:15" x14ac:dyDescent="0.3">
       <c r="D153" s="6"/>
       <c r="E153" s="6"/>
       <c r="F153" s="6"/>
@@ -4181,7 +4217,7 @@
       <c r="L153" s="6"/>
       <c r="M153" s="5"/>
     </row>
-    <row r="154" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B154" s="1" t="s">
         <v>247</v>
       </c>
@@ -4195,7 +4231,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="155" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B155" s="1" t="s">
         <v>257</v>
       </c>
@@ -4203,20 +4239,20 @@
         <v>64</v>
       </c>
     </row>
-    <row r="156" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A156" s="1"/>
       <c r="B156" s="1"/>
       <c r="C156" s="1"/>
     </row>
-    <row r="157" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B157" s="1"/>
       <c r="C157" s="1"/>
     </row>
-    <row r="158" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B158" s="1"/>
       <c r="C158" s="1"/>
     </row>
-    <row r="159" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B159" s="1" t="s">
         <v>195</v>
       </c>
@@ -4227,7 +4263,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="160" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:15" x14ac:dyDescent="0.3">
       <c r="K160" s="1" t="s">
         <v>197</v>
       </c>
@@ -4235,10 +4271,10 @@
         <v>23</v>
       </c>
     </row>
-    <row r="161" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="161" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K161" s="1"/>
     </row>
-    <row r="163" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="163" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B163" s="1" t="s">
         <v>206</v>
       </c>
@@ -4250,7 +4286,7 @@
       </c>
       <c r="O163" s="6"/>
     </row>
-    <row r="164" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="164" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K164" s="1" t="s">
         <v>26</v>
       </c>
@@ -4258,7 +4294,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="165" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="165" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K165" s="1" t="s">
         <v>41</v>
       </c>
@@ -4266,7 +4302,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="166" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="166" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K166" s="1" t="s">
         <v>33</v>
       </c>
@@ -4274,7 +4310,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="167" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="167" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K167" s="1" t="s">
         <v>199</v>
       </c>
@@ -4282,7 +4318,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="168" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="168" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K168" s="1" t="s">
         <v>150</v>
       </c>
@@ -4290,7 +4326,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="169" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="169" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B169" s="1" t="s">
         <v>227</v>
       </c>
@@ -4301,7 +4337,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="170" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="170" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B170" s="1"/>
       <c r="K170" s="1" t="s">
         <v>26</v>
@@ -4310,7 +4346,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="171" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="171" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K171" s="1" t="s">
         <v>41</v>
       </c>
@@ -4318,7 +4354,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="172" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="172" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K172" s="1" t="s">
         <v>228</v>
       </c>
@@ -4326,11 +4362,11 @@
         <v>229</v>
       </c>
     </row>
-    <row r="173" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="173" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K173" s="1"/>
       <c r="M173" s="1"/>
     </row>
-    <row r="174" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="174" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B174" s="1" t="s">
         <v>230</v>
       </c>
@@ -4341,7 +4377,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="175" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="175" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K175" s="1" t="s">
         <v>26</v>
       </c>
@@ -4349,7 +4385,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="176" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="176" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K176" s="1" t="s">
         <v>41</v>
       </c>
@@ -4357,7 +4393,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="177" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="177" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K177" s="1" t="s">
         <v>60</v>
       </c>
@@ -4365,7 +4401,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="178" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="178" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K178" s="1" t="s">
         <v>68</v>
       </c>
@@ -4373,10 +4409,10 @@
         <v>71</v>
       </c>
     </row>
-    <row r="179" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="179" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K179" s="1"/>
     </row>
-    <row r="181" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="181" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B181" s="1" t="s">
         <v>207</v>
       </c>
@@ -4390,7 +4426,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="182" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="182" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K182" s="1" t="s">
         <v>26</v>
       </c>
@@ -4401,7 +4437,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="183" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="183" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K183" s="1" t="s">
         <v>41</v>
       </c>
@@ -4412,10 +4448,10 @@
         <v>211</v>
       </c>
     </row>
-    <row r="184" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="184" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K184" s="1"/>
     </row>
-    <row r="185" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="185" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B185" s="1" t="s">
         <v>208</v>
       </c>
@@ -4426,7 +4462,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="186" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="186" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K186" s="1" t="s">
         <v>26</v>
       </c>
@@ -4434,7 +4470,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="187" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="187" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K187" s="1" t="s">
         <v>41</v>
       </c>
@@ -4442,7 +4478,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="188" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="188" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K188" s="1" t="s">
         <v>216</v>
       </c>
@@ -4450,7 +4486,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="189" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="189" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K189" s="1" t="s">
         <v>218</v>
       </c>
@@ -4458,7 +4494,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="191" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="191" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B191" s="1" t="s">
         <v>213</v>
       </c>
@@ -4469,7 +4505,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="192" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="192" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K192" s="1" t="s">
         <v>215</v>
       </c>
@@ -4477,7 +4513,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="195" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="195" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B195" s="1" t="s">
         <v>219</v>
       </c>
@@ -4491,7 +4527,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="196" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="196" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K196" s="1" t="s">
         <v>26</v>
       </c>
@@ -4502,7 +4538,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="197" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="197" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K197" s="1" t="s">
         <v>41</v>
       </c>
@@ -4513,7 +4549,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="198" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="198" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K198" s="1" t="s">
         <v>143</v>
       </c>
@@ -4521,7 +4557,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="199" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="199" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B199" s="1" t="s">
         <v>234</v>
       </c>
@@ -4532,7 +4568,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="200" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="200" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K200" s="1" t="s">
         <v>134</v>
       </c>
@@ -4540,7 +4576,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="204" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="204" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B204" s="1" t="s">
         <v>226</v>
       </c>
@@ -4554,7 +4590,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="205" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="205" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K205" s="1" t="s">
         <v>95</v>
       </c>
@@ -4562,7 +4598,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="208" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="208" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B208" s="1" t="s">
         <v>248</v>
       </c>
@@ -4573,7 +4609,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="209" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="209" spans="2:13" x14ac:dyDescent="0.3">
       <c r="K209" s="1" t="s">
         <v>26</v>
       </c>
@@ -4581,7 +4617,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="210" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="210" spans="2:13" x14ac:dyDescent="0.3">
       <c r="K210" s="1" t="s">
         <v>60</v>
       </c>
@@ -4589,7 +4625,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="211" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="211" spans="2:13" x14ac:dyDescent="0.3">
       <c r="K211" s="1" t="s">
         <v>41</v>
       </c>
@@ -4597,7 +4633,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="212" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="212" spans="2:13" x14ac:dyDescent="0.3">
       <c r="K212" s="1" t="s">
         <v>249</v>
       </c>
@@ -4605,7 +4641,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="213" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="213" spans="2:13" x14ac:dyDescent="0.3">
       <c r="K213" s="1" t="s">
         <v>250</v>
       </c>
@@ -4613,7 +4649,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="215" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="215" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B215" s="1" t="s">
         <v>275</v>
       </c>
@@ -4624,7 +4660,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="216" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="216" spans="2:13" x14ac:dyDescent="0.3">
       <c r="K216" s="1" t="s">
         <v>26</v>
       </c>
@@ -4632,7 +4668,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="217" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="217" spans="2:13" x14ac:dyDescent="0.3">
       <c r="K217" s="1" t="s">
         <v>95</v>
       </c>
@@ -4640,7 +4676,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="218" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="218" spans="2:13" x14ac:dyDescent="0.3">
       <c r="K218" s="1" t="s">
         <v>41</v>
       </c>
@@ -4648,7 +4684,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="219" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="219" spans="2:13" x14ac:dyDescent="0.3">
       <c r="K219" s="1" t="s">
         <v>216</v>
       </c>
@@ -4656,7 +4692,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="220" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="220" spans="2:13" x14ac:dyDescent="0.3">
       <c r="K220" s="1" t="s">
         <v>276</v>
       </c>
@@ -4664,12 +4700,47 @@
         <v>112</v>
       </c>
     </row>
-    <row r="221" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="221" spans="2:13" x14ac:dyDescent="0.3">
       <c r="K221" s="1" t="s">
         <v>68</v>
       </c>
       <c r="M221" s="1" t="s">
         <v>71</v>
+      </c>
+    </row>
+    <row r="222" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B222" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="K222" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="M222" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="223" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="K223" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="M223" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="224" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="K224" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="M224" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="225" spans="11:13" x14ac:dyDescent="0.3">
+      <c r="K225" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="M225" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -4684,13 +4755,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EECC075D-9730-41E5-B97E-C301603D1E48}">
-  <dimension ref="A1:Q87"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:Q90"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="27.375" customWidth="1"/>
+    <col min="2" max="2" width="27.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -4731,7 +4802,7 @@
       <c r="P1" s="12"/>
       <c r="Q1" s="12"/>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -4766,7 +4837,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>11</v>
       </c>
@@ -4803,7 +4874,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B6" s="6" t="s">
         <v>53</v>
       </c>
@@ -4820,7 +4891,7 @@
       <c r="M6" s="5"/>
       <c r="N6" s="6"/>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
         <v>141</v>
       </c>
@@ -4834,7 +4905,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="K9" s="1" t="s">
         <v>134</v>
       </c>
@@ -4845,7 +4916,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B11" s="1" t="s">
         <v>129</v>
       </c>
@@ -4859,7 +4930,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B12" s="6" t="s">
         <v>54</v>
       </c>
@@ -4887,7 +4958,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
@@ -4909,7 +4980,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
       <c r="D14" s="6"/>
@@ -4922,7 +4993,7 @@
       <c r="N14" s="6"/>
       <c r="O14" s="6"/>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B15" s="1" t="s">
         <v>74</v>
       </c>
@@ -4940,7 +5011,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="K16" s="1" t="s">
         <v>75</v>
       </c>
@@ -4951,7 +5022,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B17" s="1" t="s">
         <v>104</v>
       </c>
@@ -4968,7 +5039,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="18" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B18" s="1" t="s">
         <v>115</v>
       </c>
@@ -4982,7 +5053,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="19" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K19" s="5" t="s">
         <v>37</v>
       </c>
@@ -4990,7 +5061,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="20" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K20" s="1" t="s">
         <v>118</v>
       </c>
@@ -4998,7 +5069,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="21" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B21" s="1" t="s">
         <v>127</v>
       </c>
@@ -5012,7 +5083,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="23" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B23" s="1" t="s">
         <v>133</v>
       </c>
@@ -5026,7 +5097,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="24" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K24" s="1" t="s">
         <v>134</v>
       </c>
@@ -5034,7 +5105,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="26" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B26" s="1" t="s">
         <v>139</v>
       </c>
@@ -5048,7 +5119,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="27" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K27" s="1" t="s">
         <v>33</v>
       </c>
@@ -5056,7 +5127,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="28" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K28" s="1" t="s">
         <v>41</v>
       </c>
@@ -5064,7 +5135,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K29" s="1" t="s">
         <v>68</v>
       </c>
@@ -5072,7 +5143,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="31" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B31" s="1" t="s">
         <v>158</v>
       </c>
@@ -5086,7 +5157,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="32" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B32" s="1" t="s">
         <v>173</v>
       </c>
@@ -5100,7 +5171,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="K33" s="1" t="s">
         <v>186</v>
       </c>
@@ -5108,7 +5179,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B34" s="1" t="s">
         <v>222</v>
       </c>
@@ -5122,7 +5193,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="K35" s="1" t="s">
         <v>223</v>
       </c>
@@ -5130,7 +5201,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>180</v>
       </c>
@@ -5141,11 +5212,11 @@
         <v>128</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="K37" s="1"/>
       <c r="M37" s="1"/>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B38" s="1" t="s">
         <v>193</v>
       </c>
@@ -5159,7 +5230,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="K39" s="1" t="s">
         <v>186</v>
       </c>
@@ -5167,7 +5238,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B40" s="1" t="s">
         <v>175</v>
       </c>
@@ -5182,10 +5253,10 @@
       </c>
       <c r="N40" s="6"/>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N41" s="6"/>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B42" s="1" t="s">
         <v>116</v>
       </c>
@@ -5206,7 +5277,7 @@
       </c>
       <c r="N42" s="6"/>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B43" s="6"/>
       <c r="C43" s="5"/>
       <c r="D43" s="6"/>
@@ -5224,7 +5295,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B44" s="8"/>
       <c r="C44" s="5"/>
       <c r="D44" s="6"/>
@@ -5242,7 +5313,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B45" s="1" t="s">
         <v>188</v>
       </c>
@@ -5253,7 +5324,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="K46" s="1" t="s">
         <v>189</v>
       </c>
@@ -5261,7 +5332,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
         <v>178</v>
       </c>
@@ -5269,7 +5340,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B50" s="1" t="s">
         <v>184</v>
       </c>
@@ -5286,7 +5357,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A54" s="1"/>
       <c r="B54" s="1" t="s">
         <v>203</v>
@@ -5304,7 +5375,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
       <c r="K55" s="1" t="s">
         <v>202</v>
       </c>
@@ -5312,7 +5383,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
       <c r="K56" s="1" t="s">
         <v>204</v>
       </c>
@@ -5320,7 +5391,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B58" s="1" t="s">
         <v>232</v>
       </c>
@@ -5334,7 +5405,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
       <c r="K59" s="1" t="s">
         <v>75</v>
       </c>
@@ -5342,7 +5413,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B61" s="1" t="s">
         <v>233</v>
       </c>
@@ -5356,7 +5427,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B63" s="1" t="s">
         <v>237</v>
       </c>
@@ -5370,7 +5441,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.3">
       <c r="K64" s="1" t="s">
         <v>238</v>
       </c>
@@ -5378,7 +5449,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B65" s="1" t="s">
         <v>244</v>
       </c>
@@ -5392,7 +5463,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B67" s="1" t="s">
         <v>246</v>
       </c>
@@ -5406,9 +5477,9 @@
         <v>128</v>
       </c>
     </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B68" s="1" t="s">
-        <v>258</v>
+        <v>285</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>53</v>
@@ -5420,165 +5491,193 @@
         <v>128</v>
       </c>
     </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B69" s="1" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>53</v>
       </c>
       <c r="K69" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="M69" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B70" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="K70" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="M69" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="K70" s="1" t="s">
+      <c r="M70" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="K71" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="M70" s="1" t="s">
+      <c r="M71" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B71" s="1" t="s">
+    <row r="72" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B72" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="C71" s="1" t="s">
+      <c r="C72" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="K71" s="1" t="s">
+      <c r="K72" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="M71" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="K72" s="1" t="s">
+      <c r="M72" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="73" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="K73" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="M72" s="1" t="s">
+      <c r="M73" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B74" s="1" t="s">
+    <row r="75" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B75" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="C74" s="1" t="s">
+      <c r="C75" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="K74" s="1" t="s">
+      <c r="K75" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="M74" s="1" t="s">
+      <c r="M75" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="K75" s="1" t="s">
+    <row r="76" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="K76" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="M75" s="1" t="s">
+      <c r="M76" s="1" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B77" s="1" t="s">
+    <row r="78" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B78" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="K77" s="1" t="s">
+      <c r="K78" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="M77" s="1" t="s">
+      <c r="M78" s="1" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="78" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="K78" s="1" t="s">
+    <row r="79" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="K79" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="M78" s="1" t="s">
+      <c r="M79" s="1" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B79" s="1" t="s">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B80" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="C79" s="1" t="s">
+      <c r="C80" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="K79" s="1" t="s">
+      <c r="K80" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="M79" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B80" s="1"/>
-      <c r="C80" s="1"/>
-      <c r="K80" s="1"/>
-      <c r="M80" s="1"/>
-    </row>
-    <row r="81" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B81" s="1" t="s">
+      <c r="M80" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="81" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B81" s="1"/>
+      <c r="C81" s="1"/>
+      <c r="K81" s="1"/>
+      <c r="M81" s="1"/>
+    </row>
+    <row r="82" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B82" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="C81" s="1" t="s">
+      <c r="C82" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="K81" s="1" t="s">
+      <c r="K82" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="M81" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="83" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B83" s="1" t="s">
+      <c r="M82" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="84" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B84" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="C83" s="1" t="s">
+      <c r="C84" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="K83" s="1" t="s">
+      <c r="K84" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="M83" s="1" t="s">
+      <c r="M84" s="1" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="85" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B85" s="1" t="s">
+    <row r="86" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B86" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="C85" s="1" t="s">
+      <c r="C86" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="K85" s="1" t="s">
+      <c r="K86" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="M85" s="1" t="s">
+      <c r="M86" s="1" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="87" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B87" s="1" t="s">
+    <row r="88" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B88" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="C87" s="1" t="s">
+      <c r="C88" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="K87" s="1" t="s">
+      <c r="K88" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="M87" s="1" t="s">
+      <c r="M88" s="1" t="s">
         <v>153</v>
+      </c>
+    </row>
+    <row r="90" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B90" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="K90" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="M90" s="1" t="s">
+        <v>283</v>
       </c>
     </row>
   </sheetData>
@@ -5593,7 +5692,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEE0849C-6C30-450E-8369-1D81B45C3886}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Config/Datas/__beans__.xlsx
+++ b/Config/Datas/__beans__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93EFF309-AF19-4E34-816F-D1BE742546AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2A3B658-7702-4C5E-8F41-93285CB7B756}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="650" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="659" uniqueCount="289">
   <si>
     <t>##var</t>
   </si>
@@ -1153,6 +1153,18 @@
   </si>
   <si>
     <t>GA_获得收入</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DV_当前串空位数</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Expression</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Exp</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -3383,9 +3395,13 @@
       <c r="H101" s="6"/>
       <c r="I101" s="6"/>
       <c r="J101" s="8"/>
-      <c r="K101" s="5"/>
+      <c r="K101" s="5" t="s">
+        <v>60</v>
+      </c>
       <c r="L101" s="6"/>
-      <c r="M101" s="5"/>
+      <c r="M101" s="5" t="s">
+        <v>23</v>
+      </c>
       <c r="P101" s="7"/>
       <c r="Q101" s="6"/>
     </row>
@@ -3785,8 +3801,12 @@
     </row>
     <row r="127" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A127" s="6"/>
-      <c r="B127" s="5"/>
-      <c r="C127" s="5"/>
+      <c r="B127" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="C127" s="5" t="s">
+        <v>119</v>
+      </c>
       <c r="D127" s="6"/>
       <c r="E127" s="6"/>
       <c r="F127" s="6"/>
@@ -3794,9 +3814,13 @@
       <c r="H127" s="6"/>
       <c r="I127" s="6"/>
       <c r="J127" s="5"/>
-      <c r="K127" s="5"/>
+      <c r="K127" s="5" t="s">
+        <v>288</v>
+      </c>
       <c r="L127" s="6"/>
-      <c r="M127" s="5"/>
+      <c r="M127" s="5" t="s">
+        <v>287</v>
+      </c>
       <c r="N127" s="6"/>
       <c r="O127" s="6"/>
       <c r="P127" s="6"/>
@@ -3804,7 +3828,9 @@
     </row>
     <row r="128" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A128" s="6"/>
-      <c r="B128" s="5"/>
+      <c r="B128" s="5" t="s">
+        <v>287</v>
+      </c>
       <c r="C128" s="5"/>
       <c r="D128" s="6"/>
       <c r="E128" s="6"/>
@@ -3813,9 +3839,13 @@
       <c r="H128" s="6"/>
       <c r="I128" s="6"/>
       <c r="J128" s="5"/>
-      <c r="K128" s="5"/>
+      <c r="K128" s="5" t="s">
+        <v>105</v>
+      </c>
       <c r="L128" s="6"/>
-      <c r="M128" s="5"/>
+      <c r="M128" s="5" t="s">
+        <v>23</v>
+      </c>
       <c r="N128" s="6"/>
       <c r="O128" s="6"/>
       <c r="P128" s="6"/>
@@ -3823,24 +3853,6 @@
     </row>
     <row r="129" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A129" s="6"/>
-      <c r="B129" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="C129" s="5"/>
-      <c r="D129" s="6"/>
-      <c r="E129" s="6"/>
-      <c r="F129" s="6"/>
-      <c r="G129" s="6"/>
-      <c r="H129" s="6"/>
-      <c r="I129" s="6"/>
-      <c r="J129" s="5"/>
-      <c r="K129" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L129" s="6"/>
-      <c r="M129" s="5" t="s">
-        <v>23</v>
-      </c>
       <c r="N129" s="6"/>
       <c r="O129" s="6"/>
       <c r="P129" s="6"/>
@@ -3848,7 +3860,9 @@
     </row>
     <row r="130" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A130" s="6"/>
-      <c r="B130" s="5"/>
+      <c r="B130" s="5" t="s">
+        <v>239</v>
+      </c>
       <c r="C130" s="5"/>
       <c r="D130" s="6"/>
       <c r="E130" s="6"/>
@@ -3858,7 +3872,7 @@
       <c r="I130" s="6"/>
       <c r="J130" s="5"/>
       <c r="K130" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L130" s="6"/>
       <c r="M130" s="5" t="s">
@@ -3881,7 +3895,7 @@
       <c r="I131" s="6"/>
       <c r="J131" s="5"/>
       <c r="K131" s="5" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="L131" s="6"/>
       <c r="M131" s="5" t="s">
@@ -3904,7 +3918,7 @@
       <c r="I132" s="6"/>
       <c r="J132" s="5"/>
       <c r="K132" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="L132" s="6"/>
       <c r="M132" s="5" t="s">
@@ -3917,17 +3931,17 @@
     </row>
     <row r="133" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A133" s="6"/>
-      <c r="B133" s="6"/>
-      <c r="C133" s="6"/>
+      <c r="B133" s="5"/>
+      <c r="C133" s="5"/>
       <c r="D133" s="6"/>
       <c r="E133" s="6"/>
       <c r="F133" s="6"/>
       <c r="G133" s="6"/>
       <c r="H133" s="6"/>
       <c r="I133" s="6"/>
-      <c r="J133" s="6"/>
+      <c r="J133" s="5"/>
       <c r="K133" s="5" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="L133" s="6"/>
       <c r="M133" s="5" t="s">
@@ -3949,11 +3963,12 @@
       <c r="H134" s="6"/>
       <c r="I134" s="6"/>
       <c r="J134" s="6"/>
-      <c r="K134" s="1" t="s">
-        <v>143</v>
-      </c>
+      <c r="K134" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="L134" s="6"/>
       <c r="M134" s="5" t="s">
-        <v>241</v>
+        <v>23</v>
       </c>
       <c r="N134" s="6"/>
       <c r="O134" s="6"/>
@@ -3962,20 +3977,20 @@
     </row>
     <row r="135" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A135" s="5"/>
-      <c r="B135" s="8"/>
-      <c r="C135" s="5"/>
+      <c r="B135" s="6"/>
+      <c r="C135" s="6"/>
       <c r="D135" s="6"/>
       <c r="E135" s="6"/>
       <c r="F135" s="6"/>
       <c r="G135" s="6"/>
       <c r="H135" s="6"/>
       <c r="I135" s="6"/>
-      <c r="J135" s="8"/>
+      <c r="J135" s="6"/>
       <c r="K135" s="1" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="M135" s="5" t="s">
-        <v>103</v>
+        <v>241</v>
       </c>
       <c r="N135" s="6"/>
       <c r="O135" s="5"/>
@@ -3993,8 +4008,12 @@
       <c r="H136" s="6"/>
       <c r="I136" s="6"/>
       <c r="J136" s="8"/>
-      <c r="K136" s="1"/>
-      <c r="M136" s="5"/>
+      <c r="K136" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="M136" s="5" t="s">
+        <v>103</v>
+      </c>
       <c r="N136" s="6"/>
       <c r="O136" s="5"/>
       <c r="P136" s="6"/>
@@ -4002,23 +4021,6 @@
     </row>
     <row r="137" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A137" s="5"/>
-      <c r="B137" s="8" t="s">
-        <v>240</v>
-      </c>
-      <c r="C137" s="5"/>
-      <c r="D137" s="6"/>
-      <c r="E137" s="6"/>
-      <c r="F137" s="6"/>
-      <c r="G137" s="6"/>
-      <c r="H137" s="6"/>
-      <c r="I137" s="6"/>
-      <c r="J137" s="8"/>
-      <c r="K137" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="M137" s="1" t="s">
-        <v>242</v>
-      </c>
       <c r="N137" s="6"/>
       <c r="O137" s="5"/>
       <c r="P137" s="6"/>
@@ -4026,7 +4028,9 @@
     </row>
     <row r="138" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A138" s="5"/>
-      <c r="B138" s="8"/>
+      <c r="B138" s="8" t="s">
+        <v>240</v>
+      </c>
       <c r="C138" s="5"/>
       <c r="D138" s="6"/>
       <c r="E138" s="6"/>
@@ -4036,10 +4040,10 @@
       <c r="I138" s="6"/>
       <c r="J138" s="8"/>
       <c r="K138" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="M138" s="5" t="s">
-        <v>66</v>
+        <v>33</v>
+      </c>
+      <c r="M138" s="1" t="s">
+        <v>242</v>
       </c>
       <c r="N138" s="6"/>
       <c r="O138" s="5"/>
@@ -4057,14 +4061,27 @@
       <c r="H139" s="6"/>
       <c r="I139" s="6"/>
       <c r="J139" s="8"/>
-      <c r="K139" s="1"/>
-      <c r="M139" s="5"/>
+      <c r="K139" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="M139" s="5" t="s">
+        <v>66</v>
+      </c>
       <c r="N139" s="6"/>
       <c r="O139" s="5"/>
       <c r="P139" s="6"/>
       <c r="Q139" s="6"/>
     </row>
     <row r="140" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="B140" s="8"/>
+      <c r="C140" s="5"/>
+      <c r="D140" s="6"/>
+      <c r="E140" s="6"/>
+      <c r="F140" s="6"/>
+      <c r="G140" s="6"/>
+      <c r="H140" s="6"/>
+      <c r="I140" s="6"/>
+      <c r="J140" s="8"/>
       <c r="K140" s="1"/>
       <c r="M140" s="5"/>
     </row>

--- a/Config/Datas/__beans__.xlsx
+++ b/Config/Datas/__beans__.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2A3B658-7702-4C5E-8F41-93285CB7B756}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3EBF756-6B53-4CB0-9F1F-D9E559B4F675}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="659" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="671" uniqueCount="293">
   <si>
     <t>##var</t>
   </si>
@@ -1165,6 +1165,22 @@
   </si>
   <si>
     <t>Exp</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GA_随机触发</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DV_串上某食材数量</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>foodID</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GA_随机选卡</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1592,7 +1608,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q225"/>
+  <dimension ref="A1:Q227"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="28.75" customWidth="1"/>
@@ -3801,10 +3817,10 @@
     </row>
     <row r="127" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A127" s="6"/>
-      <c r="B127" s="5" t="s">
-        <v>286</v>
-      </c>
-      <c r="C127" s="5" t="s">
+      <c r="B127" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="C127" s="6" t="s">
         <v>119</v>
       </c>
       <c r="D127" s="6"/>
@@ -3813,13 +3829,13 @@
       <c r="G127" s="6"/>
       <c r="H127" s="6"/>
       <c r="I127" s="6"/>
-      <c r="J127" s="5"/>
-      <c r="K127" s="5" t="s">
-        <v>288</v>
+      <c r="J127" s="6"/>
+      <c r="K127" s="6" t="s">
+        <v>291</v>
       </c>
       <c r="L127" s="6"/>
-      <c r="M127" s="5" t="s">
-        <v>287</v>
+      <c r="M127" s="6" t="s">
+        <v>23</v>
       </c>
       <c r="N127" s="6"/>
       <c r="O127" s="6"/>
@@ -3828,24 +3844,18 @@
     </row>
     <row r="128" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A128" s="6"/>
-      <c r="B128" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="C128" s="5"/>
+      <c r="B128" s="6"/>
+      <c r="C128" s="6"/>
       <c r="D128" s="6"/>
       <c r="E128" s="6"/>
       <c r="F128" s="6"/>
       <c r="G128" s="6"/>
       <c r="H128" s="6"/>
       <c r="I128" s="6"/>
-      <c r="J128" s="5"/>
-      <c r="K128" s="5" t="s">
-        <v>105</v>
-      </c>
+      <c r="J128" s="6"/>
+      <c r="K128" s="6"/>
       <c r="L128" s="6"/>
-      <c r="M128" s="5" t="s">
-        <v>23</v>
-      </c>
+      <c r="M128" s="6"/>
       <c r="N128" s="6"/>
       <c r="O128" s="6"/>
       <c r="P128" s="6"/>
@@ -3853,6 +3863,26 @@
     </row>
     <row r="129" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A129" s="6"/>
+      <c r="B129" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="C129" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="D129" s="6"/>
+      <c r="E129" s="6"/>
+      <c r="F129" s="6"/>
+      <c r="G129" s="6"/>
+      <c r="H129" s="6"/>
+      <c r="I129" s="6"/>
+      <c r="J129" s="5"/>
+      <c r="K129" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="L129" s="6"/>
+      <c r="M129" s="5" t="s">
+        <v>287</v>
+      </c>
       <c r="N129" s="6"/>
       <c r="O129" s="6"/>
       <c r="P129" s="6"/>
@@ -3861,7 +3891,7 @@
     <row r="130" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A130" s="6"/>
       <c r="B130" s="5" t="s">
-        <v>239</v>
+        <v>287</v>
       </c>
       <c r="C130" s="5"/>
       <c r="D130" s="6"/>
@@ -3872,7 +3902,7 @@
       <c r="I130" s="6"/>
       <c r="J130" s="5"/>
       <c r="K130" s="5" t="s">
-        <v>25</v>
+        <v>105</v>
       </c>
       <c r="L130" s="6"/>
       <c r="M130" s="5" t="s">
@@ -3885,22 +3915,6 @@
     </row>
     <row r="131" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A131" s="6"/>
-      <c r="B131" s="5"/>
-      <c r="C131" s="5"/>
-      <c r="D131" s="6"/>
-      <c r="E131" s="6"/>
-      <c r="F131" s="6"/>
-      <c r="G131" s="6"/>
-      <c r="H131" s="6"/>
-      <c r="I131" s="6"/>
-      <c r="J131" s="5"/>
-      <c r="K131" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="L131" s="6"/>
-      <c r="M131" s="5" t="s">
-        <v>23</v>
-      </c>
       <c r="N131" s="6"/>
       <c r="O131" s="6"/>
       <c r="P131" s="6"/>
@@ -3908,7 +3922,9 @@
     </row>
     <row r="132" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A132" s="6"/>
-      <c r="B132" s="5"/>
+      <c r="B132" s="5" t="s">
+        <v>239</v>
+      </c>
       <c r="C132" s="5"/>
       <c r="D132" s="6"/>
       <c r="E132" s="6"/>
@@ -3918,7 +3934,7 @@
       <c r="I132" s="6"/>
       <c r="J132" s="5"/>
       <c r="K132" s="5" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="L132" s="6"/>
       <c r="M132" s="5" t="s">
@@ -3941,7 +3957,7 @@
       <c r="I133" s="6"/>
       <c r="J133" s="5"/>
       <c r="K133" s="5" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="L133" s="6"/>
       <c r="M133" s="5" t="s">
@@ -3954,17 +3970,17 @@
     </row>
     <row r="134" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A134" s="6"/>
-      <c r="B134" s="6"/>
-      <c r="C134" s="6"/>
+      <c r="B134" s="5"/>
+      <c r="C134" s="5"/>
       <c r="D134" s="6"/>
       <c r="E134" s="6"/>
       <c r="F134" s="6"/>
       <c r="G134" s="6"/>
       <c r="H134" s="6"/>
       <c r="I134" s="6"/>
-      <c r="J134" s="6"/>
+      <c r="J134" s="5"/>
       <c r="K134" s="5" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="L134" s="6"/>
       <c r="M134" s="5" t="s">
@@ -3976,51 +3992,68 @@
       <c r="Q134" s="6"/>
     </row>
     <row r="135" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A135" s="5"/>
-      <c r="B135" s="6"/>
-      <c r="C135" s="6"/>
+      <c r="A135" s="6"/>
+      <c r="B135" s="5"/>
+      <c r="C135" s="5"/>
       <c r="D135" s="6"/>
       <c r="E135" s="6"/>
       <c r="F135" s="6"/>
       <c r="G135" s="6"/>
       <c r="H135" s="6"/>
       <c r="I135" s="6"/>
-      <c r="J135" s="6"/>
-      <c r="K135" s="1" t="s">
-        <v>143</v>
-      </c>
+      <c r="J135" s="5"/>
+      <c r="K135" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="L135" s="6"/>
       <c r="M135" s="5" t="s">
-        <v>241</v>
+        <v>23</v>
       </c>
       <c r="N135" s="6"/>
-      <c r="O135" s="5"/>
+      <c r="O135" s="6"/>
       <c r="P135" s="6"/>
       <c r="Q135" s="6"/>
     </row>
     <row r="136" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A136" s="5"/>
-      <c r="B136" s="8"/>
-      <c r="C136" s="5"/>
+      <c r="A136" s="6"/>
+      <c r="B136" s="6"/>
+      <c r="C136" s="6"/>
       <c r="D136" s="6"/>
       <c r="E136" s="6"/>
       <c r="F136" s="6"/>
       <c r="G136" s="6"/>
       <c r="H136" s="6"/>
       <c r="I136" s="6"/>
-      <c r="J136" s="8"/>
-      <c r="K136" s="1" t="s">
-        <v>150</v>
-      </c>
+      <c r="J136" s="6"/>
+      <c r="K136" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="L136" s="6"/>
       <c r="M136" s="5" t="s">
-        <v>103</v>
+        <v>23</v>
       </c>
       <c r="N136" s="6"/>
-      <c r="O136" s="5"/>
+      <c r="O136" s="6"/>
       <c r="P136" s="6"/>
       <c r="Q136" s="6"/>
     </row>
     <row r="137" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A137" s="5"/>
+      <c r="B137" s="6"/>
+      <c r="C137" s="6"/>
+      <c r="D137" s="6"/>
+      <c r="E137" s="6"/>
+      <c r="F137" s="6"/>
+      <c r="G137" s="6"/>
+      <c r="H137" s="6"/>
+      <c r="I137" s="6"/>
+      <c r="J137" s="6"/>
+      <c r="K137" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="M137" s="5" t="s">
+        <v>241</v>
+      </c>
       <c r="N137" s="6"/>
       <c r="O137" s="5"/>
       <c r="P137" s="6"/>
@@ -4028,9 +4061,7 @@
     </row>
     <row r="138" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A138" s="5"/>
-      <c r="B138" s="8" t="s">
-        <v>240</v>
-      </c>
+      <c r="B138" s="8"/>
       <c r="C138" s="5"/>
       <c r="D138" s="6"/>
       <c r="E138" s="6"/>
@@ -4040,10 +4071,10 @@
       <c r="I138" s="6"/>
       <c r="J138" s="8"/>
       <c r="K138" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="M138" s="1" t="s">
-        <v>242</v>
+        <v>150</v>
+      </c>
+      <c r="M138" s="5" t="s">
+        <v>103</v>
       </c>
       <c r="N138" s="6"/>
       <c r="O138" s="5"/>
@@ -4052,28 +4083,16 @@
     </row>
     <row r="139" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A139" s="5"/>
-      <c r="B139" s="8"/>
-      <c r="C139" s="5"/>
-      <c r="D139" s="6"/>
-      <c r="E139" s="6"/>
-      <c r="F139" s="6"/>
-      <c r="G139" s="6"/>
-      <c r="H139" s="6"/>
-      <c r="I139" s="6"/>
-      <c r="J139" s="8"/>
-      <c r="K139" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="M139" s="5" t="s">
-        <v>66</v>
-      </c>
       <c r="N139" s="6"/>
       <c r="O139" s="5"/>
       <c r="P139" s="6"/>
       <c r="Q139" s="6"/>
     </row>
     <row r="140" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="B140" s="8"/>
+      <c r="A140" s="5"/>
+      <c r="B140" s="8" t="s">
+        <v>240</v>
+      </c>
       <c r="C140" s="5"/>
       <c r="D140" s="6"/>
       <c r="E140" s="6"/>
@@ -4082,112 +4101,123 @@
       <c r="H140" s="6"/>
       <c r="I140" s="6"/>
       <c r="J140" s="8"/>
-      <c r="K140" s="1"/>
-      <c r="M140" s="5"/>
+      <c r="K140" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M140" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="N140" s="6"/>
+      <c r="O140" s="5"/>
+      <c r="P140" s="6"/>
+      <c r="Q140" s="6"/>
     </row>
     <row r="141" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="C141" s="6"/>
+      <c r="A141" s="5"/>
+      <c r="B141" s="8"/>
+      <c r="C141" s="5"/>
       <c r="D141" s="6"/>
       <c r="E141" s="6"/>
       <c r="F141" s="6"/>
       <c r="G141" s="6"/>
       <c r="H141" s="6"/>
       <c r="I141" s="6"/>
-      <c r="J141" s="6"/>
-      <c r="K141" s="5"/>
-      <c r="L141" s="6"/>
-      <c r="M141" s="5"/>
+      <c r="J141" s="8"/>
+      <c r="K141" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="M141" s="5" t="s">
+        <v>66</v>
+      </c>
       <c r="N141" s="6"/>
-      <c r="O141" s="6"/>
+      <c r="O141" s="5"/>
+      <c r="P141" s="6"/>
+      <c r="Q141" s="6"/>
     </row>
     <row r="142" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="N142" s="6"/>
-      <c r="O142" s="6"/>
+      <c r="B142" s="8"/>
+      <c r="C142" s="5"/>
+      <c r="D142" s="6"/>
+      <c r="E142" s="6"/>
+      <c r="F142" s="6"/>
+      <c r="G142" s="6"/>
+      <c r="H142" s="6"/>
+      <c r="I142" s="6"/>
+      <c r="J142" s="8"/>
+      <c r="K142" s="1"/>
+      <c r="M142" s="5"/>
     </row>
     <row r="143" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="B143" s="6" t="s">
-        <v>64</v>
-      </c>
+      <c r="C143" s="6"/>
+      <c r="D143" s="6"/>
+      <c r="E143" s="6"/>
+      <c r="F143" s="6"/>
+      <c r="G143" s="6"/>
+      <c r="H143" s="6"/>
+      <c r="I143" s="6"/>
+      <c r="J143" s="6"/>
+      <c r="K143" s="5"/>
+      <c r="L143" s="6"/>
+      <c r="M143" s="5"/>
       <c r="N143" s="6"/>
+      <c r="O143" s="6"/>
     </row>
     <row r="144" spans="1:17" x14ac:dyDescent="0.3">
       <c r="N144" s="6"/>
       <c r="O144" s="6"/>
     </row>
     <row r="145" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B145" s="5" t="s">
+      <c r="B145" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="N145" s="6"/>
+    </row>
+    <row r="146" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="N146" s="6"/>
+      <c r="O146" s="6"/>
+    </row>
+    <row r="147" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B147" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="C145" s="6" t="s">
+      <c r="C147" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="D145" s="6"/>
-      <c r="E145" s="6"/>
-      <c r="F145" s="6"/>
-      <c r="G145" s="6"/>
-      <c r="H145" s="6"/>
-      <c r="I145" s="6"/>
-      <c r="J145" s="6"/>
-      <c r="K145" s="1" t="s">
+      <c r="D147" s="6"/>
+      <c r="E147" s="6"/>
+      <c r="F147" s="6"/>
+      <c r="G147" s="6"/>
+      <c r="H147" s="6"/>
+      <c r="I147" s="6"/>
+      <c r="J147" s="6"/>
+      <c r="K147" s="1" t="s">
         <v>124</v>
-      </c>
-      <c r="M145" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="N145" s="6"/>
-      <c r="O145" s="6"/>
-    </row>
-    <row r="146" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="K146" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="M146" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="147" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="K147" s="1" t="s">
-        <v>125</v>
       </c>
       <c r="M147" s="1" t="s">
         <v>128</v>
       </c>
+      <c r="N147" s="6"/>
+      <c r="O147" s="6"/>
+    </row>
+    <row r="148" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="K148" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="M148" s="1" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="149" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B149" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="C149" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="D149" s="6"/>
-      <c r="E149" s="6"/>
-      <c r="F149" s="6"/>
-      <c r="G149" s="6"/>
-      <c r="H149" s="6"/>
-      <c r="I149" s="6"/>
-      <c r="J149" s="6"/>
-      <c r="K149" s="5"/>
-      <c r="L149" s="6"/>
-      <c r="M149" s="5"/>
-    </row>
-    <row r="150" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B150" s="6"/>
-      <c r="C150" s="6"/>
-      <c r="D150" s="6"/>
-      <c r="E150" s="6"/>
-      <c r="F150" s="6"/>
-      <c r="G150" s="6"/>
-      <c r="H150" s="6"/>
-      <c r="I150" s="6"/>
-      <c r="J150" s="6"/>
-      <c r="K150" s="5"/>
-      <c r="L150" s="6"/>
-      <c r="M150" s="5"/>
+      <c r="K149" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="M149" s="1" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="151" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B151" s="6" t="s">
-        <v>110</v>
+        <v>65</v>
       </c>
       <c r="C151" s="6" t="s">
         <v>64</v>
@@ -4199,212 +4229,230 @@
       <c r="H151" s="6"/>
       <c r="I151" s="6"/>
       <c r="J151" s="6"/>
-      <c r="K151" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="M151" s="1" t="s">
-        <v>114</v>
-      </c>
+      <c r="K151" s="5"/>
+      <c r="L151" s="6"/>
+      <c r="M151" s="5"/>
     </row>
     <row r="152" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B152" s="6"/>
+      <c r="C152" s="6"/>
       <c r="D152" s="6"/>
       <c r="E152" s="6"/>
       <c r="F152" s="6"/>
-      <c r="G152" s="5"/>
+      <c r="G152" s="6"/>
       <c r="H152" s="6"/>
       <c r="I152" s="6"/>
-      <c r="J152" s="5"/>
-      <c r="K152" s="5" t="s">
-        <v>111</v>
-      </c>
+      <c r="J152" s="6"/>
+      <c r="K152" s="5"/>
       <c r="L152" s="6"/>
-      <c r="M152" s="5" t="s">
-        <v>112</v>
-      </c>
+      <c r="M152" s="5"/>
     </row>
     <row r="153" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B153" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="C153" s="6" t="s">
+        <v>64</v>
+      </c>
       <c r="D153" s="6"/>
       <c r="E153" s="6"/>
       <c r="F153" s="6"/>
-      <c r="G153" s="5"/>
+      <c r="G153" s="6"/>
       <c r="H153" s="6"/>
       <c r="I153" s="6"/>
-      <c r="J153" s="5"/>
-      <c r="K153" s="5"/>
-      <c r="L153" s="6"/>
-      <c r="M153" s="5"/>
+      <c r="J153" s="6"/>
+      <c r="K153" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="M153" s="1" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="154" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B154" s="1" t="s">
+      <c r="D154" s="6"/>
+      <c r="E154" s="6"/>
+      <c r="F154" s="6"/>
+      <c r="G154" s="5"/>
+      <c r="H154" s="6"/>
+      <c r="I154" s="6"/>
+      <c r="J154" s="5"/>
+      <c r="K154" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="L154" s="6"/>
+      <c r="M154" s="5" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="155" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D155" s="6"/>
+      <c r="E155" s="6"/>
+      <c r="F155" s="6"/>
+      <c r="G155" s="5"/>
+      <c r="H155" s="6"/>
+      <c r="I155" s="6"/>
+      <c r="J155" s="5"/>
+      <c r="K155" s="5"/>
+      <c r="L155" s="6"/>
+      <c r="M155" s="5"/>
+    </row>
+    <row r="156" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B156" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="C154" s="6" t="s">
+      <c r="C156" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="K154" s="1" t="s">
+      <c r="K156" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M154" s="1" t="s">
+      <c r="M156" s="1" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="155" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B155" s="1" t="s">
+    <row r="157" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B157" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="C155" s="1" t="s">
+      <c r="C157" s="1" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="156" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A156" s="1"/>
-      <c r="B156" s="1"/>
-      <c r="C156" s="1"/>
-    </row>
-    <row r="157" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B157" s="1"/>
-      <c r="C157" s="1"/>
-    </row>
     <row r="158" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A158" s="1"/>
       <c r="B158" s="1"/>
       <c r="C158" s="1"/>
+      <c r="K158" s="1"/>
+      <c r="M158" s="1"/>
     </row>
     <row r="159" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B159" s="1" t="s">
+      <c r="B159" s="1"/>
+      <c r="C159" s="1"/>
+    </row>
+    <row r="160" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B160" s="1"/>
+      <c r="C160" s="1"/>
+    </row>
+    <row r="161" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B161" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="K159" s="1" t="s">
+      <c r="K161" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="M159" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="160" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="K160" s="1" t="s">
+      <c r="M161" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="162" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="K162" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="M160" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="161" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="K161" s="1"/>
+      <c r="M162" s="1" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="163" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B163" s="1" t="s">
+      <c r="K163" s="1"/>
+    </row>
+    <row r="165" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B165" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="K163" s="1" t="s">
+      <c r="K165" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="M163" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="O163" s="6"/>
-    </row>
-    <row r="164" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="K164" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="M164" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="165" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="K165" s="1" t="s">
-        <v>41</v>
-      </c>
       <c r="M165" s="1" t="s">
         <v>23</v>
       </c>
+      <c r="O165" s="6"/>
     </row>
     <row r="166" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K166" s="1" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="M166" s="1" t="s">
-        <v>198</v>
+        <v>23</v>
       </c>
     </row>
     <row r="167" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K167" s="1" t="s">
-        <v>199</v>
+        <v>41</v>
       </c>
       <c r="M167" s="1" t="s">
-        <v>112</v>
+        <v>23</v>
       </c>
     </row>
     <row r="168" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K168" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M168" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="169" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="K169" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="M169" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="170" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="K170" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="M168" s="5" t="s">
+      <c r="M170" s="5" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="169" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B169" s="1" t="s">
+    <row r="171" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B171" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="K169" s="1" t="s">
+      <c r="K171" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="M169" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="170" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B170" s="1"/>
-      <c r="K170" s="1" t="s">
+      <c r="M171" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="172" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B172" s="1"/>
+      <c r="K172" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="M170" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="171" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="K171" s="1" t="s">
+      <c r="M172" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="173" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="K173" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="M171" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="172" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="K172" s="1" t="s">
+      <c r="M173" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="174" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="K174" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="M172" s="1" t="s">
+      <c r="M174" s="1" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="173" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="K173" s="1"/>
-      <c r="M173" s="1"/>
-    </row>
-    <row r="174" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B174" s="1" t="s">
+    <row r="175" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="K175" s="1"/>
+      <c r="M175" s="1"/>
+    </row>
+    <row r="176" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B176" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="K174" s="1" t="s">
+      <c r="K176" s="1" t="s">
         <v>25</v>
-      </c>
-      <c r="M174" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="175" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="K175" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="M175" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="176" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="K176" s="1" t="s">
-        <v>41</v>
       </c>
       <c r="M176" s="1" t="s">
         <v>23</v>
@@ -4412,7 +4460,7 @@
     </row>
     <row r="177" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K177" s="1" t="s">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="M177" s="1" t="s">
         <v>23</v>
@@ -4420,223 +4468,223 @@
     </row>
     <row r="178" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K178" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M178" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="179" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="K179" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="M179" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="180" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="K180" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="M178" s="1" t="s">
+      <c r="M180" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="179" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="K179" s="1"/>
-    </row>
     <row r="181" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B181" s="1" t="s">
+      <c r="K181" s="1"/>
+    </row>
+    <row r="183" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B183" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="K181" s="1" t="s">
+      <c r="K183" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="M181" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="O181" s="1" t="s">
+      <c r="M183" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O183" s="1" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="182" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="K182" s="1" t="s">
+    <row r="184" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="K184" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="M182" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="O182" s="1" t="s">
+      <c r="M184" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O184" s="1" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="183" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="K183" s="1" t="s">
+    <row r="185" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="K185" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="M183" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="O183" s="1" t="s">
+      <c r="M185" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O185" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="184" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="K184" s="1"/>
-    </row>
-    <row r="185" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B185" s="1" t="s">
+    <row r="186" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="K186" s="1"/>
+    </row>
+    <row r="187" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B187" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="K185" s="1" t="s">
+      <c r="K187" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="M185" s="1" t="s">
+      <c r="M187" s="1" t="s">
         <v>112</v>
-      </c>
-    </row>
-    <row r="186" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="K186" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="M186" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="187" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="K187" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="M187" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="188" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K188" s="1" t="s">
-        <v>216</v>
+        <v>26</v>
       </c>
       <c r="M188" s="1" t="s">
-        <v>103</v>
+        <v>23</v>
       </c>
     </row>
     <row r="189" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K189" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M189" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="190" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="K190" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="M190" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="191" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="K191" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="M189" s="1" t="s">
+      <c r="M191" s="1" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="191" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B191" s="1" t="s">
+    <row r="193" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B193" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="K191" s="1" t="s">
+      <c r="K193" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="M191" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="192" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="K192" s="1" t="s">
+      <c r="M193" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="194" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="K194" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="M192" s="1" t="s">
+      <c r="M194" s="1" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="195" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B195" s="1" t="s">
+    <row r="197" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B197" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="K195" s="1" t="s">
+      <c r="K197" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="M195" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="O195" s="1" t="s">
+      <c r="M197" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O197" s="1" t="s">
         <v>31</v>
-      </c>
-    </row>
-    <row r="196" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="K196" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="M196" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="O196" s="1" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="197" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="K197" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="M197" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="O197" s="1" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="198" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K198" s="1" t="s">
-        <v>143</v>
+        <v>26</v>
       </c>
       <c r="M198" s="1" t="s">
-        <v>236</v>
+        <v>23</v>
+      </c>
+      <c r="O198" s="1" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="199" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B199" s="1" t="s">
-        <v>234</v>
-      </c>
       <c r="K199" s="1" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="M199" s="1" t="s">
-        <v>235</v>
+        <v>23</v>
+      </c>
+      <c r="O199" s="1" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="200" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K200" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="M200" s="1" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="201" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B201" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="K201" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M201" s="1" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="202" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="K202" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="M200" s="1" t="s">
+      <c r="M202" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="204" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B204" s="1" t="s">
+    <row r="206" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B206" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="G204" s="1" t="s">
+      <c r="G206" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="K204" s="1" t="s">
+      <c r="K206" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="M204" s="1" t="s">
+      <c r="M206" s="1" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="205" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="K205" s="1" t="s">
+    <row r="207" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="K207" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="M205" s="1" t="s">
+      <c r="M207" s="1" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="208" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B208" s="1" t="s">
+    <row r="210" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B210" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="K208" s="1" t="s">
+      <c r="K210" s="1" t="s">
         <v>25</v>
-      </c>
-      <c r="M208" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="209" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="K209" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="M209" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="210" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="K210" s="1" t="s">
-        <v>60</v>
       </c>
       <c r="M210" s="1" t="s">
         <v>23</v>
@@ -4644,7 +4692,7 @@
     </row>
     <row r="211" spans="2:13" x14ac:dyDescent="0.3">
       <c r="K211" s="1" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="M211" s="1" t="s">
         <v>23</v>
@@ -4652,50 +4700,50 @@
     </row>
     <row r="212" spans="2:13" x14ac:dyDescent="0.3">
       <c r="K212" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="M212" s="6" t="s">
-        <v>99</v>
+        <v>60</v>
+      </c>
+      <c r="M212" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="213" spans="2:13" x14ac:dyDescent="0.3">
       <c r="K213" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M213" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="214" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="K214" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="M214" s="6" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="215" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="K215" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="M213" s="1" t="s">
+      <c r="M215" s="1" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="215" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B215" s="1" t="s">
+    <row r="217" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B217" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="K215" s="1" t="s">
+      <c r="K217" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="M215" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="216" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="K216" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="M216" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="217" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="K217" s="1" t="s">
-        <v>95</v>
-      </c>
       <c r="M217" s="1" t="s">
-        <v>112</v>
+        <v>23</v>
       </c>
     </row>
     <row r="218" spans="2:13" x14ac:dyDescent="0.3">
       <c r="K218" s="1" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="M218" s="1" t="s">
         <v>23</v>
@@ -4703,50 +4751,50 @@
     </row>
     <row r="219" spans="2:13" x14ac:dyDescent="0.3">
       <c r="K219" s="1" t="s">
-        <v>216</v>
+        <v>95</v>
       </c>
       <c r="M219" s="1" t="s">
-        <v>274</v>
+        <v>112</v>
       </c>
     </row>
     <row r="220" spans="2:13" x14ac:dyDescent="0.3">
       <c r="K220" s="1" t="s">
-        <v>276</v>
+        <v>41</v>
       </c>
       <c r="M220" s="1" t="s">
-        <v>112</v>
+        <v>23</v>
       </c>
     </row>
     <row r="221" spans="2:13" x14ac:dyDescent="0.3">
       <c r="K221" s="1" t="s">
-        <v>68</v>
+        <v>216</v>
       </c>
       <c r="M221" s="1" t="s">
-        <v>71</v>
+        <v>274</v>
       </c>
     </row>
     <row r="222" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B222" s="1" t="s">
-        <v>277</v>
-      </c>
       <c r="K222" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="M222" s="1" t="s">
-        <v>38</v>
+        <v>112</v>
       </c>
     </row>
     <row r="223" spans="2:13" x14ac:dyDescent="0.3">
       <c r="K223" s="1" t="s">
-        <v>279</v>
+        <v>68</v>
       </c>
       <c r="M223" s="1" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
     </row>
     <row r="224" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B224" s="1" t="s">
+        <v>277</v>
+      </c>
       <c r="K224" s="1" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="M224" s="1" t="s">
         <v>38</v>
@@ -4754,9 +4802,25 @@
     </row>
     <row r="225" spans="11:13" x14ac:dyDescent="0.3">
       <c r="K225" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="M225" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="226" spans="11:13" x14ac:dyDescent="0.3">
+      <c r="K226" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="M226" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="227" spans="11:13" x14ac:dyDescent="0.3">
+      <c r="K227" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="M225" s="1" t="s">
+      <c r="M227" s="1" t="s">
         <v>38</v>
       </c>
     </row>
@@ -4772,7 +4836,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EECC075D-9730-41E5-B97E-C301603D1E48}">
-  <dimension ref="A1:Q90"/>
+  <dimension ref="A1:Q95"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="27.33203125" customWidth="1"/>
@@ -5695,6 +5759,34 @@
       </c>
       <c r="M90" s="1" t="s">
         <v>283</v>
+      </c>
+    </row>
+    <row r="93" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B93" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="K93" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="M93" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="95" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B95" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="K95" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="M95" s="1" t="s">
+        <v>128</v>
       </c>
     </row>
   </sheetData>

--- a/Config/Datas/__beans__.xlsx
+++ b/Config/Datas/__beans__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3EBF756-6B53-4CB0-9F1F-D9E559B4F675}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0326CCB1-69E0-4F4F-AC69-FA028AA0A266}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1609,23 +1609,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Q227"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="28.75" customWidth="1"/>
     <col min="3" max="3" width="22" customWidth="1"/>
-    <col min="4" max="4" width="9.33203125" customWidth="1"/>
+    <col min="4" max="4" width="9.375" customWidth="1"/>
     <col min="5" max="5" width="9.5" customWidth="1"/>
-    <col min="6" max="6" width="5.83203125" customWidth="1"/>
+    <col min="6" max="6" width="5.875" customWidth="1"/>
     <col min="7" max="7" width="16" customWidth="1"/>
-    <col min="8" max="8" width="6.58203125" customWidth="1"/>
+    <col min="8" max="8" width="6.625" customWidth="1"/>
     <col min="9" max="9" width="6.75" customWidth="1"/>
-    <col min="10" max="10" width="7.33203125" customWidth="1"/>
+    <col min="10" max="10" width="7.375" customWidth="1"/>
     <col min="11" max="12" width="13.5" customWidth="1"/>
-    <col min="13" max="13" width="11.83203125" customWidth="1"/>
+    <col min="13" max="13" width="11.875" customWidth="1"/>
     <col min="14" max="14" width="20.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1666,7 +1666,7 @@
       <c r="P1" s="12"/>
       <c r="Q1" s="12"/>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -1701,7 +1701,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
         <v>11</v>
       </c>
@@ -1738,7 +1738,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
         <v>29</v>
       </c>
@@ -1767,7 +1767,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
         <v>29</v>
       </c>
@@ -1794,7 +1794,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A6" s="6"/>
       <c r="B6" s="6"/>
       <c r="C6" s="5"/>
@@ -1813,7 +1813,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A7" s="6"/>
       <c r="B7" s="6" t="s">
         <v>176</v>
@@ -1840,7 +1840,7 @@
       <c r="P7" s="6"/>
       <c r="Q7" s="6"/>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A8" s="6"/>
       <c r="B8" s="6"/>
       <c r="C8" s="5"/>
@@ -1863,7 +1863,7 @@
       <c r="P8" s="6"/>
       <c r="Q8" s="6"/>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A9" s="6"/>
       <c r="B9" s="6"/>
       <c r="C9" s="5"/>
@@ -1886,7 +1886,7 @@
       <c r="P9" s="6"/>
       <c r="Q9" s="6"/>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A10" s="6"/>
       <c r="B10" s="6"/>
       <c r="C10" s="5"/>
@@ -1908,7 +1908,7 @@
       <c r="P10" s="6"/>
       <c r="Q10" s="6"/>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A11" s="6"/>
       <c r="B11" s="6"/>
       <c r="C11" s="5"/>
@@ -1930,7 +1930,7 @@
       <c r="P11" s="6"/>
       <c r="Q11" s="6"/>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A12" s="6"/>
       <c r="B12" s="6"/>
       <c r="C12" s="5"/>
@@ -1953,7 +1953,7 @@
       <c r="P12" s="6"/>
       <c r="Q12" s="6"/>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A13" s="6"/>
       <c r="B13" s="6"/>
       <c r="C13" s="5"/>
@@ -1972,7 +1972,7 @@
       <c r="P13" s="6"/>
       <c r="Q13" s="6"/>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A14" s="6" t="s">
         <v>180</v>
       </c>
@@ -1993,7 +1993,7 @@
       <c r="P14" s="6"/>
       <c r="Q14" s="6"/>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A15" s="6"/>
       <c r="B15" s="6"/>
       <c r="C15" s="5"/>
@@ -2012,7 +2012,7 @@
       <c r="P15" s="6"/>
       <c r="Q15" s="6"/>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A16" s="6"/>
       <c r="B16" s="6"/>
       <c r="C16" s="5"/>
@@ -2031,7 +2031,7 @@
       <c r="P16" s="6"/>
       <c r="Q16" s="6"/>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A17" s="6"/>
       <c r="B17" s="6" t="s">
         <v>181</v>
@@ -2056,7 +2056,7 @@
       <c r="P17" s="6"/>
       <c r="Q17" s="6"/>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A18" s="6"/>
       <c r="B18" s="6"/>
       <c r="C18" s="5"/>
@@ -2079,7 +2079,7 @@
       <c r="P18" s="6"/>
       <c r="Q18" s="6"/>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A19" s="6"/>
       <c r="B19" s="6"/>
       <c r="C19" s="5"/>
@@ -2098,7 +2098,7 @@
       <c r="P19" s="6"/>
       <c r="Q19" s="6"/>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A20" s="6"/>
       <c r="B20" s="6" t="s">
         <v>30</v>
@@ -2127,7 +2127,7 @@
       <c r="P20" s="6"/>
       <c r="Q20" s="6"/>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A21" s="6"/>
       <c r="B21" s="6"/>
       <c r="C21" s="5"/>
@@ -2152,7 +2152,7 @@
       <c r="P21" s="6"/>
       <c r="Q21" s="6"/>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A22" s="6"/>
       <c r="D22" s="6"/>
       <c r="E22" s="6"/>
@@ -2173,7 +2173,7 @@
       <c r="P22" s="6"/>
       <c r="Q22" s="6"/>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A23" s="6"/>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
@@ -2191,7 +2191,7 @@
       <c r="P23" s="6"/>
       <c r="Q23" s="6"/>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A24" s="6"/>
       <c r="B24" s="6"/>
       <c r="C24" s="6"/>
@@ -2214,7 +2214,7 @@
       <c r="P24" s="6"/>
       <c r="Q24" s="6"/>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A25" s="6"/>
       <c r="D25" s="6"/>
       <c r="E25" s="6"/>
@@ -2235,7 +2235,7 @@
       <c r="P25" s="6"/>
       <c r="Q25" s="6"/>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A26" s="6"/>
       <c r="B26" s="6"/>
       <c r="C26" s="6"/>
@@ -2260,7 +2260,7 @@
       <c r="P26" s="6"/>
       <c r="Q26" s="6"/>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A27" s="6"/>
       <c r="B27" s="6"/>
       <c r="C27" s="6"/>
@@ -2285,7 +2285,7 @@
       <c r="P27" s="7"/>
       <c r="Q27" s="7"/>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A28" s="6"/>
       <c r="K28" s="5" t="s">
         <v>60</v>
@@ -2301,7 +2301,7 @@
       <c r="P28" s="6"/>
       <c r="Q28" s="6"/>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A29" s="6"/>
       <c r="K29" s="1" t="s">
         <v>143</v>
@@ -2315,7 +2315,7 @@
       <c r="P29" s="6"/>
       <c r="Q29" s="6"/>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A30" s="6"/>
       <c r="K30" s="1" t="s">
         <v>150</v>
@@ -2329,7 +2329,7 @@
       <c r="P30" s="6"/>
       <c r="Q30" s="6"/>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A31" s="6"/>
       <c r="K31" s="1" t="s">
         <v>95</v>
@@ -2342,7 +2342,7 @@
       </c>
       <c r="Q31" s="6"/>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A32" s="6"/>
       <c r="K32" s="1" t="s">
         <v>254</v>
@@ -2355,32 +2355,32 @@
       </c>
       <c r="Q32" s="6"/>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A33" s="6"/>
       <c r="K33" s="1"/>
       <c r="M33" s="5"/>
       <c r="O33" s="6"/>
       <c r="Q33" s="6"/>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A34" s="6"/>
       <c r="K34" s="1"/>
       <c r="M34" s="5"/>
       <c r="O34" s="6"/>
       <c r="Q34" s="6"/>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A35" s="6"/>
       <c r="K35" s="1"/>
       <c r="M35" s="5"/>
       <c r="O35" s="6"/>
       <c r="Q35" s="6"/>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A36" s="6"/>
       <c r="Q36" s="6"/>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A37" s="6"/>
       <c r="B37" s="6" t="s">
         <v>45</v>
@@ -2409,7 +2409,7 @@
       <c r="P37" s="6"/>
       <c r="Q37" s="6"/>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A38" s="6"/>
       <c r="B38" s="6"/>
       <c r="C38" s="6"/>
@@ -2434,7 +2434,7 @@
       <c r="P38" s="6"/>
       <c r="Q38" s="6"/>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A39" s="6"/>
       <c r="B39" s="6"/>
       <c r="C39" s="6"/>
@@ -2457,7 +2457,7 @@
       <c r="P39" s="6"/>
       <c r="Q39" s="6"/>
     </row>
-    <row r="40" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="6"/>
       <c r="B40" s="5"/>
       <c r="C40" s="6"/>
@@ -2482,7 +2482,7 @@
       <c r="P40" s="6"/>
       <c r="Q40" s="6"/>
     </row>
-    <row r="41" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="6"/>
       <c r="B41" s="5"/>
       <c r="C41" s="6"/>
@@ -2505,7 +2505,7 @@
       <c r="P41" s="6"/>
       <c r="Q41" s="6"/>
     </row>
-    <row r="42" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="6"/>
       <c r="B42" s="5"/>
       <c r="C42" s="6"/>
@@ -2527,7 +2527,7 @@
       <c r="P42" s="6"/>
       <c r="Q42" s="6"/>
     </row>
-    <row r="43" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="6"/>
       <c r="B43" s="5"/>
       <c r="C43" s="6"/>
@@ -2549,7 +2549,7 @@
       <c r="P43" s="6"/>
       <c r="Q43" s="6"/>
     </row>
-    <row r="44" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="6"/>
       <c r="B44" s="5"/>
       <c r="C44" s="6"/>
@@ -2574,7 +2574,7 @@
       <c r="P44" s="6"/>
       <c r="Q44" s="6"/>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A45" s="6"/>
       <c r="B45" s="6"/>
       <c r="C45" s="6"/>
@@ -2588,12 +2588,12 @@
       <c r="P45" s="6"/>
       <c r="Q45" s="6"/>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A46" s="6"/>
       <c r="P46" s="6"/>
       <c r="Q46" s="6"/>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A47" s="6"/>
       <c r="B47" s="1" t="s">
         <v>145</v>
@@ -2613,7 +2613,7 @@
       <c r="P47" s="6"/>
       <c r="Q47" s="6"/>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A48" s="6"/>
       <c r="K48" s="5" t="s">
         <v>26</v>
@@ -2627,7 +2627,7 @@
       <c r="P48" s="6"/>
       <c r="Q48" s="6"/>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A49" s="6"/>
       <c r="K49" s="5" t="s">
         <v>41</v>
@@ -2641,7 +2641,7 @@
       <c r="P49" s="6"/>
       <c r="Q49" s="6"/>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A50" s="6"/>
       <c r="K50" s="5" t="s">
         <v>161</v>
@@ -2653,7 +2653,7 @@
       <c r="P50" s="6"/>
       <c r="Q50" s="6"/>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A51" s="6"/>
       <c r="K51" s="5" t="s">
         <v>150</v>
@@ -2667,7 +2667,7 @@
       <c r="P51" s="6"/>
       <c r="Q51" s="6"/>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A52" s="6"/>
       <c r="K52" s="5" t="s">
         <v>154</v>
@@ -2681,7 +2681,7 @@
       <c r="P52" s="6"/>
       <c r="Q52" s="6"/>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A53" s="6"/>
       <c r="K53" s="5" t="s">
         <v>155</v>
@@ -2695,7 +2695,7 @@
       <c r="P53" s="6"/>
       <c r="Q53" s="6"/>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A54" s="6"/>
       <c r="K54" s="5" t="s">
         <v>157</v>
@@ -2709,18 +2709,18 @@
       <c r="P54" s="6"/>
       <c r="Q54" s="6"/>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A55" s="6"/>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A56" s="6"/>
       <c r="Q56" s="6"/>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A57" s="6"/>
       <c r="Q57" s="6"/>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A58" s="6"/>
       <c r="B58" s="6" t="s">
         <v>66</v>
@@ -2746,7 +2746,7 @@
       <c r="P58" s="6"/>
       <c r="Q58" s="6"/>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A59" s="6"/>
       <c r="K59" s="6" t="s">
         <v>67</v>
@@ -2758,7 +2758,7 @@
       <c r="P59" s="6"/>
       <c r="Q59" s="6"/>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A60" s="6"/>
       <c r="K60" s="5" t="s">
         <v>68</v>
@@ -2769,14 +2769,14 @@
       <c r="P60" s="7"/>
       <c r="Q60" s="6"/>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A61" s="6"/>
       <c r="K61" s="5"/>
       <c r="M61" s="5"/>
       <c r="P61" s="7"/>
       <c r="Q61" s="6"/>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A62" s="6"/>
       <c r="B62" s="1" t="s">
         <v>166</v>
@@ -2790,7 +2790,7 @@
       <c r="P62" s="7"/>
       <c r="Q62" s="6"/>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A63" s="6"/>
       <c r="K63" s="5" t="s">
         <v>165</v>
@@ -2801,7 +2801,7 @@
       <c r="P63" s="7"/>
       <c r="Q63" s="6"/>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A64" s="6"/>
       <c r="K64" s="5" t="s">
         <v>33</v>
@@ -2812,7 +2812,7 @@
       <c r="P64" s="7"/>
       <c r="Q64" s="6"/>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A65" s="6"/>
       <c r="K65" s="5" t="s">
         <v>169</v>
@@ -2823,14 +2823,14 @@
       <c r="P65" s="7"/>
       <c r="Q65" s="6"/>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A66" s="6"/>
       <c r="K66" s="5"/>
       <c r="M66" s="6"/>
       <c r="P66" s="7"/>
       <c r="Q66" s="6"/>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A67" s="6"/>
       <c r="B67" s="1" t="s">
         <v>265</v>
@@ -2844,7 +2844,7 @@
       <c r="P67" s="7"/>
       <c r="Q67" s="6"/>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A68" s="6"/>
       <c r="K68" s="5" t="s">
         <v>169</v>
@@ -2855,40 +2855,40 @@
       <c r="P68" s="7"/>
       <c r="Q68" s="6"/>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A69" s="6"/>
       <c r="K69" s="5"/>
       <c r="M69" s="6"/>
       <c r="P69" s="7"/>
       <c r="Q69" s="6"/>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A70" s="6"/>
       <c r="K70" s="5"/>
       <c r="M70" s="6"/>
       <c r="P70" s="7"/>
       <c r="Q70" s="6"/>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A71" s="6"/>
       <c r="K71" s="5"/>
       <c r="M71" s="6"/>
       <c r="P71" s="7"/>
       <c r="Q71" s="6"/>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A72" s="6"/>
       <c r="K72" s="5"/>
       <c r="M72" s="5"/>
       <c r="P72" s="7"/>
       <c r="Q72" s="6"/>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A73" s="6"/>
       <c r="P73" s="7"/>
       <c r="Q73" s="6"/>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A74" s="6"/>
       <c r="B74" s="5" t="s">
         <v>73</v>
@@ -2915,7 +2915,7 @@
       <c r="P74" s="6"/>
       <c r="Q74" s="6"/>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A75" s="6"/>
       <c r="B75" s="6"/>
       <c r="C75" s="6"/>
@@ -2938,7 +2938,7 @@
       <c r="P75" s="6"/>
       <c r="Q75" s="6"/>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A76" s="6"/>
       <c r="B76" s="6"/>
       <c r="C76" s="6"/>
@@ -2960,7 +2960,7 @@
       <c r="P76" s="6"/>
       <c r="Q76" s="6"/>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A77" s="6"/>
       <c r="B77" s="6"/>
       <c r="C77" s="6"/>
@@ -2980,7 +2980,7 @@
       <c r="P77" s="6"/>
       <c r="Q77" s="6"/>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A78" s="6"/>
       <c r="B78" s="6"/>
       <c r="C78" s="6"/>
@@ -3004,7 +3004,7 @@
       <c r="P78" s="6"/>
       <c r="Q78" s="6"/>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A79" s="6"/>
       <c r="B79" s="6"/>
       <c r="C79" s="6"/>
@@ -3027,7 +3027,7 @@
       <c r="P79" s="6"/>
       <c r="Q79" s="6"/>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A80" s="6"/>
       <c r="B80" s="6"/>
       <c r="C80" s="6"/>
@@ -3049,7 +3049,7 @@
       <c r="P80" s="6"/>
       <c r="Q80" s="6"/>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A81" s="6"/>
       <c r="B81" s="6"/>
       <c r="C81" s="6"/>
@@ -3068,7 +3068,7 @@
       <c r="P81" s="6"/>
       <c r="Q81" s="6"/>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A82" s="6"/>
       <c r="B82" s="5"/>
       <c r="C82" s="6"/>
@@ -3085,7 +3085,7 @@
       <c r="P82" s="6"/>
       <c r="Q82" s="6"/>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A83" s="6"/>
       <c r="B83" s="6" t="s">
         <v>79</v>
@@ -3110,7 +3110,7 @@
       <c r="P83" s="6"/>
       <c r="Q83" s="6"/>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A84" s="6"/>
       <c r="B84" s="6"/>
       <c r="C84" s="6"/>
@@ -3133,7 +3133,7 @@
       <c r="P84" s="6"/>
       <c r="Q84" s="6"/>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A85" s="6"/>
       <c r="H85" s="6"/>
       <c r="I85" s="6"/>
@@ -3150,7 +3150,7 @@
       <c r="P85" s="6"/>
       <c r="Q85" s="6"/>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A86" s="6"/>
       <c r="H86" s="6"/>
       <c r="I86" s="6"/>
@@ -3168,7 +3168,7 @@
       <c r="P86" s="6"/>
       <c r="Q86" s="6"/>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A87" s="6"/>
       <c r="K87" s="11" t="s">
         <v>144</v>
@@ -3182,7 +3182,7 @@
       <c r="P87" s="6"/>
       <c r="Q87" s="6"/>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A88" s="6"/>
       <c r="B88" s="6"/>
       <c r="C88" s="6"/>
@@ -3200,7 +3200,7 @@
       <c r="P88" s="6"/>
       <c r="Q88" s="6"/>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A89" s="6"/>
       <c r="K89" s="11"/>
       <c r="M89" s="11"/>
@@ -3208,12 +3208,12 @@
       <c r="P89" s="6"/>
       <c r="Q89" s="7"/>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A90" s="6"/>
       <c r="P90" s="6"/>
       <c r="Q90" s="6"/>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A91" s="6"/>
       <c r="B91" s="6"/>
       <c r="C91" s="6"/>
@@ -3227,7 +3227,7 @@
       <c r="P91" s="7"/>
       <c r="Q91" s="6"/>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A92" s="6"/>
       <c r="B92" s="1" t="s">
         <v>82</v>
@@ -3241,7 +3241,7 @@
       <c r="P92" s="6"/>
       <c r="Q92" s="6"/>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A93" s="5"/>
       <c r="B93" s="6"/>
       <c r="C93" s="6"/>
@@ -3254,7 +3254,7 @@
       <c r="P93" s="6"/>
       <c r="Q93" s="6"/>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A94" s="6"/>
       <c r="C94" s="6"/>
       <c r="D94" s="6"/>
@@ -3272,7 +3272,7 @@
       <c r="P94" s="6"/>
       <c r="Q94" s="6"/>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A95" s="6"/>
       <c r="B95" s="8" t="s">
         <v>89</v>
@@ -3297,7 +3297,7 @@
       <c r="P95" s="6"/>
       <c r="Q95" s="6"/>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A96" s="6"/>
       <c r="B96" s="8"/>
       <c r="C96" s="5"/>
@@ -3320,7 +3320,7 @@
       <c r="P96" s="6"/>
       <c r="Q96" s="6"/>
     </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A97" s="6"/>
       <c r="B97" s="6"/>
       <c r="C97" s="6"/>
@@ -3343,7 +3343,7 @@
       <c r="P97" s="7"/>
       <c r="Q97" s="6"/>
     </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A98" s="6"/>
       <c r="B98" s="6"/>
       <c r="C98" s="6"/>
@@ -3365,7 +3365,7 @@
       <c r="P98" s="6"/>
       <c r="Q98" s="6"/>
     </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B99" s="8"/>
       <c r="C99" s="5"/>
       <c r="D99" s="6"/>
@@ -3385,7 +3385,7 @@
       <c r="P99" s="6"/>
       <c r="Q99" s="6"/>
     </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B100" s="8"/>
       <c r="C100" s="5"/>
       <c r="D100" s="6"/>
@@ -3405,7 +3405,7 @@
       <c r="P100" s="6"/>
       <c r="Q100" s="6"/>
     </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B101" s="1"/>
       <c r="G101" s="1"/>
       <c r="H101" s="6"/>
@@ -3421,7 +3421,7 @@
       <c r="P101" s="7"/>
       <c r="Q101" s="6"/>
     </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:17" x14ac:dyDescent="0.2">
       <c r="H102" s="6"/>
       <c r="I102" s="6"/>
       <c r="J102" s="8"/>
@@ -3432,7 +3432,7 @@
       <c r="P102" s="7"/>
       <c r="Q102" s="6"/>
     </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B103" s="1" t="s">
         <v>97</v>
       </c>
@@ -3441,7 +3441,7 @@
       <c r="P103" s="7"/>
       <c r="Q103" s="7"/>
     </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B104" s="1" t="s">
         <v>107</v>
       </c>
@@ -3457,7 +3457,7 @@
       <c r="P104" s="7"/>
       <c r="Q104" s="6"/>
     </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:17" x14ac:dyDescent="0.2">
       <c r="K105" s="1" t="s">
         <v>68</v>
       </c>
@@ -3470,7 +3470,7 @@
       <c r="P105" s="6"/>
       <c r="Q105" s="6"/>
     </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A106" s="6"/>
       <c r="B106" s="1" t="s">
         <v>100</v>
@@ -3491,7 +3491,7 @@
       <c r="P106" s="6"/>
       <c r="Q106" s="6"/>
     </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A107" s="6"/>
       <c r="K107" s="1" t="s">
         <v>101</v>
@@ -3506,20 +3506,20 @@
       <c r="P107" s="6"/>
       <c r="Q107" s="6"/>
     </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A108" s="6"/>
       <c r="N108" s="6"/>
       <c r="P108" s="7"/>
       <c r="Q108" s="6"/>
     </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A109" s="6"/>
       <c r="N109" s="6"/>
       <c r="O109" s="5"/>
       <c r="P109" s="6"/>
       <c r="Q109" s="6"/>
     </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A110" s="6"/>
       <c r="H110" s="6"/>
       <c r="I110" s="6"/>
@@ -3532,7 +3532,7 @@
       <c r="P110" s="6"/>
       <c r="Q110" s="6"/>
     </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A111" s="6"/>
       <c r="H111" s="6"/>
       <c r="I111" s="6"/>
@@ -3545,7 +3545,7 @@
       <c r="P111" s="6"/>
       <c r="Q111" s="6"/>
     </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A112" s="6"/>
       <c r="D112" s="6"/>
       <c r="E112" s="6"/>
@@ -3562,7 +3562,7 @@
       <c r="P112" s="6"/>
       <c r="Q112" s="6"/>
     </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A113" s="6"/>
       <c r="B113" s="8"/>
       <c r="C113" s="5"/>
@@ -3581,25 +3581,25 @@
       <c r="P113" s="6"/>
       <c r="Q113" s="6"/>
     </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A114" s="6"/>
       <c r="O114" s="6"/>
       <c r="P114" s="6"/>
       <c r="Q114" s="6"/>
     </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A115" s="6"/>
       <c r="O115" s="6"/>
       <c r="P115" s="6"/>
       <c r="Q115" s="6"/>
     </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A116" s="6"/>
       <c r="O116" s="6"/>
       <c r="P116" s="6"/>
       <c r="Q116" s="6"/>
     </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A117" s="6"/>
       <c r="B117" s="8"/>
       <c r="C117" s="5"/>
@@ -3618,7 +3618,7 @@
       <c r="P117" s="6"/>
       <c r="Q117" s="6"/>
     </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A118" s="6"/>
       <c r="B118" s="1" t="s">
         <v>119</v>
@@ -3638,7 +3638,7 @@
       <c r="P118" s="6"/>
       <c r="Q118" s="6"/>
     </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A119" s="6"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
@@ -3648,7 +3648,7 @@
       <c r="P119" s="6"/>
       <c r="Q119" s="6"/>
     </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A120" s="6"/>
       <c r="B120" s="1" t="s">
         <v>120</v>
@@ -3675,7 +3675,7 @@
       <c r="P120" s="6"/>
       <c r="Q120" s="6"/>
     </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A121" s="6"/>
       <c r="B121" s="1" t="s">
         <v>121</v>
@@ -3702,7 +3702,7 @@
       <c r="P121" s="6"/>
       <c r="Q121" s="6"/>
     </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A122" s="6"/>
       <c r="B122" s="1" t="s">
         <v>126</v>
@@ -3725,7 +3725,7 @@
       <c r="P122" s="6"/>
       <c r="Q122" s="6"/>
     </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A123" s="6"/>
       <c r="B123" s="6" t="s">
         <v>131</v>
@@ -3744,7 +3744,7 @@
       <c r="P123" s="6"/>
       <c r="Q123" s="6"/>
     </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A124" s="6"/>
       <c r="B124" s="6" t="s">
         <v>160</v>
@@ -3769,7 +3769,7 @@
       <c r="P124" s="6"/>
       <c r="Q124" s="6"/>
     </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A125" s="6"/>
       <c r="B125" s="6" t="s">
         <v>162</v>
@@ -3792,7 +3792,7 @@
       <c r="P125" s="6"/>
       <c r="Q125" s="6"/>
     </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A126" s="6"/>
       <c r="B126" s="6" t="s">
         <v>231</v>
@@ -3815,7 +3815,7 @@
       <c r="P126" s="6"/>
       <c r="Q126" s="6"/>
     </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A127" s="6"/>
       <c r="B127" s="6" t="s">
         <v>290</v>
@@ -3842,7 +3842,7 @@
       <c r="P127" s="6"/>
       <c r="Q127" s="6"/>
     </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A128" s="6"/>
       <c r="B128" s="6"/>
       <c r="C128" s="6"/>
@@ -3861,7 +3861,7 @@
       <c r="P128" s="6"/>
       <c r="Q128" s="6"/>
     </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A129" s="6"/>
       <c r="B129" s="5" t="s">
         <v>286</v>
@@ -3888,7 +3888,7 @@
       <c r="P129" s="6"/>
       <c r="Q129" s="6"/>
     </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A130" s="6"/>
       <c r="B130" s="5" t="s">
         <v>287</v>
@@ -3913,14 +3913,14 @@
       <c r="P130" s="6"/>
       <c r="Q130" s="6"/>
     </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A131" s="6"/>
       <c r="N131" s="6"/>
       <c r="O131" s="6"/>
       <c r="P131" s="6"/>
       <c r="Q131" s="6"/>
     </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A132" s="6"/>
       <c r="B132" s="5" t="s">
         <v>239</v>
@@ -3945,7 +3945,7 @@
       <c r="P132" s="6"/>
       <c r="Q132" s="6"/>
     </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A133" s="6"/>
       <c r="B133" s="5"/>
       <c r="C133" s="5"/>
@@ -3968,7 +3968,7 @@
       <c r="P133" s="6"/>
       <c r="Q133" s="6"/>
     </row>
-    <row r="134" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A134" s="6"/>
       <c r="B134" s="5"/>
       <c r="C134" s="5"/>
@@ -3991,7 +3991,7 @@
       <c r="P134" s="6"/>
       <c r="Q134" s="6"/>
     </row>
-    <row r="135" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A135" s="6"/>
       <c r="B135" s="5"/>
       <c r="C135" s="5"/>
@@ -4014,7 +4014,7 @@
       <c r="P135" s="6"/>
       <c r="Q135" s="6"/>
     </row>
-    <row r="136" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A136" s="6"/>
       <c r="B136" s="6"/>
       <c r="C136" s="6"/>
@@ -4037,7 +4037,7 @@
       <c r="P136" s="6"/>
       <c r="Q136" s="6"/>
     </row>
-    <row r="137" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A137" s="5"/>
       <c r="B137" s="6"/>
       <c r="C137" s="6"/>
@@ -4059,7 +4059,7 @@
       <c r="P137" s="6"/>
       <c r="Q137" s="6"/>
     </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A138" s="5"/>
       <c r="B138" s="8"/>
       <c r="C138" s="5"/>
@@ -4081,14 +4081,14 @@
       <c r="P138" s="6"/>
       <c r="Q138" s="6"/>
     </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A139" s="5"/>
       <c r="N139" s="6"/>
       <c r="O139" s="5"/>
       <c r="P139" s="6"/>
       <c r="Q139" s="6"/>
     </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A140" s="5"/>
       <c r="B140" s="8" t="s">
         <v>240</v>
@@ -4112,7 +4112,7 @@
       <c r="P140" s="6"/>
       <c r="Q140" s="6"/>
     </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A141" s="5"/>
       <c r="B141" s="8"/>
       <c r="C141" s="5"/>
@@ -4134,7 +4134,7 @@
       <c r="P141" s="6"/>
       <c r="Q141" s="6"/>
     </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B142" s="8"/>
       <c r="C142" s="5"/>
       <c r="D142" s="6"/>
@@ -4147,7 +4147,7 @@
       <c r="K142" s="1"/>
       <c r="M142" s="5"/>
     </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C143" s="6"/>
       <c r="D143" s="6"/>
       <c r="E143" s="6"/>
@@ -4162,21 +4162,21 @@
       <c r="N143" s="6"/>
       <c r="O143" s="6"/>
     </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:17" x14ac:dyDescent="0.2">
       <c r="N144" s="6"/>
       <c r="O144" s="6"/>
     </row>
-    <row r="145" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B145" s="6" t="s">
         <v>64</v>
       </c>
       <c r="N145" s="6"/>
     </row>
-    <row r="146" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:15" x14ac:dyDescent="0.2">
       <c r="N146" s="6"/>
       <c r="O146" s="6"/>
     </row>
-    <row r="147" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B147" s="5" t="s">
         <v>123</v>
       </c>
@@ -4199,7 +4199,7 @@
       <c r="N147" s="6"/>
       <c r="O147" s="6"/>
     </row>
-    <row r="148" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:15" x14ac:dyDescent="0.2">
       <c r="K148" s="1" t="s">
         <v>113</v>
       </c>
@@ -4207,7 +4207,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="149" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:15" x14ac:dyDescent="0.2">
       <c r="K149" s="1" t="s">
         <v>125</v>
       </c>
@@ -4215,7 +4215,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="151" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B151" s="6" t="s">
         <v>65</v>
       </c>
@@ -4233,7 +4233,7 @@
       <c r="L151" s="6"/>
       <c r="M151" s="5"/>
     </row>
-    <row r="152" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B152" s="6"/>
       <c r="C152" s="6"/>
       <c r="D152" s="6"/>
@@ -4247,7 +4247,7 @@
       <c r="L152" s="6"/>
       <c r="M152" s="5"/>
     </row>
-    <row r="153" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B153" s="6" t="s">
         <v>110</v>
       </c>
@@ -4268,7 +4268,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="154" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D154" s="6"/>
       <c r="E154" s="6"/>
       <c r="F154" s="6"/>
@@ -4284,7 +4284,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="155" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D155" s="6"/>
       <c r="E155" s="6"/>
       <c r="F155" s="6"/>
@@ -4296,7 +4296,7 @@
       <c r="L155" s="6"/>
       <c r="M155" s="5"/>
     </row>
-    <row r="156" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B156" s="1" t="s">
         <v>247</v>
       </c>
@@ -4310,7 +4310,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="157" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B157" s="1" t="s">
         <v>257</v>
       </c>
@@ -4318,22 +4318,22 @@
         <v>64</v>
       </c>
     </row>
-    <row r="158" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A158" s="1"/>
       <c r="B158" s="1"/>
       <c r="C158" s="1"/>
       <c r="K158" s="1"/>
       <c r="M158" s="1"/>
     </row>
-    <row r="159" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B159" s="1"/>
       <c r="C159" s="1"/>
     </row>
-    <row r="160" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B160" s="1"/>
       <c r="C160" s="1"/>
     </row>
-    <row r="161" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="161" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B161" s="1" t="s">
         <v>195</v>
       </c>
@@ -4344,7 +4344,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="162" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="162" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K162" s="1" t="s">
         <v>197</v>
       </c>
@@ -4352,10 +4352,10 @@
         <v>23</v>
       </c>
     </row>
-    <row r="163" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="163" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K163" s="1"/>
     </row>
-    <row r="165" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="165" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B165" s="1" t="s">
         <v>206</v>
       </c>
@@ -4367,7 +4367,7 @@
       </c>
       <c r="O165" s="6"/>
     </row>
-    <row r="166" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="166" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K166" s="1" t="s">
         <v>26</v>
       </c>
@@ -4375,7 +4375,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="167" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="167" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K167" s="1" t="s">
         <v>41</v>
       </c>
@@ -4383,7 +4383,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="168" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="168" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K168" s="1" t="s">
         <v>33</v>
       </c>
@@ -4391,7 +4391,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="169" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="169" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K169" s="1" t="s">
         <v>199</v>
       </c>
@@ -4399,7 +4399,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="170" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="170" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K170" s="1" t="s">
         <v>150</v>
       </c>
@@ -4407,7 +4407,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="171" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="171" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B171" s="1" t="s">
         <v>227</v>
       </c>
@@ -4418,7 +4418,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="172" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="172" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B172" s="1"/>
       <c r="K172" s="1" t="s">
         <v>26</v>
@@ -4427,7 +4427,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="173" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="173" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K173" s="1" t="s">
         <v>41</v>
       </c>
@@ -4435,7 +4435,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="174" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="174" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K174" s="1" t="s">
         <v>228</v>
       </c>
@@ -4443,11 +4443,11 @@
         <v>229</v>
       </c>
     </row>
-    <row r="175" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="175" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K175" s="1"/>
       <c r="M175" s="1"/>
     </row>
-    <row r="176" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="176" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B176" s="1" t="s">
         <v>230</v>
       </c>
@@ -4458,7 +4458,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="177" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="177" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K177" s="1" t="s">
         <v>26</v>
       </c>
@@ -4466,7 +4466,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="178" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="178" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K178" s="1" t="s">
         <v>41</v>
       </c>
@@ -4474,7 +4474,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="179" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="179" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K179" s="1" t="s">
         <v>60</v>
       </c>
@@ -4482,7 +4482,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="180" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="180" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K180" s="1" t="s">
         <v>68</v>
       </c>
@@ -4490,10 +4490,10 @@
         <v>71</v>
       </c>
     </row>
-    <row r="181" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="181" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K181" s="1"/>
     </row>
-    <row r="183" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="183" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B183" s="1" t="s">
         <v>207</v>
       </c>
@@ -4507,7 +4507,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="184" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="184" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K184" s="1" t="s">
         <v>26</v>
       </c>
@@ -4518,7 +4518,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="185" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="185" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K185" s="1" t="s">
         <v>41</v>
       </c>
@@ -4529,10 +4529,10 @@
         <v>211</v>
       </c>
     </row>
-    <row r="186" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="186" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K186" s="1"/>
     </row>
-    <row r="187" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="187" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B187" s="1" t="s">
         <v>208</v>
       </c>
@@ -4543,7 +4543,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="188" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="188" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K188" s="1" t="s">
         <v>26</v>
       </c>
@@ -4551,7 +4551,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="189" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="189" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K189" s="1" t="s">
         <v>41</v>
       </c>
@@ -4559,7 +4559,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="190" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="190" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K190" s="1" t="s">
         <v>216</v>
       </c>
@@ -4567,7 +4567,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="191" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="191" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K191" s="1" t="s">
         <v>218</v>
       </c>
@@ -4575,7 +4575,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="193" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="193" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B193" s="1" t="s">
         <v>213</v>
       </c>
@@ -4586,7 +4586,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="194" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="194" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K194" s="1" t="s">
         <v>215</v>
       </c>
@@ -4594,7 +4594,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="197" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="197" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B197" s="1" t="s">
         <v>219</v>
       </c>
@@ -4608,7 +4608,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="198" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="198" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K198" s="1" t="s">
         <v>26</v>
       </c>
@@ -4619,7 +4619,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="199" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="199" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K199" s="1" t="s">
         <v>41</v>
       </c>
@@ -4630,7 +4630,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="200" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="200" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K200" s="1" t="s">
         <v>143</v>
       </c>
@@ -4638,7 +4638,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="201" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="201" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B201" s="1" t="s">
         <v>234</v>
       </c>
@@ -4649,7 +4649,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="202" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="202" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K202" s="1" t="s">
         <v>134</v>
       </c>
@@ -4657,7 +4657,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="206" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="206" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B206" s="1" t="s">
         <v>226</v>
       </c>
@@ -4671,7 +4671,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="207" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="207" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K207" s="1" t="s">
         <v>95</v>
       </c>
@@ -4679,7 +4679,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="210" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="210" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B210" s="1" t="s">
         <v>248</v>
       </c>
@@ -4690,7 +4690,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="211" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="211" spans="2:13" x14ac:dyDescent="0.2">
       <c r="K211" s="1" t="s">
         <v>26</v>
       </c>
@@ -4698,7 +4698,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="212" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="212" spans="2:13" x14ac:dyDescent="0.2">
       <c r="K212" s="1" t="s">
         <v>60</v>
       </c>
@@ -4706,7 +4706,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="213" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="213" spans="2:13" x14ac:dyDescent="0.2">
       <c r="K213" s="1" t="s">
         <v>41</v>
       </c>
@@ -4714,7 +4714,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="214" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="214" spans="2:13" x14ac:dyDescent="0.2">
       <c r="K214" s="1" t="s">
         <v>249</v>
       </c>
@@ -4722,7 +4722,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="215" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="215" spans="2:13" x14ac:dyDescent="0.2">
       <c r="K215" s="1" t="s">
         <v>250</v>
       </c>
@@ -4730,7 +4730,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="217" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="217" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B217" s="1" t="s">
         <v>275</v>
       </c>
@@ -4741,7 +4741,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="218" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="218" spans="2:13" x14ac:dyDescent="0.2">
       <c r="K218" s="1" t="s">
         <v>26</v>
       </c>
@@ -4749,7 +4749,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="219" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="219" spans="2:13" x14ac:dyDescent="0.2">
       <c r="K219" s="1" t="s">
         <v>95</v>
       </c>
@@ -4757,7 +4757,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="220" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="220" spans="2:13" x14ac:dyDescent="0.2">
       <c r="K220" s="1" t="s">
         <v>41</v>
       </c>
@@ -4765,7 +4765,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="221" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="221" spans="2:13" x14ac:dyDescent="0.2">
       <c r="K221" s="1" t="s">
         <v>216</v>
       </c>
@@ -4773,7 +4773,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="222" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="222" spans="2:13" x14ac:dyDescent="0.2">
       <c r="K222" s="1" t="s">
         <v>276</v>
       </c>
@@ -4781,7 +4781,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="223" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="223" spans="2:13" x14ac:dyDescent="0.2">
       <c r="K223" s="1" t="s">
         <v>68</v>
       </c>
@@ -4789,7 +4789,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="224" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="224" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B224" s="1" t="s">
         <v>277</v>
       </c>
@@ -4800,7 +4800,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="225" spans="11:13" x14ac:dyDescent="0.3">
+    <row r="225" spans="11:13" x14ac:dyDescent="0.2">
       <c r="K225" s="1" t="s">
         <v>279</v>
       </c>
@@ -4808,7 +4808,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="226" spans="11:13" x14ac:dyDescent="0.3">
+    <row r="226" spans="11:13" x14ac:dyDescent="0.2">
       <c r="K226" s="1" t="s">
         <v>280</v>
       </c>
@@ -4816,7 +4816,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="227" spans="11:13" x14ac:dyDescent="0.3">
+    <row r="227" spans="11:13" x14ac:dyDescent="0.2">
       <c r="K227" s="1" t="s">
         <v>281</v>
       </c>
@@ -4837,12 +4837,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EECC075D-9730-41E5-B97E-C301603D1E48}">
   <dimension ref="A1:Q95"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="27.33203125" customWidth="1"/>
+    <col min="2" max="2" width="27.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -4883,7 +4883,7 @@
       <c r="P1" s="12"/>
       <c r="Q1" s="12"/>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -4918,7 +4918,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
         <v>11</v>
       </c>
@@ -4955,7 +4955,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="6" t="s">
         <v>53</v>
       </c>
@@ -4972,7 +4972,7 @@
       <c r="M6" s="5"/>
       <c r="N6" s="6"/>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B8" s="1" t="s">
         <v>141</v>
       </c>
@@ -4986,7 +4986,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="K9" s="1" t="s">
         <v>134</v>
       </c>
@@ -4997,7 +4997,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B11" s="1" t="s">
         <v>129</v>
       </c>
@@ -5011,7 +5011,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B12" s="6" t="s">
         <v>54</v>
       </c>
@@ -5039,7 +5039,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
@@ -5061,7 +5061,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
       <c r="D14" s="6"/>
@@ -5074,7 +5074,7 @@
       <c r="N14" s="6"/>
       <c r="O14" s="6"/>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B15" s="1" t="s">
         <v>74</v>
       </c>
@@ -5092,7 +5092,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="K16" s="1" t="s">
         <v>75</v>
       </c>
@@ -5103,7 +5103,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B17" s="1" t="s">
         <v>104</v>
       </c>
@@ -5120,7 +5120,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="18" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B18" s="1" t="s">
         <v>115</v>
       </c>
@@ -5134,7 +5134,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="19" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K19" s="5" t="s">
         <v>37</v>
       </c>
@@ -5142,7 +5142,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="20" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K20" s="1" t="s">
         <v>118</v>
       </c>
@@ -5150,7 +5150,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="21" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B21" s="1" t="s">
         <v>127</v>
       </c>
@@ -5164,7 +5164,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="23" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B23" s="1" t="s">
         <v>133</v>
       </c>
@@ -5178,7 +5178,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="24" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K24" s="1" t="s">
         <v>134</v>
       </c>
@@ -5186,7 +5186,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="26" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B26" s="1" t="s">
         <v>139</v>
       </c>
@@ -5200,7 +5200,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="27" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K27" s="1" t="s">
         <v>33</v>
       </c>
@@ -5208,7 +5208,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="28" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K28" s="1" t="s">
         <v>41</v>
       </c>
@@ -5216,7 +5216,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K29" s="1" t="s">
         <v>68</v>
       </c>
@@ -5224,7 +5224,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="31" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B31" s="1" t="s">
         <v>158</v>
       </c>
@@ -5238,7 +5238,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="32" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B32" s="1" t="s">
         <v>173</v>
       </c>
@@ -5252,7 +5252,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
       <c r="K33" s="1" t="s">
         <v>186</v>
       </c>
@@ -5260,7 +5260,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B34" s="1" t="s">
         <v>222</v>
       </c>
@@ -5274,7 +5274,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
       <c r="K35" s="1" t="s">
         <v>223</v>
       </c>
@@ -5282,7 +5282,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>180</v>
       </c>
@@ -5293,11 +5293,11 @@
         <v>128</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
       <c r="K37" s="1"/>
       <c r="M37" s="1"/>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B38" s="1" t="s">
         <v>193</v>
       </c>
@@ -5311,7 +5311,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
       <c r="K39" s="1" t="s">
         <v>186</v>
       </c>
@@ -5319,7 +5319,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B40" s="1" t="s">
         <v>175</v>
       </c>
@@ -5334,10 +5334,10 @@
       </c>
       <c r="N40" s="6"/>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.2">
       <c r="N41" s="6"/>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B42" s="1" t="s">
         <v>116</v>
       </c>
@@ -5358,7 +5358,7 @@
       </c>
       <c r="N42" s="6"/>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B43" s="6"/>
       <c r="C43" s="5"/>
       <c r="D43" s="6"/>
@@ -5376,7 +5376,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B44" s="8"/>
       <c r="C44" s="5"/>
       <c r="D44" s="6"/>
@@ -5394,7 +5394,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B45" s="1" t="s">
         <v>188</v>
       </c>
@@ -5405,7 +5405,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.2">
       <c r="K46" s="1" t="s">
         <v>189</v>
       </c>
@@ -5413,7 +5413,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
         <v>178</v>
       </c>
@@ -5421,7 +5421,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B50" s="1" t="s">
         <v>184</v>
       </c>
@@ -5438,7 +5438,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A54" s="1"/>
       <c r="B54" s="1" t="s">
         <v>203</v>
@@ -5456,7 +5456,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.2">
       <c r="K55" s="1" t="s">
         <v>202</v>
       </c>
@@ -5464,7 +5464,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.2">
       <c r="K56" s="1" t="s">
         <v>204</v>
       </c>
@@ -5472,7 +5472,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B58" s="1" t="s">
         <v>232</v>
       </c>
@@ -5486,7 +5486,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.2">
       <c r="K59" s="1" t="s">
         <v>75</v>
       </c>
@@ -5494,7 +5494,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B61" s="1" t="s">
         <v>233</v>
       </c>
@@ -5508,7 +5508,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B63" s="1" t="s">
         <v>237</v>
       </c>
@@ -5522,7 +5522,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.2">
       <c r="K64" s="1" t="s">
         <v>238</v>
       </c>
@@ -5530,7 +5530,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B65" s="1" t="s">
         <v>244</v>
       </c>
@@ -5544,7 +5544,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B67" s="1" t="s">
         <v>246</v>
       </c>
@@ -5558,7 +5558,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B68" s="1" t="s">
         <v>285</v>
       </c>
@@ -5572,7 +5572,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B69" s="1" t="s">
         <v>258</v>
       </c>
@@ -5586,7 +5586,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B70" s="1" t="s">
         <v>251</v>
       </c>
@@ -5600,7 +5600,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="K71" s="1" t="s">
         <v>75</v>
       </c>
@@ -5608,7 +5608,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B72" s="1" t="s">
         <v>253</v>
       </c>
@@ -5622,7 +5622,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="K73" s="1" t="s">
         <v>75</v>
       </c>
@@ -5630,7 +5630,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B75" s="1" t="s">
         <v>260</v>
       </c>
@@ -5644,7 +5644,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="K76" s="1" t="s">
         <v>118</v>
       </c>
@@ -5652,7 +5652,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="78" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B78" s="1" t="s">
         <v>261</v>
       </c>
@@ -5663,7 +5663,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="K79" s="1" t="s">
         <v>75</v>
       </c>
@@ -5671,7 +5671,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B80" s="1" t="s">
         <v>269</v>
       </c>
@@ -5685,13 +5685,13 @@
         <v>23</v>
       </c>
     </row>
-    <row r="81" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="81" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
       <c r="K81" s="1"/>
       <c r="M81" s="1"/>
     </row>
-    <row r="82" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B82" s="1" t="s">
         <v>270</v>
       </c>
@@ -5705,7 +5705,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="84" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B84" s="1" t="s">
         <v>271</v>
       </c>
@@ -5719,7 +5719,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="86" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B86" s="1" t="s">
         <v>272</v>
       </c>
@@ -5733,7 +5733,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="88" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="88" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B88" s="1" t="s">
         <v>273</v>
       </c>
@@ -5747,7 +5747,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="90" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="90" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B90" s="1" t="s">
         <v>282</v>
       </c>
@@ -5761,7 +5761,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="93" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="93" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B93" s="1" t="s">
         <v>289</v>
       </c>
@@ -5775,7 +5775,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="95" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="95" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B95" s="1" t="s">
         <v>292</v>
       </c>
@@ -5801,7 +5801,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEE0849C-6C30-450E-8369-1D81B45C3886}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Config/Datas/__beans__.xlsx
+++ b/Config/Datas/__beans__.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0326CCB1-69E0-4F4F-AC69-FA028AA0A266}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B5F589C-4C2C-47E2-8718-6B1BDC91C47C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1608,24 +1608,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q227"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:Q228"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="28.75" customWidth="1"/>
     <col min="3" max="3" width="22" customWidth="1"/>
-    <col min="4" max="4" width="9.375" customWidth="1"/>
+    <col min="4" max="4" width="9.33203125" customWidth="1"/>
     <col min="5" max="5" width="9.5" customWidth="1"/>
-    <col min="6" max="6" width="5.875" customWidth="1"/>
+    <col min="6" max="6" width="5.83203125" customWidth="1"/>
     <col min="7" max="7" width="16" customWidth="1"/>
-    <col min="8" max="8" width="6.625" customWidth="1"/>
+    <col min="8" max="8" width="6.58203125" customWidth="1"/>
     <col min="9" max="9" width="6.75" customWidth="1"/>
-    <col min="10" max="10" width="7.375" customWidth="1"/>
+    <col min="10" max="10" width="7.33203125" customWidth="1"/>
     <col min="11" max="12" width="13.5" customWidth="1"/>
-    <col min="13" max="13" width="11.875" customWidth="1"/>
+    <col min="13" max="13" width="11.83203125" customWidth="1"/>
     <col min="14" max="14" width="20.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1666,7 +1666,7 @@
       <c r="P1" s="12"/>
       <c r="Q1" s="12"/>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -1701,7 +1701,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>11</v>
       </c>
@@ -1738,7 +1738,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
         <v>29</v>
       </c>
@@ -1767,7 +1767,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
         <v>29</v>
       </c>
@@ -1794,7 +1794,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" s="6"/>
       <c r="B6" s="6"/>
       <c r="C6" s="5"/>
@@ -1813,7 +1813,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" s="6"/>
       <c r="B7" s="6" t="s">
         <v>176</v>
@@ -1840,7 +1840,7 @@
       <c r="P7" s="6"/>
       <c r="Q7" s="6"/>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" s="6"/>
       <c r="B8" s="6"/>
       <c r="C8" s="5"/>
@@ -1863,7 +1863,7 @@
       <c r="P8" s="6"/>
       <c r="Q8" s="6"/>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" s="6"/>
       <c r="B9" s="6"/>
       <c r="C9" s="5"/>
@@ -1886,7 +1886,7 @@
       <c r="P9" s="6"/>
       <c r="Q9" s="6"/>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" s="6"/>
       <c r="B10" s="6"/>
       <c r="C10" s="5"/>
@@ -1908,7 +1908,7 @@
       <c r="P10" s="6"/>
       <c r="Q10" s="6"/>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" s="6"/>
       <c r="B11" s="6"/>
       <c r="C11" s="5"/>
@@ -1930,7 +1930,7 @@
       <c r="P11" s="6"/>
       <c r="Q11" s="6"/>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" s="6"/>
       <c r="B12" s="6"/>
       <c r="C12" s="5"/>
@@ -1953,7 +1953,7 @@
       <c r="P12" s="6"/>
       <c r="Q12" s="6"/>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" s="6"/>
       <c r="B13" s="6"/>
       <c r="C13" s="5"/>
@@ -1972,7 +1972,7 @@
       <c r="P13" s="6"/>
       <c r="Q13" s="6"/>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
         <v>180</v>
       </c>
@@ -1993,7 +1993,7 @@
       <c r="P14" s="6"/>
       <c r="Q14" s="6"/>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15" s="6"/>
       <c r="B15" s="6"/>
       <c r="C15" s="5"/>
@@ -2012,7 +2012,7 @@
       <c r="P15" s="6"/>
       <c r="Q15" s="6"/>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" s="6"/>
       <c r="B16" s="6"/>
       <c r="C16" s="5"/>
@@ -2031,7 +2031,7 @@
       <c r="P16" s="6"/>
       <c r="Q16" s="6"/>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17" s="6"/>
       <c r="B17" s="6" t="s">
         <v>181</v>
@@ -2056,7 +2056,7 @@
       <c r="P17" s="6"/>
       <c r="Q17" s="6"/>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A18" s="6"/>
       <c r="B18" s="6"/>
       <c r="C18" s="5"/>
@@ -2079,7 +2079,7 @@
       <c r="P18" s="6"/>
       <c r="Q18" s="6"/>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A19" s="6"/>
       <c r="B19" s="6"/>
       <c r="C19" s="5"/>
@@ -2098,7 +2098,7 @@
       <c r="P19" s="6"/>
       <c r="Q19" s="6"/>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A20" s="6"/>
       <c r="B20" s="6" t="s">
         <v>30</v>
@@ -2127,7 +2127,7 @@
       <c r="P20" s="6"/>
       <c r="Q20" s="6"/>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A21" s="6"/>
       <c r="B21" s="6"/>
       <c r="C21" s="5"/>
@@ -2152,7 +2152,7 @@
       <c r="P21" s="6"/>
       <c r="Q21" s="6"/>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A22" s="6"/>
       <c r="D22" s="6"/>
       <c r="E22" s="6"/>
@@ -2173,7 +2173,7 @@
       <c r="P22" s="6"/>
       <c r="Q22" s="6"/>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A23" s="6"/>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
@@ -2191,7 +2191,7 @@
       <c r="P23" s="6"/>
       <c r="Q23" s="6"/>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A24" s="6"/>
       <c r="B24" s="6"/>
       <c r="C24" s="6"/>
@@ -2214,7 +2214,7 @@
       <c r="P24" s="6"/>
       <c r="Q24" s="6"/>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A25" s="6"/>
       <c r="D25" s="6"/>
       <c r="E25" s="6"/>
@@ -2235,7 +2235,7 @@
       <c r="P25" s="6"/>
       <c r="Q25" s="6"/>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A26" s="6"/>
       <c r="B26" s="6"/>
       <c r="C26" s="6"/>
@@ -2260,7 +2260,7 @@
       <c r="P26" s="6"/>
       <c r="Q26" s="6"/>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A27" s="6"/>
       <c r="B27" s="6"/>
       <c r="C27" s="6"/>
@@ -2285,7 +2285,7 @@
       <c r="P27" s="7"/>
       <c r="Q27" s="7"/>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A28" s="6"/>
       <c r="K28" s="5" t="s">
         <v>60</v>
@@ -2301,7 +2301,7 @@
       <c r="P28" s="6"/>
       <c r="Q28" s="6"/>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A29" s="6"/>
       <c r="K29" s="1" t="s">
         <v>143</v>
@@ -2315,7 +2315,7 @@
       <c r="P29" s="6"/>
       <c r="Q29" s="6"/>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A30" s="6"/>
       <c r="K30" s="1" t="s">
         <v>150</v>
@@ -2329,7 +2329,7 @@
       <c r="P30" s="6"/>
       <c r="Q30" s="6"/>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A31" s="6"/>
       <c r="K31" s="1" t="s">
         <v>95</v>
@@ -2342,7 +2342,7 @@
       </c>
       <c r="Q31" s="6"/>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A32" s="6"/>
       <c r="K32" s="1" t="s">
         <v>254</v>
@@ -2355,32 +2355,32 @@
       </c>
       <c r="Q32" s="6"/>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A33" s="6"/>
       <c r="K33" s="1"/>
       <c r="M33" s="5"/>
       <c r="O33" s="6"/>
       <c r="Q33" s="6"/>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A34" s="6"/>
       <c r="K34" s="1"/>
       <c r="M34" s="5"/>
       <c r="O34" s="6"/>
       <c r="Q34" s="6"/>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A35" s="6"/>
       <c r="K35" s="1"/>
       <c r="M35" s="5"/>
       <c r="O35" s="6"/>
       <c r="Q35" s="6"/>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A36" s="6"/>
       <c r="Q36" s="6"/>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A37" s="6"/>
       <c r="B37" s="6" t="s">
         <v>45</v>
@@ -2409,7 +2409,7 @@
       <c r="P37" s="6"/>
       <c r="Q37" s="6"/>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A38" s="6"/>
       <c r="B38" s="6"/>
       <c r="C38" s="6"/>
@@ -2434,7 +2434,7 @@
       <c r="P38" s="6"/>
       <c r="Q38" s="6"/>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A39" s="6"/>
       <c r="B39" s="6"/>
       <c r="C39" s="6"/>
@@ -2457,7 +2457,7 @@
       <c r="P39" s="6"/>
       <c r="Q39" s="6"/>
     </row>
-    <row r="40" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="6"/>
       <c r="B40" s="5"/>
       <c r="C40" s="6"/>
@@ -2482,7 +2482,7 @@
       <c r="P40" s="6"/>
       <c r="Q40" s="6"/>
     </row>
-    <row r="41" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="6"/>
       <c r="B41" s="5"/>
       <c r="C41" s="6"/>
@@ -2505,7 +2505,7 @@
       <c r="P41" s="6"/>
       <c r="Q41" s="6"/>
     </row>
-    <row r="42" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="6"/>
       <c r="B42" s="5"/>
       <c r="C42" s="6"/>
@@ -2527,7 +2527,7 @@
       <c r="P42" s="6"/>
       <c r="Q42" s="6"/>
     </row>
-    <row r="43" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="6"/>
       <c r="B43" s="5"/>
       <c r="C43" s="6"/>
@@ -2549,7 +2549,7 @@
       <c r="P43" s="6"/>
       <c r="Q43" s="6"/>
     </row>
-    <row r="44" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="6"/>
       <c r="B44" s="5"/>
       <c r="C44" s="6"/>
@@ -2574,7 +2574,7 @@
       <c r="P44" s="6"/>
       <c r="Q44" s="6"/>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A45" s="6"/>
       <c r="B45" s="6"/>
       <c r="C45" s="6"/>
@@ -2588,12 +2588,12 @@
       <c r="P45" s="6"/>
       <c r="Q45" s="6"/>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A46" s="6"/>
       <c r="P46" s="6"/>
       <c r="Q46" s="6"/>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A47" s="6"/>
       <c r="B47" s="1" t="s">
         <v>145</v>
@@ -2613,7 +2613,7 @@
       <c r="P47" s="6"/>
       <c r="Q47" s="6"/>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A48" s="6"/>
       <c r="K48" s="5" t="s">
         <v>26</v>
@@ -2627,7 +2627,7 @@
       <c r="P48" s="6"/>
       <c r="Q48" s="6"/>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A49" s="6"/>
       <c r="K49" s="5" t="s">
         <v>41</v>
@@ -2641,7 +2641,7 @@
       <c r="P49" s="6"/>
       <c r="Q49" s="6"/>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A50" s="6"/>
       <c r="K50" s="5" t="s">
         <v>161</v>
@@ -2653,7 +2653,7 @@
       <c r="P50" s="6"/>
       <c r="Q50" s="6"/>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A51" s="6"/>
       <c r="K51" s="5" t="s">
         <v>150</v>
@@ -2667,7 +2667,7 @@
       <c r="P51" s="6"/>
       <c r="Q51" s="6"/>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A52" s="6"/>
       <c r="K52" s="5" t="s">
         <v>154</v>
@@ -2681,7 +2681,7 @@
       <c r="P52" s="6"/>
       <c r="Q52" s="6"/>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A53" s="6"/>
       <c r="K53" s="5" t="s">
         <v>155</v>
@@ -2695,7 +2695,7 @@
       <c r="P53" s="6"/>
       <c r="Q53" s="6"/>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A54" s="6"/>
       <c r="K54" s="5" t="s">
         <v>157</v>
@@ -2709,18 +2709,18 @@
       <c r="P54" s="6"/>
       <c r="Q54" s="6"/>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A55" s="6"/>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A56" s="6"/>
       <c r="Q56" s="6"/>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A57" s="6"/>
       <c r="Q57" s="6"/>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A58" s="6"/>
       <c r="B58" s="6" t="s">
         <v>66</v>
@@ -2746,7 +2746,7 @@
       <c r="P58" s="6"/>
       <c r="Q58" s="6"/>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A59" s="6"/>
       <c r="K59" s="6" t="s">
         <v>67</v>
@@ -2758,7 +2758,7 @@
       <c r="P59" s="6"/>
       <c r="Q59" s="6"/>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A60" s="6"/>
       <c r="K60" s="5" t="s">
         <v>68</v>
@@ -2769,14 +2769,14 @@
       <c r="P60" s="7"/>
       <c r="Q60" s="6"/>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A61" s="6"/>
       <c r="K61" s="5"/>
       <c r="M61" s="5"/>
       <c r="P61" s="7"/>
       <c r="Q61" s="6"/>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A62" s="6"/>
       <c r="B62" s="1" t="s">
         <v>166</v>
@@ -2790,7 +2790,7 @@
       <c r="P62" s="7"/>
       <c r="Q62" s="6"/>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A63" s="6"/>
       <c r="K63" s="5" t="s">
         <v>165</v>
@@ -2801,7 +2801,7 @@
       <c r="P63" s="7"/>
       <c r="Q63" s="6"/>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A64" s="6"/>
       <c r="K64" s="5" t="s">
         <v>33</v>
@@ -2812,7 +2812,7 @@
       <c r="P64" s="7"/>
       <c r="Q64" s="6"/>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A65" s="6"/>
       <c r="K65" s="5" t="s">
         <v>169</v>
@@ -2823,14 +2823,14 @@
       <c r="P65" s="7"/>
       <c r="Q65" s="6"/>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A66" s="6"/>
       <c r="K66" s="5"/>
       <c r="M66" s="6"/>
       <c r="P66" s="7"/>
       <c r="Q66" s="6"/>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A67" s="6"/>
       <c r="B67" s="1" t="s">
         <v>265</v>
@@ -2844,7 +2844,7 @@
       <c r="P67" s="7"/>
       <c r="Q67" s="6"/>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A68" s="6"/>
       <c r="K68" s="5" t="s">
         <v>169</v>
@@ -2855,40 +2855,40 @@
       <c r="P68" s="7"/>
       <c r="Q68" s="6"/>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A69" s="6"/>
       <c r="K69" s="5"/>
       <c r="M69" s="6"/>
       <c r="P69" s="7"/>
       <c r="Q69" s="6"/>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A70" s="6"/>
       <c r="K70" s="5"/>
       <c r="M70" s="6"/>
       <c r="P70" s="7"/>
       <c r="Q70" s="6"/>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A71" s="6"/>
       <c r="K71" s="5"/>
       <c r="M71" s="6"/>
       <c r="P71" s="7"/>
       <c r="Q71" s="6"/>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A72" s="6"/>
       <c r="K72" s="5"/>
       <c r="M72" s="5"/>
       <c r="P72" s="7"/>
       <c r="Q72" s="6"/>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A73" s="6"/>
       <c r="P73" s="7"/>
       <c r="Q73" s="6"/>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A74" s="6"/>
       <c r="B74" s="5" t="s">
         <v>73</v>
@@ -2915,7 +2915,7 @@
       <c r="P74" s="6"/>
       <c r="Q74" s="6"/>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A75" s="6"/>
       <c r="B75" s="6"/>
       <c r="C75" s="6"/>
@@ -2938,7 +2938,7 @@
       <c r="P75" s="6"/>
       <c r="Q75" s="6"/>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A76" s="6"/>
       <c r="B76" s="6"/>
       <c r="C76" s="6"/>
@@ -2960,7 +2960,7 @@
       <c r="P76" s="6"/>
       <c r="Q76" s="6"/>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A77" s="6"/>
       <c r="B77" s="6"/>
       <c r="C77" s="6"/>
@@ -2980,7 +2980,7 @@
       <c r="P77" s="6"/>
       <c r="Q77" s="6"/>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A78" s="6"/>
       <c r="B78" s="6"/>
       <c r="C78" s="6"/>
@@ -3004,7 +3004,7 @@
       <c r="P78" s="6"/>
       <c r="Q78" s="6"/>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A79" s="6"/>
       <c r="B79" s="6"/>
       <c r="C79" s="6"/>
@@ -3027,7 +3027,7 @@
       <c r="P79" s="6"/>
       <c r="Q79" s="6"/>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A80" s="6"/>
       <c r="B80" s="6"/>
       <c r="C80" s="6"/>
@@ -3049,7 +3049,7 @@
       <c r="P80" s="6"/>
       <c r="Q80" s="6"/>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A81" s="6"/>
       <c r="B81" s="6"/>
       <c r="C81" s="6"/>
@@ -3068,7 +3068,7 @@
       <c r="P81" s="6"/>
       <c r="Q81" s="6"/>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A82" s="6"/>
       <c r="B82" s="5"/>
       <c r="C82" s="6"/>
@@ -3085,7 +3085,7 @@
       <c r="P82" s="6"/>
       <c r="Q82" s="6"/>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A83" s="6"/>
       <c r="B83" s="6" t="s">
         <v>79</v>
@@ -3110,7 +3110,7 @@
       <c r="P83" s="6"/>
       <c r="Q83" s="6"/>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A84" s="6"/>
       <c r="B84" s="6"/>
       <c r="C84" s="6"/>
@@ -3133,7 +3133,7 @@
       <c r="P84" s="6"/>
       <c r="Q84" s="6"/>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A85" s="6"/>
       <c r="H85" s="6"/>
       <c r="I85" s="6"/>
@@ -3150,7 +3150,7 @@
       <c r="P85" s="6"/>
       <c r="Q85" s="6"/>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A86" s="6"/>
       <c r="H86" s="6"/>
       <c r="I86" s="6"/>
@@ -3168,7 +3168,7 @@
       <c r="P86" s="6"/>
       <c r="Q86" s="6"/>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A87" s="6"/>
       <c r="K87" s="11" t="s">
         <v>144</v>
@@ -3182,7 +3182,7 @@
       <c r="P87" s="6"/>
       <c r="Q87" s="6"/>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A88" s="6"/>
       <c r="B88" s="6"/>
       <c r="C88" s="6"/>
@@ -3200,7 +3200,7 @@
       <c r="P88" s="6"/>
       <c r="Q88" s="6"/>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A89" s="6"/>
       <c r="K89" s="11"/>
       <c r="M89" s="11"/>
@@ -3208,12 +3208,12 @@
       <c r="P89" s="6"/>
       <c r="Q89" s="7"/>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A90" s="6"/>
       <c r="P90" s="6"/>
       <c r="Q90" s="6"/>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A91" s="6"/>
       <c r="B91" s="6"/>
       <c r="C91" s="6"/>
@@ -3227,7 +3227,7 @@
       <c r="P91" s="7"/>
       <c r="Q91" s="6"/>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A92" s="6"/>
       <c r="B92" s="1" t="s">
         <v>82</v>
@@ -3241,7 +3241,7 @@
       <c r="P92" s="6"/>
       <c r="Q92" s="6"/>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A93" s="5"/>
       <c r="B93" s="6"/>
       <c r="C93" s="6"/>
@@ -3254,7 +3254,7 @@
       <c r="P93" s="6"/>
       <c r="Q93" s="6"/>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A94" s="6"/>
       <c r="C94" s="6"/>
       <c r="D94" s="6"/>
@@ -3272,7 +3272,7 @@
       <c r="P94" s="6"/>
       <c r="Q94" s="6"/>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A95" s="6"/>
       <c r="B95" s="8" t="s">
         <v>89</v>
@@ -3297,7 +3297,7 @@
       <c r="P95" s="6"/>
       <c r="Q95" s="6"/>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A96" s="6"/>
       <c r="B96" s="8"/>
       <c r="C96" s="5"/>
@@ -3320,7 +3320,7 @@
       <c r="P96" s="6"/>
       <c r="Q96" s="6"/>
     </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A97" s="6"/>
       <c r="B97" s="6"/>
       <c r="C97" s="6"/>
@@ -3343,7 +3343,7 @@
       <c r="P97" s="7"/>
       <c r="Q97" s="6"/>
     </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A98" s="6"/>
       <c r="B98" s="6"/>
       <c r="C98" s="6"/>
@@ -3365,7 +3365,7 @@
       <c r="P98" s="6"/>
       <c r="Q98" s="6"/>
     </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B99" s="8"/>
       <c r="C99" s="5"/>
       <c r="D99" s="6"/>
@@ -3385,7 +3385,7 @@
       <c r="P99" s="6"/>
       <c r="Q99" s="6"/>
     </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B100" s="8"/>
       <c r="C100" s="5"/>
       <c r="D100" s="6"/>
@@ -3405,7 +3405,7 @@
       <c r="P100" s="6"/>
       <c r="Q100" s="6"/>
     </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B101" s="1"/>
       <c r="G101" s="1"/>
       <c r="H101" s="6"/>
@@ -3421,7 +3421,7 @@
       <c r="P101" s="7"/>
       <c r="Q101" s="6"/>
     </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:17" x14ac:dyDescent="0.3">
       <c r="H102" s="6"/>
       <c r="I102" s="6"/>
       <c r="J102" s="8"/>
@@ -3432,7 +3432,7 @@
       <c r="P102" s="7"/>
       <c r="Q102" s="6"/>
     </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B103" s="1" t="s">
         <v>97</v>
       </c>
@@ -3441,7 +3441,7 @@
       <c r="P103" s="7"/>
       <c r="Q103" s="7"/>
     </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B104" s="1" t="s">
         <v>107</v>
       </c>
@@ -3457,7 +3457,7 @@
       <c r="P104" s="7"/>
       <c r="Q104" s="6"/>
     </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:17" x14ac:dyDescent="0.3">
       <c r="K105" s="1" t="s">
         <v>68</v>
       </c>
@@ -3470,7 +3470,7 @@
       <c r="P105" s="6"/>
       <c r="Q105" s="6"/>
     </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A106" s="6"/>
       <c r="B106" s="1" t="s">
         <v>100</v>
@@ -3491,7 +3491,7 @@
       <c r="P106" s="6"/>
       <c r="Q106" s="6"/>
     </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A107" s="6"/>
       <c r="K107" s="1" t="s">
         <v>101</v>
@@ -3506,20 +3506,20 @@
       <c r="P107" s="6"/>
       <c r="Q107" s="6"/>
     </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A108" s="6"/>
       <c r="N108" s="6"/>
       <c r="P108" s="7"/>
       <c r="Q108" s="6"/>
     </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A109" s="6"/>
       <c r="N109" s="6"/>
       <c r="O109" s="5"/>
       <c r="P109" s="6"/>
       <c r="Q109" s="6"/>
     </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A110" s="6"/>
       <c r="H110" s="6"/>
       <c r="I110" s="6"/>
@@ -3532,7 +3532,7 @@
       <c r="P110" s="6"/>
       <c r="Q110" s="6"/>
     </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A111" s="6"/>
       <c r="H111" s="6"/>
       <c r="I111" s="6"/>
@@ -3545,7 +3545,7 @@
       <c r="P111" s="6"/>
       <c r="Q111" s="6"/>
     </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A112" s="6"/>
       <c r="D112" s="6"/>
       <c r="E112" s="6"/>
@@ -3562,7 +3562,7 @@
       <c r="P112" s="6"/>
       <c r="Q112" s="6"/>
     </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A113" s="6"/>
       <c r="B113" s="8"/>
       <c r="C113" s="5"/>
@@ -3581,25 +3581,25 @@
       <c r="P113" s="6"/>
       <c r="Q113" s="6"/>
     </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A114" s="6"/>
       <c r="O114" s="6"/>
       <c r="P114" s="6"/>
       <c r="Q114" s="6"/>
     </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A115" s="6"/>
       <c r="O115" s="6"/>
       <c r="P115" s="6"/>
       <c r="Q115" s="6"/>
     </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A116" s="6"/>
       <c r="O116" s="6"/>
       <c r="P116" s="6"/>
       <c r="Q116" s="6"/>
     </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A117" s="6"/>
       <c r="B117" s="8"/>
       <c r="C117" s="5"/>
@@ -3618,7 +3618,7 @@
       <c r="P117" s="6"/>
       <c r="Q117" s="6"/>
     </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A118" s="6"/>
       <c r="B118" s="1" t="s">
         <v>119</v>
@@ -3638,7 +3638,7 @@
       <c r="P118" s="6"/>
       <c r="Q118" s="6"/>
     </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A119" s="6"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
@@ -3648,7 +3648,7 @@
       <c r="P119" s="6"/>
       <c r="Q119" s="6"/>
     </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A120" s="6"/>
       <c r="B120" s="1" t="s">
         <v>120</v>
@@ -3675,7 +3675,7 @@
       <c r="P120" s="6"/>
       <c r="Q120" s="6"/>
     </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A121" s="6"/>
       <c r="B121" s="1" t="s">
         <v>121</v>
@@ -3702,7 +3702,7 @@
       <c r="P121" s="6"/>
       <c r="Q121" s="6"/>
     </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A122" s="6"/>
       <c r="B122" s="1" t="s">
         <v>126</v>
@@ -3725,7 +3725,7 @@
       <c r="P122" s="6"/>
       <c r="Q122" s="6"/>
     </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A123" s="6"/>
       <c r="B123" s="6" t="s">
         <v>131</v>
@@ -3744,7 +3744,7 @@
       <c r="P123" s="6"/>
       <c r="Q123" s="6"/>
     </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A124" s="6"/>
       <c r="B124" s="6" t="s">
         <v>160</v>
@@ -3769,7 +3769,7 @@
       <c r="P124" s="6"/>
       <c r="Q124" s="6"/>
     </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A125" s="6"/>
       <c r="B125" s="6" t="s">
         <v>162</v>
@@ -3792,7 +3792,7 @@
       <c r="P125" s="6"/>
       <c r="Q125" s="6"/>
     </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A126" s="6"/>
       <c r="B126" s="6" t="s">
         <v>231</v>
@@ -3815,7 +3815,7 @@
       <c r="P126" s="6"/>
       <c r="Q126" s="6"/>
     </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A127" s="6"/>
       <c r="B127" s="6" t="s">
         <v>290</v>
@@ -3842,7 +3842,7 @@
       <c r="P127" s="6"/>
       <c r="Q127" s="6"/>
     </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A128" s="6"/>
       <c r="B128" s="6"/>
       <c r="C128" s="6"/>
@@ -3861,7 +3861,7 @@
       <c r="P128" s="6"/>
       <c r="Q128" s="6"/>
     </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A129" s="6"/>
       <c r="B129" s="5" t="s">
         <v>286</v>
@@ -3888,7 +3888,7 @@
       <c r="P129" s="6"/>
       <c r="Q129" s="6"/>
     </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A130" s="6"/>
       <c r="B130" s="5" t="s">
         <v>287</v>
@@ -3913,14 +3913,14 @@
       <c r="P130" s="6"/>
       <c r="Q130" s="6"/>
     </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A131" s="6"/>
       <c r="N131" s="6"/>
       <c r="O131" s="6"/>
       <c r="P131" s="6"/>
       <c r="Q131" s="6"/>
     </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A132" s="6"/>
       <c r="B132" s="5" t="s">
         <v>239</v>
@@ -3945,7 +3945,7 @@
       <c r="P132" s="6"/>
       <c r="Q132" s="6"/>
     </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A133" s="6"/>
       <c r="B133" s="5"/>
       <c r="C133" s="5"/>
@@ -3968,7 +3968,7 @@
       <c r="P133" s="6"/>
       <c r="Q133" s="6"/>
     </row>
-    <row r="134" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A134" s="6"/>
       <c r="B134" s="5"/>
       <c r="C134" s="5"/>
@@ -3991,7 +3991,7 @@
       <c r="P134" s="6"/>
       <c r="Q134" s="6"/>
     </row>
-    <row r="135" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A135" s="6"/>
       <c r="B135" s="5"/>
       <c r="C135" s="5"/>
@@ -4014,7 +4014,7 @@
       <c r="P135" s="6"/>
       <c r="Q135" s="6"/>
     </row>
-    <row r="136" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A136" s="6"/>
       <c r="B136" s="6"/>
       <c r="C136" s="6"/>
@@ -4037,7 +4037,7 @@
       <c r="P136" s="6"/>
       <c r="Q136" s="6"/>
     </row>
-    <row r="137" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A137" s="5"/>
       <c r="B137" s="6"/>
       <c r="C137" s="6"/>
@@ -4059,7 +4059,7 @@
       <c r="P137" s="6"/>
       <c r="Q137" s="6"/>
     </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A138" s="5"/>
       <c r="B138" s="8"/>
       <c r="C138" s="5"/>
@@ -4081,14 +4081,14 @@
       <c r="P138" s="6"/>
       <c r="Q138" s="6"/>
     </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A139" s="5"/>
       <c r="N139" s="6"/>
       <c r="O139" s="5"/>
       <c r="P139" s="6"/>
       <c r="Q139" s="6"/>
     </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A140" s="5"/>
       <c r="B140" s="8" t="s">
         <v>240</v>
@@ -4112,7 +4112,7 @@
       <c r="P140" s="6"/>
       <c r="Q140" s="6"/>
     </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A141" s="5"/>
       <c r="B141" s="8"/>
       <c r="C141" s="5"/>
@@ -4134,7 +4134,7 @@
       <c r="P141" s="6"/>
       <c r="Q141" s="6"/>
     </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B142" s="8"/>
       <c r="C142" s="5"/>
       <c r="D142" s="6"/>
@@ -4147,7 +4147,7 @@
       <c r="K142" s="1"/>
       <c r="M142" s="5"/>
     </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:17" x14ac:dyDescent="0.3">
       <c r="C143" s="6"/>
       <c r="D143" s="6"/>
       <c r="E143" s="6"/>
@@ -4162,21 +4162,21 @@
       <c r="N143" s="6"/>
       <c r="O143" s="6"/>
     </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:17" x14ac:dyDescent="0.3">
       <c r="N144" s="6"/>
       <c r="O144" s="6"/>
     </row>
-    <row r="145" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B145" s="6" t="s">
         <v>64</v>
       </c>
       <c r="N145" s="6"/>
     </row>
-    <row r="146" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:15" x14ac:dyDescent="0.3">
       <c r="N146" s="6"/>
       <c r="O146" s="6"/>
     </row>
-    <row r="147" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B147" s="5" t="s">
         <v>123</v>
       </c>
@@ -4199,7 +4199,7 @@
       <c r="N147" s="6"/>
       <c r="O147" s="6"/>
     </row>
-    <row r="148" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:15" x14ac:dyDescent="0.3">
       <c r="K148" s="1" t="s">
         <v>113</v>
       </c>
@@ -4207,7 +4207,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="149" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:15" x14ac:dyDescent="0.3">
       <c r="K149" s="1" t="s">
         <v>125</v>
       </c>
@@ -4215,7 +4215,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="151" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B151" s="6" t="s">
         <v>65</v>
       </c>
@@ -4233,7 +4233,7 @@
       <c r="L151" s="6"/>
       <c r="M151" s="5"/>
     </row>
-    <row r="152" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B152" s="6"/>
       <c r="C152" s="6"/>
       <c r="D152" s="6"/>
@@ -4247,7 +4247,7 @@
       <c r="L152" s="6"/>
       <c r="M152" s="5"/>
     </row>
-    <row r="153" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B153" s="6" t="s">
         <v>110</v>
       </c>
@@ -4268,7 +4268,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="154" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:15" x14ac:dyDescent="0.3">
       <c r="D154" s="6"/>
       <c r="E154" s="6"/>
       <c r="F154" s="6"/>
@@ -4284,7 +4284,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="155" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:15" x14ac:dyDescent="0.3">
       <c r="D155" s="6"/>
       <c r="E155" s="6"/>
       <c r="F155" s="6"/>
@@ -4296,7 +4296,7 @@
       <c r="L155" s="6"/>
       <c r="M155" s="5"/>
     </row>
-    <row r="156" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B156" s="1" t="s">
         <v>247</v>
       </c>
@@ -4310,7 +4310,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="157" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B157" s="1" t="s">
         <v>257</v>
       </c>
@@ -4318,22 +4318,22 @@
         <v>64</v>
       </c>
     </row>
-    <row r="158" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A158" s="1"/>
       <c r="B158" s="1"/>
       <c r="C158" s="1"/>
       <c r="K158" s="1"/>
       <c r="M158" s="1"/>
     </row>
-    <row r="159" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B159" s="1"/>
       <c r="C159" s="1"/>
     </row>
-    <row r="160" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B160" s="1"/>
       <c r="C160" s="1"/>
     </row>
-    <row r="161" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="161" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B161" s="1" t="s">
         <v>195</v>
       </c>
@@ -4344,7 +4344,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="162" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="162" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K162" s="1" t="s">
         <v>197</v>
       </c>
@@ -4352,10 +4352,10 @@
         <v>23</v>
       </c>
     </row>
-    <row r="163" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="163" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K163" s="1"/>
     </row>
-    <row r="165" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="165" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B165" s="1" t="s">
         <v>206</v>
       </c>
@@ -4367,7 +4367,7 @@
       </c>
       <c r="O165" s="6"/>
     </row>
-    <row r="166" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="166" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K166" s="1" t="s">
         <v>26</v>
       </c>
@@ -4375,7 +4375,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="167" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="167" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K167" s="1" t="s">
         <v>41</v>
       </c>
@@ -4383,7 +4383,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="168" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="168" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K168" s="1" t="s">
         <v>33</v>
       </c>
@@ -4391,7 +4391,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="169" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="169" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K169" s="1" t="s">
         <v>199</v>
       </c>
@@ -4399,7 +4399,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="170" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="170" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K170" s="1" t="s">
         <v>150</v>
       </c>
@@ -4407,7 +4407,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="171" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="171" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B171" s="1" t="s">
         <v>227</v>
       </c>
@@ -4418,7 +4418,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="172" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="172" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B172" s="1"/>
       <c r="K172" s="1" t="s">
         <v>26</v>
@@ -4427,7 +4427,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="173" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="173" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K173" s="1" t="s">
         <v>41</v>
       </c>
@@ -4435,7 +4435,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="174" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="174" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K174" s="1" t="s">
         <v>228</v>
       </c>
@@ -4443,11 +4443,11 @@
         <v>229</v>
       </c>
     </row>
-    <row r="175" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="175" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K175" s="1"/>
       <c r="M175" s="1"/>
     </row>
-    <row r="176" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="176" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B176" s="1" t="s">
         <v>230</v>
       </c>
@@ -4458,7 +4458,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="177" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="177" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K177" s="1" t="s">
         <v>26</v>
       </c>
@@ -4466,7 +4466,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="178" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="178" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K178" s="1" t="s">
         <v>41</v>
       </c>
@@ -4474,7 +4474,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="179" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="179" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K179" s="1" t="s">
         <v>60</v>
       </c>
@@ -4482,7 +4482,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="180" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="180" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K180" s="1" t="s">
         <v>68</v>
       </c>
@@ -4490,10 +4490,10 @@
         <v>71</v>
       </c>
     </row>
-    <row r="181" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="181" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K181" s="1"/>
     </row>
-    <row r="183" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="183" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B183" s="1" t="s">
         <v>207</v>
       </c>
@@ -4507,7 +4507,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="184" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="184" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K184" s="1" t="s">
         <v>26</v>
       </c>
@@ -4518,7 +4518,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="185" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="185" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K185" s="1" t="s">
         <v>41</v>
       </c>
@@ -4529,10 +4529,10 @@
         <v>211</v>
       </c>
     </row>
-    <row r="186" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="186" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K186" s="1"/>
     </row>
-    <row r="187" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="187" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B187" s="1" t="s">
         <v>208</v>
       </c>
@@ -4543,7 +4543,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="188" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="188" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K188" s="1" t="s">
         <v>26</v>
       </c>
@@ -4551,7 +4551,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="189" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="189" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K189" s="1" t="s">
         <v>41</v>
       </c>
@@ -4559,7 +4559,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="190" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="190" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K190" s="1" t="s">
         <v>216</v>
       </c>
@@ -4567,7 +4567,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="191" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="191" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K191" s="1" t="s">
         <v>218</v>
       </c>
@@ -4575,7 +4575,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="193" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="193" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B193" s="1" t="s">
         <v>213</v>
       </c>
@@ -4586,7 +4586,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="194" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="194" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K194" s="1" t="s">
         <v>215</v>
       </c>
@@ -4594,7 +4594,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="197" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="197" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B197" s="1" t="s">
         <v>219</v>
       </c>
@@ -4608,7 +4608,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="198" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="198" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K198" s="1" t="s">
         <v>26</v>
       </c>
@@ -4619,7 +4619,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="199" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="199" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K199" s="1" t="s">
         <v>41</v>
       </c>
@@ -4630,7 +4630,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="200" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="200" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K200" s="1" t="s">
         <v>143</v>
       </c>
@@ -4638,7 +4638,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="201" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="201" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B201" s="1" t="s">
         <v>234</v>
       </c>
@@ -4649,7 +4649,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="202" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="202" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K202" s="1" t="s">
         <v>134</v>
       </c>
@@ -4657,7 +4657,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="206" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="206" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B206" s="1" t="s">
         <v>226</v>
       </c>
@@ -4671,7 +4671,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="207" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="207" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K207" s="1" t="s">
         <v>95</v>
       </c>
@@ -4679,7 +4679,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="210" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="210" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B210" s="1" t="s">
         <v>248</v>
       </c>
@@ -4690,7 +4690,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="211" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="211" spans="2:13" x14ac:dyDescent="0.3">
       <c r="K211" s="1" t="s">
         <v>26</v>
       </c>
@@ -4698,7 +4698,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="212" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="212" spans="2:13" x14ac:dyDescent="0.3">
       <c r="K212" s="1" t="s">
         <v>60</v>
       </c>
@@ -4706,7 +4706,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="213" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="213" spans="2:13" x14ac:dyDescent="0.3">
       <c r="K213" s="1" t="s">
         <v>41</v>
       </c>
@@ -4714,7 +4714,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="214" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="214" spans="2:13" x14ac:dyDescent="0.3">
       <c r="K214" s="1" t="s">
         <v>249</v>
       </c>
@@ -4722,7 +4722,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="215" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="215" spans="2:13" x14ac:dyDescent="0.3">
       <c r="K215" s="1" t="s">
         <v>250</v>
       </c>
@@ -4730,7 +4730,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="217" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="217" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B217" s="1" t="s">
         <v>275</v>
       </c>
@@ -4741,7 +4741,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="218" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="218" spans="2:13" x14ac:dyDescent="0.3">
       <c r="K218" s="1" t="s">
         <v>26</v>
       </c>
@@ -4749,7 +4749,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="219" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="219" spans="2:13" x14ac:dyDescent="0.3">
       <c r="K219" s="1" t="s">
         <v>95</v>
       </c>
@@ -4757,7 +4757,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="220" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="220" spans="2:13" x14ac:dyDescent="0.3">
       <c r="K220" s="1" t="s">
         <v>41</v>
       </c>
@@ -4765,7 +4765,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="221" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="221" spans="2:13" x14ac:dyDescent="0.3">
       <c r="K221" s="1" t="s">
         <v>216</v>
       </c>
@@ -4773,7 +4773,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="222" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="222" spans="2:13" x14ac:dyDescent="0.3">
       <c r="K222" s="1" t="s">
         <v>276</v>
       </c>
@@ -4781,7 +4781,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="223" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="223" spans="2:13" x14ac:dyDescent="0.3">
       <c r="K223" s="1" t="s">
         <v>68</v>
       </c>
@@ -4789,38 +4789,42 @@
         <v>71</v>
       </c>
     </row>
-    <row r="224" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B224" s="1" t="s">
+    <row r="224" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="K224" s="1"/>
+      <c r="M224" s="1"/>
+    </row>
+    <row r="225" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B225" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="K224" s="1" t="s">
+      <c r="K225" s="1" t="s">
         <v>278</v>
-      </c>
-      <c r="M224" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="225" spans="11:13" x14ac:dyDescent="0.2">
-      <c r="K225" s="1" t="s">
-        <v>279</v>
       </c>
       <c r="M225" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="226" spans="11:13" x14ac:dyDescent="0.2">
+    <row r="226" spans="2:13" x14ac:dyDescent="0.3">
       <c r="K226" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="M226" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="227" spans="11:13" x14ac:dyDescent="0.2">
+    <row r="227" spans="2:13" x14ac:dyDescent="0.3">
       <c r="K227" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="M227" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="228" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="K228" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="M227" s="1" t="s">
+      <c r="M228" s="1" t="s">
         <v>38</v>
       </c>
     </row>
@@ -4837,12 +4841,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EECC075D-9730-41E5-B97E-C301603D1E48}">
   <dimension ref="A1:Q95"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="27.375" customWidth="1"/>
+    <col min="2" max="2" width="27.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -4883,7 +4887,7 @@
       <c r="P1" s="12"/>
       <c r="Q1" s="12"/>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -4918,7 +4922,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>11</v>
       </c>
@@ -4955,7 +4959,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B6" s="6" t="s">
         <v>53</v>
       </c>
@@ -4972,7 +4976,7 @@
       <c r="M6" s="5"/>
       <c r="N6" s="6"/>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
         <v>141</v>
       </c>
@@ -4986,7 +4990,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="K9" s="1" t="s">
         <v>134</v>
       </c>
@@ -4997,7 +5001,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B11" s="1" t="s">
         <v>129</v>
       </c>
@@ -5011,7 +5015,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B12" s="6" t="s">
         <v>54</v>
       </c>
@@ -5039,7 +5043,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
@@ -5061,7 +5065,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
       <c r="D14" s="6"/>
@@ -5074,7 +5078,7 @@
       <c r="N14" s="6"/>
       <c r="O14" s="6"/>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B15" s="1" t="s">
         <v>74</v>
       </c>
@@ -5092,7 +5096,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="K16" s="1" t="s">
         <v>75</v>
       </c>
@@ -5103,7 +5107,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B17" s="1" t="s">
         <v>104</v>
       </c>
@@ -5120,7 +5124,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="18" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B18" s="1" t="s">
         <v>115</v>
       </c>
@@ -5134,7 +5138,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="19" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K19" s="5" t="s">
         <v>37</v>
       </c>
@@ -5142,7 +5146,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="20" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K20" s="1" t="s">
         <v>118</v>
       </c>
@@ -5150,7 +5154,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="21" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B21" s="1" t="s">
         <v>127</v>
       </c>
@@ -5164,7 +5168,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="23" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B23" s="1" t="s">
         <v>133</v>
       </c>
@@ -5178,7 +5182,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="24" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K24" s="1" t="s">
         <v>134</v>
       </c>
@@ -5186,7 +5190,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="26" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B26" s="1" t="s">
         <v>139</v>
       </c>
@@ -5200,7 +5204,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="27" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K27" s="1" t="s">
         <v>33</v>
       </c>
@@ -5208,7 +5212,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="28" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K28" s="1" t="s">
         <v>41</v>
       </c>
@@ -5216,7 +5220,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K29" s="1" t="s">
         <v>68</v>
       </c>
@@ -5224,7 +5228,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="31" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B31" s="1" t="s">
         <v>158</v>
       </c>
@@ -5238,7 +5242,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="32" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B32" s="1" t="s">
         <v>173</v>
       </c>
@@ -5252,7 +5256,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="K33" s="1" t="s">
         <v>186</v>
       </c>
@@ -5260,7 +5264,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B34" s="1" t="s">
         <v>222</v>
       </c>
@@ -5274,7 +5278,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="K35" s="1" t="s">
         <v>223</v>
       </c>
@@ -5282,7 +5286,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>180</v>
       </c>
@@ -5293,11 +5297,11 @@
         <v>128</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="K37" s="1"/>
       <c r="M37" s="1"/>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B38" s="1" t="s">
         <v>193</v>
       </c>
@@ -5311,7 +5315,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="K39" s="1" t="s">
         <v>186</v>
       </c>
@@ -5319,7 +5323,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B40" s="1" t="s">
         <v>175</v>
       </c>
@@ -5334,10 +5338,10 @@
       </c>
       <c r="N40" s="6"/>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N41" s="6"/>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B42" s="1" t="s">
         <v>116</v>
       </c>
@@ -5358,7 +5362,7 @@
       </c>
       <c r="N42" s="6"/>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B43" s="6"/>
       <c r="C43" s="5"/>
       <c r="D43" s="6"/>
@@ -5376,7 +5380,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B44" s="8"/>
       <c r="C44" s="5"/>
       <c r="D44" s="6"/>
@@ -5394,7 +5398,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B45" s="1" t="s">
         <v>188</v>
       </c>
@@ -5405,7 +5409,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="K46" s="1" t="s">
         <v>189</v>
       </c>
@@ -5413,7 +5417,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
         <v>178</v>
       </c>
@@ -5421,7 +5425,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B50" s="1" t="s">
         <v>184</v>
       </c>
@@ -5438,7 +5442,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A54" s="1"/>
       <c r="B54" s="1" t="s">
         <v>203</v>
@@ -5456,7 +5460,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
       <c r="K55" s="1" t="s">
         <v>202</v>
       </c>
@@ -5464,7 +5468,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
       <c r="K56" s="1" t="s">
         <v>204</v>
       </c>
@@ -5472,7 +5476,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B58" s="1" t="s">
         <v>232</v>
       </c>
@@ -5486,7 +5490,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
       <c r="K59" s="1" t="s">
         <v>75</v>
       </c>
@@ -5494,7 +5498,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B61" s="1" t="s">
         <v>233</v>
       </c>
@@ -5508,7 +5512,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B63" s="1" t="s">
         <v>237</v>
       </c>
@@ -5522,7 +5526,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.3">
       <c r="K64" s="1" t="s">
         <v>238</v>
       </c>
@@ -5530,7 +5534,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B65" s="1" t="s">
         <v>244</v>
       </c>
@@ -5544,7 +5548,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B67" s="1" t="s">
         <v>246</v>
       </c>
@@ -5558,7 +5562,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B68" s="1" t="s">
         <v>285</v>
       </c>
@@ -5572,7 +5576,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B69" s="1" t="s">
         <v>258</v>
       </c>
@@ -5586,7 +5590,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B70" s="1" t="s">
         <v>251</v>
       </c>
@@ -5600,7 +5604,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:13" x14ac:dyDescent="0.3">
       <c r="K71" s="1" t="s">
         <v>75</v>
       </c>
@@ -5608,7 +5612,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B72" s="1" t="s">
         <v>253</v>
       </c>
@@ -5622,7 +5626,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:13" x14ac:dyDescent="0.3">
       <c r="K73" s="1" t="s">
         <v>75</v>
       </c>
@@ -5630,7 +5634,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B75" s="1" t="s">
         <v>260</v>
       </c>
@@ -5644,7 +5648,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:13" x14ac:dyDescent="0.3">
       <c r="K76" s="1" t="s">
         <v>118</v>
       </c>
@@ -5652,7 +5656,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="78" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="78" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B78" s="1" t="s">
         <v>261</v>
       </c>
@@ -5663,7 +5667,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:13" x14ac:dyDescent="0.3">
       <c r="K79" s="1" t="s">
         <v>75</v>
       </c>
@@ -5671,7 +5675,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B80" s="1" t="s">
         <v>269</v>
       </c>
@@ -5685,13 +5689,13 @@
         <v>23</v>
       </c>
     </row>
-    <row r="81" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="81" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
       <c r="K81" s="1"/>
       <c r="M81" s="1"/>
     </row>
-    <row r="82" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="82" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B82" s="1" t="s">
         <v>270</v>
       </c>
@@ -5705,7 +5709,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="84" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="84" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B84" s="1" t="s">
         <v>271</v>
       </c>
@@ -5719,7 +5723,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="86" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="86" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B86" s="1" t="s">
         <v>272</v>
       </c>
@@ -5733,7 +5737,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="88" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="88" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B88" s="1" t="s">
         <v>273</v>
       </c>
@@ -5747,7 +5751,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="90" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="90" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B90" s="1" t="s">
         <v>282</v>
       </c>
@@ -5761,7 +5765,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="93" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="93" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B93" s="1" t="s">
         <v>289</v>
       </c>
@@ -5775,7 +5779,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="95" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="95" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B95" s="1" t="s">
         <v>292</v>
       </c>
@@ -5801,7 +5805,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEE0849C-6C30-450E-8369-1D81B45C3886}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Config/Datas/__beans__.xlsx
+++ b/Config/Datas/__beans__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B5F589C-4C2C-47E2-8718-6B1BDC91C47C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EF887DA-F51F-4208-A515-38DE5C4B97D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="671" uniqueCount="293">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="682" uniqueCount="301">
   <si>
     <t>##var</t>
   </si>
@@ -1181,6 +1181,38 @@
   </si>
   <si>
     <t>GA_随机选卡</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GuideStepData</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>flowID</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>stepID</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>教程步骤标识符</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>流程标识符</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>guideText</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PlayerActionType</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>triggerAction</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1188,7 +1220,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1262,6 +1294,11 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FFE2BFFF"/>
+      <name val="JetBrains Mono"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -1298,7 +1335,7 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1331,6 +1368,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1608,7 +1648,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q228"/>
+  <dimension ref="A1:Q233"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="28.75" customWidth="1"/>
@@ -4793,7 +4833,7 @@
       <c r="K224" s="1"/>
       <c r="M224" s="1"/>
     </row>
-    <row r="225" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="225" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B225" s="1" t="s">
         <v>277</v>
       </c>
@@ -4804,7 +4844,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="226" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="226" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K226" s="1" t="s">
         <v>279</v>
       </c>
@@ -4812,7 +4852,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="227" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="227" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K227" s="1" t="s">
         <v>280</v>
       </c>
@@ -4820,12 +4860,54 @@
         <v>38</v>
       </c>
     </row>
-    <row r="228" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="228" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K228" s="1" t="s">
         <v>281</v>
       </c>
       <c r="M228" s="1" t="s">
         <v>38</v>
+      </c>
+    </row>
+    <row r="230" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B230" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="K230" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="M230" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O230" s="1" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="231" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="K231" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="M231" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O231" s="1" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="232" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="K232" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="M232" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="233" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B233" s="1"/>
+      <c r="K233" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="M233" s="13" t="s">
+        <v>299</v>
       </c>
     </row>
   </sheetData>

--- a/Config/Datas/__beans__.xlsx
+++ b/Config/Datas/__beans__.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EF887DA-F51F-4208-A515-38DE5C4B97D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{503A9987-9302-419D-9C9B-44C390A1F917}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="682" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="689" uniqueCount="305">
   <si>
     <t>##var</t>
   </si>
@@ -1213,6 +1213,22 @@
   </si>
   <si>
     <t>triggerAction</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>stepName</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GuideTargetType</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>是否聚焦</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>isConcerned</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1366,11 +1382,11 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1648,7 +1664,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q233"/>
+  <dimension ref="A1:Q236"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="28.75" customWidth="1"/>
@@ -1696,15 +1712,15 @@
       <c r="J1" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="K1" s="12" t="s">
+      <c r="K1" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="L1" s="12"/>
-      <c r="M1" s="12"/>
-      <c r="N1" s="12"/>
-      <c r="O1" s="12"/>
-      <c r="P1" s="12"/>
-      <c r="Q1" s="12"/>
+      <c r="L1" s="13"/>
+      <c r="M1" s="13"/>
+      <c r="N1" s="13"/>
+      <c r="O1" s="13"/>
+      <c r="P1" s="13"/>
+      <c r="Q1" s="13"/>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
@@ -4884,7 +4900,7 @@
     </row>
     <row r="231" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K231" s="1" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="M231" s="1" t="s">
         <v>23</v>
@@ -4895,7 +4911,7 @@
     </row>
     <row r="232" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K232" s="1" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="M232" s="1" t="s">
         <v>23</v>
@@ -4904,10 +4920,37 @@
     <row r="233" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B233" s="1"/>
       <c r="K233" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="M233" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="234" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="K234" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="M233" s="13" t="s">
+      <c r="M234" s="12" t="s">
         <v>299</v>
+      </c>
+    </row>
+    <row r="235" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="K235" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="M235" s="1" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="236" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="K236" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="M236" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="O236" s="1" t="s">
+        <v>303</v>
       </c>
     </row>
   </sheetData>
@@ -4959,15 +5002,15 @@
       <c r="J1" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="K1" s="12" t="s">
+      <c r="K1" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="L1" s="12"/>
-      <c r="M1" s="12"/>
-      <c r="N1" s="12"/>
-      <c r="O1" s="12"/>
-      <c r="P1" s="12"/>
-      <c r="Q1" s="12"/>
+      <c r="L1" s="13"/>
+      <c r="M1" s="13"/>
+      <c r="N1" s="13"/>
+      <c r="O1" s="13"/>
+      <c r="P1" s="13"/>
+      <c r="Q1" s="13"/>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">

--- a/Config/Datas/__beans__.xlsx
+++ b/Config/Datas/__beans__.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{503A9987-9302-419D-9C9B-44C390A1F917}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4D99F8E-6B19-444D-8EBE-10445B31A7F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="689" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="691" uniqueCount="306">
   <si>
     <t>##var</t>
   </si>
@@ -1229,6 +1229,10 @@
   </si>
   <si>
     <t>isConcerned</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>spriteName</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1664,7 +1668,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q236"/>
+  <dimension ref="A1:Q237"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="28.75" customWidth="1"/>
@@ -4677,78 +4681,79 @@
     </row>
     <row r="199" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K199" s="1" t="s">
-        <v>41</v>
+        <v>305</v>
       </c>
       <c r="M199" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="O199" s="1" t="s">
-        <v>221</v>
-      </c>
+      <c r="O199" s="1"/>
     </row>
     <row r="200" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K200" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M200" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O200" s="1" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="201" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="K201" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="M200" s="1" t="s">
+      <c r="M201" s="1" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="201" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B201" s="1" t="s">
+    <row r="202" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B202" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="K201" s="1" t="s">
+      <c r="K202" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M201" s="1" t="s">
+      <c r="M202" s="1" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="202" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="K202" s="1" t="s">
+    <row r="203" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="K203" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="M202" s="1" t="s">
+      <c r="M203" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="206" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B206" s="1" t="s">
+    <row r="207" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B207" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="G206" s="1" t="s">
+      <c r="G207" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="K206" s="1" t="s">
+      <c r="K207" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="M206" s="1" t="s">
+      <c r="M207" s="1" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="207" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="K207" s="1" t="s">
+    <row r="208" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="K208" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="M207" s="1" t="s">
+      <c r="M208" s="1" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="210" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B210" s="1" t="s">
+    <row r="211" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B211" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="K210" s="1" t="s">
+      <c r="K211" s="1" t="s">
         <v>25</v>
-      </c>
-      <c r="M210" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="211" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="K211" s="1" t="s">
-        <v>26</v>
       </c>
       <c r="M211" s="1" t="s">
         <v>23</v>
@@ -4756,7 +4761,7 @@
     </row>
     <row r="212" spans="2:13" x14ac:dyDescent="0.3">
       <c r="K212" s="1" t="s">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="M212" s="1" t="s">
         <v>23</v>
@@ -4764,7 +4769,7 @@
     </row>
     <row r="213" spans="2:13" x14ac:dyDescent="0.3">
       <c r="K213" s="1" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="M213" s="1" t="s">
         <v>23</v>
@@ -4772,34 +4777,34 @@
     </row>
     <row r="214" spans="2:13" x14ac:dyDescent="0.3">
       <c r="K214" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="M214" s="6" t="s">
-        <v>99</v>
+        <v>41</v>
+      </c>
+      <c r="M214" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="215" spans="2:13" x14ac:dyDescent="0.3">
       <c r="K215" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="M215" s="6" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="216" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="K216" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="M215" s="1" t="s">
+      <c r="M216" s="1" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="217" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B217" s="1" t="s">
+    <row r="218" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B218" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="K217" s="1" t="s">
+      <c r="K218" s="1" t="s">
         <v>25</v>
-      </c>
-      <c r="M217" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="218" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="K218" s="1" t="s">
-        <v>26</v>
       </c>
       <c r="M218" s="1" t="s">
         <v>23</v>
@@ -4807,62 +4812,62 @@
     </row>
     <row r="219" spans="2:13" x14ac:dyDescent="0.3">
       <c r="K219" s="1" t="s">
-        <v>95</v>
+        <v>26</v>
       </c>
       <c r="M219" s="1" t="s">
-        <v>112</v>
+        <v>23</v>
       </c>
     </row>
     <row r="220" spans="2:13" x14ac:dyDescent="0.3">
       <c r="K220" s="1" t="s">
-        <v>41</v>
+        <v>95</v>
       </c>
       <c r="M220" s="1" t="s">
-        <v>23</v>
+        <v>112</v>
       </c>
     </row>
     <row r="221" spans="2:13" x14ac:dyDescent="0.3">
       <c r="K221" s="1" t="s">
-        <v>216</v>
+        <v>41</v>
       </c>
       <c r="M221" s="1" t="s">
-        <v>274</v>
+        <v>23</v>
       </c>
     </row>
     <row r="222" spans="2:13" x14ac:dyDescent="0.3">
       <c r="K222" s="1" t="s">
-        <v>276</v>
+        <v>216</v>
       </c>
       <c r="M222" s="1" t="s">
-        <v>112</v>
+        <v>274</v>
       </c>
     </row>
     <row r="223" spans="2:13" x14ac:dyDescent="0.3">
       <c r="K223" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="M223" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="224" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="K224" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="M223" s="1" t="s">
+      <c r="M224" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="224" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="K224" s="1"/>
-      <c r="M224" s="1"/>
-    </row>
     <row r="225" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B225" s="1" t="s">
+      <c r="K225" s="1"/>
+      <c r="M225" s="1"/>
+    </row>
+    <row r="226" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B226" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="K225" s="1" t="s">
+      <c r="K226" s="1" t="s">
         <v>278</v>
-      </c>
-      <c r="M225" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="226" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="K226" s="1" t="s">
-        <v>279</v>
       </c>
       <c r="M226" s="1" t="s">
         <v>38</v>
@@ -4870,7 +4875,7 @@
     </row>
     <row r="227" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K227" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="M227" s="1" t="s">
         <v>38</v>
@@ -4878,78 +4883,86 @@
     </row>
     <row r="228" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K228" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="M228" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="230" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B230" s="1" t="s">
+    <row r="229" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="K229" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="M229" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="231" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B231" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="K230" s="1" t="s">
+      <c r="K231" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="M230" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="O230" s="1" t="s">
+      <c r="M231" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O231" s="1" t="s">
         <v>296</v>
-      </c>
-    </row>
-    <row r="231" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="K231" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="M231" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="O231" s="1" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="232" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K232" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="M232" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O232" s="1" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="233" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="K233" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="M232" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="233" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B233" s="1"/>
-      <c r="K233" s="1" t="s">
+      <c r="M233" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="234" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B234" s="1"/>
+      <c r="K234" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="M233" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="234" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="K234" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="M234" s="12" t="s">
-        <v>299</v>
+      <c r="M234" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="235" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K235" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="M235" s="1" t="s">
-        <v>302</v>
+        <v>300</v>
+      </c>
+      <c r="M235" s="12" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="236" spans="2:15" x14ac:dyDescent="0.3">
       <c r="K236" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="M236" s="1" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="237" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="K237" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="M236" s="1" t="s">
+      <c r="M237" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="O236" s="1" t="s">
+      <c r="O237" s="1" t="s">
         <v>303</v>
       </c>
     </row>

--- a/Config/Datas/__beans__.xlsx
+++ b/Config/Datas/__beans__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4D99F8E-6B19-444D-8EBE-10445B31A7F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFCAF94A-8DA8-4AF3-BAC5-4A6159DAD9E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="691" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="703" uniqueCount="312">
   <si>
     <t>##var</t>
   </si>
@@ -1233,6 +1233,30 @@
   </si>
   <si>
     <t>spriteName</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GridShapeData</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>网格形状数据</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>pattern</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GridShapeType</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CellType</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>shapeID</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1668,7 +1692,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q237"/>
+  <dimension ref="A1:Q242"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="28.75" customWidth="1"/>
@@ -4966,6 +4990,36 @@
         <v>303</v>
       </c>
     </row>
+    <row r="240" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B240" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="G240" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="K240" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="M240" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="241" spans="11:13" x14ac:dyDescent="0.3">
+      <c r="K241" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M241" s="1" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="242" spans="11:13" x14ac:dyDescent="0.3">
+      <c r="K242" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="M242" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="K1:Q1"/>
@@ -4978,7 +5032,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EECC075D-9730-41E5-B97E-C301603D1E48}">
-  <dimension ref="A1:Q95"/>
+  <dimension ref="A1:Q96"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="27.33203125" customWidth="1"/>
@@ -5549,160 +5603,162 @@
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="K46" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M46" s="1" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="K47" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="M46" s="5" t="s">
+      <c r="M47" s="5" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A48" s="1" t="s">
+      <c r="K48" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="M48" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A49" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="B48" s="1" t="s">
+      <c r="B49" s="1" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B50" s="1" t="s">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B51" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="C50" s="1" t="s">
+      <c r="C51" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="G50" s="1" t="s">
+      <c r="G51" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="K50" s="1" t="s">
+      <c r="K51" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="M50" s="1" t="s">
+      <c r="M51" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A54" s="1"/>
-      <c r="B54" s="1" t="s">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A55" s="1"/>
+      <c r="B55" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="C54" s="1" t="s">
+      <c r="C55" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="G54" s="1" t="s">
+      <c r="G55" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="K54" s="1" t="s">
+      <c r="K55" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="M54" s="1" t="s">
+      <c r="M55" s="1" t="s">
         <v>38</v>
-      </c>
-    </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="K55" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="M55" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.3">
       <c r="K56" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="M56" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="K57" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="M56" s="1" t="s">
+      <c r="M57" s="1" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B58" s="1" t="s">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B59" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="C58" s="1" t="s">
+      <c r="C59" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="K58" s="1" t="s">
+      <c r="K59" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="M58" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="K59" s="1" t="s">
+      <c r="M59" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="K60" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="M59" s="1" t="s">
+      <c r="M60" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B61" s="1" t="s">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B62" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="C61" s="1" t="s">
+      <c r="C62" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="K61" s="1" t="s">
+      <c r="K62" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="M61" s="1" t="s">
+      <c r="M62" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B63" s="1" t="s">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B64" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="C63" s="1" t="s">
+      <c r="C64" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="K63" s="1" t="s">
+      <c r="K64" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="M63" s="1" t="s">
+      <c r="M64" s="1" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="K64" s="1" t="s">
+    <row r="65" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="K65" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="M64" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B65" s="1" t="s">
+      <c r="M65" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B66" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="C65" s="1" t="s">
+      <c r="C66" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="K65" s="1" t="s">
+      <c r="K66" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="M65" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B67" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="K67" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="M67" s="1" t="s">
-        <v>128</v>
+      <c r="M66" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="68" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B68" s="1" t="s">
-        <v>285</v>
+        <v>246</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>53</v>
@@ -5716,7 +5772,7 @@
     </row>
     <row r="69" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B69" s="1" t="s">
-        <v>258</v>
+        <v>285</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>53</v>
@@ -5730,204 +5786,218 @@
     </row>
     <row r="70" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B70" s="1" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>53</v>
       </c>
       <c r="K70" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="M70" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B71" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="K71" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="M70" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="K71" s="1" t="s">
+      <c r="M71" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="K72" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="M71" s="1" t="s">
+      <c r="M72" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B72" s="1" t="s">
+    <row r="73" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B73" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="C72" s="1" t="s">
+      <c r="C73" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="K72" s="1" t="s">
+      <c r="K73" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="M72" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="K73" s="1" t="s">
+      <c r="M73" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="K74" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="M73" s="1" t="s">
+      <c r="M74" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B75" s="1" t="s">
+    <row r="76" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B76" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="C75" s="1" t="s">
+      <c r="C76" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="K75" s="1" t="s">
+      <c r="K76" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="M75" s="1" t="s">
+      <c r="M76" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="K76" s="1" t="s">
+    <row r="77" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="K77" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="M76" s="1" t="s">
+      <c r="M77" s="1" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="78" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B78" s="1" t="s">
+    <row r="79" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B79" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="K78" s="1" t="s">
+      <c r="K79" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="M78" s="1" t="s">
+      <c r="M79" s="1" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="K79" s="1" t="s">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="K80" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="M79" s="1" t="s">
+      <c r="M80" s="1" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B80" s="1" t="s">
+    <row r="81" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B81" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="C80" s="1" t="s">
+      <c r="C81" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="K80" s="1" t="s">
+      <c r="K81" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="M80" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="81" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B81" s="1"/>
-      <c r="C81" s="1"/>
-      <c r="K81" s="1"/>
-      <c r="M81" s="1"/>
+      <c r="M81" s="1" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="82" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B82" s="1" t="s">
+      <c r="B82" s="1"/>
+      <c r="C82" s="1"/>
+      <c r="K82" s="1"/>
+      <c r="M82" s="1"/>
+    </row>
+    <row r="83" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B83" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="C82" s="1" t="s">
+      <c r="C83" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="K82" s="1" t="s">
+      <c r="K83" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="M82" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="84" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B84" s="1" t="s">
+      <c r="M83" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="85" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B85" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="C84" s="1" t="s">
+      <c r="C85" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="K84" s="1" t="s">
+      <c r="K85" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="M84" s="1" t="s">
+      <c r="M85" s="1" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="86" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B86" s="1" t="s">
+    <row r="87" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B87" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="C86" s="1" t="s">
+      <c r="C87" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="K86" s="1" t="s">
+      <c r="K87" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="M86" s="1" t="s">
+      <c r="M87" s="1" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="88" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B88" s="1" t="s">
+    <row r="89" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B89" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="C88" s="1" t="s">
+      <c r="C89" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="K88" s="1" t="s">
+      <c r="K89" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="M88" s="1" t="s">
+      <c r="M89" s="1" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="90" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B90" s="1" t="s">
+    <row r="91" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B91" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="C90" s="1" t="s">
+      <c r="C91" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="K90" s="1" t="s">
+      <c r="K91" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="M90" s="1" t="s">
+      <c r="M91" s="1" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="93" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B93" s="1" t="s">
+    <row r="94" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B94" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="C93" s="1" t="s">
+      <c r="C94" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="K93" s="1" t="s">
+      <c r="K94" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="M93" s="1" t="s">
+      <c r="M94" s="1" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="95" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B95" s="1" t="s">
+    <row r="96" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B96" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="C95" s="1" t="s">
+      <c r="C96" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="K95" s="1" t="s">
+      <c r="K96" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="M95" s="1" t="s">
+      <c r="M96" s="1" t="s">
         <v>128</v>
       </c>
     </row>

--- a/Config/Datas/__beans__.xlsx
+++ b/Config/Datas/__beans__.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFCAF94A-8DA8-4AF3-BAC5-4A6159DAD9E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5BECCAA-44C8-4CC4-9E4D-67EB1EEF58D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
